--- a/outputs/bond_results_tier2_oas.xlsx
+++ b/outputs/bond_results_tier2_oas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="70">
   <si>
     <t>bond_id</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>shock</t>
+  </si>
+  <si>
+    <t>Test_change_coupon_type</t>
   </si>
   <si>
     <t>VCBH2230004</t>
@@ -578,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -603,16 +606,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>104.4102654916629</v>
+        <v>99.39118065167645</v>
       </c>
       <c r="C2">
-        <v>104.2975535277135</v>
+        <v>99.4175104210877</v>
       </c>
       <c r="D2">
-        <v>0.1127119639494083</v>
+        <v>-0.02632976941124809</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -620,16 +623,16 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>104.0139088705514</v>
+        <v>91.71152036401712</v>
       </c>
       <c r="C3">
-        <v>103.9079239567337</v>
+        <v>91.64550210775943</v>
       </c>
       <c r="D3">
-        <v>0.1059849138177356</v>
+        <v>0.06601825625769209</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -637,16 +640,16 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>105.6395785308202</v>
+        <v>107.6790532548355</v>
       </c>
       <c r="C4">
-        <v>105.5189273180302</v>
+        <v>109.6498382311094</v>
       </c>
       <c r="D4">
-        <v>0.1206512127900652</v>
+        <v>-1.970784976273961</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -654,16 +657,16 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>102.7694033553193</v>
+        <v>97.35349500005347</v>
       </c>
       <c r="C5">
-        <v>102.656134878459</v>
+        <v>97.2916801669969</v>
       </c>
       <c r="D5">
-        <v>0.1132684768602843</v>
+        <v>0.06181483305657309</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -671,16 +674,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>106.1835106747425</v>
+        <v>99.46769251326324</v>
       </c>
       <c r="C6">
-        <v>106.0725325691629</v>
+        <v>100.6122239440398</v>
       </c>
       <c r="D6">
-        <v>0.110978105579548</v>
+        <v>-1.144531430776567</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -688,16 +691,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>105.9358623015307</v>
+        <v>96.7405577127613</v>
       </c>
       <c r="C7">
-        <v>105.8271920706346</v>
+        <v>97.25698393741723</v>
       </c>
       <c r="D7">
-        <v>0.108670230896152</v>
+        <v>-0.5164262246559304</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -705,16 +708,16 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>103.2692266182532</v>
+        <v>101.866985126583</v>
       </c>
       <c r="C8">
-        <v>103.1519237721811</v>
+        <v>101.9373424554063</v>
       </c>
       <c r="D8">
-        <v>0.1173028460721497</v>
+        <v>-0.07035732882329171</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -722,16 +725,16 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>96.07728454684298</v>
+        <v>104.4102654916629</v>
       </c>
       <c r="C9">
-        <v>96.02938091308665</v>
+        <v>104.2975535277135</v>
       </c>
       <c r="D9">
-        <v>0.04790363375632012</v>
+        <v>0.1127119639494083</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -739,16 +742,16 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>72.14998402688487</v>
+        <v>104.0139088705514</v>
       </c>
       <c r="C10">
-        <v>72.06261338053741</v>
+        <v>103.9079239567337</v>
       </c>
       <c r="D10">
-        <v>0.08737064634745195</v>
+        <v>0.1059849138177356</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -756,16 +759,16 @@
         <v>6</v>
       </c>
       <c r="B11">
-        <v>123.1821785985844</v>
+        <v>105.6395785308202</v>
       </c>
       <c r="C11">
-        <v>131.5539553868444</v>
+        <v>105.5189273180302</v>
       </c>
       <c r="D11">
-        <v>-8.371776788260007</v>
+        <v>0.1206512127900652</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -773,16 +776,16 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>84.37449067229173</v>
+        <v>102.7694033553193</v>
       </c>
       <c r="C12">
-        <v>84.27009809399169</v>
+        <v>102.656134878459</v>
       </c>
       <c r="D12">
-        <v>0.1043925783000361</v>
+        <v>0.1132684768602843</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -790,16 +793,16 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>101.0636977829673</v>
+        <v>106.1835106747425</v>
       </c>
       <c r="C13">
-        <v>103.7382165570747</v>
+        <v>106.0725325691629</v>
       </c>
       <c r="D13">
-        <v>-2.674518774107383</v>
+        <v>0.110978105579548</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -807,16 +810,16 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>91.34365758573638</v>
+        <v>105.9358623015307</v>
       </c>
       <c r="C14">
-        <v>91.62430424202047</v>
+        <v>105.8271920706346</v>
       </c>
       <c r="D14">
-        <v>-0.280646656284091</v>
+        <v>0.108670230896152</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -824,16 +827,16 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>100.7264989854941</v>
+        <v>103.2692266182532</v>
       </c>
       <c r="C15">
-        <v>100.6746144959441</v>
+        <v>103.1519237721811</v>
       </c>
       <c r="D15">
-        <v>0.05188448954997682</v>
+        <v>0.1173028460721497</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -841,16 +844,16 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>96.22745766814171</v>
+        <v>96.07728454684298</v>
       </c>
       <c r="C16">
-        <v>96.18002297841115</v>
+        <v>96.02938091308665</v>
       </c>
       <c r="D16">
-        <v>0.04743468973056508</v>
+        <v>0.04790363375632012</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -858,16 +861,16 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>72.31562050137848</v>
+        <v>72.14998402688487</v>
       </c>
       <c r="C17">
-        <v>72.22821850694849</v>
+        <v>72.06261338053741</v>
       </c>
       <c r="D17">
-        <v>0.08740199442998176</v>
+        <v>0.08737064634745195</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -875,16 +878,16 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>123.2690407914781</v>
+        <v>123.1821785985844</v>
       </c>
       <c r="C18">
-        <v>131.6630243615105</v>
+        <v>131.5539553868444</v>
       </c>
       <c r="D18">
-        <v>-8.393983570032375</v>
+        <v>-8.371776788260007</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -892,16 +895,16 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>84.53943683780454</v>
+        <v>84.37449067229173</v>
       </c>
       <c r="C19">
-        <v>84.43501342948099</v>
+        <v>84.27009809399169</v>
       </c>
       <c r="D19">
-        <v>0.1044234083235551</v>
+        <v>0.1043925783000361</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -909,16 +912,16 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>101.1879053782059</v>
+        <v>101.0636977829673</v>
       </c>
       <c r="C20">
-        <v>103.8728901129752</v>
+        <v>103.7382165570747</v>
       </c>
       <c r="D20">
-        <v>-2.684984734769301</v>
+        <v>-2.674518774107383</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -926,16 +929,16 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>91.49032300834574</v>
+        <v>91.34365758573638</v>
       </c>
       <c r="C21">
-        <v>91.7734681124123</v>
+        <v>91.62430424202047</v>
       </c>
       <c r="D21">
-        <v>-0.2831451040665627</v>
+        <v>-0.280646656284091</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -943,16 +946,16 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>100.8786178822768</v>
+        <v>100.7264989854941</v>
       </c>
       <c r="C22">
-        <v>100.8268728694112</v>
+        <v>100.6746144959441</v>
       </c>
       <c r="D22">
-        <v>0.05174501286559519</v>
+        <v>0.05188448954997682</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -960,16 +963,16 @@
         <v>8</v>
       </c>
       <c r="B23">
-        <v>96.30796145237021</v>
+        <v>96.22745766814171</v>
       </c>
       <c r="C23">
-        <v>96.26053788014993</v>
+        <v>96.18002297841115</v>
       </c>
       <c r="D23">
-        <v>0.04742357222028204</v>
+        <v>0.04743468973056508</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -977,16 +980,16 @@
         <v>8</v>
       </c>
       <c r="B24">
-        <v>72.40074071683797</v>
+        <v>72.31562050137848</v>
       </c>
       <c r="C24">
-        <v>72.31333164477174</v>
+        <v>72.22821850694849</v>
       </c>
       <c r="D24">
-        <v>0.0874090720662366</v>
+        <v>0.08740199442998176</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -994,16 +997,16 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>123.318638888538</v>
+        <v>123.2690407914781</v>
       </c>
       <c r="C25">
-        <v>131.7315127552218</v>
+        <v>131.6630243615105</v>
       </c>
       <c r="D25">
-        <v>-8.412873866683796</v>
+        <v>-8.393983570032375</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1011,16 +1014,16 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>84.62384443387523</v>
+        <v>84.53943683780454</v>
       </c>
       <c r="C26">
-        <v>84.51941412064576</v>
+        <v>84.43501342948099</v>
       </c>
       <c r="D26">
-        <v>0.1044303132294715</v>
+        <v>0.1044234083235551</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1028,16 +1031,16 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>101.2580754335972</v>
+        <v>101.1879053782059</v>
       </c>
       <c r="C27">
-        <v>103.9491818941398</v>
+        <v>103.8728901129752</v>
       </c>
       <c r="D27">
-        <v>-2.691106460542571</v>
+        <v>-2.684984734769301</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1045,16 +1048,16 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>91.57004233190094</v>
+        <v>91.49032300834574</v>
       </c>
       <c r="C28">
-        <v>91.85392925115049</v>
+        <v>91.7734681124123</v>
       </c>
       <c r="D28">
-        <v>-0.2838869192495537</v>
+        <v>-0.2831451040665627</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1062,16 +1065,16 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>100.9591920924578</v>
+        <v>100.8786178822768</v>
       </c>
       <c r="C29">
-        <v>100.9073952734782</v>
+        <v>100.8268728694112</v>
       </c>
       <c r="D29">
-        <v>0.05179681897965338</v>
+        <v>0.05174501286559519</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1079,16 +1082,16 @@
         <v>9</v>
       </c>
       <c r="B30">
-        <v>99.55225107759921</v>
+        <v>96.30796145237021</v>
       </c>
       <c r="C30">
-        <v>99.45503188770415</v>
+        <v>96.26053788014993</v>
       </c>
       <c r="D30">
-        <v>0.09721918989505696</v>
+        <v>0.04742357222028204</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1096,16 +1099,16 @@
         <v>9</v>
       </c>
       <c r="B31">
-        <v>98.28325736621581</v>
+        <v>72.40074071683797</v>
       </c>
       <c r="C31">
-        <v>98.19070471200973</v>
+        <v>72.31333164477174</v>
       </c>
       <c r="D31">
-        <v>0.09255265420607373</v>
+        <v>0.0874090720662366</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1113,16 +1116,16 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>101.3855180917988</v>
+        <v>123.318638888538</v>
       </c>
       <c r="C32">
-        <v>101.2828965611392</v>
+        <v>131.7315127552218</v>
       </c>
       <c r="D32">
-        <v>0.1026215306596328</v>
+        <v>-8.412873866683796</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1130,16 +1133,16 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>98.3810376306275</v>
+        <v>84.62384443387523</v>
       </c>
       <c r="C33">
-        <v>98.28360319441096</v>
+        <v>84.51941412064576</v>
       </c>
       <c r="D33">
-        <v>0.09743443621654535</v>
+        <v>0.1044303132294715</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1147,16 +1150,16 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>100.5299300036076</v>
+        <v>101.2580754335972</v>
       </c>
       <c r="C34">
-        <v>100.4338182215674</v>
+        <v>103.9491818941398</v>
       </c>
       <c r="D34">
-        <v>0.09611178204018245</v>
+        <v>-2.691106460542571</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1164,16 +1167,16 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>100.0012479374046</v>
+        <v>91.57004233190094</v>
       </c>
       <c r="C35">
-        <v>99.90674897737416</v>
+        <v>91.85392925115049</v>
       </c>
       <c r="D35">
-        <v>0.09449896003040692</v>
+        <v>-0.2838869192495537</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1181,16 +1184,16 @@
         <v>9</v>
       </c>
       <c r="B36">
-        <v>99.27223824851229</v>
+        <v>100.9591920924578</v>
       </c>
       <c r="C36">
-        <v>99.172010019773</v>
+        <v>100.9073952734782</v>
       </c>
       <c r="D36">
-        <v>0.1002282287392973</v>
+        <v>0.05179681897965338</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1198,16 +1201,16 @@
         <v>10</v>
       </c>
       <c r="B37">
-        <v>101.7249160236879</v>
+        <v>99.55225107759921</v>
       </c>
       <c r="C37">
-        <v>101.6191121329918</v>
+        <v>99.45503188770415</v>
       </c>
       <c r="D37">
-        <v>0.1058038906960803</v>
+        <v>0.09721918989505696</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1215,16 +1218,16 @@
         <v>10</v>
       </c>
       <c r="B38">
-        <v>100.8195818586646</v>
+        <v>98.28325736621581</v>
       </c>
       <c r="C38">
-        <v>100.7187746127366</v>
+        <v>98.19070471200973</v>
       </c>
       <c r="D38">
-        <v>0.1008072459280385</v>
+        <v>0.09255265420607373</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1232,16 +1235,16 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>103.1547967289418</v>
+        <v>101.3855180917988</v>
       </c>
       <c r="C39">
-        <v>103.0432094733371</v>
+        <v>101.2828965611392</v>
       </c>
       <c r="D39">
-        <v>0.1115872556047321</v>
+        <v>0.1026215306596328</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1249,16 +1252,16 @@
         <v>10</v>
       </c>
       <c r="B40">
-        <v>101.0222889814896</v>
+        <v>98.3810376306275</v>
       </c>
       <c r="C40">
-        <v>100.915696665837</v>
+        <v>98.28360319441096</v>
       </c>
       <c r="D40">
-        <v>0.1065923156526338</v>
+        <v>0.09743443621654535</v>
       </c>
       <c r="E40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1266,16 +1269,16 @@
         <v>10</v>
       </c>
       <c r="B41">
-        <v>102.4030674014402</v>
+        <v>100.5299300036076</v>
       </c>
       <c r="C41">
-        <v>102.2989080955252</v>
+        <v>100.4338182215674</v>
       </c>
       <c r="D41">
-        <v>0.1041593059150046</v>
+        <v>0.09611178204018245</v>
       </c>
       <c r="E41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1283,16 +1286,16 @@
         <v>10</v>
       </c>
       <c r="B42">
-        <v>102.0536096239265</v>
+        <v>100.0012479374046</v>
       </c>
       <c r="C42">
-        <v>101.9511166997827</v>
+        <v>99.90674897737416</v>
       </c>
       <c r="D42">
-        <v>0.1024929241437889</v>
+        <v>0.09449896003040692</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1300,16 +1303,16 @@
         <v>10</v>
       </c>
       <c r="B43">
-        <v>101.6492849672439</v>
+        <v>99.27223824851229</v>
       </c>
       <c r="C43">
-        <v>101.5397508216573</v>
+        <v>99.172010019773</v>
       </c>
       <c r="D43">
-        <v>0.1095341455866077</v>
+        <v>0.1002282287392973</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1317,16 +1320,16 @@
         <v>11</v>
       </c>
       <c r="B44">
-        <v>98.84770517359279</v>
+        <v>101.7249160236879</v>
       </c>
       <c r="C44">
-        <v>98.8922126558614</v>
+        <v>101.6191121329918</v>
       </c>
       <c r="D44">
-        <v>-0.04450748226861378</v>
+        <v>0.1058038906960803</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1334,16 +1337,16 @@
         <v>11</v>
       </c>
       <c r="B45">
-        <v>82.43401067209508</v>
+        <v>100.8195818586646</v>
       </c>
       <c r="C45">
-        <v>82.33599331174439</v>
+        <v>100.7187746127366</v>
       </c>
       <c r="D45">
-        <v>0.09801736035069553</v>
+        <v>0.1008072459280385</v>
       </c>
       <c r="E45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1351,16 +1354,16 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>105.1098463445913</v>
+        <v>103.1547967289418</v>
       </c>
       <c r="C46">
-        <v>119.2858125851054</v>
+        <v>103.0432094733371</v>
       </c>
       <c r="D46">
-        <v>-14.17596624051416</v>
+        <v>0.1115872556047321</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1368,16 +1371,16 @@
         <v>11</v>
       </c>
       <c r="B47">
-        <v>95.43068968099956</v>
+        <v>101.0222889814896</v>
       </c>
       <c r="C47">
-        <v>95.32671592848472</v>
+        <v>100.915696665837</v>
       </c>
       <c r="D47">
-        <v>0.1039737525148468</v>
+        <v>0.1065923156526338</v>
       </c>
       <c r="E47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1385,16 +1388,16 @@
         <v>11</v>
       </c>
       <c r="B48">
-        <v>98.18780037899438</v>
+        <v>102.4030674014402</v>
       </c>
       <c r="C48">
-        <v>98.93130730334087</v>
+        <v>102.2989080955252</v>
       </c>
       <c r="D48">
-        <v>-0.7435069243464909</v>
+        <v>0.1041593059150046</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1402,16 +1405,16 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <v>92.57844728681931</v>
+        <v>102.0536096239265</v>
       </c>
       <c r="C49">
-        <v>92.49633756560749</v>
+        <v>101.9511166997827</v>
       </c>
       <c r="D49">
-        <v>0.08210972121182181</v>
+        <v>0.1024929241437889</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1419,16 +1422,16 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>104.1692127275694</v>
+        <v>101.6492849672439</v>
       </c>
       <c r="C50">
-        <v>105.7434428628753</v>
+        <v>101.5397508216573</v>
       </c>
       <c r="D50">
-        <v>-1.574230135305967</v>
+        <v>0.1095341455866077</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1436,16 +1439,16 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>99.57897761498015</v>
+        <v>98.84770517359279</v>
       </c>
       <c r="C51">
-        <v>99.61781340288334</v>
+        <v>98.8922126558614</v>
       </c>
       <c r="D51">
-        <v>-0.03883578790319575</v>
+        <v>-0.04450748226861378</v>
       </c>
       <c r="E51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1453,16 +1456,16 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>83.3613303912599</v>
+        <v>82.43401067209508</v>
       </c>
       <c r="C52">
-        <v>83.26324473824684</v>
+        <v>82.33599331174439</v>
       </c>
       <c r="D52">
-        <v>0.09808565301305805</v>
+        <v>0.09801736035069553</v>
       </c>
       <c r="E52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1470,16 +1473,16 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>105.2427825792741</v>
+        <v>105.1098463445913</v>
       </c>
       <c r="C53">
-        <v>119.6902148336369</v>
+        <v>119.2858125851054</v>
       </c>
       <c r="D53">
-        <v>-14.44743225436278</v>
+        <v>-14.17596624051416</v>
       </c>
       <c r="E53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1487,16 +1490,16 @@
         <v>12</v>
       </c>
       <c r="B54">
-        <v>96.33594645675997</v>
+        <v>95.43068968099956</v>
       </c>
       <c r="C54">
-        <v>96.23145185006493</v>
+        <v>95.32671592848472</v>
       </c>
       <c r="D54">
-        <v>0.1044946066950416</v>
+        <v>0.1039737525148468</v>
       </c>
       <c r="E54" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1504,16 +1507,16 @@
         <v>12</v>
       </c>
       <c r="B55">
-        <v>98.86710790709704</v>
+        <v>98.18780037899438</v>
       </c>
       <c r="C55">
-        <v>99.51618868204066</v>
+        <v>98.93130730334087</v>
       </c>
       <c r="D55">
-        <v>-0.6490807749436271</v>
+        <v>-0.7435069243464909</v>
       </c>
       <c r="E55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1521,16 +1524,16 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>93.27803342218539</v>
+        <v>92.57844728681931</v>
       </c>
       <c r="C56">
-        <v>93.18727311147114</v>
+        <v>92.49633756560749</v>
       </c>
       <c r="D56">
-        <v>0.09076031071424495</v>
+        <v>0.08210972121182181</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1538,16 +1541,16 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>104.6150179360975</v>
+        <v>104.1692127275694</v>
       </c>
       <c r="C57">
-        <v>106.5076012280771</v>
+        <v>105.7434428628753</v>
       </c>
       <c r="D57">
-        <v>-1.892583291979562</v>
+        <v>-1.574230135305967</v>
       </c>
       <c r="E57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1555,16 +1558,16 @@
         <v>13</v>
       </c>
       <c r="B58">
-        <v>99.62385383477128</v>
+        <v>99.57897761498015</v>
       </c>
       <c r="C58">
-        <v>99.6609749003029</v>
+        <v>99.61781340288334</v>
       </c>
       <c r="D58">
-        <v>-0.03712106553162187</v>
+        <v>-0.03883578790319575</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1572,16 +1575,16 @@
         <v>13</v>
       </c>
       <c r="B59">
-        <v>83.41687970535173</v>
+        <v>83.3613303912599</v>
       </c>
       <c r="C59">
-        <v>83.31879863968439</v>
+        <v>83.26324473824684</v>
       </c>
       <c r="D59">
-        <v>0.09808106566734409</v>
+        <v>0.09808565301305805</v>
       </c>
       <c r="E59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1589,16 +1592,16 @@
         <v>13</v>
       </c>
       <c r="B60">
-        <v>105.2235468659093</v>
+        <v>105.2427825792741</v>
       </c>
       <c r="C60">
-        <v>119.7141584884807</v>
+        <v>119.6902148336369</v>
       </c>
       <c r="D60">
-        <v>-14.49061162257139</v>
+        <v>-14.44743225436278</v>
       </c>
       <c r="E60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1606,16 +1609,16 @@
         <v>13</v>
       </c>
       <c r="B61">
-        <v>96.38935702666858</v>
+        <v>96.33594645675997</v>
       </c>
       <c r="C61">
-        <v>96.28459589770934</v>
+        <v>96.23145185006493</v>
       </c>
       <c r="D61">
-        <v>0.1047611289592396</v>
+        <v>0.1044946066950416</v>
       </c>
       <c r="E61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1623,16 +1626,16 @@
         <v>13</v>
       </c>
       <c r="B62">
-        <v>98.91399788419535</v>
+        <v>98.86710790709704</v>
       </c>
       <c r="C62">
-        <v>99.55174750945126</v>
+        <v>99.51618868204066</v>
       </c>
       <c r="D62">
-        <v>-0.6377496252559069</v>
+        <v>-0.6490807749436271</v>
       </c>
       <c r="E62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1640,16 +1643,16 @@
         <v>13</v>
       </c>
       <c r="B63">
-        <v>93.3209279131063</v>
+        <v>93.27803342218539</v>
       </c>
       <c r="C63">
-        <v>93.22912671690634</v>
+        <v>93.18727311147114</v>
       </c>
       <c r="D63">
-        <v>0.09180119619996674</v>
+        <v>0.09076031071424495</v>
       </c>
       <c r="E63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1657,16 +1660,16 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>104.6276718480467</v>
+        <v>104.6150179360975</v>
       </c>
       <c r="C64">
-        <v>106.552247441821</v>
+        <v>106.5076012280771</v>
       </c>
       <c r="D64">
-        <v>-1.924575593774321</v>
+        <v>-1.892583291979562</v>
       </c>
       <c r="E64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1674,16 +1677,16 @@
         <v>14</v>
       </c>
       <c r="B65">
-        <v>96.01772077750338</v>
+        <v>99.62385383477128</v>
       </c>
       <c r="C65">
-        <v>95.92796072599644</v>
+        <v>99.6609749003029</v>
       </c>
       <c r="D65">
-        <v>0.08976005150694277</v>
+        <v>-0.03712106553162187</v>
       </c>
       <c r="E65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1691,16 +1694,16 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>94.73751953279063</v>
+        <v>83.41687970535173</v>
       </c>
       <c r="C66">
-        <v>94.63991586196512</v>
+        <v>83.31879863968439</v>
       </c>
       <c r="D66">
-        <v>0.09760367082550658</v>
+        <v>0.09808106566734409</v>
       </c>
       <c r="E66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1708,16 +1711,16 @@
         <v>14</v>
       </c>
       <c r="B67">
-        <v>98.17707257970754</v>
+        <v>105.2235468659093</v>
       </c>
       <c r="C67">
-        <v>98.86558860137328</v>
+        <v>119.7141584884807</v>
       </c>
       <c r="D67">
-        <v>-0.688516021665734</v>
+        <v>-14.49061162257139</v>
       </c>
       <c r="E67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1725,16 +1728,16 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>91.92046861581468</v>
+        <v>96.38935702666858</v>
       </c>
       <c r="C68">
-        <v>91.83023484362694</v>
+        <v>96.28459589770934</v>
       </c>
       <c r="D68">
-        <v>0.09023377218774442</v>
+        <v>0.1047611289592396</v>
       </c>
       <c r="E68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1742,16 +1745,16 @@
         <v>14</v>
       </c>
       <c r="B69">
-        <v>100.0479421354363</v>
+        <v>98.91399788419535</v>
       </c>
       <c r="C69">
-        <v>100.2101138709991</v>
+        <v>99.55174750945126</v>
       </c>
       <c r="D69">
-        <v>-0.1621717355627226</v>
+        <v>-0.6377496252559069</v>
       </c>
       <c r="E69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1759,16 +1762,16 @@
         <v>14</v>
       </c>
       <c r="B70">
-        <v>99.21149427980595</v>
+        <v>93.3209279131063</v>
       </c>
       <c r="C70">
-        <v>99.22003042665956</v>
+        <v>93.22912671690634</v>
       </c>
       <c r="D70">
-        <v>-0.008536146853614923</v>
+        <v>0.09180119619996674</v>
       </c>
       <c r="E70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1776,16 +1779,16 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>92.93434258622409</v>
+        <v>104.6276718480467</v>
       </c>
       <c r="C71">
-        <v>92.90653684424497</v>
+        <v>106.552247441821</v>
       </c>
       <c r="D71">
-        <v>0.02780574197912244</v>
+        <v>-1.924575593774321</v>
       </c>
       <c r="E71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1793,16 +1796,16 @@
         <v>15</v>
       </c>
       <c r="B72">
-        <v>103.9404112261997</v>
+        <v>96.01772077750338</v>
       </c>
       <c r="C72">
-        <v>103.8273463373159</v>
+        <v>95.92796072599644</v>
       </c>
       <c r="D72">
-        <v>0.1130648888837413</v>
+        <v>0.08976005150694277</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1810,16 +1813,16 @@
         <v>15</v>
       </c>
       <c r="B73">
-        <v>103.3465577913727</v>
+        <v>94.73751953279063</v>
       </c>
       <c r="C73">
-        <v>103.2403026764264</v>
+        <v>94.63991586196512</v>
       </c>
       <c r="D73">
-        <v>0.1062551149463218</v>
+        <v>0.09760367082550658</v>
       </c>
       <c r="E73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1827,16 +1830,16 @@
         <v>15</v>
       </c>
       <c r="B74">
-        <v>105.3783713518261</v>
+        <v>98.17707257970754</v>
       </c>
       <c r="C74">
-        <v>105.2572502688447</v>
+        <v>98.86558860137328</v>
       </c>
       <c r="D74">
-        <v>0.1211210829814036</v>
+        <v>-0.688516021665734</v>
       </c>
       <c r="E74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1844,16 +1847,16 @@
         <v>15</v>
       </c>
       <c r="B75">
-        <v>102.37458698058</v>
+        <v>91.92046861581468</v>
       </c>
       <c r="C75">
-        <v>102.2610170570968</v>
+        <v>91.83023484362694</v>
       </c>
       <c r="D75">
-        <v>0.1135699234832401</v>
+        <v>0.09023377218774442</v>
       </c>
       <c r="E75" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1861,16 +1864,16 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>105.5962973710966</v>
+        <v>100.0479421354363</v>
       </c>
       <c r="C76">
-        <v>105.4849297440026</v>
+        <v>100.2101138709991</v>
       </c>
       <c r="D76">
-        <v>0.1113676270939834</v>
+        <v>-0.1621717355627226</v>
       </c>
       <c r="E76" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1878,16 +1881,16 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>105.2816319264011</v>
+        <v>99.21149427980595</v>
       </c>
       <c r="C77">
-        <v>105.1726077931943</v>
+        <v>99.22003042665956</v>
       </c>
       <c r="D77">
-        <v>0.1090241332068445</v>
+        <v>-0.008536146853614923</v>
       </c>
       <c r="E77" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1895,16 +1898,16 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>102.9754299581952</v>
+        <v>92.93434258622409</v>
       </c>
       <c r="C78">
-        <v>102.8577702911113</v>
+        <v>92.90653684424497</v>
       </c>
       <c r="D78">
-        <v>0.1176596670838705</v>
+        <v>0.02780574197912244</v>
       </c>
       <c r="E78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1912,16 +1915,16 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>104.8984881404407</v>
+        <v>103.9404112261997</v>
       </c>
       <c r="C79">
-        <v>106.7044007164347</v>
+        <v>103.8273463373159</v>
       </c>
       <c r="D79">
-        <v>-1.805912575993943</v>
+        <v>0.1130648888837413</v>
       </c>
       <c r="E79" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1929,16 +1932,16 @@
         <v>16</v>
       </c>
       <c r="B80">
-        <v>87.39869666119598</v>
+        <v>103.3465577913727</v>
       </c>
       <c r="C80">
-        <v>87.29497263358331</v>
+        <v>103.2403026764264</v>
       </c>
       <c r="D80">
-        <v>0.103724027612671</v>
+        <v>0.1062551149463218</v>
       </c>
       <c r="E80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1946,16 +1949,16 @@
         <v>16</v>
       </c>
       <c r="B81">
-        <v>111.7146170687134</v>
+        <v>105.3783713518261</v>
       </c>
       <c r="C81">
-        <v>131.3844327380201</v>
+        <v>105.2572502688447</v>
       </c>
       <c r="D81">
-        <v>-19.66981566930679</v>
+        <v>0.1211210829814036</v>
       </c>
       <c r="E81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1963,16 +1966,16 @@
         <v>16</v>
       </c>
       <c r="B82">
-        <v>101.2828205326606</v>
+        <v>102.37458698058</v>
       </c>
       <c r="C82">
-        <v>101.2827346053352</v>
+        <v>102.2610170570968</v>
       </c>
       <c r="D82">
-        <v>8.592732537238135E-05</v>
+        <v>0.1135699234832401</v>
       </c>
       <c r="E82" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1980,16 +1983,16 @@
         <v>16</v>
       </c>
       <c r="B83">
-        <v>102.347260527848</v>
+        <v>105.5962973710966</v>
       </c>
       <c r="C83">
-        <v>108.0848724085326</v>
+        <v>105.4849297440026</v>
       </c>
       <c r="D83">
-        <v>-5.737611880684611</v>
+        <v>0.1113676270939834</v>
       </c>
       <c r="E83" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1997,16 +2000,16 @@
         <v>16</v>
       </c>
       <c r="B84">
-        <v>98.84820250192381</v>
+        <v>105.2816319264011</v>
       </c>
       <c r="C84">
-        <v>100.2368949387817</v>
+        <v>105.1726077931943</v>
       </c>
       <c r="D84">
-        <v>-1.388692436857852</v>
+        <v>0.1090241332068445</v>
       </c>
       <c r="E84" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2014,16 +2017,16 @@
         <v>16</v>
       </c>
       <c r="B85">
-        <v>110.4213057157285</v>
+        <v>102.9754299581952</v>
       </c>
       <c r="C85">
-        <v>113.6048992418702</v>
+        <v>102.8577702911113</v>
       </c>
       <c r="D85">
-        <v>-3.183593526141735</v>
+        <v>0.1176596670838705</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2031,16 +2034,16 @@
         <v>17</v>
       </c>
       <c r="B86">
-        <v>105.1862757371466</v>
+        <v>104.8984881404407</v>
       </c>
       <c r="C86">
-        <v>107.0262792301261</v>
+        <v>106.7044007164347</v>
       </c>
       <c r="D86">
-        <v>-1.840003492979562</v>
+        <v>-1.805912575993943</v>
       </c>
       <c r="E86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2048,16 +2051,16 @@
         <v>17</v>
       </c>
       <c r="B87">
-        <v>87.79714421570989</v>
+        <v>87.39869666119598</v>
       </c>
       <c r="C87">
-        <v>87.69334799494605</v>
+        <v>87.29497263358331</v>
       </c>
       <c r="D87">
-        <v>0.1037962207638401</v>
+        <v>0.103724027612671</v>
       </c>
       <c r="E87" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2065,16 +2068,16 @@
         <v>17</v>
       </c>
       <c r="B88">
-        <v>111.8376381404162</v>
+        <v>111.7146170687134</v>
       </c>
       <c r="C88">
-        <v>131.5752410014853</v>
+        <v>131.3844327380201</v>
       </c>
       <c r="D88">
-        <v>-19.73760286106911</v>
+        <v>-19.66981566930679</v>
       </c>
       <c r="E88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2082,16 +2085,16 @@
         <v>17</v>
       </c>
       <c r="B89">
-        <v>101.6720037015705</v>
+        <v>101.2828205326606</v>
       </c>
       <c r="C89">
-        <v>101.6823396090849</v>
+        <v>101.2827346053352</v>
       </c>
       <c r="D89">
-        <v>-0.01033590751440272</v>
+        <v>8.592732537238135E-05</v>
       </c>
       <c r="E89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2099,16 +2102,16 @@
         <v>17</v>
       </c>
       <c r="B90">
-        <v>102.632745940937</v>
+        <v>102.347260527848</v>
       </c>
       <c r="C90">
-        <v>108.3396892335838</v>
+        <v>108.0848724085326</v>
       </c>
       <c r="D90">
-        <v>-5.706943292646741</v>
+        <v>-5.737611880684611</v>
       </c>
       <c r="E90" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2116,16 +2119,16 @@
         <v>17</v>
       </c>
       <c r="B91">
-        <v>99.16582411787645</v>
+        <v>98.84820250192381</v>
       </c>
       <c r="C91">
-        <v>100.5363359182203</v>
+        <v>100.2368949387817</v>
       </c>
       <c r="D91">
-        <v>-1.370511800343877</v>
+        <v>-1.388692436857852</v>
       </c>
       <c r="E91" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2133,16 +2136,16 @@
         <v>17</v>
       </c>
       <c r="B92">
-        <v>110.6475556783861</v>
+        <v>110.4213057157285</v>
       </c>
       <c r="C92">
-        <v>113.9519542543775</v>
+        <v>113.6048992418702</v>
       </c>
       <c r="D92">
-        <v>-3.304398575991456</v>
+        <v>-3.183593526141735</v>
       </c>
       <c r="E92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2150,16 +2153,16 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>95.48660298126229</v>
+        <v>105.1862757371466</v>
       </c>
       <c r="C93">
-        <v>95.44327306106776</v>
+        <v>107.0262792301261</v>
       </c>
       <c r="D93">
-        <v>0.04332992019453741</v>
+        <v>-1.840003492979562</v>
       </c>
       <c r="E93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2167,16 +2170,16 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>93.7319259057287</v>
+        <v>87.79714421570989</v>
       </c>
       <c r="C94">
-        <v>93.65790100485989</v>
+        <v>87.69334799494605</v>
       </c>
       <c r="D94">
-        <v>0.07402490086880675</v>
+        <v>0.1037962207638401</v>
       </c>
       <c r="E94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2184,16 +2187,16 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>97.58561134658328</v>
+        <v>111.8376381404162</v>
       </c>
       <c r="C95">
-        <v>98.49546619648869</v>
+        <v>131.5752410014853</v>
       </c>
       <c r="D95">
-        <v>-0.9098548499054147</v>
+        <v>-19.73760286106911</v>
       </c>
       <c r="E95" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2201,16 +2204,16 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>92.9869463694335</v>
+        <v>101.6720037015705</v>
       </c>
       <c r="C96">
-        <v>92.94471898690271</v>
+        <v>101.6823396090849</v>
       </c>
       <c r="D96">
-        <v>0.04222738253078262</v>
+        <v>-0.01033590751440272</v>
       </c>
       <c r="E96" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2218,16 +2221,16 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>97.56240250414623</v>
+        <v>102.632745940937</v>
       </c>
       <c r="C97">
-        <v>97.87822083842035</v>
+        <v>108.3396892335838</v>
       </c>
       <c r="D97">
-        <v>-0.3158183342741125</v>
+        <v>-5.706943292646741</v>
       </c>
       <c r="E97" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2235,16 +2238,16 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>96.83658083106562</v>
+        <v>99.16582411787645</v>
       </c>
       <c r="C98">
-        <v>96.95341789566866</v>
+        <v>100.5363359182203</v>
       </c>
       <c r="D98">
-        <v>-0.1168370646030468</v>
+        <v>-1.370511800343877</v>
       </c>
       <c r="E98" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2252,16 +2255,16 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>94.13578040824737</v>
+        <v>110.6475556783861</v>
       </c>
       <c r="C99">
-        <v>94.21001462456701</v>
+        <v>113.9519542543775</v>
       </c>
       <c r="D99">
-        <v>-0.07423421631963834</v>
+        <v>-3.304398575991456</v>
       </c>
       <c r="E99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2269,16 +2272,16 @@
         <v>19</v>
       </c>
       <c r="B100">
-        <v>102.2548764078642</v>
+        <v>95.48660298126229</v>
       </c>
       <c r="C100">
-        <v>102.1639332948339</v>
+        <v>95.44327306106776</v>
       </c>
       <c r="D100">
-        <v>0.09094311303029201</v>
+        <v>0.04332992019453741</v>
       </c>
       <c r="E100" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2286,16 +2289,16 @@
         <v>19</v>
       </c>
       <c r="B101">
-        <v>102.368886410102</v>
+        <v>93.7319259057287</v>
       </c>
       <c r="C101">
-        <v>102.2804562303099</v>
+        <v>93.65790100485989</v>
       </c>
       <c r="D101">
-        <v>0.08843017979202727</v>
+        <v>0.07402490086880675</v>
       </c>
       <c r="E101" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2303,16 +2306,16 @@
         <v>19</v>
       </c>
       <c r="B102">
-        <v>102.3671651629121</v>
+        <v>97.58561134658328</v>
       </c>
       <c r="C102">
-        <v>102.2734179852597</v>
+        <v>98.49546619648869</v>
       </c>
       <c r="D102">
-        <v>0.09374717765238927</v>
+        <v>-0.9098548499054147</v>
       </c>
       <c r="E102" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2320,16 +2323,16 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>101.7096958603295</v>
+        <v>92.9869463694335</v>
       </c>
       <c r="C103">
-        <v>101.6179580612776</v>
+        <v>92.94471898690271</v>
       </c>
       <c r="D103">
-        <v>0.09173779905188439</v>
+        <v>0.04222738253078262</v>
       </c>
       <c r="E103" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2337,16 +2340,16 @@
         <v>19</v>
       </c>
       <c r="B104">
-        <v>102.9181338601868</v>
+        <v>97.56240250414623</v>
       </c>
       <c r="C104">
-        <v>102.8284075152933</v>
+        <v>97.87822083842035</v>
       </c>
       <c r="D104">
-        <v>0.08972634489353482</v>
+        <v>-0.3158183342741125</v>
       </c>
       <c r="E104" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2354,16 +2357,16 @@
         <v>19</v>
       </c>
       <c r="B105">
-        <v>102.9246113408304</v>
+        <v>96.83658083106562</v>
       </c>
       <c r="C105">
-        <v>102.8356973338008</v>
+        <v>96.95341789566866</v>
       </c>
       <c r="D105">
-        <v>0.08891400702960084</v>
+        <v>-0.1168370646030468</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2371,16 +2374,16 @@
         <v>19</v>
       </c>
       <c r="B106">
-        <v>101.7277533677134</v>
+        <v>94.13578040824737</v>
       </c>
       <c r="C106">
-        <v>101.6345672427153</v>
+        <v>94.21001462456701</v>
       </c>
       <c r="D106">
-        <v>0.09318612499812673</v>
+        <v>-0.07423421631963834</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2388,16 +2391,16 @@
         <v>20</v>
       </c>
       <c r="B107">
-        <v>95.64820239929452</v>
+        <v>102.2548764078642</v>
       </c>
       <c r="C107">
-        <v>95.60052139139654</v>
+        <v>102.1639332948339</v>
       </c>
       <c r="D107">
-        <v>0.04768100789797813</v>
+        <v>0.09094311303029201</v>
       </c>
       <c r="E107" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2405,16 +2408,16 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>93.96550537136601</v>
+        <v>102.368886410102</v>
       </c>
       <c r="C108">
-        <v>93.89025651406405</v>
+        <v>102.2804562303099</v>
       </c>
       <c r="D108">
-        <v>0.07524885730195763</v>
+        <v>0.08843017979202727</v>
       </c>
       <c r="E108" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2422,16 +2425,16 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>97.67407262773919</v>
+        <v>102.3671651629121</v>
       </c>
       <c r="C109">
-        <v>98.57033096763369</v>
+        <v>102.2734179852597</v>
       </c>
       <c r="D109">
-        <v>-0.8962583398945014</v>
+        <v>0.09374717765238927</v>
       </c>
       <c r="E109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2439,16 +2442,16 @@
         <v>20</v>
       </c>
       <c r="B110">
-        <v>93.1544987962383</v>
+        <v>101.7096958603295</v>
       </c>
       <c r="C110">
-        <v>93.10992093322707</v>
+        <v>101.6179580612776</v>
       </c>
       <c r="D110">
-        <v>0.04457786301122724</v>
+        <v>0.09173779905188439</v>
       </c>
       <c r="E110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2456,16 +2459,16 @@
         <v>20</v>
       </c>
       <c r="B111">
-        <v>97.74233553079529</v>
+        <v>102.9181338601868</v>
       </c>
       <c r="C111">
-        <v>98.04059636573558</v>
+        <v>102.8284075152933</v>
       </c>
       <c r="D111">
-        <v>-0.2982608349402938</v>
+        <v>0.08972634489353482</v>
       </c>
       <c r="E111" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2473,16 +2476,16 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>97.04268771214892</v>
+        <v>102.9246113408304</v>
       </c>
       <c r="C112">
-        <v>97.14675552170492</v>
+        <v>102.8356973338008</v>
       </c>
       <c r="D112">
-        <v>-0.1040678095559997</v>
+        <v>0.08891400702960084</v>
       </c>
       <c r="E112" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2490,16 +2493,16 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>94.26565255392909</v>
+        <v>101.7277533677134</v>
       </c>
       <c r="C113">
-        <v>94.33663570943423</v>
+        <v>101.6345672427153</v>
       </c>
       <c r="D113">
-        <v>-0.07098315550514656</v>
+        <v>0.09318612499812673</v>
       </c>
       <c r="E113" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2507,16 +2510,16 @@
         <v>21</v>
       </c>
       <c r="B114">
-        <v>102.5014492513059</v>
+        <v>95.64820239929452</v>
       </c>
       <c r="C114">
-        <v>102.4111892937343</v>
+        <v>95.60052139139654</v>
       </c>
       <c r="D114">
-        <v>0.09025995757161809</v>
+        <v>0.04768100789797813</v>
       </c>
       <c r="E114" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2524,16 +2527,16 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>102.7495067579277</v>
+        <v>93.96550537136601</v>
       </c>
       <c r="C115">
-        <v>102.6616780733299</v>
+        <v>93.89025651406405</v>
       </c>
       <c r="D115">
-        <v>0.08782868459783799</v>
+        <v>0.07524885730195763</v>
       </c>
       <c r="E115" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2541,16 +2544,16 @@
         <v>21</v>
       </c>
       <c r="B116">
-        <v>102.4753341745071</v>
+        <v>97.67407262773919</v>
       </c>
       <c r="C116">
-        <v>102.3823636579091</v>
+        <v>98.57033096763369</v>
       </c>
       <c r="D116">
-        <v>0.09297051659795841</v>
+        <v>-0.8962583398945014</v>
       </c>
       <c r="E116" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2558,16 +2561,16 @@
         <v>21</v>
       </c>
       <c r="B117">
-        <v>101.9242265925669</v>
+        <v>93.1544987962383</v>
       </c>
       <c r="C117">
-        <v>101.8331645411286</v>
+        <v>93.10992093322707</v>
       </c>
       <c r="D117">
-        <v>0.09106205143828561</v>
+        <v>0.04457786301122724</v>
       </c>
       <c r="E117" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2575,16 +2578,16 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>103.2227426124319</v>
+        <v>97.74233553079529</v>
       </c>
       <c r="C118">
-        <v>103.1336930512006</v>
+        <v>98.04059636573558</v>
       </c>
       <c r="D118">
-        <v>0.08904956123133445</v>
+        <v>-0.2982608349402938</v>
       </c>
       <c r="E118" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2592,16 +2595,16 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>103.2714544255207</v>
+        <v>97.04268771214892</v>
       </c>
       <c r="C119">
-        <v>103.1831907722486</v>
+        <v>97.14675552170492</v>
       </c>
       <c r="D119">
-        <v>0.08826365327203689</v>
+        <v>-0.1040678095559997</v>
       </c>
       <c r="E119" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2609,16 +2612,16 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>101.876563743982</v>
+        <v>94.26565255392909</v>
       </c>
       <c r="C120">
-        <v>101.784097116044</v>
+        <v>94.33663570943423</v>
       </c>
       <c r="D120">
-        <v>0.09246662793799487</v>
+        <v>-0.07098315550514656</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2626,16 +2629,16 @@
         <v>22</v>
       </c>
       <c r="B121">
-        <v>102.4140746993041</v>
+        <v>102.5014492513059</v>
       </c>
       <c r="C121">
-        <v>102.323620435305</v>
+        <v>102.4111892937343</v>
       </c>
       <c r="D121">
-        <v>0.09045426399903533</v>
+        <v>0.09025995757161809</v>
       </c>
       <c r="E121" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2643,16 +2646,16 @@
         <v>22</v>
       </c>
       <c r="B122">
-        <v>102.6175611192371</v>
+        <v>102.7495067579277</v>
       </c>
       <c r="C122">
-        <v>102.5295603877825</v>
+        <v>102.6616780733299</v>
       </c>
       <c r="D122">
-        <v>0.08800073145458498</v>
+        <v>0.08782868459783799</v>
       </c>
       <c r="E122" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2660,16 +2663,16 @@
         <v>22</v>
       </c>
       <c r="B123">
-        <v>102.4335821809334</v>
+        <v>102.4753341745071</v>
       </c>
       <c r="C123">
-        <v>102.3403916079477</v>
+        <v>102.3823636579091</v>
       </c>
       <c r="D123">
-        <v>0.09319057298570499</v>
+        <v>0.09297051659795841</v>
       </c>
       <c r="E123" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2677,16 +2680,16 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>101.8507953432165</v>
+        <v>101.9242265925669</v>
       </c>
       <c r="C124">
-        <v>101.7595407066255</v>
+        <v>101.8331645411286</v>
       </c>
       <c r="D124">
-        <v>0.09125463659098898</v>
+        <v>0.09106205143828561</v>
       </c>
       <c r="E124" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2694,16 +2697,16 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>103.1126080527711</v>
+        <v>103.2227426124319</v>
       </c>
       <c r="C125">
-        <v>103.0233662114269</v>
+        <v>103.1336930512006</v>
       </c>
       <c r="D125">
-        <v>0.08924184134411917</v>
+        <v>0.08904956123133445</v>
       </c>
       <c r="E125" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2711,16 +2714,16 @@
         <v>22</v>
       </c>
       <c r="B126">
-        <v>103.1473430183639</v>
+        <v>103.2714544255207</v>
       </c>
       <c r="C126">
-        <v>103.0588942667672</v>
+        <v>103.1831907722486</v>
       </c>
       <c r="D126">
-        <v>0.08844875159674359</v>
+        <v>0.08826365327203689</v>
       </c>
       <c r="E126" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2728,16 +2731,16 @@
         <v>22</v>
       </c>
       <c r="B127">
-        <v>101.8249290652489</v>
+        <v>101.876563743982</v>
       </c>
       <c r="C127">
-        <v>101.7322579309781</v>
+        <v>101.784097116044</v>
       </c>
       <c r="D127">
-        <v>0.09267113427078755</v>
+        <v>0.09246662793799487</v>
       </c>
       <c r="E127" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2745,16 +2748,16 @@
         <v>23</v>
       </c>
       <c r="B128">
-        <v>104.3507350405985</v>
+        <v>102.4140746993041</v>
       </c>
       <c r="C128">
-        <v>104.2804502711753</v>
+        <v>102.323620435305</v>
       </c>
       <c r="D128">
-        <v>0.07028476942326733</v>
+        <v>0.09045426399903533</v>
       </c>
       <c r="E128" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2762,16 +2765,16 @@
         <v>23</v>
       </c>
       <c r="B129">
-        <v>105.1559611687937</v>
+        <v>102.6175611192371</v>
       </c>
       <c r="C129">
-        <v>105.0861560935237</v>
+        <v>102.5295603877825</v>
       </c>
       <c r="D129">
-        <v>0.06980507527001123</v>
+        <v>0.08800073145458498</v>
       </c>
       <c r="E129" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2779,16 +2782,16 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>103.584472676976</v>
+        <v>102.4335821809334</v>
       </c>
       <c r="C130">
-        <v>103.5136643032324</v>
+        <v>102.3403916079477</v>
       </c>
       <c r="D130">
-        <v>0.07080837374356008</v>
+        <v>0.09319057298570499</v>
       </c>
       <c r="E130" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2796,16 +2799,16 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>103.9004943042871</v>
+        <v>101.8507953432165</v>
       </c>
       <c r="C131">
-        <v>103.8299102691146</v>
+        <v>101.7595407066255</v>
       </c>
       <c r="D131">
-        <v>0.07058403517248735</v>
+        <v>0.09125463659098898</v>
       </c>
       <c r="E131" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2813,16 +2816,16 @@
         <v>23</v>
       </c>
       <c r="B132">
-        <v>104.9945122830247</v>
+        <v>103.1126080527711</v>
       </c>
       <c r="C132">
-        <v>104.9246009240009</v>
+        <v>103.0233662114269</v>
       </c>
       <c r="D132">
-        <v>0.06991135902374879</v>
+        <v>0.08924184134411917</v>
       </c>
       <c r="E132" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2830,16 +2833,16 @@
         <v>23</v>
       </c>
       <c r="B133">
-        <v>105.2360194841764</v>
+        <v>103.1473430183639</v>
       </c>
       <c r="C133">
-        <v>105.1662591172353</v>
+        <v>103.0588942667672</v>
       </c>
       <c r="D133">
-        <v>0.06976036694116772</v>
+        <v>0.08844875159674359</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2847,16 +2850,16 @@
         <v>23</v>
       </c>
       <c r="B134">
-        <v>103.4909611943969</v>
+        <v>101.8249290652489</v>
       </c>
       <c r="C134">
-        <v>103.4201094593854</v>
+        <v>101.7322579309781</v>
       </c>
       <c r="D134">
-        <v>0.07085173501151587</v>
+        <v>0.09267113427078755</v>
       </c>
       <c r="E134" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2864,16 +2867,16 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>104.1383478355649</v>
+        <v>104.3507350405985</v>
       </c>
       <c r="C135">
-        <v>105.1411904335369</v>
+        <v>104.2804502711753</v>
       </c>
       <c r="D135">
-        <v>-1.002842597971977</v>
+        <v>0.07028476942326733</v>
       </c>
       <c r="E135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2881,16 +2884,16 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>83.80602452163981</v>
+        <v>105.1559611687937</v>
       </c>
       <c r="C136">
-        <v>83.70355322444031</v>
+        <v>105.0861560935237</v>
       </c>
       <c r="D136">
-        <v>0.1024712971995001</v>
+        <v>0.06980507527001123</v>
       </c>
       <c r="E136" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2898,16 +2901,16 @@
         <v>24</v>
       </c>
       <c r="B137">
-        <v>116.3234621141064</v>
+        <v>103.584472676976</v>
       </c>
       <c r="C137">
-        <v>133.4712790041389</v>
+        <v>103.5136643032324</v>
       </c>
       <c r="D137">
-        <v>-17.14781689003253</v>
+        <v>0.07080837374356008</v>
       </c>
       <c r="E137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2915,16 +2918,16 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>97.8047485808525</v>
+        <v>103.9004943042871</v>
       </c>
       <c r="C138">
-        <v>97.70481989202449</v>
+        <v>103.8299102691146</v>
       </c>
       <c r="D138">
-        <v>0.09992868882801531</v>
+        <v>0.07058403517248735</v>
       </c>
       <c r="E138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2932,16 +2935,16 @@
         <v>24</v>
       </c>
       <c r="B139">
-        <v>102.2980982463725</v>
+        <v>104.9945122830247</v>
       </c>
       <c r="C139">
-        <v>108.2421207594155</v>
+        <v>104.9246009240009</v>
       </c>
       <c r="D139">
-        <v>-5.944022513043009</v>
+        <v>0.06991135902374879</v>
       </c>
       <c r="E139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2949,16 +2952,16 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>97.51679529015789</v>
+        <v>105.2360194841764</v>
       </c>
       <c r="C140">
-        <v>99.06942163879438</v>
+        <v>105.1662591172353</v>
       </c>
       <c r="D140">
-        <v>-1.552626348636494</v>
+        <v>0.06976036694116772</v>
       </c>
       <c r="E140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2966,16 +2969,16 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>110.4073853825261</v>
+        <v>103.4909611943969</v>
       </c>
       <c r="C141">
-        <v>111.5977095552461</v>
+        <v>103.4201094593854</v>
       </c>
       <c r="D141">
-        <v>-1.190324172720011</v>
+        <v>0.07085173501151587</v>
       </c>
       <c r="E141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2983,16 +2986,16 @@
         <v>25</v>
       </c>
       <c r="B142">
-        <v>104.4102654916629</v>
+        <v>104.1383478355649</v>
       </c>
       <c r="C142">
-        <v>104.2975535277135</v>
+        <v>105.1411904335369</v>
       </c>
       <c r="D142">
-        <v>0.1127119639494083</v>
+        <v>-1.002842597971977</v>
       </c>
       <c r="E142" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3000,16 +3003,16 @@
         <v>25</v>
       </c>
       <c r="B143">
-        <v>104.0139088705514</v>
+        <v>83.80602452163981</v>
       </c>
       <c r="C143">
-        <v>103.9079239567337</v>
+        <v>83.70355322444031</v>
       </c>
       <c r="D143">
-        <v>0.1059849138177356</v>
+        <v>0.1024712971995001</v>
       </c>
       <c r="E143" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3017,16 +3020,16 @@
         <v>25</v>
       </c>
       <c r="B144">
-        <v>105.6395785308202</v>
+        <v>116.3234621141064</v>
       </c>
       <c r="C144">
-        <v>105.5189273180302</v>
+        <v>133.4712790041389</v>
       </c>
       <c r="D144">
-        <v>0.1206512127900652</v>
+        <v>-17.14781689003253</v>
       </c>
       <c r="E144" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3034,16 +3037,16 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>102.7694033553193</v>
+        <v>97.8047485808525</v>
       </c>
       <c r="C145">
-        <v>102.656134878459</v>
+        <v>97.70481989202449</v>
       </c>
       <c r="D145">
-        <v>0.1132684768602843</v>
+        <v>0.09992868882801531</v>
       </c>
       <c r="E145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3051,16 +3054,16 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>106.1835106747425</v>
+        <v>102.2980982463725</v>
       </c>
       <c r="C146">
-        <v>106.0725325691629</v>
+        <v>108.2421207594155</v>
       </c>
       <c r="D146">
-        <v>0.110978105579548</v>
+        <v>-5.944022513043009</v>
       </c>
       <c r="E146" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3068,16 +3071,16 @@
         <v>25</v>
       </c>
       <c r="B147">
-        <v>105.9358623015307</v>
+        <v>97.51679529015789</v>
       </c>
       <c r="C147">
-        <v>105.8271920706346</v>
+        <v>99.06942163879438</v>
       </c>
       <c r="D147">
-        <v>0.108670230896152</v>
+        <v>-1.552626348636494</v>
       </c>
       <c r="E147" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3085,16 +3088,16 @@
         <v>25</v>
       </c>
       <c r="B148">
-        <v>103.2692266182532</v>
+        <v>110.4073853825261</v>
       </c>
       <c r="C148">
-        <v>103.1519237721811</v>
+        <v>111.5977095552461</v>
       </c>
       <c r="D148">
-        <v>0.1173028460721497</v>
+        <v>-1.190324172720011</v>
       </c>
       <c r="E148" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3102,16 +3105,16 @@
         <v>26</v>
       </c>
       <c r="B149">
-        <v>105.6049252129322</v>
+        <v>104.4102654916629</v>
       </c>
       <c r="C149">
-        <v>106.7187951710539</v>
+        <v>104.2975535277135</v>
       </c>
       <c r="D149">
-        <v>-1.113869958121725</v>
+        <v>0.1127119639494083</v>
       </c>
       <c r="E149" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3119,16 +3122,16 @@
         <v>26</v>
       </c>
       <c r="B150">
-        <v>85.6613272638338</v>
+        <v>104.0139088705514</v>
       </c>
       <c r="C150">
-        <v>85.55855731867103</v>
+        <v>103.9079239567337</v>
       </c>
       <c r="D150">
-        <v>0.1027699451627626</v>
+        <v>0.1059849138177356</v>
       </c>
       <c r="E150" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3136,16 +3139,16 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>116.9036140281033</v>
+        <v>105.6395785308202</v>
       </c>
       <c r="C151">
-        <v>134.5215743901397</v>
+        <v>105.5189273180302</v>
       </c>
       <c r="D151">
-        <v>-17.6179603620364</v>
+        <v>0.1206512127900652</v>
       </c>
       <c r="E151" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3153,16 +3156,16 @@
         <v>26</v>
       </c>
       <c r="B152">
-        <v>99.67227316684985</v>
+        <v>102.7694033553193</v>
       </c>
       <c r="C152">
-        <v>99.58081640647698</v>
+        <v>102.656134878459</v>
       </c>
       <c r="D152">
-        <v>0.09145676037286421</v>
+        <v>0.1132684768602843</v>
       </c>
       <c r="E152" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3170,16 +3173,16 @@
         <v>26</v>
       </c>
       <c r="B153">
-        <v>103.5424377144012</v>
+        <v>106.1835106747425</v>
       </c>
       <c r="C153">
-        <v>109.5593412227191</v>
+        <v>106.0725325691629</v>
       </c>
       <c r="D153">
-        <v>-6.01690350831791</v>
+        <v>0.110978105579548</v>
       </c>
       <c r="E153" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3187,16 +3190,16 @@
         <v>26</v>
       </c>
       <c r="B154">
-        <v>99.00617887021099</v>
+        <v>105.9358623015307</v>
       </c>
       <c r="C154">
-        <v>100.5872470905939</v>
+        <v>105.8271920706346</v>
       </c>
       <c r="D154">
-        <v>-1.581068220382903</v>
+        <v>0.108670230896152</v>
       </c>
       <c r="E154" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3204,16 +3207,16 @@
         <v>26</v>
       </c>
       <c r="B155">
-        <v>111.841950901682</v>
+        <v>103.2692266182532</v>
       </c>
       <c r="C155">
-        <v>113.240873819161</v>
+        <v>103.1519237721811</v>
       </c>
       <c r="D155">
-        <v>-1.398922917478913</v>
+        <v>0.1173028460721497</v>
       </c>
       <c r="E155" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3221,16 +3224,16 @@
         <v>27</v>
       </c>
       <c r="B156">
-        <v>107.1079622228388</v>
+        <v>105.6049252129322</v>
       </c>
       <c r="C156">
-        <v>107.0449820681002</v>
+        <v>106.7187951710539</v>
       </c>
       <c r="D156">
-        <v>0.06298015473855401</v>
+        <v>-1.113869958121725</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3238,16 +3241,16 @@
         <v>27</v>
       </c>
       <c r="B157">
-        <v>102.2492162480294</v>
+        <v>85.6613272638338</v>
       </c>
       <c r="C157">
-        <v>102.189184015697</v>
+        <v>85.55855731867103</v>
       </c>
       <c r="D157">
-        <v>0.06003223233238941</v>
+        <v>0.1027699451627626</v>
       </c>
       <c r="E157" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3255,16 +3258,16 @@
         <v>27</v>
       </c>
       <c r="B158">
-        <v>112.206253924484</v>
+        <v>116.9036140281033</v>
       </c>
       <c r="C158">
-        <v>112.1401789703836</v>
+        <v>134.5215743901397</v>
       </c>
       <c r="D158">
-        <v>0.06607495410041508</v>
+        <v>-17.6179603620364</v>
       </c>
       <c r="E158" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3272,16 +3275,16 @@
         <v>27</v>
       </c>
       <c r="B159">
-        <v>109.4199886240067</v>
+        <v>99.67227316684985</v>
       </c>
       <c r="C159">
-        <v>109.3556185806588</v>
+        <v>99.58081640647698</v>
       </c>
       <c r="D159">
-        <v>0.06437004334789265</v>
+        <v>0.09145676037286421</v>
       </c>
       <c r="E159" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3289,16 +3292,16 @@
         <v>27</v>
       </c>
       <c r="B160">
-        <v>103.8345139743774</v>
+        <v>103.5424377144012</v>
       </c>
       <c r="C160">
-        <v>103.7735068698799</v>
+        <v>109.5593412227191</v>
       </c>
       <c r="D160">
-        <v>0.06100710449744895</v>
+        <v>-6.01690350831791</v>
       </c>
       <c r="E160" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3306,16 +3309,16 @@
         <v>27</v>
       </c>
       <c r="B161">
-        <v>102.3100056930851</v>
+        <v>99.00617887021099</v>
       </c>
       <c r="C161">
-        <v>102.2499244548089</v>
+        <v>100.5872470905939</v>
       </c>
       <c r="D161">
-        <v>0.06008123827622569</v>
+        <v>-1.581068220382903</v>
       </c>
       <c r="E161" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3323,16 +3326,16 @@
         <v>27</v>
       </c>
       <c r="B162">
-        <v>112.1372619479288</v>
+        <v>111.841950901682</v>
       </c>
       <c r="C162">
-        <v>112.0712414560099</v>
+        <v>113.240873819161</v>
       </c>
       <c r="D162">
-        <v>0.06602049191890558</v>
+        <v>-1.398922917478913</v>
       </c>
       <c r="E162" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3340,16 +3343,16 @@
         <v>28</v>
       </c>
       <c r="B163">
-        <v>104.9579119843815</v>
+        <v>107.1079622228388</v>
       </c>
       <c r="C163">
-        <v>106.0207505520693</v>
+        <v>107.0449820681002</v>
       </c>
       <c r="D163">
-        <v>-1.062838567687791</v>
+        <v>0.06298015473855401</v>
       </c>
       <c r="E163" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3357,16 +3360,16 @@
         <v>28</v>
       </c>
       <c r="B164">
-        <v>84.83976685403302</v>
+        <v>102.2492162480294</v>
       </c>
       <c r="C164">
-        <v>84.73710160533427</v>
+        <v>102.189184015697</v>
       </c>
       <c r="D164">
-        <v>0.1026652486987416</v>
+        <v>0.06003223233238941</v>
       </c>
       <c r="E164" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3374,16 +3377,16 @@
         <v>28</v>
       </c>
       <c r="B165">
-        <v>116.6590410671116</v>
+        <v>112.206253924484</v>
       </c>
       <c r="C165">
-        <v>134.0558448258811</v>
+        <v>112.1401789703836</v>
       </c>
       <c r="D165">
-        <v>-17.39680375876952</v>
+        <v>0.06607495410041508</v>
       </c>
       <c r="E165" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3391,16 +3394,16 @@
         <v>28</v>
       </c>
       <c r="B166">
-        <v>98.85102403100562</v>
+        <v>109.4199886240067</v>
       </c>
       <c r="C166">
-        <v>98.75425653050213</v>
+        <v>109.3556185806588</v>
       </c>
       <c r="D166">
-        <v>0.09676750050348915</v>
+        <v>0.06437004334789265</v>
       </c>
       <c r="E166" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3408,16 +3411,16 @@
         <v>28</v>
       </c>
       <c r="B167">
-        <v>102.9848632679722</v>
+        <v>103.8345139743774</v>
       </c>
       <c r="C167">
-        <v>108.9724093969097</v>
+        <v>103.7735068698799</v>
       </c>
       <c r="D167">
-        <v>-5.987546128937495</v>
+        <v>0.06100710449744895</v>
       </c>
       <c r="E167" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3425,16 +3428,16 @@
         <v>28</v>
       </c>
       <c r="B168">
-        <v>98.34274012086618</v>
+        <v>102.3100056930851</v>
       </c>
       <c r="C168">
-        <v>99.9123383882679</v>
+        <v>102.2499244548089</v>
       </c>
       <c r="D168">
-        <v>-1.569598267401716</v>
+        <v>0.06008123827622569</v>
       </c>
       <c r="E168" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3442,16 +3445,16 @@
         <v>28</v>
       </c>
       <c r="B169">
-        <v>111.2159499552103</v>
+        <v>112.1372619479288</v>
       </c>
       <c r="C169">
-        <v>112.5173183939743</v>
+        <v>112.0712414560099</v>
       </c>
       <c r="D169">
-        <v>-1.301368438763916</v>
+        <v>0.06602049191890558</v>
       </c>
       <c r="E169" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3459,16 +3462,16 @@
         <v>29</v>
       </c>
       <c r="B170">
-        <v>105.4528327887368</v>
+        <v>104.9579119843815</v>
       </c>
       <c r="C170">
-        <v>106.5547324052203</v>
+        <v>106.0207505520693</v>
       </c>
       <c r="D170">
-        <v>-1.101899616483422</v>
+        <v>-1.062838567687791</v>
       </c>
       <c r="E170" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3476,16 +3479,16 @@
         <v>29</v>
       </c>
       <c r="B171">
-        <v>85.46608841971141</v>
+        <v>84.83976685403302</v>
       </c>
       <c r="C171">
-        <v>85.36334274023008</v>
+        <v>84.73710160533427</v>
       </c>
       <c r="D171">
-        <v>0.1027456794813304</v>
+        <v>0.1026652486987416</v>
       </c>
       <c r="E171" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3493,16 +3496,16 @@
         <v>29</v>
       </c>
       <c r="B172">
-        <v>116.8462131491031</v>
+        <v>116.6590410671116</v>
       </c>
       <c r="C172">
-        <v>134.415906177119</v>
+        <v>134.0558448258811</v>
       </c>
       <c r="D172">
-        <v>-17.56969302801591</v>
+        <v>-17.39680375876952</v>
       </c>
       <c r="E172" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3510,16 +3513,16 @@
         <v>29</v>
       </c>
       <c r="B173">
-        <v>99.47708336541847</v>
+        <v>98.85102403100562</v>
       </c>
       <c r="C173">
-        <v>99.38473078390709</v>
+        <v>98.75425653050213</v>
       </c>
       <c r="D173">
-        <v>0.09235258151137771</v>
+        <v>0.09676750050348915</v>
       </c>
       <c r="E173" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3527,16 +3530,16 @@
         <v>29</v>
       </c>
       <c r="B174">
-        <v>103.4122869434186</v>
+        <v>102.9848632679722</v>
       </c>
       <c r="C174">
-        <v>109.4228292017821</v>
+        <v>108.9724093969097</v>
       </c>
       <c r="D174">
-        <v>-6.010542258363444</v>
+        <v>-5.987546128937495</v>
       </c>
       <c r="E174" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3544,16 +3547,16 @@
         <v>29</v>
       </c>
       <c r="B175">
-        <v>98.85015245399266</v>
+        <v>98.34274012086618</v>
       </c>
       <c r="C175">
-        <v>100.4286626064006</v>
+        <v>99.9123383882679</v>
       </c>
       <c r="D175">
-        <v>-1.578510152407972</v>
+        <v>-1.569598267401716</v>
       </c>
       <c r="E175" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3561,16 +3564,16 @@
         <v>29</v>
       </c>
       <c r="B176">
-        <v>111.6947923733483</v>
+        <v>111.2159499552103</v>
       </c>
       <c r="C176">
-        <v>113.0707656466028</v>
+        <v>112.5173183939743</v>
       </c>
       <c r="D176">
-        <v>-1.375973273254488</v>
+        <v>-1.301368438763916</v>
       </c>
       <c r="E176" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3578,16 +3581,16 @@
         <v>30</v>
       </c>
       <c r="B177">
-        <v>105.4988639990026</v>
+        <v>105.4528327887368</v>
       </c>
       <c r="C177">
-        <v>106.6066999572787</v>
+        <v>106.5547324052203</v>
       </c>
       <c r="D177">
-        <v>-1.10783595827607</v>
+        <v>-1.101899616483422</v>
       </c>
       <c r="E177" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3595,16 +3598,16 @@
         <v>30</v>
       </c>
       <c r="B178">
-        <v>85.54093804204811</v>
+        <v>85.46608841971141</v>
       </c>
       <c r="C178">
-        <v>85.43818731043199</v>
+        <v>85.36334274023008</v>
       </c>
       <c r="D178">
-        <v>0.1027507316161262</v>
+        <v>0.1027456794813304</v>
       </c>
       <c r="E178" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3612,16 +3615,16 @@
         <v>30</v>
       </c>
       <c r="B179">
-        <v>116.8491507728496</v>
+        <v>116.8462131491031</v>
       </c>
       <c r="C179">
-        <v>134.425272563136</v>
+        <v>134.415906177119</v>
       </c>
       <c r="D179">
-        <v>-17.57612179028634</v>
+        <v>-17.56969302801591</v>
       </c>
       <c r="E179" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3629,16 +3632,16 @@
         <v>30</v>
       </c>
       <c r="B180">
-        <v>99.55102220989978</v>
+        <v>99.47708336541847</v>
       </c>
       <c r="C180">
-        <v>99.45924986741812</v>
+        <v>99.38473078390709</v>
       </c>
       <c r="D180">
-        <v>0.09177234248166144</v>
+        <v>0.09235258151137771</v>
       </c>
       <c r="E180" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3646,16 +3649,16 @@
         <v>30</v>
       </c>
       <c r="B181">
-        <v>103.4469867216055</v>
+        <v>103.4122869434186</v>
       </c>
       <c r="C181">
-        <v>109.4555301238295</v>
+        <v>109.4228292017821</v>
       </c>
       <c r="D181">
-        <v>-6.008543402224021</v>
+        <v>-6.010542258363444</v>
       </c>
       <c r="E181" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3663,16 +3666,16 @@
         <v>30</v>
       </c>
       <c r="B182">
-        <v>98.89768078497382</v>
+        <v>98.85015245399266</v>
       </c>
       <c r="C182">
-        <v>100.4774362827739</v>
+        <v>100.4286626064006</v>
       </c>
       <c r="D182">
-        <v>-1.579755497800051</v>
+        <v>-1.578510152407972</v>
       </c>
       <c r="E182" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3680,16 +3683,16 @@
         <v>30</v>
       </c>
       <c r="B183">
-        <v>111.7391941380343</v>
+        <v>111.6947923733483</v>
       </c>
       <c r="C183">
-        <v>113.1263110717645</v>
+        <v>113.0707656466028</v>
       </c>
       <c r="D183">
-        <v>-1.387116933730226</v>
+        <v>-1.375973273254488</v>
       </c>
       <c r="E183" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3697,16 +3700,16 @@
         <v>31</v>
       </c>
       <c r="B184">
-        <v>105.1226887835173</v>
+        <v>105.4988639990026</v>
       </c>
       <c r="C184">
-        <v>106.9530735360714</v>
+        <v>106.6066999572787</v>
       </c>
       <c r="D184">
-        <v>-1.830384752554011</v>
+        <v>-1.10783595827607</v>
       </c>
       <c r="E184" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3714,16 +3717,16 @@
         <v>31</v>
       </c>
       <c r="B185">
-        <v>87.69407582018482</v>
+        <v>85.54093804204811</v>
       </c>
       <c r="C185">
-        <v>87.5902948695486</v>
+        <v>85.43818731043199</v>
       </c>
       <c r="D185">
-        <v>0.1037809506362208</v>
+        <v>0.1027507316161262</v>
       </c>
       <c r="E185" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3731,16 +3734,16 @@
         <v>31</v>
       </c>
       <c r="B186">
-        <v>111.8142326225407</v>
+        <v>116.8491507728496</v>
       </c>
       <c r="C186">
-        <v>131.5530801685402</v>
+        <v>134.425272563136</v>
       </c>
       <c r="D186">
-        <v>-19.73884754599956</v>
+        <v>-17.57612179028634</v>
       </c>
       <c r="E186" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3748,16 +3751,16 @@
         <v>31</v>
       </c>
       <c r="B187">
-        <v>101.572623329851</v>
+        <v>99.55102220989978</v>
       </c>
       <c r="C187">
-        <v>101.5795424552437</v>
+        <v>99.45924986741812</v>
       </c>
       <c r="D187">
-        <v>-0.006919125392641945</v>
+        <v>0.09177234248166144</v>
       </c>
       <c r="E187" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3765,16 +3768,16 @@
         <v>31</v>
       </c>
       <c r="B188">
-        <v>102.5719181382452</v>
+        <v>103.4469867216055</v>
       </c>
       <c r="C188">
-        <v>108.2919092714632</v>
+        <v>109.4555301238295</v>
       </c>
       <c r="D188">
-        <v>-5.719991133218016</v>
+        <v>-6.008543402224021</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3782,16 +3785,16 @@
         <v>31</v>
       </c>
       <c r="B189">
-        <v>99.09608559752451</v>
+        <v>98.89768078497382</v>
       </c>
       <c r="C189">
-        <v>100.4711801887106</v>
+        <v>100.4774362827739</v>
       </c>
       <c r="D189">
-        <v>-1.375094591186141</v>
+        <v>-1.579755497800051</v>
       </c>
       <c r="E189" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3799,16 +3802,16 @@
         <v>31</v>
       </c>
       <c r="B190">
-        <v>110.5981593242575</v>
+        <v>111.7391941380343</v>
       </c>
       <c r="C190">
-        <v>113.8696459906438</v>
+        <v>113.1263110717645</v>
       </c>
       <c r="D190">
-        <v>-3.27148666638638</v>
+        <v>-1.387116933730226</v>
       </c>
       <c r="E190" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3816,16 +3819,16 @@
         <v>32</v>
       </c>
       <c r="B191">
-        <v>100.2418787728176</v>
+        <v>105.1226887835173</v>
       </c>
       <c r="C191">
-        <v>100.2732036551172</v>
+        <v>106.9530735360714</v>
       </c>
       <c r="D191">
-        <v>-0.03132488229957175</v>
+        <v>-1.830384752554011</v>
       </c>
       <c r="E191" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3833,16 +3836,16 @@
         <v>32</v>
       </c>
       <c r="B192">
-        <v>82.40934090868309</v>
+        <v>87.69407582018482</v>
       </c>
       <c r="C192">
-        <v>82.31172005902241</v>
+        <v>87.5902948695486</v>
       </c>
       <c r="D192">
-        <v>0.09762084966068585</v>
+        <v>0.1037809506362208</v>
       </c>
       <c r="E192" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3850,16 +3853,16 @@
         <v>32</v>
       </c>
       <c r="B193">
-        <v>109.8313208786433</v>
+        <v>111.8142326225407</v>
       </c>
       <c r="C193">
-        <v>122.9806413572697</v>
+        <v>131.5530801685402</v>
       </c>
       <c r="D193">
-        <v>-13.14932047862639</v>
+        <v>-19.73884754599956</v>
       </c>
       <c r="E193" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3867,16 +3870,16 @@
         <v>32</v>
       </c>
       <c r="B194">
-        <v>95.51730432285693</v>
+        <v>101.572623329851</v>
       </c>
       <c r="C194">
-        <v>95.40719743340033</v>
+        <v>101.5795424552437</v>
       </c>
       <c r="D194">
-        <v>0.1101068894566026</v>
+        <v>-0.006919125392641945</v>
       </c>
       <c r="E194" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3884,16 +3887,16 @@
         <v>32</v>
       </c>
       <c r="B195">
-        <v>99.93961840980975</v>
+        <v>102.5719181382452</v>
       </c>
       <c r="C195">
-        <v>101.3708897454307</v>
+        <v>108.2919092714632</v>
       </c>
       <c r="D195">
-        <v>-1.431271335620906</v>
+        <v>-5.719991133218016</v>
       </c>
       <c r="E195" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3901,16 +3904,16 @@
         <v>32</v>
       </c>
       <c r="B196">
-        <v>94.14350842000616</v>
+        <v>99.09608559752451</v>
       </c>
       <c r="C196">
-        <v>94.16117947857694</v>
+        <v>100.4711801887106</v>
       </c>
       <c r="D196">
-        <v>-0.01767105857078377</v>
+        <v>-1.375094591186141</v>
       </c>
       <c r="E196" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3918,16 +3921,16 @@
         <v>32</v>
       </c>
       <c r="B197">
-        <v>106.1477189528232</v>
+        <v>110.5981593242575</v>
       </c>
       <c r="C197">
-        <v>106.8019017849316</v>
+        <v>113.8696459906438</v>
       </c>
       <c r="D197">
-        <v>-0.6541828321084182</v>
+        <v>-3.27148666638638</v>
       </c>
       <c r="E197" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3935,16 +3938,16 @@
         <v>33</v>
       </c>
       <c r="B198">
-        <v>104.997605517938</v>
+        <v>100.2418787728176</v>
       </c>
       <c r="C198">
-        <v>106.0637142263577</v>
+        <v>100.2732036551172</v>
       </c>
       <c r="D198">
-        <v>-1.066108708419691</v>
+        <v>-0.03132488229957175</v>
       </c>
       <c r="E198" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3952,16 +3955,16 @@
         <v>33</v>
       </c>
       <c r="B199">
-        <v>84.88251149200511</v>
+        <v>82.40934090868309</v>
       </c>
       <c r="C199">
-        <v>84.77984738789677</v>
+        <v>82.31172005902241</v>
       </c>
       <c r="D199">
-        <v>0.1026641041083423</v>
+        <v>0.09762084966068585</v>
       </c>
       <c r="E199" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3969,16 +3972,16 @@
         <v>33</v>
       </c>
       <c r="B200">
-        <v>116.6745974682617</v>
+        <v>109.8313208786433</v>
       </c>
       <c r="C200">
-        <v>134.0992696216449</v>
+        <v>122.9806413572697</v>
       </c>
       <c r="D200">
-        <v>-17.42467215338323</v>
+        <v>-13.14932047862639</v>
       </c>
       <c r="E200" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3986,16 +3989,16 @@
         <v>33</v>
       </c>
       <c r="B201">
-        <v>98.89192877167487</v>
+        <v>95.51730432285693</v>
       </c>
       <c r="C201">
-        <v>98.7968458202424</v>
+        <v>95.40719743340033</v>
       </c>
       <c r="D201">
-        <v>0.09508295143247381</v>
+        <v>0.1101068894566026</v>
       </c>
       <c r="E201" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4003,16 +4006,16 @@
         <v>33</v>
       </c>
       <c r="B202">
-        <v>103.0254899050612</v>
+        <v>99.93961840980975</v>
       </c>
       <c r="C202">
-        <v>109.0156831508581</v>
+        <v>101.3708897454307</v>
       </c>
       <c r="D202">
-        <v>-5.990193245796974</v>
+        <v>-1.431271335620906</v>
       </c>
       <c r="E202" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4020,16 +4023,16 @@
         <v>33</v>
       </c>
       <c r="B203">
-        <v>98.38526354751922</v>
+        <v>94.14350842000616</v>
       </c>
       <c r="C203">
-        <v>99.9554086672258</v>
+        <v>94.16117947857694</v>
       </c>
       <c r="D203">
-        <v>-1.570145119706581</v>
+        <v>-0.01767105857078377</v>
       </c>
       <c r="E203" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4037,16 +4040,16 @@
         <v>33</v>
       </c>
       <c r="B204">
-        <v>111.2521561826648</v>
+        <v>106.1477189528232</v>
       </c>
       <c r="C204">
-        <v>112.5601955071123</v>
+        <v>106.8019017849316</v>
       </c>
       <c r="D204">
-        <v>-1.308039324447421</v>
+        <v>-0.6541828321084182</v>
       </c>
       <c r="E204" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4054,16 +4057,16 @@
         <v>34</v>
       </c>
       <c r="B205">
-        <v>105.1491722647487</v>
+        <v>104.997605517938</v>
       </c>
       <c r="C205">
-        <v>106.2271887439795</v>
+        <v>106.0637142263577</v>
       </c>
       <c r="D205">
-        <v>-1.07801647923074</v>
+        <v>-1.066108708419691</v>
       </c>
       <c r="E205" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4071,16 +4074,16 @@
         <v>34</v>
       </c>
       <c r="B206">
-        <v>85.0766784882375</v>
+        <v>84.88251149200511</v>
       </c>
       <c r="C206">
-        <v>84.97398580293675</v>
+        <v>84.77984738789677</v>
       </c>
       <c r="D206">
-        <v>0.1026926853007524</v>
+        <v>0.1026641041083423</v>
       </c>
       <c r="E206" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4088,16 +4091,16 @@
         <v>34</v>
       </c>
       <c r="B207">
-        <v>116.7317040193808</v>
+        <v>116.6745974682617</v>
       </c>
       <c r="C207">
-        <v>134.2047492293683</v>
+        <v>134.0992696216449</v>
       </c>
       <c r="D207">
-        <v>-17.47304520998757</v>
+        <v>-17.42467215338323</v>
       </c>
       <c r="E207" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4105,16 +4108,16 @@
         <v>34</v>
       </c>
       <c r="B208">
-        <v>99.08690757287691</v>
+        <v>98.89192877167487</v>
       </c>
       <c r="C208">
-        <v>98.99274153824337</v>
+        <v>98.7968458202424</v>
       </c>
       <c r="D208">
-        <v>0.09416603463354534</v>
+        <v>0.09508295143247381</v>
       </c>
       <c r="E208" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4122,16 +4125,16 @@
         <v>34</v>
       </c>
       <c r="B209">
-        <v>103.1538154489844</v>
+        <v>103.0254899050612</v>
       </c>
       <c r="C209">
-        <v>109.1509978214199</v>
+        <v>109.0156831508581</v>
       </c>
       <c r="D209">
-        <v>-5.997182372435546</v>
+        <v>-5.990193245796974</v>
       </c>
       <c r="E209" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4139,16 +4142,16 @@
         <v>34</v>
       </c>
       <c r="B210">
-        <v>98.53969432386062</v>
+        <v>98.38526354751922</v>
       </c>
       <c r="C210">
-        <v>100.1127415353614</v>
+        <v>99.9554086672258</v>
       </c>
       <c r="D210">
-        <v>-1.573047211500779</v>
+        <v>-1.570145119706581</v>
       </c>
       <c r="E210" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4156,16 +4159,16 @@
         <v>34</v>
       </c>
       <c r="B211">
-        <v>111.3998949007002</v>
+        <v>111.2521561826648</v>
       </c>
       <c r="C211">
-        <v>112.730422100051</v>
+        <v>112.5601955071123</v>
       </c>
       <c r="D211">
-        <v>-1.330527199350811</v>
+        <v>-1.308039324447421</v>
       </c>
       <c r="E211" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4173,16 +4176,16 @@
         <v>35</v>
       </c>
       <c r="B212">
-        <v>104.1832137966851</v>
+        <v>105.1491722647487</v>
       </c>
       <c r="C212">
-        <v>105.901418558694</v>
+        <v>106.2271887439795</v>
       </c>
       <c r="D212">
-        <v>-1.718204762008924</v>
+        <v>-1.07801647923074</v>
       </c>
       <c r="E212" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4190,16 +4193,16 @@
         <v>35</v>
       </c>
       <c r="B213">
-        <v>86.39731408808406</v>
+        <v>85.0766784882375</v>
       </c>
       <c r="C213">
-        <v>86.29378902549817</v>
+        <v>84.97398580293675</v>
       </c>
       <c r="D213">
-        <v>0.1035250625858879</v>
+        <v>0.1026926853007524</v>
       </c>
       <c r="E213" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4207,16 +4210,16 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>111.4285568509014</v>
+        <v>116.7317040193808</v>
       </c>
       <c r="C214">
-        <v>130.9236150342279</v>
+        <v>134.2047492293683</v>
       </c>
       <c r="D214">
-        <v>-19.49505818332655</v>
+        <v>-17.47304520998757</v>
       </c>
       <c r="E214" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4224,16 +4227,16 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>100.2973418086848</v>
+        <v>99.08690757287691</v>
       </c>
       <c r="C215">
-        <v>100.2749684723782</v>
+        <v>98.99274153824337</v>
       </c>
       <c r="D215">
-        <v>0.02237333630655769</v>
+        <v>0.09416603463354534</v>
       </c>
       <c r="E215" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4241,16 +4244,16 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>101.644865239721</v>
+        <v>103.1538154489844</v>
       </c>
       <c r="C216">
-        <v>107.4600838508705</v>
+        <v>109.1509978214199</v>
       </c>
       <c r="D216">
-        <v>-5.815218611149447</v>
+        <v>-5.997182372435546</v>
       </c>
       <c r="E216" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4258,16 +4261,16 @@
         <v>35</v>
       </c>
       <c r="B217">
-        <v>98.06092566921488</v>
+        <v>98.53969432386062</v>
       </c>
       <c r="C217">
-        <v>99.49528268824609</v>
+        <v>100.1127415353614</v>
       </c>
       <c r="D217">
-        <v>-1.434357019031211</v>
+        <v>-1.573047211500779</v>
       </c>
       <c r="E217" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4275,16 +4278,16 @@
         <v>35</v>
       </c>
       <c r="B218">
-        <v>109.803609637066</v>
+        <v>111.3998949007002</v>
       </c>
       <c r="C218">
-        <v>112.7332010098815</v>
+        <v>112.730422100051</v>
       </c>
       <c r="D218">
-        <v>-2.929591372815494</v>
+        <v>-1.330527199350811</v>
       </c>
       <c r="E218" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4292,16 +4295,16 @@
         <v>36</v>
       </c>
       <c r="B219">
-        <v>100.3765161161741</v>
+        <v>104.1832137966851</v>
       </c>
       <c r="C219">
-        <v>100.7995846244417</v>
+        <v>105.901418558694</v>
       </c>
       <c r="D219">
-        <v>-0.4230685082676615</v>
+        <v>-1.718204762008924</v>
       </c>
       <c r="E219" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4309,16 +4312,16 @@
         <v>36</v>
       </c>
       <c r="B220">
-        <v>97.53257676845587</v>
+        <v>86.39731408808406</v>
       </c>
       <c r="C220">
-        <v>97.56101242915429</v>
+        <v>86.29378902549817</v>
       </c>
       <c r="D220">
-        <v>-0.02843566069842041</v>
+        <v>0.1035250625858879</v>
       </c>
       <c r="E220" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4326,16 +4329,16 @@
         <v>36</v>
       </c>
       <c r="B221">
-        <v>103.5468219082129</v>
+        <v>111.4285568509014</v>
       </c>
       <c r="C221">
-        <v>107.3030062938209</v>
+        <v>130.9236150342279</v>
       </c>
       <c r="D221">
-        <v>-3.756184385608023</v>
+        <v>-19.49505818332655</v>
       </c>
       <c r="E221" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4343,16 +4346,16 @@
         <v>36</v>
       </c>
       <c r="B222">
-        <v>92.28975015654859</v>
+        <v>100.2973418086848</v>
       </c>
       <c r="C222">
-        <v>92.20760021382283</v>
+        <v>100.2749684723782</v>
       </c>
       <c r="D222">
-        <v>0.08214994272576348</v>
+        <v>0.02237333630655769</v>
       </c>
       <c r="E222" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4360,16 +4363,16 @@
         <v>36</v>
       </c>
       <c r="B223">
-        <v>105.1675170341382</v>
+        <v>101.644865239721</v>
       </c>
       <c r="C223">
-        <v>109.9377591870332</v>
+        <v>107.4600838508705</v>
       </c>
       <c r="D223">
-        <v>-4.770242152894951</v>
+        <v>-5.815218611149447</v>
       </c>
       <c r="E223" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4377,16 +4380,16 @@
         <v>36</v>
       </c>
       <c r="B224">
-        <v>104.2486417335563</v>
+        <v>98.06092566921488</v>
       </c>
       <c r="C224">
-        <v>106.8605766912061</v>
+        <v>99.49528268824609</v>
       </c>
       <c r="D224">
-        <v>-2.611934957649893</v>
+        <v>-1.434357019031211</v>
       </c>
       <c r="E224" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4394,16 +4397,16 @@
         <v>36</v>
       </c>
       <c r="B225">
-        <v>94.82482468912521</v>
+        <v>109.803609637066</v>
       </c>
       <c r="C225">
-        <v>94.89533289876225</v>
+        <v>112.7332010098815</v>
       </c>
       <c r="D225">
-        <v>-0.07050820963704041</v>
+        <v>-2.929591372815494</v>
       </c>
       <c r="E225" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4411,16 +4414,16 @@
         <v>37</v>
       </c>
       <c r="B226">
-        <v>102.2294011072405</v>
+        <v>100.3765161161741</v>
       </c>
       <c r="C226">
-        <v>103.4721051204377</v>
+        <v>100.7995846244417</v>
       </c>
       <c r="D226">
-        <v>-1.242704013197269</v>
+        <v>-0.4230685082676615</v>
       </c>
       <c r="E226" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4428,16 +4431,16 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>100.1294989024095</v>
+        <v>97.53257676845587</v>
       </c>
       <c r="C227">
-        <v>100.4639509872304</v>
+        <v>97.56101242915429</v>
       </c>
       <c r="D227">
-        <v>-0.3344520848209243</v>
+        <v>-0.02843566069842041</v>
       </c>
       <c r="E227" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4445,16 +4448,16 @@
         <v>37</v>
       </c>
       <c r="B228">
-        <v>102.7737124671302</v>
+        <v>103.5468219082129</v>
       </c>
       <c r="C228">
-        <v>107.9456395983277</v>
+        <v>107.3030062938209</v>
       </c>
       <c r="D228">
-        <v>-5.17192713119745</v>
+        <v>-3.756184385608023</v>
       </c>
       <c r="E228" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4462,16 +4465,16 @@
         <v>37</v>
       </c>
       <c r="B229">
-        <v>100.0720819657586</v>
+        <v>92.28975015654859</v>
       </c>
       <c r="C229">
-        <v>100.7957183045757</v>
+        <v>92.20760021382283</v>
       </c>
       <c r="D229">
-        <v>-0.7236363388171156</v>
+        <v>0.08214994272576348</v>
       </c>
       <c r="E229" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4479,16 +4482,16 @@
         <v>37</v>
       </c>
       <c r="B230">
-        <v>103.1222784383786</v>
+        <v>105.1675170341382</v>
       </c>
       <c r="C230">
-        <v>105.8210567232339</v>
+        <v>109.9377591870332</v>
       </c>
       <c r="D230">
-        <v>-2.698778284855237</v>
+        <v>-4.770242152894951</v>
       </c>
       <c r="E230" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4496,16 +4499,16 @@
         <v>37</v>
       </c>
       <c r="B231">
-        <v>102.7096224719023</v>
+        <v>104.2486417335563</v>
       </c>
       <c r="C231">
-        <v>104.4253122015573</v>
+        <v>106.8605766912061</v>
       </c>
       <c r="D231">
-        <v>-1.715689729655011</v>
+        <v>-2.611934957649893</v>
       </c>
       <c r="E231" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4513,16 +4516,16 @@
         <v>37</v>
       </c>
       <c r="B232">
-        <v>101.1431442537347</v>
+        <v>94.82482468912521</v>
       </c>
       <c r="C232">
-        <v>102.8088700180732</v>
+        <v>94.89533289876225</v>
       </c>
       <c r="D232">
-        <v>-1.665725764338546</v>
+        <v>-0.07050820963704041</v>
       </c>
       <c r="E232" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4530,16 +4533,16 @@
         <v>38</v>
       </c>
       <c r="B233">
-        <v>97.55601889271624</v>
+        <v>102.2294011072405</v>
       </c>
       <c r="C233">
-        <v>97.58275756300439</v>
+        <v>103.4721051204377</v>
       </c>
       <c r="D233">
-        <v>-0.0267386702881538</v>
+        <v>-1.242704013197269</v>
       </c>
       <c r="E233" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4547,16 +4550,16 @@
         <v>38</v>
       </c>
       <c r="B234">
-        <v>94.84486444141822</v>
+        <v>100.1294989024095</v>
       </c>
       <c r="C234">
-        <v>94.77773314685145</v>
+        <v>100.4639509872304</v>
       </c>
       <c r="D234">
-        <v>0.06713129456677791</v>
+        <v>-0.3344520848209243</v>
       </c>
       <c r="E234" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4564,16 +4567,16 @@
         <v>38</v>
       </c>
       <c r="B235">
-        <v>100.8298629328187</v>
+        <v>102.7737124671302</v>
       </c>
       <c r="C235">
-        <v>102.8026134956058</v>
+        <v>107.9456395983277</v>
       </c>
       <c r="D235">
-        <v>-1.972750562787098</v>
+        <v>-5.17192713119745</v>
       </c>
       <c r="E235" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4581,16 +4584,16 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <v>92.81058407104159</v>
+        <v>100.0720819657586</v>
       </c>
       <c r="C236">
-        <v>92.74999291500882</v>
+        <v>100.7957183045757</v>
       </c>
       <c r="D236">
-        <v>0.06059115603277121</v>
+        <v>-0.7236363388171156</v>
       </c>
       <c r="E236" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4598,16 +4601,16 @@
         <v>38</v>
       </c>
       <c r="B237">
-        <v>101.3636407400726</v>
+        <v>103.1222784383786</v>
       </c>
       <c r="C237">
-        <v>102.5074589427751</v>
+        <v>105.8210567232339</v>
       </c>
       <c r="D237">
-        <v>-1.143818202702505</v>
+        <v>-2.698778284855237</v>
       </c>
       <c r="E237" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4615,16 +4618,16 @@
         <v>38</v>
       </c>
       <c r="B238">
-        <v>100.1792437555197</v>
+        <v>102.7096224719023</v>
       </c>
       <c r="C238">
-        <v>100.6944853155229</v>
+        <v>104.4253122015573</v>
       </c>
       <c r="D238">
-        <v>-0.515241560003119</v>
+        <v>-1.715689729655011</v>
       </c>
       <c r="E238" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4632,16 +4635,16 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>94.69357251026149</v>
+        <v>101.1431442537347</v>
       </c>
       <c r="C239">
-        <v>94.76597534989432</v>
+        <v>102.8088700180732</v>
       </c>
       <c r="D239">
-        <v>-0.07240283963282934</v>
+        <v>-1.665725764338546</v>
       </c>
       <c r="E239" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4649,16 +4652,16 @@
         <v>39</v>
       </c>
       <c r="B240">
-        <v>98.69554597971941</v>
+        <v>97.55601889271624</v>
       </c>
       <c r="C240">
-        <v>98.62627252356684</v>
+        <v>97.58275756300439</v>
       </c>
       <c r="D240">
-        <v>0.06927345615257252</v>
+        <v>-0.0267386702881538</v>
       </c>
       <c r="E240" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4666,16 +4669,16 @@
         <v>39</v>
       </c>
       <c r="B241">
-        <v>96.16959395033481</v>
+        <v>94.84486444141822</v>
       </c>
       <c r="C241">
-        <v>96.08066487729739</v>
+        <v>94.77773314685145</v>
       </c>
       <c r="D241">
-        <v>0.08892907303741993</v>
+        <v>0.06713129456677791</v>
       </c>
       <c r="E241" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4683,16 +4686,16 @@
         <v>39</v>
       </c>
       <c r="B242">
-        <v>102.3082554638168</v>
+        <v>100.8298629328187</v>
       </c>
       <c r="C242">
-        <v>103.1932290203828</v>
+        <v>102.8026134956058</v>
       </c>
       <c r="D242">
-        <v>-0.8849735565660666</v>
+        <v>-1.972750562787098</v>
       </c>
       <c r="E242" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4700,16 +4703,16 @@
         <v>39</v>
       </c>
       <c r="B243">
-        <v>91.96551360846544</v>
+        <v>92.81058407104159</v>
       </c>
       <c r="C243">
-        <v>91.86180833463781</v>
+        <v>92.74999291500882</v>
       </c>
       <c r="D243">
-        <v>0.1037052738276287</v>
+        <v>0.06059115603277121</v>
       </c>
       <c r="E243" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4717,16 +4720,16 @@
         <v>39</v>
       </c>
       <c r="B244">
-        <v>104.4442634447755</v>
+        <v>101.3636407400726</v>
       </c>
       <c r="C244">
-        <v>105.2882276776264</v>
+        <v>102.5074589427751</v>
       </c>
       <c r="D244">
-        <v>-0.8439642328509507</v>
+        <v>-1.143818202702505</v>
       </c>
       <c r="E244" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4734,16 +4737,16 @@
         <v>39</v>
       </c>
       <c r="B245">
-        <v>102.4800823929831</v>
+        <v>100.1792437555197</v>
       </c>
       <c r="C245">
-        <v>102.7164549359843</v>
+        <v>100.6944853155229</v>
       </c>
       <c r="D245">
-        <v>-0.2363725430011669</v>
+        <v>-0.515241560003119</v>
       </c>
       <c r="E245" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4751,16 +4754,16 @@
         <v>39</v>
       </c>
       <c r="B246">
-        <v>94.77463638637404</v>
+        <v>94.69357251026149</v>
       </c>
       <c r="C246">
-        <v>94.72695081600537</v>
+        <v>94.76597534989432</v>
       </c>
       <c r="D246">
-        <v>0.04768557036867094</v>
+        <v>-0.07240283963282934</v>
       </c>
       <c r="E246" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4768,16 +4771,16 @@
         <v>40</v>
       </c>
       <c r="B247">
-        <v>100.6256491097889</v>
+        <v>98.69554597971941</v>
       </c>
       <c r="C247">
-        <v>100.6360390583657</v>
+        <v>98.62627252356684</v>
       </c>
       <c r="D247">
-        <v>-0.0103899485768153</v>
+        <v>0.06927345615257252</v>
       </c>
       <c r="E247" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4785,16 +4788,16 @@
         <v>40</v>
       </c>
       <c r="B248">
-        <v>99.04917259345407</v>
+        <v>96.16959395033481</v>
       </c>
       <c r="C248">
-        <v>98.96840155582525</v>
+        <v>96.08066487729739</v>
       </c>
       <c r="D248">
-        <v>0.08077103762882132</v>
+        <v>0.08892907303741993</v>
       </c>
       <c r="E248" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4802,16 +4805,16 @@
         <v>40</v>
       </c>
       <c r="B249">
-        <v>102.5241231844777</v>
+        <v>102.3082554638168</v>
       </c>
       <c r="C249">
-        <v>104.5741784919224</v>
+        <v>103.1932290203828</v>
       </c>
       <c r="D249">
-        <v>-2.050055307444723</v>
+        <v>-0.8849735565660666</v>
       </c>
       <c r="E249" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4819,16 +4822,16 @@
         <v>40</v>
       </c>
       <c r="B250">
-        <v>94.71726128149932</v>
+        <v>91.96551360846544</v>
       </c>
       <c r="C250">
-        <v>94.64703895360701</v>
+        <v>91.86180833463781</v>
       </c>
       <c r="D250">
-        <v>0.07022232789230998</v>
+        <v>0.1037052738276287</v>
       </c>
       <c r="E250" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4836,16 +4839,16 @@
         <v>40</v>
       </c>
       <c r="B251">
-        <v>105.868815597866</v>
+        <v>104.4442634447755</v>
       </c>
       <c r="C251">
-        <v>106.9374892292422</v>
+        <v>105.2882276776264</v>
       </c>
       <c r="D251">
-        <v>-1.068673631376271</v>
+        <v>-0.8439642328509507</v>
       </c>
       <c r="E251" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4853,16 +4856,16 @@
         <v>40</v>
       </c>
       <c r="B252">
-        <v>105.0466189391316</v>
+        <v>102.4800823929831</v>
       </c>
       <c r="C252">
-        <v>105.4916986506749</v>
+        <v>102.7164549359843</v>
       </c>
       <c r="D252">
-        <v>-0.4450797115432721</v>
+        <v>-0.2363725430011669</v>
       </c>
       <c r="E252" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4870,16 +4873,16 @@
         <v>40</v>
       </c>
       <c r="B253">
-        <v>96.02025315965695</v>
+        <v>94.77463638637404</v>
       </c>
       <c r="C253">
-        <v>96.08539617565962</v>
+        <v>94.72695081600537</v>
       </c>
       <c r="D253">
-        <v>-0.06514301600267913</v>
+        <v>0.04768557036867094</v>
       </c>
       <c r="E253" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4887,16 +4890,16 @@
         <v>41</v>
       </c>
       <c r="B254">
-        <v>99.45270691600022</v>
+        <v>100.6256491097889</v>
       </c>
       <c r="C254">
-        <v>99.44859746239956</v>
+        <v>100.6360390583657</v>
       </c>
       <c r="D254">
-        <v>0.004109453600662505</v>
+        <v>-0.0103899485768153</v>
       </c>
       <c r="E254" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4904,16 +4907,16 @@
         <v>41</v>
       </c>
       <c r="B255">
-        <v>97.54826870540779</v>
+        <v>99.04917259345407</v>
       </c>
       <c r="C255">
-        <v>97.46566660422596</v>
+        <v>98.96840155582525</v>
       </c>
       <c r="D255">
-        <v>0.08260210118183409</v>
+        <v>0.08077103762882132</v>
       </c>
       <c r="E255" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4921,16 +4924,16 @@
         <v>41</v>
       </c>
       <c r="B256">
-        <v>101.8483636570298</v>
+        <v>102.5241231844777</v>
       </c>
       <c r="C256">
-        <v>103.7262934324435</v>
+        <v>104.5741784919224</v>
       </c>
       <c r="D256">
-        <v>-1.877929775413691</v>
+        <v>-2.050055307444723</v>
       </c>
       <c r="E256" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4938,16 +4941,16 @@
         <v>41</v>
       </c>
       <c r="B257">
-        <v>93.60063888169931</v>
+        <v>94.71726128149932</v>
       </c>
       <c r="C257">
-        <v>93.52104600042912</v>
+        <v>94.64703895360701</v>
       </c>
       <c r="D257">
-        <v>0.07959288127018738</v>
+        <v>0.07022232789230998</v>
       </c>
       <c r="E257" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4955,16 +4958,16 @@
         <v>41</v>
       </c>
       <c r="B258">
-        <v>104.5772541298888</v>
+        <v>105.868815597866</v>
       </c>
       <c r="C258">
-        <v>105.6296341809036</v>
+        <v>106.9374892292422</v>
       </c>
       <c r="D258">
-        <v>-1.052380051014765</v>
+        <v>-1.068673631376271</v>
       </c>
       <c r="E258" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4972,16 +4975,16 @@
         <v>41</v>
       </c>
       <c r="B259">
-        <v>103.5924900772574</v>
+        <v>105.0466189391316</v>
       </c>
       <c r="C259">
-        <v>104.0276605327914</v>
+        <v>105.4916986506749</v>
       </c>
       <c r="D259">
-        <v>-0.4351704555340206</v>
+        <v>-0.4450797115432721</v>
       </c>
       <c r="E259" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4989,16 +4992,16 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>95.08943150847577</v>
+        <v>96.02025315965695</v>
       </c>
       <c r="C260">
-        <v>95.1262775135523</v>
+        <v>96.08539617565962</v>
       </c>
       <c r="D260">
-        <v>-0.03684600507652647</v>
+        <v>-0.06514301600267913</v>
       </c>
       <c r="E260" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5006,16 +5009,16 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>105.0469210890513</v>
+        <v>99.45270691600022</v>
       </c>
       <c r="C261">
-        <v>104.934854189452</v>
+        <v>99.44859746239956</v>
       </c>
       <c r="D261">
-        <v>0.1120668995993412</v>
+        <v>0.004109453600662505</v>
       </c>
       <c r="E261" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5023,16 +5026,16 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>104.9209317049088</v>
+        <v>97.54826870540779</v>
       </c>
       <c r="C262">
-        <v>104.815488544885</v>
+        <v>97.46566660422596</v>
       </c>
       <c r="D262">
-        <v>0.1054431600237251</v>
+        <v>0.08260210118183409</v>
       </c>
       <c r="E262" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5040,16 +5043,16 @@
         <v>42</v>
       </c>
       <c r="B263">
-        <v>105.9899624052343</v>
+        <v>101.8483636570298</v>
       </c>
       <c r="C263">
-        <v>105.8701124222063</v>
+        <v>103.7262934324435</v>
       </c>
       <c r="D263">
-        <v>0.1198499830279758</v>
+        <v>-1.877929775413691</v>
       </c>
       <c r="E263" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5057,16 +5060,16 @@
         <v>42</v>
       </c>
       <c r="B264">
-        <v>103.3132132430596</v>
+        <v>93.60063888169931</v>
       </c>
       <c r="C264">
-        <v>103.2004943468681</v>
+        <v>93.52104600042912</v>
       </c>
       <c r="D264">
-        <v>0.1127188961914811</v>
+        <v>0.07959288127018738</v>
       </c>
       <c r="E264" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5074,16 +5077,16 @@
         <v>42</v>
       </c>
       <c r="B265">
-        <v>106.9721578817352</v>
+        <v>104.5772541298888</v>
       </c>
       <c r="C265">
-        <v>106.8619024607075</v>
+        <v>105.6296341809036</v>
       </c>
       <c r="D265">
-        <v>0.1102554210277304</v>
+        <v>-1.052380051014765</v>
       </c>
       <c r="E265" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5091,16 +5094,16 @@
         <v>42</v>
       </c>
       <c r="B266">
-        <v>106.8177712164456</v>
+        <v>103.5924900772574</v>
       </c>
       <c r="C266">
-        <v>106.7097761331666</v>
+        <v>104.0276605327914</v>
       </c>
       <c r="D266">
-        <v>0.1079950832789507</v>
+        <v>-0.4351704555340206</v>
       </c>
       <c r="E266" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5108,16 +5111,16 @@
         <v>42</v>
       </c>
       <c r="B267">
-        <v>103.675941103797</v>
+        <v>95.08943150847577</v>
       </c>
       <c r="C267">
-        <v>103.55926104372</v>
+        <v>95.1262775135523</v>
       </c>
       <c r="D267">
-        <v>0.1166800600770728</v>
+        <v>-0.03684600507652647</v>
       </c>
       <c r="E267" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5125,16 +5128,16 @@
         <v>43</v>
       </c>
       <c r="B268">
-        <v>101.9229831929245</v>
+        <v>105.0469210890513</v>
       </c>
       <c r="C268">
-        <v>100.6593702130711</v>
+        <v>104.934854189452</v>
       </c>
       <c r="D268">
-        <v>1.263612979853349</v>
+        <v>0.1120668995993412</v>
       </c>
       <c r="E268" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5142,16 +5145,16 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>99.51527079742749</v>
+        <v>104.9209317049088</v>
       </c>
       <c r="C269">
-        <v>95.04997009851439</v>
+        <v>104.815488544885</v>
       </c>
       <c r="D269">
-        <v>4.465300698913097</v>
+        <v>0.1054431600237251</v>
       </c>
       <c r="E269" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5159,16 +5162,16 @@
         <v>43</v>
       </c>
       <c r="B270">
-        <v>104.3889487482931</v>
+        <v>105.9899624052343</v>
       </c>
       <c r="C270">
-        <v>106.6090103361114</v>
+        <v>105.8701124222063</v>
       </c>
       <c r="D270">
-        <v>-2.220061587818236</v>
+        <v>0.1198499830279758</v>
       </c>
       <c r="E270" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5176,16 +5179,16 @@
         <v>43</v>
       </c>
       <c r="B271">
-        <v>103.5609526407742</v>
+        <v>103.3132132430596</v>
       </c>
       <c r="C271">
-        <v>102.9673002535509</v>
+        <v>103.2004943468681</v>
       </c>
       <c r="D271">
-        <v>0.59365238722323</v>
+        <v>0.1127188961914811</v>
       </c>
       <c r="E271" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5193,16 +5196,16 @@
         <v>43</v>
       </c>
       <c r="B272">
-        <v>99.80760335902156</v>
+        <v>106.9721578817352</v>
       </c>
       <c r="C272">
-        <v>97.2355169738895</v>
+        <v>106.8619024607075</v>
       </c>
       <c r="D272">
-        <v>2.572086385132053</v>
+        <v>0.1102554210277304</v>
       </c>
       <c r="E272" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5210,16 +5213,16 @@
         <v>43</v>
       </c>
       <c r="B273">
-        <v>99.08768731646236</v>
+        <v>106.8177712164456</v>
       </c>
       <c r="C273">
-        <v>95.44783676713506</v>
+        <v>106.7097761331666</v>
       </c>
       <c r="D273">
-        <v>3.639850549327306</v>
+        <v>0.1079950832789507</v>
       </c>
       <c r="E273" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5227,16 +5230,16 @@
         <v>43</v>
       </c>
       <c r="B274">
-        <v>104.8394082482462</v>
+        <v>103.675941103797</v>
       </c>
       <c r="C274">
-        <v>106.1605563051736</v>
+        <v>103.55926104372</v>
       </c>
       <c r="D274">
-        <v>-1.321148056927399</v>
+        <v>0.1166800600770728</v>
       </c>
       <c r="E274" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5244,16 +5247,16 @@
         <v>44</v>
       </c>
       <c r="B275">
-        <v>101.5705047436691</v>
+        <v>101.9229831929245</v>
       </c>
       <c r="C275">
-        <v>98.81308519430915</v>
+        <v>100.6593702130711</v>
       </c>
       <c r="D275">
-        <v>2.757419549359994</v>
+        <v>1.263612979853349</v>
       </c>
       <c r="E275" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5261,16 +5264,16 @@
         <v>44</v>
       </c>
       <c r="B276">
-        <v>97.9961175953152</v>
+        <v>99.51527079742749</v>
       </c>
       <c r="C276">
-        <v>92.12140045928801</v>
+        <v>95.04997009851439</v>
       </c>
       <c r="D276">
-        <v>5.874717136027186</v>
+        <v>4.465300698913097</v>
       </c>
       <c r="E276" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5278,16 +5281,16 @@
         <v>44</v>
       </c>
       <c r="B277">
-        <v>105.2810829582148</v>
+        <v>104.3889487482931</v>
       </c>
       <c r="C277">
-        <v>106.0246480797973</v>
+        <v>106.6090103361114</v>
       </c>
       <c r="D277">
-        <v>-0.7435651215825203</v>
+        <v>-2.220061587818236</v>
       </c>
       <c r="E277" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5295,16 +5298,16 @@
         <v>44</v>
       </c>
       <c r="B278">
-        <v>103.5774202608119</v>
+        <v>103.5609526407742</v>
       </c>
       <c r="C278">
-        <v>100.8834619450059</v>
+        <v>102.9673002535509</v>
       </c>
       <c r="D278">
-        <v>2.693958315806015</v>
+        <v>0.59365238722323</v>
       </c>
       <c r="E278" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5312,16 +5315,16 @@
         <v>44</v>
       </c>
       <c r="B279">
-        <v>98.85954632053668</v>
+        <v>99.80760335902156</v>
       </c>
       <c r="C279">
-        <v>95.39425031277501</v>
+        <v>97.2355169738895</v>
       </c>
       <c r="D279">
-        <v>3.465296007761665</v>
+        <v>2.572086385132053</v>
       </c>
       <c r="E279" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5329,16 +5332,16 @@
         <v>44</v>
       </c>
       <c r="B280">
-        <v>97.76091852274479</v>
+        <v>99.08768731646236</v>
       </c>
       <c r="C280">
-        <v>93.21395155760256</v>
+        <v>95.44783676713506</v>
       </c>
       <c r="D280">
-        <v>4.546966965142232</v>
+        <v>3.639850549327306</v>
       </c>
       <c r="E280" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5346,16 +5349,16 @@
         <v>44</v>
       </c>
       <c r="B281">
-        <v>105.5347417797663</v>
+        <v>104.8394082482462</v>
       </c>
       <c r="C281">
-        <v>104.7676893661906</v>
+        <v>106.1605563051736</v>
       </c>
       <c r="D281">
-        <v>0.7670524135757546</v>
+        <v>-1.321148056927399</v>
       </c>
       <c r="E281" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5363,16 +5366,16 @@
         <v>45</v>
       </c>
       <c r="B282">
-        <v>99.91410117101903</v>
+        <v>101.5705047436691</v>
       </c>
       <c r="C282">
-        <v>96.69459713292947</v>
+        <v>98.81308519430915</v>
       </c>
       <c r="D282">
-        <v>3.219504038089553</v>
+        <v>2.757419549359994</v>
       </c>
       <c r="E282" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5380,16 +5383,16 @@
         <v>45</v>
       </c>
       <c r="B283">
-        <v>97.65489751817806</v>
+        <v>97.9961175953152</v>
       </c>
       <c r="C283">
-        <v>91.344436322275</v>
+        <v>92.12140045928801</v>
       </c>
       <c r="D283">
-        <v>6.310461195903059</v>
+        <v>5.874717136027186</v>
       </c>
       <c r="E283" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5397,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="B284">
-        <v>102.2255705194341</v>
+        <v>105.2810829582148</v>
       </c>
       <c r="C284">
-        <v>102.3645906790227</v>
+        <v>106.0246480797973</v>
       </c>
       <c r="D284">
-        <v>-0.1390201595885827</v>
+        <v>-0.7435651215825203</v>
       </c>
       <c r="E284" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5414,16 +5417,16 @@
         <v>45</v>
       </c>
       <c r="B285">
-        <v>101.4719515543709</v>
+        <v>103.5774202608119</v>
       </c>
       <c r="C285">
-        <v>98.92306292065564</v>
+        <v>100.8834619450059</v>
       </c>
       <c r="D285">
-        <v>2.548888633715279</v>
+        <v>2.693958315806015</v>
       </c>
       <c r="E285" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5431,16 +5434,16 @@
         <v>45</v>
       </c>
       <c r="B286">
-        <v>97.90768844290409</v>
+        <v>98.85954632053668</v>
       </c>
       <c r="C286">
-        <v>93.40278542318539</v>
+        <v>95.39425031277501</v>
       </c>
       <c r="D286">
-        <v>4.504903019718697</v>
+        <v>3.465296007761665</v>
       </c>
       <c r="E286" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5448,16 +5451,16 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>97.23359000519416</v>
+        <v>97.76091852274479</v>
       </c>
       <c r="C287">
-        <v>91.69997918963946</v>
+        <v>93.21395155760256</v>
       </c>
       <c r="D287">
-        <v>5.533610815554695</v>
+        <v>4.546966965142232</v>
       </c>
       <c r="E287" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5465,16 +5468,16 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>102.6685079948128</v>
+        <v>105.5347417797663</v>
       </c>
       <c r="C288">
-        <v>101.9649588704356</v>
+        <v>104.7676893661906</v>
       </c>
       <c r="D288">
-        <v>0.7035491243772043</v>
+        <v>0.7670524135757546</v>
       </c>
       <c r="E288" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5482,16 +5485,16 @@
         <v>46</v>
       </c>
       <c r="B289">
-        <v>104.7425300861989</v>
+        <v>99.91410117101903</v>
       </c>
       <c r="C289">
-        <v>98.94832187775796</v>
+        <v>96.69459713292947</v>
       </c>
       <c r="D289">
-        <v>5.794208208440978</v>
+        <v>3.219504038089553</v>
       </c>
       <c r="E289" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5499,16 +5502,16 @@
         <v>46</v>
       </c>
       <c r="B290">
-        <v>104.5567339958388</v>
+        <v>97.65489751817806</v>
       </c>
       <c r="C290">
-        <v>92.54615646655762</v>
+        <v>91.344436322275</v>
       </c>
       <c r="D290">
-        <v>12.01057752928122</v>
+        <v>6.310461195903059</v>
       </c>
       <c r="E290" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5516,16 +5519,16 @@
         <v>46</v>
       </c>
       <c r="B291">
-        <v>104.9286563340331</v>
+        <v>102.2255705194341</v>
       </c>
       <c r="C291">
-        <v>105.825270430989</v>
+        <v>102.3645906790227</v>
       </c>
       <c r="D291">
-        <v>-0.8966140969558865</v>
+        <v>-0.1390201595885827</v>
       </c>
       <c r="E291" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5533,16 +5536,16 @@
         <v>46</v>
       </c>
       <c r="B292">
-        <v>104.8967477163994</v>
+        <v>101.4719515543709</v>
       </c>
       <c r="C292">
-        <v>101.060670348169</v>
+        <v>98.92306292065564</v>
       </c>
       <c r="D292">
-        <v>3.83607736823042</v>
+        <v>2.548888633715279</v>
       </c>
       <c r="E292" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5550,16 +5553,16 @@
         <v>46</v>
       </c>
       <c r="B293">
-        <v>104.5492285712636</v>
+        <v>97.90768844290409</v>
       </c>
       <c r="C293">
-        <v>95.54802751886486</v>
+        <v>93.40278542318539</v>
       </c>
       <c r="D293">
-        <v>9.001201052398713</v>
+        <v>4.504903019718697</v>
       </c>
       <c r="E293" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5567,16 +5570,16 @@
         <v>46</v>
       </c>
       <c r="B294">
-        <v>104.4953386961058</v>
+        <v>97.23359000519416</v>
       </c>
       <c r="C294">
-        <v>93.4682232377552</v>
+        <v>91.69997918963946</v>
       </c>
       <c r="D294">
-        <v>11.02711545835064</v>
+        <v>5.533610815554695</v>
       </c>
       <c r="E294" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5584,16 +5587,16 @@
         <v>46</v>
       </c>
       <c r="B295">
-        <v>104.9903062256608</v>
+        <v>102.6685079948128</v>
       </c>
       <c r="C295">
-        <v>104.7697320289855</v>
+        <v>101.9649588704356</v>
       </c>
       <c r="D295">
-        <v>0.2205741966752583</v>
+        <v>0.7035491243772043</v>
       </c>
       <c r="E295" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5601,16 +5604,16 @@
         <v>47</v>
       </c>
       <c r="B296">
-        <v>100.1232279134955</v>
+        <v>104.7425300861989</v>
       </c>
       <c r="C296">
-        <v>97.49091858613812</v>
+        <v>98.94832187775796</v>
       </c>
       <c r="D296">
-        <v>2.632309327357419</v>
+        <v>5.794208208440978</v>
       </c>
       <c r="E296" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5618,16 +5621,16 @@
         <v>47</v>
       </c>
       <c r="B297">
-        <v>97.75803088557709</v>
+        <v>104.5567339958388</v>
       </c>
       <c r="C297">
-        <v>91.19634782932248</v>
+        <v>92.54615646655762</v>
       </c>
       <c r="D297">
-        <v>6.561683056254608</v>
+        <v>12.01057752928122</v>
       </c>
       <c r="E297" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5635,16 +5638,16 @@
         <v>47</v>
       </c>
       <c r="B298">
-        <v>102.5456494674216</v>
+        <v>104.9286563340331</v>
       </c>
       <c r="C298">
-        <v>104.2311938623516</v>
+        <v>105.825270430989</v>
       </c>
       <c r="D298">
-        <v>-1.68554439493002</v>
+        <v>-0.8966140969558865</v>
       </c>
       <c r="E298" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5652,16 +5655,16 @@
         <v>47</v>
       </c>
       <c r="B299">
-        <v>101.7322741090132</v>
+        <v>104.8967477163994</v>
       </c>
       <c r="C299">
-        <v>99.619256137965</v>
+        <v>101.060670348169</v>
       </c>
       <c r="D299">
-        <v>2.113017971048237</v>
+        <v>3.83607736823042</v>
       </c>
       <c r="E299" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5669,16 +5672,16 @@
         <v>47</v>
       </c>
       <c r="B300">
-        <v>98.04520144097199</v>
+        <v>104.5492285712636</v>
       </c>
       <c r="C300">
-        <v>94.18945723996777</v>
+        <v>95.54802751886486</v>
       </c>
       <c r="D300">
-        <v>3.855744201004228</v>
+        <v>9.001201052398713</v>
       </c>
       <c r="E300" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5686,16 +5689,16 @@
         <v>47</v>
       </c>
       <c r="B301">
-        <v>97.33799767053974</v>
+        <v>104.4953386961058</v>
       </c>
       <c r="C301">
-        <v>92.3026073164876</v>
+        <v>93.4682232377552</v>
       </c>
       <c r="D301">
-        <v>5.03539035405214</v>
+        <v>11.02711545835064</v>
       </c>
       <c r="E301" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5703,16 +5706,16 @@
         <v>47</v>
       </c>
       <c r="B302">
-        <v>102.9881547568737</v>
+        <v>104.9903062256608</v>
       </c>
       <c r="C302">
-        <v>102.9751005955365</v>
+        <v>104.7697320289855</v>
       </c>
       <c r="D302">
-        <v>0.01305416133722304</v>
+        <v>0.2205741966752583</v>
       </c>
       <c r="E302" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5720,16 +5723,16 @@
         <v>48</v>
       </c>
       <c r="B303">
-        <v>101.9502325061552</v>
+        <v>100.1232279134955</v>
       </c>
       <c r="C303">
-        <v>96.73657356840648</v>
+        <v>97.49091858613812</v>
       </c>
       <c r="D303">
-        <v>5.213658937748676</v>
+        <v>2.632309327357419</v>
       </c>
       <c r="E303" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5737,16 +5740,16 @@
         <v>48</v>
       </c>
       <c r="B304">
-        <v>100.4695873910087</v>
+        <v>97.75803088557709</v>
       </c>
       <c r="C304">
-        <v>89.04481367165511</v>
+        <v>91.19634782932248</v>
       </c>
       <c r="D304">
-        <v>11.42477371935364</v>
+        <v>6.561683056254608</v>
       </c>
       <c r="E304" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5754,16 +5757,16 @@
         <v>48</v>
       </c>
       <c r="B305">
-        <v>103.4526982539322</v>
+        <v>102.5456494674216</v>
       </c>
       <c r="C305">
-        <v>105.1298970734496</v>
+        <v>104.2311938623516</v>
       </c>
       <c r="D305">
-        <v>-1.677198819517386</v>
+        <v>-1.68554439493002</v>
       </c>
       <c r="E305" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5771,16 +5774,16 @@
         <v>48</v>
       </c>
       <c r="B306">
-        <v>103.0838139976804</v>
+        <v>101.7322741090132</v>
       </c>
       <c r="C306">
-        <v>98.54152873344309</v>
+        <v>99.619256137965</v>
       </c>
       <c r="D306">
-        <v>4.542285264237293</v>
+        <v>2.113017971048237</v>
       </c>
       <c r="E306" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5788,16 +5791,16 @@
         <v>48</v>
       </c>
       <c r="B307">
-        <v>100.5181388222082</v>
+        <v>98.04520144097199</v>
       </c>
       <c r="C307">
-        <v>93.37096803330924</v>
+        <v>94.18945723996777</v>
       </c>
       <c r="D307">
-        <v>7.147170788899004</v>
+        <v>3.855744201004228</v>
       </c>
       <c r="E307" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5805,16 +5808,16 @@
         <v>48</v>
       </c>
       <c r="B308">
-        <v>100.083810073087</v>
+        <v>97.33799767053974</v>
       </c>
       <c r="C308">
-        <v>90.83580266136184</v>
+        <v>92.3026073164876</v>
       </c>
       <c r="D308">
-        <v>9.248007411725155</v>
+        <v>5.03539035405214</v>
       </c>
       <c r="E308" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5822,16 +5825,16 @@
         <v>48</v>
       </c>
       <c r="B309">
-        <v>103.8514610951452</v>
+        <v>102.9881547568737</v>
       </c>
       <c r="C309">
-        <v>103.0343445217546</v>
+        <v>102.9751005955365</v>
       </c>
       <c r="D309">
-        <v>0.8171165733906491</v>
+        <v>0.01305416133722304</v>
       </c>
       <c r="E309" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5839,16 +5842,16 @@
         <v>49</v>
       </c>
       <c r="B310">
-        <v>100.6710591156055</v>
+        <v>101.9502325061552</v>
       </c>
       <c r="C310">
-        <v>97.91949917476222</v>
+        <v>96.73657356840648</v>
       </c>
       <c r="D310">
-        <v>2.751559940843308</v>
+        <v>5.213658937748676</v>
       </c>
       <c r="E310" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5856,16 +5859,16 @@
         <v>49</v>
       </c>
       <c r="B311">
-        <v>96.73421748474941</v>
+        <v>100.4695873910087</v>
       </c>
       <c r="C311">
-        <v>90.88949512383789</v>
+        <v>89.04481367165511</v>
       </c>
       <c r="D311">
-        <v>5.844722360911518</v>
+        <v>11.42477371935364</v>
       </c>
       <c r="E311" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5873,16 +5876,16 @@
         <v>49</v>
       </c>
       <c r="B312">
-        <v>104.7741665047963</v>
+        <v>103.4526982539322</v>
       </c>
       <c r="C312">
-        <v>105.5278498991754</v>
+        <v>105.1298970734496</v>
       </c>
       <c r="D312">
-        <v>-0.7536833943790242</v>
+        <v>-1.677198819517386</v>
       </c>
       <c r="E312" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5890,16 +5893,16 @@
         <v>49</v>
       </c>
       <c r="B313">
-        <v>102.7663222370925</v>
+        <v>103.0838139976804</v>
       </c>
       <c r="C313">
-        <v>99.91300706244543</v>
+        <v>98.54152873344309</v>
       </c>
       <c r="D313">
-        <v>2.853315174647022</v>
+        <v>4.542285264237293</v>
       </c>
       <c r="E313" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5907,16 +5910,16 @@
         <v>49</v>
       </c>
       <c r="B314">
-        <v>97.80020626629396</v>
+        <v>100.5181388222082</v>
       </c>
       <c r="C314">
-        <v>94.50604123461331</v>
+        <v>93.37096803330924</v>
       </c>
       <c r="D314">
-        <v>3.294165031680649</v>
+        <v>7.147170788899004</v>
       </c>
       <c r="E314" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5924,16 +5927,16 @@
         <v>49</v>
       </c>
       <c r="B315">
-        <v>96.58185907713542</v>
+        <v>100.083810073087</v>
       </c>
       <c r="C315">
-        <v>92.20651515057573</v>
+        <v>90.83580266136184</v>
       </c>
       <c r="D315">
-        <v>4.375343926559694</v>
+        <v>9.248007411725155</v>
       </c>
       <c r="E315" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5941,16 +5944,16 @@
         <v>49</v>
       </c>
       <c r="B316">
-        <v>104.939088966752</v>
+        <v>103.8514610951452</v>
       </c>
       <c r="C316">
-        <v>104.0034535332947</v>
+        <v>103.0343445217546</v>
       </c>
       <c r="D316">
-        <v>0.9356354334573211</v>
+        <v>0.8171165733906491</v>
       </c>
       <c r="E316" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5958,16 +5961,16 @@
         <v>50</v>
       </c>
       <c r="B317">
-        <v>103.3440692082781</v>
+        <v>100.6710591156055</v>
       </c>
       <c r="C317">
-        <v>100.4467652356561</v>
+        <v>97.91949917476222</v>
       </c>
       <c r="D317">
-        <v>2.89730397262197</v>
+        <v>2.751559940843308</v>
       </c>
       <c r="E317" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5975,16 +5978,16 @@
         <v>50</v>
       </c>
       <c r="B318">
-        <v>102.5693891448442</v>
+        <v>96.73421748474941</v>
       </c>
       <c r="C318">
-        <v>96.53475413633566</v>
+        <v>90.88949512383789</v>
       </c>
       <c r="D318">
-        <v>6.034635008508531</v>
+        <v>5.844722360911518</v>
       </c>
       <c r="E318" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5992,16 +5995,16 @@
         <v>50</v>
       </c>
       <c r="B319">
-        <v>104.1246002298358</v>
+        <v>104.7741665047963</v>
       </c>
       <c r="C319">
-        <v>104.5231890831979</v>
+        <v>105.5278498991754</v>
       </c>
       <c r="D319">
-        <v>-0.3985888533620425</v>
+        <v>-0.7536833943790242</v>
       </c>
       <c r="E319" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6009,16 +6012,16 @@
         <v>50</v>
       </c>
       <c r="B320">
-        <v>103.990470790756</v>
+        <v>102.7663222370925</v>
       </c>
       <c r="C320">
-        <v>102.534376568907</v>
+        <v>99.91300706244543</v>
       </c>
       <c r="D320">
-        <v>1.456094221849</v>
+        <v>2.853315174647022</v>
       </c>
       <c r="E320" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -6026,16 +6029,16 @@
         <v>50</v>
       </c>
       <c r="B321">
-        <v>102.5381886657457</v>
+        <v>97.80020626629396</v>
       </c>
       <c r="C321">
-        <v>97.58848417621684</v>
+        <v>94.50604123461331</v>
       </c>
       <c r="D321">
-        <v>4.949704489528813</v>
+        <v>3.294165031680649</v>
       </c>
       <c r="E321" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -6043,16 +6046,16 @@
         <v>50</v>
       </c>
       <c r="B322">
-        <v>102.3143782720726</v>
+        <v>96.58185907713542</v>
       </c>
       <c r="C322">
-        <v>96.37822731993201</v>
+        <v>92.20651515057573</v>
       </c>
       <c r="D322">
-        <v>5.936150952140565</v>
+        <v>4.375343926559694</v>
       </c>
       <c r="E322" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6060,16 +6063,16 @@
         <v>50</v>
       </c>
       <c r="B323">
-        <v>104.3841229443364</v>
+        <v>104.939088966752</v>
       </c>
       <c r="C323">
-        <v>104.6926201713064</v>
+        <v>104.0034535332947</v>
       </c>
       <c r="D323">
-        <v>-0.3084972269699904</v>
+        <v>0.9356354334573211</v>
       </c>
       <c r="E323" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -6077,16 +6080,16 @@
         <v>51</v>
       </c>
       <c r="B324">
-        <v>103.2464375334023</v>
+        <v>103.3440692082781</v>
       </c>
       <c r="C324">
-        <v>100.2586674664994</v>
+        <v>100.4467652356561</v>
       </c>
       <c r="D324">
-        <v>2.987770066902868</v>
+        <v>2.89730397262197</v>
       </c>
       <c r="E324" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6094,16 +6097,16 @@
         <v>51</v>
       </c>
       <c r="B325">
-        <v>102.4724893292097</v>
+        <v>102.5693891448442</v>
       </c>
       <c r="C325">
-        <v>96.35106641146771</v>
+        <v>96.53475413633566</v>
       </c>
       <c r="D325">
-        <v>6.121422917741981</v>
+        <v>6.034635008508531</v>
       </c>
       <c r="E325" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6111,16 +6114,16 @@
         <v>51</v>
       </c>
       <c r="B326">
-        <v>104.0262311681752</v>
+        <v>104.1246002298358</v>
       </c>
       <c r="C326">
-        <v>104.3305201568943</v>
+        <v>104.5231890831979</v>
       </c>
       <c r="D326">
-        <v>-0.3042889887190796</v>
+        <v>-0.3985888533620425</v>
       </c>
       <c r="E326" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6128,16 +6131,16 @@
         <v>51</v>
       </c>
       <c r="B327">
-        <v>103.8922284444636</v>
+        <v>103.990470790756</v>
       </c>
       <c r="C327">
-        <v>102.3437134491517</v>
+        <v>102.534376568907</v>
       </c>
       <c r="D327">
-        <v>1.548514995311905</v>
+        <v>1.456094221849</v>
       </c>
       <c r="E327" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6145,16 +6148,16 @@
         <v>51</v>
       </c>
       <c r="B328">
-        <v>102.4413183259684</v>
+        <v>102.5381886657457</v>
       </c>
       <c r="C328">
-        <v>97.40382673883738</v>
+        <v>97.58848417621684</v>
       </c>
       <c r="D328">
-        <v>5.037491587131029</v>
+        <v>4.949704489528813</v>
       </c>
       <c r="E328" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6162,16 +6165,16 @@
         <v>51</v>
       </c>
       <c r="B329">
-        <v>102.2177193714593</v>
+        <v>102.3143782720726</v>
       </c>
       <c r="C329">
-        <v>96.19491978588395</v>
+        <v>96.37822731993201</v>
       </c>
       <c r="D329">
-        <v>6.022799585575299</v>
+        <v>5.936150952140565</v>
       </c>
       <c r="E329" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6179,16 +6182,16 @@
         <v>51</v>
       </c>
       <c r="B330">
-        <v>104.2855087052072</v>
+        <v>104.3841229443364</v>
       </c>
       <c r="C330">
-        <v>104.4995546813235</v>
+        <v>104.6926201713064</v>
       </c>
       <c r="D330">
-        <v>-0.21404597611631</v>
+        <v>-0.3084972269699904</v>
       </c>
       <c r="E330" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6196,16 +6199,16 @@
         <v>52</v>
       </c>
       <c r="B331">
-        <v>101.1809011053704</v>
+        <v>103.2464375334023</v>
       </c>
       <c r="C331">
-        <v>98.01051974825486</v>
+        <v>100.2586674664994</v>
       </c>
       <c r="D331">
-        <v>3.170381357115531</v>
+        <v>2.987770066902868</v>
       </c>
       <c r="E331" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6213,16 +6216,16 @@
         <v>52</v>
       </c>
       <c r="B332">
-        <v>99.60019526064582</v>
+        <v>102.4724893292097</v>
       </c>
       <c r="C332">
-        <v>93.31617970552955</v>
+        <v>96.35106641146771</v>
       </c>
       <c r="D332">
-        <v>6.28401555511627</v>
+        <v>6.121422917741981</v>
       </c>
       <c r="E332" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6230,16 +6233,16 @@
         <v>52</v>
       </c>
       <c r="B333">
-        <v>102.7866935572146</v>
+        <v>104.0262311681752</v>
       </c>
       <c r="C333">
-        <v>102.9470037236309</v>
+        <v>104.3305201568943</v>
       </c>
       <c r="D333">
-        <v>-0.1603101664162381</v>
+        <v>-0.3042889887190796</v>
       </c>
       <c r="E333" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6247,16 +6250,16 @@
         <v>52</v>
       </c>
       <c r="B334">
-        <v>102.3745838274864</v>
+        <v>103.8922284444636</v>
       </c>
       <c r="C334">
-        <v>100.2116806783557</v>
+        <v>102.3437134491517</v>
       </c>
       <c r="D334">
-        <v>2.16290314913077</v>
+        <v>1.548514995311905</v>
       </c>
       <c r="E334" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6264,16 +6267,16 @@
         <v>52</v>
       </c>
       <c r="B335">
-        <v>99.66936175274516</v>
+        <v>102.4413183259684</v>
       </c>
       <c r="C335">
-        <v>94.88150568603582</v>
+        <v>97.40382673883738</v>
       </c>
       <c r="D335">
-        <v>4.787856066709338</v>
+        <v>5.037491587131029</v>
       </c>
       <c r="E335" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6281,16 +6284,16 @@
         <v>52</v>
       </c>
       <c r="B336">
-        <v>99.20460448818741</v>
+        <v>102.2177193714593</v>
       </c>
       <c r="C336">
-        <v>93.40658335906356</v>
+        <v>96.19491978588395</v>
       </c>
       <c r="D336">
-        <v>5.798021129123853</v>
+        <v>6.022799585575299</v>
       </c>
       <c r="E336" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6298,16 +6301,16 @@
         <v>52</v>
       </c>
       <c r="B337">
-        <v>103.1965683580116</v>
+        <v>104.2855087052072</v>
       </c>
       <c r="C337">
-        <v>102.8457126163961</v>
+        <v>104.4995546813235</v>
       </c>
       <c r="D337">
-        <v>0.3508557416155327</v>
+        <v>-0.21404597611631</v>
       </c>
       <c r="E337" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6315,16 +6318,16 @@
         <v>53</v>
       </c>
       <c r="B338">
-        <v>103.4417008831539</v>
+        <v>101.1809011053704</v>
       </c>
       <c r="C338">
-        <v>100.6348630048129</v>
+        <v>98.01051974825486</v>
       </c>
       <c r="D338">
-        <v>2.806837878341</v>
+        <v>3.170381357115531</v>
       </c>
       <c r="E338" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6332,16 +6335,16 @@
         <v>53</v>
       </c>
       <c r="B339">
-        <v>102.6662889604787</v>
+        <v>99.60019526064582</v>
       </c>
       <c r="C339">
-        <v>96.71844186120352</v>
+        <v>93.31617970552955</v>
       </c>
       <c r="D339">
-        <v>5.94784709927518</v>
+        <v>6.28401555511627</v>
       </c>
       <c r="E339" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6349,16 +6352,16 @@
         <v>53</v>
       </c>
       <c r="B340">
-        <v>104.2229692914965</v>
+        <v>102.7866935572146</v>
       </c>
       <c r="C340">
-        <v>104.7158580095015</v>
+        <v>102.9470037236309</v>
       </c>
       <c r="D340">
-        <v>-0.492888718004977</v>
+        <v>-0.1603101664162381</v>
       </c>
       <c r="E340" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6366,16 +6369,16 @@
         <v>53</v>
       </c>
       <c r="B341">
-        <v>104.0887131370484</v>
+        <v>102.3745838274864</v>
       </c>
       <c r="C341">
-        <v>102.7250396886622</v>
+        <v>100.2116806783557</v>
       </c>
       <c r="D341">
-        <v>1.363673448386166</v>
+        <v>2.16290314913077</v>
       </c>
       <c r="E341" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6383,16 +6386,16 @@
         <v>53</v>
       </c>
       <c r="B342">
-        <v>102.6350590055229</v>
+        <v>99.66936175274516</v>
       </c>
       <c r="C342">
-        <v>97.77314161359637</v>
+        <v>94.88150568603582</v>
       </c>
       <c r="D342">
-        <v>4.861917391926525</v>
+        <v>4.787856066709338</v>
       </c>
       <c r="E342" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6400,16 +6403,16 @@
         <v>53</v>
       </c>
       <c r="B343">
-        <v>102.4110371726859</v>
+        <v>99.20460448818741</v>
       </c>
       <c r="C343">
-        <v>96.56153485398005</v>
+        <v>93.40658335906356</v>
       </c>
       <c r="D343">
-        <v>5.849502318705845</v>
+        <v>5.798021129123853</v>
       </c>
       <c r="E343" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6417,16 +6420,16 @@
         <v>53</v>
       </c>
       <c r="B344">
-        <v>104.4827371834657</v>
+        <v>103.1965683580116</v>
       </c>
       <c r="C344">
-        <v>104.8856856612893</v>
+        <v>102.8457126163961</v>
       </c>
       <c r="D344">
-        <v>-0.4029484778235854</v>
+        <v>0.3508557416155327</v>
       </c>
       <c r="E344" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6434,16 +6437,16 @@
         <v>54</v>
       </c>
       <c r="B345">
-        <v>103.4825981905367</v>
+        <v>103.4417008831539</v>
       </c>
       <c r="C345">
-        <v>103.4716031579401</v>
+        <v>100.6348630048129</v>
       </c>
       <c r="D345">
-        <v>0.01099503259661105</v>
+        <v>2.806837878341</v>
       </c>
       <c r="E345" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6451,16 +6454,16 @@
         <v>54</v>
       </c>
       <c r="B346">
-        <v>102.8198231993877</v>
+        <v>102.6662889604787</v>
       </c>
       <c r="C346">
-        <v>102.8088985866758</v>
+        <v>96.71844186120352</v>
       </c>
       <c r="D346">
-        <v>0.01092461271188938</v>
+        <v>5.94784709927518</v>
       </c>
       <c r="E346" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6468,16 +6471,16 @@
         <v>54</v>
       </c>
       <c r="B347">
-        <v>104.1496454190348</v>
+        <v>104.2229692914965</v>
       </c>
       <c r="C347">
-        <v>104.1385795126281</v>
+        <v>104.7158580095015</v>
       </c>
       <c r="D347">
-        <v>0.01106590640671357</v>
+        <v>-0.492888718004977</v>
       </c>
       <c r="E347" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6485,16 +6488,16 @@
         <v>54</v>
       </c>
       <c r="B348">
-        <v>104.0350695871731</v>
+        <v>104.0887131370484</v>
       </c>
       <c r="C348">
-        <v>104.0240158544558</v>
+        <v>102.7250396886622</v>
       </c>
       <c r="D348">
-        <v>0.01105373271735743</v>
+        <v>1.363673448386166</v>
       </c>
       <c r="E348" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6502,16 +6505,16 @@
         <v>54</v>
       </c>
       <c r="B349">
-        <v>102.7931144482502</v>
+        <v>102.6350590055229</v>
       </c>
       <c r="C349">
-        <v>102.7821926733448</v>
+        <v>97.77314161359637</v>
       </c>
       <c r="D349">
-        <v>0.01092177490538404</v>
+        <v>4.861917391926525</v>
       </c>
       <c r="E349" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6519,16 +6522,16 @@
         <v>54</v>
       </c>
       <c r="B350">
-        <v>102.601489741369</v>
+        <v>102.4110371726859</v>
       </c>
       <c r="C350">
-        <v>102.5905883266009</v>
+        <v>96.56153485398005</v>
       </c>
       <c r="D350">
-        <v>0.01090141476812789</v>
+        <v>5.849502318705845</v>
       </c>
       <c r="E350" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6536,16 +6539,16 @@
         <v>54</v>
       </c>
       <c r="B351">
-        <v>104.3712733144297</v>
+        <v>104.4827371834657</v>
       </c>
       <c r="C351">
-        <v>104.360183860045</v>
+        <v>104.8856856612893</v>
       </c>
       <c r="D351">
-        <v>0.01108945438467401</v>
+        <v>-0.4029484778235854</v>
       </c>
       <c r="E351" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6553,16 +6556,16 @@
         <v>55</v>
       </c>
       <c r="B352">
-        <v>101.2224582762651</v>
+        <v>103.4825981905367</v>
       </c>
       <c r="C352">
-        <v>101.1722336785614</v>
+        <v>103.4716031579401</v>
       </c>
       <c r="D352">
-        <v>0.05022459770366083</v>
+        <v>0.01099503259661105</v>
       </c>
       <c r="E352" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6570,16 +6573,16 @@
         <v>55</v>
       </c>
       <c r="B353">
-        <v>96.90933687386934</v>
+        <v>102.8198231993877</v>
       </c>
       <c r="C353">
-        <v>96.86133476431516</v>
+        <v>102.8088985866758</v>
       </c>
       <c r="D353">
-        <v>0.04800210955417583</v>
+        <v>0.01092461271188938</v>
       </c>
       <c r="E353" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6587,16 +6590,16 @@
         <v>55</v>
       </c>
       <c r="B354">
-        <v>105.7358604375961</v>
+        <v>104.1496454190348</v>
       </c>
       <c r="C354">
-        <v>105.6833096445418</v>
+        <v>104.1385795126281</v>
       </c>
       <c r="D354">
-        <v>0.05255079305426591</v>
+        <v>0.01106590640671357</v>
       </c>
       <c r="E354" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6604,16 +6607,16 @@
         <v>55</v>
       </c>
       <c r="B355">
-        <v>103.3462206739145</v>
+        <v>104.0350695871731</v>
       </c>
       <c r="C355">
-        <v>103.2949059473374</v>
+        <v>104.0240158544558</v>
       </c>
       <c r="D355">
-        <v>0.0513147265771039</v>
+        <v>0.01105373271735743</v>
       </c>
       <c r="E355" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6621,16 +6624,16 @@
         <v>55</v>
       </c>
       <c r="B356">
-        <v>98.29972201269233</v>
+        <v>102.7931144482502</v>
       </c>
       <c r="C356">
-        <v>98.25099896929063</v>
+        <v>102.7821926733448</v>
       </c>
       <c r="D356">
-        <v>0.04872304340169364</v>
+        <v>0.01092177490538404</v>
       </c>
       <c r="E356" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6638,16 +6641,16 @@
         <v>55</v>
       </c>
       <c r="B357">
-        <v>97.04211285052223</v>
+        <v>102.601489741369</v>
       </c>
       <c r="C357">
-        <v>96.99403786294221</v>
+        <v>102.5905883266009</v>
       </c>
       <c r="D357">
-        <v>0.04807498758002282</v>
+        <v>0.01090141476812789</v>
       </c>
       <c r="E357" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6655,16 +6658,16 @@
         <v>55</v>
       </c>
       <c r="B358">
-        <v>105.5898406930666</v>
+        <v>104.3712733144297</v>
       </c>
       <c r="C358">
-        <v>105.5373696937649</v>
+        <v>104.360183860045</v>
       </c>
       <c r="D358">
-        <v>0.05247099930170407</v>
+        <v>0.01108945438467401</v>
       </c>
       <c r="E358" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6672,16 +6675,16 @@
         <v>56</v>
       </c>
       <c r="B359">
-        <v>99.527214621135</v>
+        <v>101.2224582762651</v>
       </c>
       <c r="C359">
-        <v>99.48192381970912</v>
+        <v>101.1722336785614</v>
       </c>
       <c r="D359">
-        <v>0.04529080142587816</v>
+        <v>0.05022459770366083</v>
       </c>
       <c r="E359" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6689,16 +6692,16 @@
         <v>56</v>
       </c>
       <c r="B360">
-        <v>95.74553054938541</v>
+        <v>96.90933687386934</v>
       </c>
       <c r="C360">
-        <v>95.70202247348386</v>
+        <v>96.86133476431516</v>
       </c>
       <c r="D360">
-        <v>0.04350807590154204</v>
+        <v>0.04800210955417583</v>
       </c>
       <c r="E360" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6706,16 +6709,16 @@
         <v>56</v>
       </c>
       <c r="B361">
-        <v>103.4639849949931</v>
+        <v>105.7358604375961</v>
       </c>
       <c r="C361">
-        <v>103.4168382342616</v>
+        <v>105.6833096445418</v>
       </c>
       <c r="D361">
-        <v>0.04714676073153612</v>
+        <v>0.05255079305426591</v>
       </c>
       <c r="E361" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6723,16 +6726,16 @@
         <v>56</v>
       </c>
       <c r="B362">
-        <v>101.5452787110711</v>
+        <v>103.3462206739145</v>
       </c>
       <c r="C362">
-        <v>101.4990375156714</v>
+        <v>103.2949059473374</v>
       </c>
       <c r="D362">
-        <v>0.04624119539978722</v>
+        <v>0.0513147265771039</v>
       </c>
       <c r="E362" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6740,16 +6743,16 @@
         <v>56</v>
       </c>
       <c r="B363">
-        <v>96.80479345518198</v>
+        <v>98.29972201269233</v>
       </c>
       <c r="C363">
-        <v>96.76078501261122</v>
+        <v>98.25099896929063</v>
       </c>
       <c r="D363">
-        <v>0.04400844257075676</v>
+        <v>0.04872304340169364</v>
       </c>
       <c r="E363" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6757,16 +6760,16 @@
         <v>56</v>
       </c>
       <c r="B364">
-        <v>95.70463952161548</v>
+        <v>97.04211285052223</v>
       </c>
       <c r="C364">
-        <v>95.66114970595771</v>
+        <v>96.99403786294221</v>
       </c>
       <c r="D364">
-        <v>0.04348981565776455</v>
+        <v>0.04807498758002282</v>
       </c>
       <c r="E364" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6774,16 +6777,16 @@
         <v>56</v>
       </c>
       <c r="B365">
-        <v>103.5081329994673</v>
+        <v>105.5898406930666</v>
       </c>
       <c r="C365">
-        <v>103.460966444945</v>
+        <v>105.5373696937649</v>
       </c>
       <c r="D365">
-        <v>0.04716655452223506</v>
+        <v>0.05247099930170407</v>
       </c>
       <c r="E365" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6791,16 +6794,16 @@
         <v>57</v>
       </c>
       <c r="B366">
-        <v>99.72057357344767</v>
+        <v>99.527214621135</v>
       </c>
       <c r="C366">
-        <v>99.68738322556231</v>
+        <v>99.48192381970912</v>
       </c>
       <c r="D366">
-        <v>0.03319034788535191</v>
+        <v>0.04529080142587816</v>
       </c>
       <c r="E366" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6808,16 +6811,16 @@
         <v>57</v>
       </c>
       <c r="B367">
-        <v>97.45659133719549</v>
+        <v>95.74553054938541</v>
       </c>
       <c r="C367">
-        <v>97.42415451844994</v>
+        <v>95.70202247348386</v>
       </c>
       <c r="D367">
-        <v>0.03243681874555193</v>
+        <v>0.04350807590154204</v>
       </c>
       <c r="E367" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6825,16 +6828,16 @@
         <v>57</v>
       </c>
       <c r="B368">
-        <v>102.037149641433</v>
+        <v>103.4639849949931</v>
       </c>
       <c r="C368">
-        <v>102.0031882594186</v>
+        <v>103.4168382342616</v>
       </c>
       <c r="D368">
-        <v>0.03396138201442511</v>
+        <v>0.04714676073153612</v>
       </c>
       <c r="E368" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6842,16 +6845,16 @@
         <v>57</v>
       </c>
       <c r="B369">
-        <v>101.279811366006</v>
+        <v>101.5452787110711</v>
       </c>
       <c r="C369">
-        <v>101.2461020515432</v>
+        <v>101.4990375156714</v>
       </c>
       <c r="D369">
-        <v>0.03370931446281134</v>
+        <v>0.04624119539978722</v>
       </c>
       <c r="E369" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6859,16 +6862,16 @@
         <v>57</v>
       </c>
       <c r="B370">
-        <v>97.71188135784485</v>
+        <v>96.80479345518198</v>
       </c>
       <c r="C370">
-        <v>97.67935957002736</v>
+        <v>96.76078501261122</v>
       </c>
       <c r="D370">
-        <v>0.03252178781748682</v>
+        <v>0.04400844257075676</v>
       </c>
       <c r="E370" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6876,16 +6879,16 @@
         <v>57</v>
       </c>
       <c r="B371">
-        <v>97.03622845099271</v>
+        <v>95.70463952161548</v>
       </c>
       <c r="C371">
-        <v>97.0039315430994</v>
+        <v>95.66114970595771</v>
       </c>
       <c r="D371">
-        <v>0.0322969078933113</v>
+        <v>0.04348981565776455</v>
       </c>
       <c r="E371" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6893,16 +6896,16 @@
         <v>57</v>
       </c>
       <c r="B372">
-        <v>102.4791766184484</v>
+        <v>103.5081329994673</v>
       </c>
       <c r="C372">
-        <v>102.4450681150466</v>
+        <v>103.460966444945</v>
       </c>
       <c r="D372">
-        <v>0.03410850340188176</v>
+        <v>0.04716655452223506</v>
       </c>
       <c r="E372" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6910,16 +6913,16 @@
         <v>58</v>
       </c>
       <c r="B373">
-        <v>100.543812508687</v>
+        <v>99.72057357344767</v>
       </c>
       <c r="C373">
-        <v>100.5119703364907</v>
+        <v>99.68738322556231</v>
       </c>
       <c r="D373">
-        <v>0.03184217219627783</v>
+        <v>0.03319034788535191</v>
       </c>
       <c r="E373" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6927,16 +6930,16 @@
         <v>58</v>
       </c>
       <c r="B374">
-        <v>98.39009767741442</v>
+        <v>97.45659133719549</v>
       </c>
       <c r="C374">
-        <v>98.35893758556499</v>
+        <v>97.42415451844994</v>
       </c>
       <c r="D374">
-        <v>0.03116009184942925</v>
+        <v>0.03243681874555193</v>
       </c>
       <c r="E374" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6944,16 +6947,16 @@
         <v>58</v>
       </c>
       <c r="B375">
-        <v>102.7446711855695</v>
+        <v>102.037149641433</v>
       </c>
       <c r="C375">
-        <v>102.7121320025953</v>
+        <v>102.0031882594186</v>
       </c>
       <c r="D375">
-        <v>0.03253918297420455</v>
+        <v>0.03396138201442511</v>
       </c>
       <c r="E375" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6961,16 +6964,16 @@
         <v>58</v>
       </c>
       <c r="B376">
-        <v>102.0525599909961</v>
+        <v>101.279811366006</v>
       </c>
       <c r="C376">
-        <v>102.0202399992708</v>
+        <v>101.2461020515432</v>
       </c>
       <c r="D376">
-        <v>0.03231999172528788</v>
+        <v>0.03370931446281134</v>
       </c>
       <c r="E376" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6978,16 +6981,16 @@
         <v>58</v>
       </c>
       <c r="B377">
-        <v>98.60670832398981</v>
+        <v>97.71188135784485</v>
       </c>
       <c r="C377">
-        <v>98.57547963166331</v>
+        <v>97.67935957002736</v>
       </c>
       <c r="D377">
-        <v>0.0312286923264935</v>
+        <v>0.03252178781748682</v>
       </c>
       <c r="E377" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6995,16 +6998,16 @@
         <v>58</v>
       </c>
       <c r="B378">
-        <v>97.96567519535067</v>
+        <v>97.03622845099271</v>
       </c>
       <c r="C378">
-        <v>97.93464951787669</v>
+        <v>97.0039315430994</v>
       </c>
       <c r="D378">
-        <v>0.031025677473977</v>
+        <v>0.0322969078933113</v>
       </c>
       <c r="E378" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7012,16 +7015,16 @@
         <v>58</v>
       </c>
       <c r="B379">
-        <v>103.1897979942853</v>
+        <v>102.4791766184484</v>
       </c>
       <c r="C379">
-        <v>103.1571178398864</v>
+        <v>102.4450681150466</v>
       </c>
       <c r="D379">
-        <v>0.03268015439888927</v>
+        <v>0.03410850340188176</v>
       </c>
       <c r="E379" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -7029,16 +7032,16 @@
         <v>59</v>
       </c>
       <c r="B380">
-        <v>100.8995133753122</v>
+        <v>100.543812508687</v>
       </c>
       <c r="C380">
-        <v>100.8679100864914</v>
+        <v>100.5119703364907</v>
       </c>
       <c r="D380">
-        <v>0.03160328882077579</v>
+        <v>0.03184217219627783</v>
       </c>
       <c r="E380" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -7046,16 +7049,16 @@
         <v>59</v>
       </c>
       <c r="B381">
-        <v>98.76583642143494</v>
+        <v>98.39009767741442</v>
       </c>
       <c r="C381">
-        <v>98.73490143325083</v>
+        <v>98.35893758556499</v>
       </c>
       <c r="D381">
-        <v>0.03093498818411433</v>
+        <v>0.03116009184942925</v>
       </c>
       <c r="E381" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7063,16 +7066,16 @@
         <v>59</v>
       </c>
       <c r="B382">
-        <v>103.0792849860917</v>
+        <v>102.7446711855695</v>
       </c>
       <c r="C382">
-        <v>103.0469989590746</v>
+        <v>102.7121320025953</v>
       </c>
       <c r="D382">
-        <v>0.03228602701712191</v>
+        <v>0.03253918297420455</v>
       </c>
       <c r="E382" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7080,16 +7083,16 @@
         <v>59</v>
       </c>
       <c r="B383">
-        <v>102.3996396786317</v>
+        <v>102.0525599909961</v>
       </c>
       <c r="C383">
-        <v>102.3675665270411</v>
+        <v>102.0202399992708</v>
       </c>
       <c r="D383">
-        <v>0.03207315159059476</v>
+        <v>0.03231999172528788</v>
       </c>
       <c r="E383" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7097,16 +7100,16 @@
         <v>59</v>
       </c>
       <c r="B384">
-        <v>98.97483679759441</v>
+        <v>98.60670832398981</v>
       </c>
       <c r="C384">
-        <v>98.94383634725861</v>
+        <v>98.57547963166331</v>
       </c>
       <c r="D384">
-        <v>0.0310004503357959</v>
+        <v>0.0312286923264935</v>
       </c>
       <c r="E384" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7114,16 +7117,16 @@
         <v>59</v>
       </c>
       <c r="B385">
-        <v>98.34013089148243</v>
+        <v>97.96567519535067</v>
       </c>
       <c r="C385">
-        <v>98.30932924085731</v>
+        <v>97.93464951787669</v>
       </c>
       <c r="D385">
-        <v>0.03080165062512208</v>
+        <v>0.031025677473977</v>
       </c>
       <c r="E385" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7131,16 +7134,16 @@
         <v>59</v>
       </c>
       <c r="B386">
-        <v>103.5255058853759</v>
+        <v>103.1897979942853</v>
       </c>
       <c r="C386">
-        <v>103.4930800950687</v>
+        <v>103.1571178398864</v>
       </c>
       <c r="D386">
-        <v>0.03242579030721515</v>
+        <v>0.03268015439888927</v>
       </c>
       <c r="E386" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7148,16 +7151,16 @@
         <v>60</v>
       </c>
       <c r="B387">
-        <v>101.0887295584996</v>
+        <v>100.8995133753122</v>
       </c>
       <c r="C387">
-        <v>101.058366597128</v>
+        <v>100.8679100864914</v>
       </c>
       <c r="D387">
-        <v>0.0303629613715799</v>
+        <v>0.03160328882077579</v>
       </c>
       <c r="E387" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7165,16 +7168,16 @@
         <v>60</v>
       </c>
       <c r="B388">
-        <v>99.05242581475973</v>
+        <v>98.76583642143494</v>
       </c>
       <c r="C388">
-        <v>99.02267447658477</v>
+        <v>98.73490143325083</v>
       </c>
       <c r="D388">
-        <v>0.02975133817496101</v>
+        <v>0.03093498818411433</v>
       </c>
       <c r="E388" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7182,16 +7185,16 @@
         <v>60</v>
       </c>
       <c r="B389">
-        <v>103.1668953051401</v>
+        <v>103.0792849860917</v>
       </c>
       <c r="C389">
-        <v>103.1359081469212</v>
+        <v>103.0469989590746</v>
       </c>
       <c r="D389">
-        <v>0.03098715821887765</v>
+        <v>0.03228602701712191</v>
       </c>
       <c r="E389" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7199,16 +7202,16 @@
         <v>60</v>
       </c>
       <c r="B390">
-        <v>102.539384557055</v>
+        <v>102.3996396786317</v>
       </c>
       <c r="C390">
-        <v>102.5085858776575</v>
+        <v>102.3675665270411</v>
       </c>
       <c r="D390">
-        <v>0.03079867939752035</v>
+        <v>0.03207315159059476</v>
       </c>
       <c r="E390" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7216,16 +7219,16 @@
         <v>60</v>
       </c>
       <c r="B391">
-        <v>99.23224191188497</v>
+        <v>98.97483679759441</v>
       </c>
       <c r="C391">
-        <v>99.20243656423503</v>
+        <v>98.94383634725861</v>
       </c>
       <c r="D391">
-        <v>0.02980534764994047</v>
+        <v>0.0310004503357959</v>
       </c>
       <c r="E391" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7233,16 +7236,16 @@
         <v>60</v>
       </c>
       <c r="B392">
-        <v>98.62777153068382</v>
+        <v>98.34013089148243</v>
       </c>
       <c r="C392">
-        <v>98.59814774146196</v>
+        <v>98.30932924085731</v>
       </c>
       <c r="D392">
-        <v>0.02962378922185849</v>
+        <v>0.03080165062512208</v>
       </c>
       <c r="E392" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7250,16 +7253,16 @@
         <v>60</v>
       </c>
       <c r="B393">
-        <v>103.6110933579421</v>
+        <v>103.5255058853759</v>
       </c>
       <c r="C393">
-        <v>103.5799727806134</v>
+        <v>103.4930800950687</v>
       </c>
       <c r="D393">
-        <v>0.03112057732877815</v>
+        <v>0.03242579030721515</v>
       </c>
       <c r="E393" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7267,16 +7270,16 @@
         <v>61</v>
       </c>
       <c r="B394">
-        <v>103.3402788879597</v>
+        <v>101.0887295584996</v>
       </c>
       <c r="C394">
-        <v>103.3230114170216</v>
+        <v>101.058366597128</v>
       </c>
       <c r="D394">
-        <v>0.0172674709380658</v>
+        <v>0.0303629613715799</v>
       </c>
       <c r="E394" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7284,16 +7287,16 @@
         <v>61</v>
       </c>
       <c r="B395">
-        <v>102.267124598571</v>
+        <v>99.05242581475973</v>
       </c>
       <c r="C395">
-        <v>102.2500364445528</v>
+        <v>99.02267447658477</v>
       </c>
       <c r="D395">
-        <v>0.01708815401825348</v>
+        <v>0.02975133817496101</v>
       </c>
       <c r="E395" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7301,16 +7304,16 @@
         <v>61</v>
       </c>
       <c r="B396">
-        <v>104.4246944710765</v>
+        <v>103.1668953051401</v>
       </c>
       <c r="C396">
-        <v>104.4072458015316</v>
+        <v>103.1359081469212</v>
       </c>
       <c r="D396">
-        <v>0.01744866954490476</v>
+        <v>0.03098715821887765</v>
       </c>
       <c r="E396" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7318,16 +7321,16 @@
         <v>61</v>
       </c>
       <c r="B397">
-        <v>104.2056411158236</v>
+        <v>102.539384557055</v>
       </c>
       <c r="C397">
-        <v>104.1882290486325</v>
+        <v>102.5085858776575</v>
       </c>
       <c r="D397">
-        <v>0.01741206719115951</v>
+        <v>0.03079867939752035</v>
       </c>
       <c r="E397" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7335,16 +7338,16 @@
         <v>61</v>
       </c>
       <c r="B398">
-        <v>102.2560912686474</v>
+        <v>99.23224191188497</v>
       </c>
       <c r="C398">
-        <v>102.239004958225</v>
+        <v>99.20243656423503</v>
       </c>
       <c r="D398">
-        <v>0.01708631042245656</v>
+        <v>0.02980534764994047</v>
       </c>
       <c r="E398" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7352,16 +7355,16 @@
         <v>61</v>
       </c>
       <c r="B399">
-        <v>101.9441348839087</v>
+        <v>98.62777153068382</v>
       </c>
       <c r="C399">
-        <v>101.9271006993162</v>
+        <v>98.59814774146196</v>
       </c>
       <c r="D399">
-        <v>0.01703418459248951</v>
+        <v>0.02962378922185849</v>
       </c>
       <c r="E399" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7369,16 +7372,135 @@
         <v>61</v>
       </c>
       <c r="B400">
+        <v>103.6110933579421</v>
+      </c>
+      <c r="C400">
+        <v>103.5799727806134</v>
+      </c>
+      <c r="D400">
+        <v>0.03112057732877815</v>
+      </c>
+      <c r="E400" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" t="s">
+        <v>62</v>
+      </c>
+      <c r="B401">
+        <v>103.3402788879597</v>
+      </c>
+      <c r="C401">
+        <v>103.3230114170216</v>
+      </c>
+      <c r="D401">
+        <v>0.0172674709380658</v>
+      </c>
+      <c r="E401" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" t="s">
+        <v>62</v>
+      </c>
+      <c r="B402">
+        <v>102.267124598571</v>
+      </c>
+      <c r="C402">
+        <v>102.2500364445528</v>
+      </c>
+      <c r="D402">
+        <v>0.01708815401825348</v>
+      </c>
+      <c r="E402" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" t="s">
+        <v>62</v>
+      </c>
+      <c r="B403">
+        <v>104.4246944710765</v>
+      </c>
+      <c r="C403">
+        <v>104.4072458015316</v>
+      </c>
+      <c r="D403">
+        <v>0.01744866954490476</v>
+      </c>
+      <c r="E403" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" t="s">
+        <v>62</v>
+      </c>
+      <c r="B404">
+        <v>104.2056411158236</v>
+      </c>
+      <c r="C404">
+        <v>104.1882290486325</v>
+      </c>
+      <c r="D404">
+        <v>0.01741206719115951</v>
+      </c>
+      <c r="E404" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" t="s">
+        <v>62</v>
+      </c>
+      <c r="B405">
+        <v>102.2560912686474</v>
+      </c>
+      <c r="C405">
+        <v>102.239004958225</v>
+      </c>
+      <c r="D405">
+        <v>0.01708631042245656</v>
+      </c>
+      <c r="E405" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" t="s">
+        <v>62</v>
+      </c>
+      <c r="B406">
+        <v>101.9441348839087</v>
+      </c>
+      <c r="C406">
+        <v>101.9271006993162</v>
+      </c>
+      <c r="D406">
+        <v>0.01703418459248951</v>
+      </c>
+      <c r="E406" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" t="s">
+        <v>62</v>
+      </c>
+      <c r="B407">
         <v>104.7555433454067</v>
       </c>
-      <c r="C400">
+      <c r="C407">
         <v>104.7380393932229</v>
       </c>
-      <c r="D400">
+      <c r="D407">
         <v>0.01750395218387268</v>
       </c>
-      <c r="E400" t="s">
-        <v>68</v>
+      <c r="E407" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/bond_results_tier2_oas.xlsx
+++ b/outputs/bond_results_tier2_oas.xlsx
@@ -606,13 +606,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.39118065167645</v>
+        <v>78.71632465393753</v>
       </c>
       <c r="C2">
-        <v>99.4175104210877</v>
+        <v>78.61800974190142</v>
       </c>
       <c r="D2">
-        <v>-0.02632976941124809</v>
+        <v>0.0983149120361162</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
@@ -623,13 +623,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>91.71152036401712</v>
+        <v>62.55112430626606</v>
       </c>
       <c r="C3">
-        <v>91.64550210775943</v>
+        <v>62.47574730567867</v>
       </c>
       <c r="D3">
-        <v>0.06601825625769209</v>
+        <v>0.0753770005873875</v>
       </c>
       <c r="E3" t="s">
         <v>64</v>
@@ -640,13 +640,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>107.6790532548355</v>
+        <v>99.88602801317066</v>
       </c>
       <c r="C4">
-        <v>109.6498382311094</v>
+        <v>99.9094013158531</v>
       </c>
       <c r="D4">
-        <v>-1.970784976273961</v>
+        <v>-0.02337330268244386</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -657,13 +657,13 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>97.35349500005347</v>
+        <v>72.81859329746192</v>
       </c>
       <c r="C5">
-        <v>97.2916801669969</v>
+        <v>72.72898903587709</v>
       </c>
       <c r="D5">
-        <v>0.06181483305657309</v>
+        <v>0.08960426158482448</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -674,13 +674,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>99.46769251326324</v>
+        <v>81.32835344913367</v>
       </c>
       <c r="C6">
-        <v>100.6122239440398</v>
+        <v>81.22620470161775</v>
       </c>
       <c r="D6">
-        <v>-1.144531430776567</v>
+        <v>0.1021487475159262</v>
       </c>
       <c r="E6" t="s">
         <v>67</v>
@@ -691,13 +691,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>96.7405577127613</v>
+        <v>74.46635902185859</v>
       </c>
       <c r="C7">
-        <v>97.25698393741723</v>
+        <v>74.3737790519146</v>
       </c>
       <c r="D7">
-        <v>-0.5164262246559304</v>
+        <v>0.09257996994399775</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
@@ -708,13 +708,13 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>101.866985126583</v>
+        <v>83.22752315091005</v>
       </c>
       <c r="C8">
-        <v>101.9373424554063</v>
+        <v>83.12311314704344</v>
       </c>
       <c r="D8">
-        <v>-0.07035732882329171</v>
+        <v>0.1044100038666045</v>
       </c>
       <c r="E8" t="s">
         <v>69</v>
@@ -725,13 +725,13 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>104.4102654916629</v>
+        <v>86.92124127858565</v>
       </c>
       <c r="C9">
-        <v>104.2975535277135</v>
+        <v>86.82326312635855</v>
       </c>
       <c r="D9">
-        <v>0.1127119639494083</v>
+        <v>0.09797815222709971</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
@@ -742,13 +742,13 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>104.0139088705514</v>
+        <v>75.01159072882399</v>
       </c>
       <c r="C10">
-        <v>103.9079239567337</v>
+        <v>74.92789141620285</v>
       </c>
       <c r="D10">
-        <v>0.1059849138177356</v>
+        <v>0.08369931262113539</v>
       </c>
       <c r="E10" t="s">
         <v>64</v>
@@ -759,13 +759,13 @@
         <v>6</v>
       </c>
       <c r="B11">
-        <v>105.6395785308202</v>
+        <v>100.8895759068823</v>
       </c>
       <c r="C11">
-        <v>105.5189273180302</v>
+        <v>100.7748317904294</v>
       </c>
       <c r="D11">
-        <v>0.1206512127900652</v>
+        <v>0.1147441164529397</v>
       </c>
       <c r="E11" t="s">
         <v>65</v>
@@ -776,13 +776,13 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>102.7694033553193</v>
+        <v>85.96046271672296</v>
       </c>
       <c r="C12">
-        <v>102.656134878459</v>
+        <v>85.86372331766567</v>
       </c>
       <c r="D12">
-        <v>0.1132684768602843</v>
+        <v>0.09673939905728446</v>
       </c>
       <c r="E12" t="s">
         <v>66</v>
@@ -793,13 +793,13 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>106.1835106747425</v>
+        <v>85.32664861938335</v>
       </c>
       <c r="C13">
-        <v>106.0725325691629</v>
+        <v>85.23049714258354</v>
       </c>
       <c r="D13">
-        <v>0.110978105579548</v>
+        <v>0.09615147679980396</v>
       </c>
       <c r="E13" t="s">
         <v>67</v>
@@ -810,13 +810,13 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>105.9358623015307</v>
+        <v>80.98994465457615</v>
       </c>
       <c r="C14">
-        <v>105.8271920706346</v>
+        <v>80.89900034277123</v>
       </c>
       <c r="D14">
-        <v>0.108670230896152</v>
+        <v>0.09094431180491824</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
@@ -827,13 +827,13 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>103.2692266182532</v>
+        <v>93.31047777482208</v>
       </c>
       <c r="C15">
-        <v>103.1519237721811</v>
+        <v>93.20491656666901</v>
       </c>
       <c r="D15">
-        <v>0.1173028460721497</v>
+        <v>0.1055612081530626</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -844,13 +844,13 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>96.07728454684298</v>
+        <v>96.0873820711391</v>
       </c>
       <c r="C16">
-        <v>96.02938091308665</v>
+        <v>96.0395235455366</v>
       </c>
       <c r="D16">
-        <v>0.04790363375632012</v>
+        <v>0.04785852560250703</v>
       </c>
       <c r="E16" t="s">
         <v>63</v>
@@ -861,13 +861,13 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>72.14998402688487</v>
+        <v>72.15720106325075</v>
       </c>
       <c r="C17">
-        <v>72.06261338053741</v>
+        <v>72.06982043446787</v>
       </c>
       <c r="D17">
-        <v>0.08737064634745195</v>
+        <v>0.08738062878288133</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>123.1821785985844</v>
+        <v>123.1947224060987</v>
       </c>
       <c r="C18">
-        <v>131.5539553868444</v>
+        <v>131.5684974482242</v>
       </c>
       <c r="D18">
-        <v>-8.371776788260007</v>
+        <v>-8.373775042125473</v>
       </c>
       <c r="E18" t="s">
         <v>65</v>
@@ -895,13 +895,13 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>84.37449067229173</v>
+        <v>84.38312280669099</v>
       </c>
       <c r="C19">
-        <v>84.27009809399169</v>
+        <v>84.27871832441537</v>
       </c>
       <c r="D19">
-        <v>0.1043925783000361</v>
+        <v>0.1044044822756263</v>
       </c>
       <c r="E19" t="s">
         <v>66</v>
@@ -912,13 +912,13 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>101.0636977829673</v>
+        <v>101.0739672670428</v>
       </c>
       <c r="C20">
-        <v>103.7382165570747</v>
+        <v>103.7493911069637</v>
       </c>
       <c r="D20">
-        <v>-2.674518774107383</v>
+        <v>-2.675423839920924</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
@@ -929,13 +929,13 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>91.34365758573638</v>
+        <v>91.35313935204866</v>
       </c>
       <c r="C21">
-        <v>91.62430424202047</v>
+        <v>91.63397321133549</v>
       </c>
       <c r="D21">
-        <v>-0.280646656284091</v>
+        <v>-0.2808338592868296</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
@@ -946,13 +946,13 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>100.7264989854941</v>
+        <v>100.7371193000324</v>
       </c>
       <c r="C22">
-        <v>100.6746144959441</v>
+        <v>100.6852561861928</v>
       </c>
       <c r="D22">
-        <v>0.05188448954997682</v>
+        <v>0.05186311383967279</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
@@ -963,13 +963,13 @@
         <v>8</v>
       </c>
       <c r="B23">
-        <v>96.22745766814171</v>
+        <v>96.23755522659482</v>
       </c>
       <c r="C23">
-        <v>96.18002297841115</v>
+        <v>96.19016607626369</v>
       </c>
       <c r="D23">
-        <v>0.04743468973056508</v>
+        <v>0.04738915033112789</v>
       </c>
       <c r="E23" t="s">
         <v>63</v>
@@ -980,13 +980,13 @@
         <v>8</v>
       </c>
       <c r="B24">
-        <v>72.31562050137848</v>
+        <v>72.32284012738599</v>
       </c>
       <c r="C24">
-        <v>72.22821850694849</v>
+        <v>72.23542814589148</v>
       </c>
       <c r="D24">
-        <v>0.08740199442998176</v>
+        <v>0.08741198149451179</v>
       </c>
       <c r="E24" t="s">
         <v>64</v>
@@ -997,13 +997,13 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>123.2690407914781</v>
+        <v>123.2815701511858</v>
       </c>
       <c r="C25">
-        <v>131.6630243615105</v>
+        <v>131.6775611695413</v>
       </c>
       <c r="D25">
-        <v>-8.393983570032375</v>
+        <v>-8.395991018355446</v>
       </c>
       <c r="E25" t="s">
         <v>65</v>
@@ -1014,13 +1014,13 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>84.53943683780454</v>
+        <v>84.54807156169649</v>
       </c>
       <c r="C26">
-        <v>84.43501342948099</v>
+        <v>84.44363624581592</v>
       </c>
       <c r="D26">
-        <v>0.1044234083235551</v>
+        <v>0.1044353158805649</v>
       </c>
       <c r="E26" t="s">
         <v>66</v>
@@ -1031,13 +1031,13 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>101.1879053782059</v>
+        <v>101.1981675639944</v>
       </c>
       <c r="C27">
-        <v>103.8728901129752</v>
+        <v>103.8840628139921</v>
       </c>
       <c r="D27">
-        <v>-2.684984734769301</v>
+        <v>-2.685895249997685</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
@@ -1048,13 +1048,13 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>91.49032300834574</v>
+        <v>91.49980348368406</v>
       </c>
       <c r="C28">
-        <v>91.7734681124123</v>
+        <v>91.78313723321827</v>
       </c>
       <c r="D28">
-        <v>-0.2831451040665627</v>
+        <v>-0.2833337495342079</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
@@ -1065,13 +1065,13 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>100.8786178822768</v>
+        <v>100.8892387842838</v>
       </c>
       <c r="C29">
-        <v>100.8268728694112</v>
+        <v>100.8375153602018</v>
       </c>
       <c r="D29">
-        <v>0.05174501286559519</v>
+        <v>0.05172342408204145</v>
       </c>
       <c r="E29" t="s">
         <v>69</v>
@@ -1082,13 +1082,13 @@
         <v>9</v>
       </c>
       <c r="B30">
-        <v>96.30796145237021</v>
+        <v>96.31805870373194</v>
       </c>
       <c r="C30">
-        <v>96.26053788014993</v>
+        <v>96.27068090419684</v>
       </c>
       <c r="D30">
-        <v>0.04742357222028204</v>
+        <v>0.04737779953509857</v>
       </c>
       <c r="E30" t="s">
         <v>63</v>
@@ -1099,13 +1099,13 @@
         <v>9</v>
       </c>
       <c r="B31">
-        <v>72.40074071683797</v>
+        <v>72.40796092102532</v>
       </c>
       <c r="C31">
-        <v>72.31333164477174</v>
+        <v>72.32054186128596</v>
       </c>
       <c r="D31">
-        <v>0.0874090720662366</v>
+        <v>0.0874190597393607</v>
       </c>
       <c r="E31" t="s">
         <v>64</v>
@@ -1116,13 +1116,13 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>123.318638888538</v>
+        <v>123.3311600615986</v>
       </c>
       <c r="C32">
-        <v>131.7315127552218</v>
+        <v>131.7460478365371</v>
       </c>
       <c r="D32">
-        <v>-8.412873866683796</v>
+        <v>-8.414887774938521</v>
       </c>
       <c r="E32" t="s">
         <v>65</v>
@@ -1133,13 +1133,13 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>84.62384443387523</v>
+        <v>84.63247963118317</v>
       </c>
       <c r="C33">
-        <v>84.51941412064576</v>
+        <v>84.52803741034249</v>
       </c>
       <c r="D33">
-        <v>0.1044303132294715</v>
+        <v>0.1044422208406814</v>
       </c>
       <c r="E33" t="s">
         <v>66</v>
@@ -1150,13 +1150,13 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>101.2580754335972</v>
+        <v>101.2683335930186</v>
       </c>
       <c r="C34">
-        <v>103.9491818941398</v>
+        <v>103.960353938079</v>
       </c>
       <c r="D34">
-        <v>-2.691106460542571</v>
+        <v>-2.692020345060413</v>
       </c>
       <c r="E34" t="s">
         <v>67</v>
@@ -1167,13 +1167,13 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>91.57004233190094</v>
+        <v>91.57952192813079</v>
       </c>
       <c r="C35">
-        <v>91.85392925115049</v>
+        <v>91.86359828908215</v>
       </c>
       <c r="D35">
-        <v>-0.2838869192495537</v>
+        <v>-0.2840763609513601</v>
       </c>
       <c r="E35" t="s">
         <v>68</v>
@@ -1184,13 +1184,13 @@
         <v>9</v>
       </c>
       <c r="B36">
-        <v>100.9591920924578</v>
+        <v>100.9698128120773</v>
       </c>
       <c r="C36">
-        <v>100.9073952734782</v>
+        <v>100.9180376975664</v>
       </c>
       <c r="D36">
-        <v>0.05179681897965338</v>
+        <v>0.05177511451091732</v>
       </c>
       <c r="E36" t="s">
         <v>69</v>
@@ -1201,13 +1201,13 @@
         <v>10</v>
       </c>
       <c r="B37">
-        <v>99.55225107759921</v>
+        <v>88.37446227582153</v>
       </c>
       <c r="C37">
-        <v>99.45503188770415</v>
+        <v>88.28607311972657</v>
       </c>
       <c r="D37">
-        <v>0.09721918989505696</v>
+        <v>0.08838915609496212</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
@@ -1218,13 +1218,13 @@
         <v>10</v>
       </c>
       <c r="B38">
-        <v>98.28325736621581</v>
+        <v>79.01753819654715</v>
       </c>
       <c r="C38">
-        <v>98.19070471200973</v>
+        <v>78.93884863338364</v>
       </c>
       <c r="D38">
-        <v>0.09255265420607373</v>
+        <v>0.07868956316350761</v>
       </c>
       <c r="E38" t="s">
         <v>64</v>
@@ -1235,13 +1235,13 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>101.3855180917988</v>
+        <v>98.89597929644924</v>
       </c>
       <c r="C39">
-        <v>101.2828965611392</v>
+        <v>98.79667304354521</v>
       </c>
       <c r="D39">
-        <v>0.1026215306596328</v>
+        <v>0.09930625290402872</v>
       </c>
       <c r="E39" t="s">
         <v>65</v>
@@ -1252,13 +1252,13 @@
         <v>10</v>
       </c>
       <c r="B40">
-        <v>98.3810376306275</v>
+        <v>89.15278566485262</v>
       </c>
       <c r="C40">
-        <v>98.28360319441096</v>
+        <v>89.06364916649731</v>
       </c>
       <c r="D40">
-        <v>0.09743443621654535</v>
+        <v>0.0891364983553018</v>
       </c>
       <c r="E40" t="s">
         <v>66</v>
@@ -1269,13 +1269,13 @@
         <v>10</v>
       </c>
       <c r="B41">
-        <v>100.5299300036076</v>
+        <v>85.6407876441604</v>
       </c>
       <c r="C41">
-        <v>100.4338182215674</v>
+        <v>85.55517390949241</v>
       </c>
       <c r="D41">
-        <v>0.09611178204018245</v>
+        <v>0.08561373466798727</v>
       </c>
       <c r="E41" t="s">
         <v>67</v>
@@ -1286,13 +1286,13 @@
         <v>10</v>
       </c>
       <c r="B42">
-        <v>100.0012479374046</v>
+        <v>82.42394512894987</v>
       </c>
       <c r="C42">
-        <v>99.90674897737416</v>
+        <v>82.34167050512636</v>
       </c>
       <c r="D42">
-        <v>0.09449896003040692</v>
+        <v>0.08227462382350836</v>
       </c>
       <c r="E42" t="s">
         <v>68</v>
@@ -1303,13 +1303,13 @@
         <v>10</v>
       </c>
       <c r="B43">
-        <v>99.27223824851229</v>
+        <v>94.76646612471112</v>
       </c>
       <c r="C43">
-        <v>99.172010019773</v>
+        <v>94.67150347292613</v>
       </c>
       <c r="D43">
-        <v>0.1002282287392973</v>
+        <v>0.0949626517849822</v>
       </c>
       <c r="E43" t="s">
         <v>69</v>
@@ -1320,13 +1320,13 @@
         <v>11</v>
       </c>
       <c r="B44">
-        <v>101.7249160236879</v>
+        <v>87.61504534942506</v>
       </c>
       <c r="C44">
-        <v>101.6191121329918</v>
+        <v>87.52139258207693</v>
       </c>
       <c r="D44">
-        <v>0.1058038906960803</v>
+        <v>0.09365276734813222</v>
       </c>
       <c r="E44" t="s">
         <v>63</v>
@@ -1337,13 +1337,13 @@
         <v>11</v>
       </c>
       <c r="B45">
-        <v>100.8195818586646</v>
+        <v>77.03818280215367</v>
       </c>
       <c r="C45">
-        <v>100.7187746127366</v>
+        <v>76.95635380539592</v>
       </c>
       <c r="D45">
-        <v>0.1008072459280385</v>
+        <v>0.08182899675774991</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
@@ -1354,13 +1354,13 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>103.1547967289418</v>
+        <v>99.74069203692518</v>
       </c>
       <c r="C46">
-        <v>103.0432094733371</v>
+        <v>99.63346682974144</v>
       </c>
       <c r="D46">
-        <v>0.1115872556047321</v>
+        <v>0.1072252071837454</v>
       </c>
       <c r="E46" t="s">
         <v>65</v>
@@ -1371,13 +1371,13 @@
         <v>11</v>
       </c>
       <c r="B47">
-        <v>101.0222889814896</v>
+        <v>87.69574114649237</v>
       </c>
       <c r="C47">
-        <v>100.915696665837</v>
+        <v>87.60208901737445</v>
       </c>
       <c r="D47">
-        <v>0.1065923156526338</v>
+        <v>0.09365212911791332</v>
       </c>
       <c r="E47" t="s">
         <v>66</v>
@@ -1388,13 +1388,13 @@
         <v>11</v>
       </c>
       <c r="B48">
-        <v>102.4030674014402</v>
+        <v>85.2911519355945</v>
       </c>
       <c r="C48">
-        <v>102.2989080955252</v>
+        <v>85.20000823323899</v>
       </c>
       <c r="D48">
-        <v>0.1041593059150046</v>
+        <v>0.0911437023555095</v>
       </c>
       <c r="E48" t="s">
         <v>67</v>
@@ -1405,13 +1405,13 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <v>102.0536096239265</v>
+        <v>81.56129064794052</v>
       </c>
       <c r="C49">
-        <v>101.9511166997827</v>
+        <v>81.47432385688894</v>
       </c>
       <c r="D49">
-        <v>0.1024929241437889</v>
+        <v>0.08696679105158012</v>
       </c>
       <c r="E49" t="s">
         <v>68</v>
@@ -1422,13 +1422,13 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>101.6492849672439</v>
+        <v>94.13305533124489</v>
       </c>
       <c r="C50">
-        <v>101.5397508216573</v>
+        <v>94.03219659762779</v>
       </c>
       <c r="D50">
-        <v>0.1095341455866077</v>
+        <v>0.1008587336171018</v>
       </c>
       <c r="E50" t="s">
         <v>69</v>
@@ -1439,13 +1439,13 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>98.84770517359279</v>
+        <v>98.85693377104015</v>
       </c>
       <c r="C51">
-        <v>98.8922126558614</v>
+        <v>98.90208347664061</v>
       </c>
       <c r="D51">
-        <v>-0.04450748226861378</v>
+        <v>-0.0451497056004655</v>
       </c>
       <c r="E51" t="s">
         <v>63</v>
@@ -1456,13 +1456,13 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>82.43401067209508</v>
+        <v>82.44210559726139</v>
       </c>
       <c r="C52">
-        <v>82.33599331174439</v>
+        <v>82.34407796277968</v>
       </c>
       <c r="D52">
-        <v>0.09801736035069553</v>
+        <v>0.09802763448170992</v>
       </c>
       <c r="E52" t="s">
         <v>64</v>
@@ -1473,13 +1473,13 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>105.1098463445913</v>
+        <v>105.1128245192902</v>
       </c>
       <c r="C53">
-        <v>119.2858125851054</v>
+        <v>119.2978931893979</v>
       </c>
       <c r="D53">
-        <v>-14.17596624051416</v>
+        <v>-14.18506867010773</v>
       </c>
       <c r="E53" t="s">
         <v>65</v>
@@ -1490,13 +1490,13 @@
         <v>12</v>
       </c>
       <c r="B54">
-        <v>95.43068968099956</v>
+        <v>95.44010060775334</v>
       </c>
       <c r="C54">
-        <v>95.32671592848472</v>
+        <v>95.33616857135027</v>
       </c>
       <c r="D54">
-        <v>0.1039737525148468</v>
+        <v>0.1039320364030658</v>
       </c>
       <c r="E54" t="s">
         <v>66</v>
@@ -1507,13 +1507,13 @@
         <v>12</v>
       </c>
       <c r="B55">
-        <v>98.18780037899438</v>
+        <v>98.19477500788254</v>
       </c>
       <c r="C55">
-        <v>98.93130730334087</v>
+        <v>98.94121528148678</v>
       </c>
       <c r="D55">
-        <v>-0.7435069243464909</v>
+        <v>-0.7464402736042359</v>
       </c>
       <c r="E55" t="s">
         <v>67</v>
@@ -1524,13 +1524,13 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>92.57844728681931</v>
+        <v>92.5874634322206</v>
       </c>
       <c r="C56">
-        <v>92.49633756560749</v>
+        <v>92.50554732150455</v>
       </c>
       <c r="D56">
-        <v>0.08210972121182181</v>
+        <v>0.08191611071605109</v>
       </c>
       <c r="E56" t="s">
         <v>68</v>
@@ -1541,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>104.1692127275694</v>
+        <v>104.1750033034132</v>
       </c>
       <c r="C57">
-        <v>105.7434428628753</v>
+        <v>105.7540226638049</v>
       </c>
       <c r="D57">
-        <v>-1.574230135305967</v>
+        <v>-1.579019360391698</v>
       </c>
       <c r="E57" t="s">
         <v>69</v>
@@ -1558,13 +1558,13 @@
         <v>13</v>
       </c>
       <c r="B58">
-        <v>99.57897761498015</v>
+        <v>99.58824786548189</v>
       </c>
       <c r="C58">
-        <v>99.61781340288334</v>
+        <v>99.62765858831003</v>
       </c>
       <c r="D58">
-        <v>-0.03883578790319575</v>
+        <v>-0.03941072282813707</v>
       </c>
       <c r="E58" t="s">
         <v>63</v>
@@ -1575,13 +1575,13 @@
         <v>13</v>
       </c>
       <c r="B59">
-        <v>83.3613303912599</v>
+        <v>83.3694309271886</v>
       </c>
       <c r="C59">
-        <v>83.26324473824684</v>
+        <v>83.27133504588286</v>
       </c>
       <c r="D59">
-        <v>0.09808565301305805</v>
+        <v>0.09809588130573843</v>
       </c>
       <c r="E59" t="s">
         <v>64</v>
@@ -1592,13 +1592,13 @@
         <v>13</v>
       </c>
       <c r="B60">
-        <v>105.2427825792741</v>
+        <v>105.2454230198436</v>
       </c>
       <c r="C60">
-        <v>119.6902148336369</v>
+        <v>119.7022230878312</v>
       </c>
       <c r="D60">
-        <v>-14.44743225436278</v>
+        <v>-14.45680006798756</v>
       </c>
       <c r="E60" t="s">
         <v>65</v>
@@ -1609,13 +1609,13 @@
         <v>13</v>
       </c>
       <c r="B61">
-        <v>96.33594645675997</v>
+        <v>96.34536974466447</v>
       </c>
       <c r="C61">
-        <v>96.23145185006493</v>
+        <v>96.24090065435361</v>
       </c>
       <c r="D61">
-        <v>0.1044946066950416</v>
+        <v>0.1044690903108574</v>
       </c>
       <c r="E61" t="s">
         <v>66</v>
@@ -1626,13 +1626,13 @@
         <v>13</v>
       </c>
       <c r="B62">
-        <v>98.86710790709704</v>
+        <v>98.8739916535918</v>
       </c>
       <c r="C62">
-        <v>99.51618868204066</v>
+        <v>99.52605539793429</v>
       </c>
       <c r="D62">
-        <v>-0.6490807749436271</v>
+        <v>-0.6520637443424846</v>
       </c>
       <c r="E62" t="s">
         <v>67</v>
@@ -1643,13 +1643,13 @@
         <v>13</v>
       </c>
       <c r="B63">
-        <v>93.27803342218539</v>
+        <v>93.28706407228421</v>
       </c>
       <c r="C63">
-        <v>93.18727311147114</v>
+        <v>93.19645687702705</v>
       </c>
       <c r="D63">
-        <v>0.09076031071424495</v>
+        <v>0.09060719525716365</v>
       </c>
       <c r="E63" t="s">
         <v>68</v>
@@ -1660,13 +1660,13 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>104.6150179360975</v>
+        <v>104.6205569960759</v>
       </c>
       <c r="C64">
-        <v>106.5076012280771</v>
+        <v>106.5181559736313</v>
       </c>
       <c r="D64">
-        <v>-1.892583291979562</v>
+        <v>-1.897598977555376</v>
       </c>
       <c r="E64" t="s">
         <v>69</v>
@@ -1677,13 +1677,13 @@
         <v>14</v>
       </c>
       <c r="B65">
-        <v>99.62385383477128</v>
+        <v>99.63313074564924</v>
       </c>
       <c r="C65">
-        <v>99.6609749003029</v>
+        <v>99.67081786330752</v>
       </c>
       <c r="D65">
-        <v>-0.03712106553162187</v>
+        <v>-0.03768711765827959</v>
       </c>
       <c r="E65" t="s">
         <v>63</v>
@@ -1694,13 +1694,13 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>83.41687970535173</v>
+        <v>83.42497986085765</v>
       </c>
       <c r="C66">
-        <v>83.31879863968439</v>
+        <v>83.32688857018495</v>
       </c>
       <c r="D66">
-        <v>0.09808106566734409</v>
+        <v>0.09809129067269851</v>
       </c>
       <c r="E66" t="s">
         <v>64</v>
@@ -1711,13 +1711,13 @@
         <v>14</v>
       </c>
       <c r="B67">
-        <v>105.2235468659093</v>
+        <v>105.2261459876978</v>
       </c>
       <c r="C67">
-        <v>119.7141584884807</v>
+        <v>119.7261618004958</v>
       </c>
       <c r="D67">
-        <v>-14.49061162257139</v>
+        <v>-14.50001581279803</v>
       </c>
       <c r="E67" t="s">
         <v>65</v>
@@ -1728,13 +1728,13 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>96.38935702666858</v>
+        <v>96.39878114013763</v>
       </c>
       <c r="C68">
-        <v>96.28459589770934</v>
+        <v>96.29404369846223</v>
       </c>
       <c r="D68">
-        <v>0.1047611289592396</v>
+        <v>0.1047374416753968</v>
       </c>
       <c r="E68" t="s">
         <v>66</v>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="B69">
-        <v>98.91399788419535</v>
+        <v>98.92087215249826</v>
       </c>
       <c r="C69">
-        <v>99.55174750945126</v>
+        <v>99.56161114980507</v>
       </c>
       <c r="D69">
-        <v>-0.6377496252559069</v>
+        <v>-0.6407389973068121</v>
       </c>
       <c r="E69" t="s">
         <v>67</v>
@@ -1762,13 +1762,13 @@
         <v>14</v>
       </c>
       <c r="B70">
-        <v>93.3209279131063</v>
+        <v>93.32996133861703</v>
       </c>
       <c r="C70">
-        <v>93.22912671690634</v>
+        <v>93.23830829230479</v>
       </c>
       <c r="D70">
-        <v>0.09180119619996674</v>
+        <v>0.09165304631223137</v>
       </c>
       <c r="E70" t="s">
         <v>68</v>
@@ -1779,13 +1779,13 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>104.6276718480467</v>
+        <v>104.6331796025454</v>
       </c>
       <c r="C71">
-        <v>106.552247441821</v>
+        <v>106.5627999419577</v>
       </c>
       <c r="D71">
-        <v>-1.924575593774321</v>
+        <v>-1.929620339412224</v>
       </c>
       <c r="E71" t="s">
         <v>69</v>
@@ -1796,13 +1796,13 @@
         <v>15</v>
       </c>
       <c r="B72">
-        <v>96.01772077750338</v>
+        <v>72.50690857839989</v>
       </c>
       <c r="C72">
-        <v>95.92796072599644</v>
+        <v>72.41361652806917</v>
       </c>
       <c r="D72">
-        <v>0.08976005150694277</v>
+        <v>0.0932920503307173</v>
       </c>
       <c r="E72" t="s">
         <v>63</v>
@@ -1813,13 +1813,13 @@
         <v>15</v>
       </c>
       <c r="B73">
-        <v>94.73751953279063</v>
+        <v>58.03336271275611</v>
       </c>
       <c r="C73">
-        <v>94.63991586196512</v>
+        <v>57.96018511178455</v>
       </c>
       <c r="D73">
-        <v>0.09760367082550658</v>
+        <v>0.07317760097156167</v>
       </c>
       <c r="E73" t="s">
         <v>64</v>
@@ -1830,13 +1830,13 @@
         <v>15</v>
       </c>
       <c r="B74">
-        <v>98.17707257970754</v>
+        <v>91.04101077344455</v>
       </c>
       <c r="C74">
-        <v>98.86558860137328</v>
+        <v>90.92876116645532</v>
       </c>
       <c r="D74">
-        <v>-0.688516021665734</v>
+        <v>0.1122496069892378</v>
       </c>
       <c r="E74" t="s">
         <v>65</v>
@@ -1847,13 +1847,13 @@
         <v>15</v>
       </c>
       <c r="B75">
-        <v>91.92046861581468</v>
+        <v>67.94005089009451</v>
       </c>
       <c r="C75">
-        <v>91.83023484362694</v>
+        <v>67.85325367027372</v>
       </c>
       <c r="D75">
-        <v>0.09023377218774442</v>
+        <v>0.08679721982079514</v>
       </c>
       <c r="E75" t="s">
         <v>66</v>
@@ -1864,13 +1864,13 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>100.0479421354363</v>
+        <v>74.03763430324058</v>
       </c>
       <c r="C76">
-        <v>100.2101138709991</v>
+        <v>73.94206790641491</v>
       </c>
       <c r="D76">
-        <v>-0.1621717355627226</v>
+        <v>0.09556639682567436</v>
       </c>
       <c r="E76" t="s">
         <v>67</v>
@@ -1881,13 +1881,13 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>99.21149427980595</v>
+        <v>68.12929791451522</v>
       </c>
       <c r="C77">
-        <v>99.22003042665956</v>
+        <v>68.04196017714062</v>
       </c>
       <c r="D77">
-        <v>-0.008536146853614923</v>
+        <v>0.08733773737459671</v>
       </c>
       <c r="E77" t="s">
         <v>68</v>
@@ -1898,13 +1898,13 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>92.93434258622409</v>
+        <v>77.18175437109248</v>
       </c>
       <c r="C78">
-        <v>92.90653684424497</v>
+        <v>77.0820975852088</v>
       </c>
       <c r="D78">
-        <v>0.02780574197912244</v>
+        <v>0.09965678588368121</v>
       </c>
       <c r="E78" t="s">
         <v>69</v>
@@ -1915,13 +1915,13 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>103.9404112261997</v>
+        <v>86.52724841860909</v>
       </c>
       <c r="C79">
-        <v>103.8273463373159</v>
+        <v>86.42904522660545</v>
       </c>
       <c r="D79">
-        <v>0.1130648888837413</v>
+        <v>0.0982031920036377</v>
       </c>
       <c r="E79" t="s">
         <v>63</v>
@@ -1932,13 +1932,13 @@
         <v>16</v>
       </c>
       <c r="B80">
-        <v>103.3465577913727</v>
+        <v>74.52274330135653</v>
       </c>
       <c r="C80">
-        <v>103.2403026764264</v>
+        <v>74.4390000592737</v>
       </c>
       <c r="D80">
-        <v>0.1062551149463218</v>
+        <v>0.08374324208283213</v>
       </c>
       <c r="E80" t="s">
         <v>64</v>
@@ -1949,13 +1949,13 @@
         <v>16</v>
       </c>
       <c r="B81">
-        <v>105.3783713518261</v>
+        <v>100.6335600020557</v>
       </c>
       <c r="C81">
-        <v>105.2572502688447</v>
+        <v>100.5183447762463</v>
       </c>
       <c r="D81">
-        <v>0.1211210829814036</v>
+        <v>0.1152152258094219</v>
       </c>
       <c r="E81" t="s">
         <v>65</v>
@@ -1966,13 +1966,13 @@
         <v>16</v>
       </c>
       <c r="B82">
-        <v>102.37458698058</v>
+        <v>85.47598766225333</v>
       </c>
       <c r="C82">
-        <v>102.2610170570968</v>
+        <v>85.37914416970932</v>
       </c>
       <c r="D82">
-        <v>0.1135699234832401</v>
+        <v>0.0968434925440107</v>
       </c>
       <c r="E82" t="s">
         <v>66</v>
@@ -1983,13 +1983,13 @@
         <v>16</v>
       </c>
       <c r="B83">
-        <v>105.5962973710966</v>
+        <v>85.00137954412477</v>
       </c>
       <c r="C83">
-        <v>105.4849297440026</v>
+        <v>84.90492278015843</v>
       </c>
       <c r="D83">
-        <v>0.1113676270939834</v>
+        <v>0.09645676396634428</v>
       </c>
       <c r="E83" t="s">
         <v>67</v>
@@ -2000,13 +2000,13 @@
         <v>16</v>
       </c>
       <c r="B84">
-        <v>105.2816319264011</v>
+        <v>80.6181396484771</v>
       </c>
       <c r="C84">
-        <v>105.1726077931943</v>
+        <v>80.52697109104169</v>
       </c>
       <c r="D84">
-        <v>0.1090241332068445</v>
+        <v>0.09116855743540953</v>
       </c>
       <c r="E84" t="s">
         <v>68</v>
@@ -2017,13 +2017,13 @@
         <v>16</v>
       </c>
       <c r="B85">
-        <v>102.9754299581952</v>
+        <v>92.89137999020053</v>
       </c>
       <c r="C85">
-        <v>102.8577702911113</v>
+        <v>92.78559395993679</v>
       </c>
       <c r="D85">
-        <v>0.1176596670838705</v>
+        <v>0.1057860302637437</v>
       </c>
       <c r="E85" t="s">
         <v>69</v>
@@ -2034,13 +2034,13 @@
         <v>17</v>
       </c>
       <c r="B86">
-        <v>104.8984881404407</v>
+        <v>104.9060519405605</v>
       </c>
       <c r="C86">
-        <v>106.7044007164347</v>
+        <v>106.7151637579515</v>
       </c>
       <c r="D86">
-        <v>-1.805912575993943</v>
+        <v>-1.809111817391042</v>
       </c>
       <c r="E86" t="s">
         <v>63</v>
@@ -2051,13 +2051,13 @@
         <v>17</v>
       </c>
       <c r="B87">
-        <v>87.39869666119598</v>
+        <v>87.40730075026894</v>
       </c>
       <c r="C87">
-        <v>87.29497263358331</v>
+        <v>87.30356668987594</v>
       </c>
       <c r="D87">
-        <v>0.103724027612671</v>
+        <v>0.103734060393009</v>
       </c>
       <c r="E87" t="s">
         <v>64</v>
@@ -2068,13 +2068,13 @@
         <v>17</v>
       </c>
       <c r="B88">
-        <v>111.7146170687134</v>
+        <v>111.7205180043511</v>
       </c>
       <c r="C88">
-        <v>131.3844327380201</v>
+        <v>131.3979710671924</v>
       </c>
       <c r="D88">
-        <v>-19.66981566930679</v>
+        <v>-19.67745306284131</v>
       </c>
       <c r="E88" t="s">
         <v>65</v>
@@ -2085,13 +2085,13 @@
         <v>17</v>
       </c>
       <c r="B89">
-        <v>101.2828205326606</v>
+        <v>101.2925319955577</v>
       </c>
       <c r="C89">
-        <v>101.2827346053352</v>
+        <v>101.2928398897354</v>
       </c>
       <c r="D89">
-        <v>8.592732537238135E-05</v>
+        <v>-0.0003078941776522015</v>
       </c>
       <c r="E89" t="s">
         <v>66</v>
@@ -2102,13 +2102,13 @@
         <v>17</v>
       </c>
       <c r="B90">
-        <v>102.347260527848</v>
+        <v>102.3533590157611</v>
       </c>
       <c r="C90">
-        <v>108.0848724085326</v>
+        <v>108.0958413912315</v>
       </c>
       <c r="D90">
-        <v>-5.737611880684611</v>
+        <v>-5.742482375470317</v>
       </c>
       <c r="E90" t="s">
         <v>67</v>
@@ -2119,13 +2119,13 @@
         <v>17</v>
       </c>
       <c r="B91">
-        <v>98.84820250192381</v>
+        <v>98.85607177674574</v>
       </c>
       <c r="C91">
-        <v>100.2368949387817</v>
+        <v>100.2469798380881</v>
       </c>
       <c r="D91">
-        <v>-1.388692436857852</v>
+        <v>-1.390908061342316</v>
       </c>
       <c r="E91" t="s">
         <v>68</v>
@@ -2136,13 +2136,13 @@
         <v>17</v>
       </c>
       <c r="B92">
-        <v>110.4213057157285</v>
+        <v>110.4284727252258</v>
       </c>
       <c r="C92">
-        <v>113.6048992418702</v>
+        <v>113.6163865913574</v>
       </c>
       <c r="D92">
-        <v>-3.183593526141735</v>
+        <v>-3.187913866131609</v>
       </c>
       <c r="E92" t="s">
         <v>69</v>
@@ -2153,13 +2153,13 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>105.1862757371466</v>
+        <v>105.1937845505193</v>
       </c>
       <c r="C93">
-        <v>107.0262792301261</v>
+        <v>107.0370347979289</v>
       </c>
       <c r="D93">
-        <v>-1.840003492979562</v>
+        <v>-1.843250247409628</v>
       </c>
       <c r="E93" t="s">
         <v>63</v>
@@ -2170,13 +2170,13 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>87.79714421570989</v>
+        <v>87.80575262223469</v>
       </c>
       <c r="C94">
-        <v>87.69334799494605</v>
+        <v>87.70194630143386</v>
       </c>
       <c r="D94">
-        <v>0.1037962207638401</v>
+        <v>0.1038063208008282</v>
       </c>
       <c r="E94" t="s">
         <v>64</v>
@@ -2187,13 +2187,13 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>111.8376381404162</v>
+        <v>111.8434402356179</v>
       </c>
       <c r="C95">
-        <v>131.5752410014853</v>
+        <v>131.5887529707466</v>
       </c>
       <c r="D95">
-        <v>-19.73760286106911</v>
+        <v>-19.74531273512872</v>
       </c>
       <c r="E95" t="s">
         <v>65</v>
@@ -2204,13 +2204,13 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>101.6720037015705</v>
+        <v>101.6817180019322</v>
       </c>
       <c r="C96">
-        <v>101.6823396090849</v>
+        <v>101.6924472356592</v>
       </c>
       <c r="D96">
-        <v>-0.01033590751440272</v>
+        <v>-0.01072923372707635</v>
       </c>
       <c r="E96" t="s">
         <v>66</v>
@@ -2221,13 +2221,13 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>102.632745940937</v>
+        <v>102.6387658809387</v>
       </c>
       <c r="C97">
-        <v>108.3396892335838</v>
+        <v>108.3506427544998</v>
       </c>
       <c r="D97">
-        <v>-5.706943292646741</v>
+        <v>-5.71187687356101</v>
       </c>
       <c r="E97" t="s">
         <v>67</v>
@@ -2238,13 +2238,13 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>99.16582411787645</v>
+        <v>99.17365945398458</v>
       </c>
       <c r="C98">
-        <v>100.5363359182203</v>
+        <v>100.5464117099415</v>
       </c>
       <c r="D98">
-        <v>-1.370511800343877</v>
+        <v>-1.372752255956897</v>
       </c>
       <c r="E98" t="s">
         <v>68</v>
@@ -2255,13 +2255,13 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>110.6475556783861</v>
+        <v>110.6546454799219</v>
       </c>
       <c r="C99">
-        <v>113.9519542543775</v>
+        <v>113.9634360361408</v>
       </c>
       <c r="D99">
-        <v>-3.304398575991456</v>
+        <v>-3.308790556218938</v>
       </c>
       <c r="E99" t="s">
         <v>69</v>
@@ -2272,13 +2272,13 @@
         <v>19</v>
       </c>
       <c r="B100">
-        <v>95.48660298126229</v>
+        <v>75.36246684023007</v>
       </c>
       <c r="C100">
-        <v>95.44327306106776</v>
+        <v>75.26738390657738</v>
       </c>
       <c r="D100">
-        <v>0.04332992019453741</v>
+        <v>0.09508293365269083</v>
       </c>
       <c r="E100" t="s">
         <v>63</v>
@@ -2289,13 +2289,13 @@
         <v>19</v>
       </c>
       <c r="B101">
-        <v>93.7319259057287</v>
+        <v>61.74925750099757</v>
       </c>
       <c r="C101">
-        <v>93.65790100485989</v>
+        <v>61.67237646482638</v>
       </c>
       <c r="D101">
-        <v>0.07402490086880675</v>
+        <v>0.07688103617119424</v>
       </c>
       <c r="E101" t="s">
         <v>64</v>
@@ -2306,13 +2306,13 @@
         <v>19</v>
       </c>
       <c r="B102">
-        <v>97.58561134658328</v>
+        <v>92.26619357357418</v>
       </c>
       <c r="C102">
-        <v>98.49546619648869</v>
+        <v>92.14959007695178</v>
       </c>
       <c r="D102">
-        <v>-0.9098548499054147</v>
+        <v>0.1166034966224032</v>
       </c>
       <c r="E102" t="s">
         <v>65</v>
@@ -2323,13 +2323,13 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>92.9869463694335</v>
+        <v>71.98898681556766</v>
       </c>
       <c r="C103">
-        <v>92.94471898690271</v>
+        <v>71.89857142871456</v>
       </c>
       <c r="D103">
-        <v>0.04222738253078262</v>
+        <v>0.09041538685309547</v>
       </c>
       <c r="E103" t="s">
         <v>66</v>
@@ -2340,13 +2340,13 @@
         <v>19</v>
       </c>
       <c r="B104">
-        <v>97.56240250414623</v>
+        <v>75.82828646862804</v>
       </c>
       <c r="C104">
-        <v>97.87822083842035</v>
+        <v>75.73242640347435</v>
       </c>
       <c r="D104">
-        <v>-0.3158183342741125</v>
+        <v>0.09586006515368695</v>
       </c>
       <c r="E104" t="s">
         <v>67</v>
@@ -2357,13 +2357,13 @@
         <v>19</v>
       </c>
       <c r="B105">
-        <v>96.83658083106562</v>
+        <v>70.4802307198062</v>
       </c>
       <c r="C105">
-        <v>96.95341789566866</v>
+        <v>70.39153828796204</v>
       </c>
       <c r="D105">
-        <v>-0.1168370646030468</v>
+        <v>0.08869243184416575</v>
       </c>
       <c r="E105" t="s">
         <v>68</v>
@@ -2374,13 +2374,13 @@
         <v>19</v>
       </c>
       <c r="B106">
-        <v>94.13578040824737</v>
+        <v>80.59464889908031</v>
       </c>
       <c r="C106">
-        <v>94.21001462456701</v>
+        <v>80.49271022341516</v>
       </c>
       <c r="D106">
-        <v>-0.07423421631963834</v>
+        <v>0.1019386756651528</v>
       </c>
       <c r="E106" t="s">
         <v>69</v>
@@ -2391,13 +2391,13 @@
         <v>20</v>
       </c>
       <c r="B107">
-        <v>102.2548764078642</v>
+        <v>91.056720256291</v>
       </c>
       <c r="C107">
-        <v>102.1639332948339</v>
+        <v>90.97449995735786</v>
       </c>
       <c r="D107">
-        <v>0.09094311303029201</v>
+        <v>0.08222029893313731</v>
       </c>
       <c r="E107" t="s">
         <v>63</v>
@@ -2408,13 +2408,13 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>102.368886410102</v>
+        <v>83.06603804171542</v>
       </c>
       <c r="C108">
-        <v>102.2804562303099</v>
+        <v>82.99124706397902</v>
       </c>
       <c r="D108">
-        <v>0.08843017979202727</v>
+        <v>0.07479097773639864</v>
       </c>
       <c r="E108" t="s">
         <v>64</v>
@@ -2425,13 +2425,13 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>102.3671651629121</v>
+        <v>99.84671822037885</v>
       </c>
       <c r="C109">
-        <v>102.2734179852597</v>
+        <v>99.75631977431951</v>
       </c>
       <c r="D109">
-        <v>0.09374717765238927</v>
+        <v>0.09039844605933922</v>
       </c>
       <c r="E109" t="s">
         <v>65</v>
@@ -2442,13 +2442,13 @@
         <v>20</v>
       </c>
       <c r="B110">
-        <v>101.7096958603295</v>
+        <v>92.55703404105563</v>
       </c>
       <c r="C110">
-        <v>101.6179580612776</v>
+        <v>92.4734550782</v>
       </c>
       <c r="D110">
-        <v>0.09173779905188439</v>
+        <v>0.0835789628556256</v>
       </c>
       <c r="E110" t="s">
         <v>66</v>
@@ -2459,13 +2459,13 @@
         <v>20</v>
       </c>
       <c r="B111">
-        <v>102.9181338601868</v>
+        <v>87.91269018384962</v>
       </c>
       <c r="C111">
-        <v>102.8284075152933</v>
+        <v>87.8333572991849</v>
       </c>
       <c r="D111">
-        <v>0.08972634489353482</v>
+        <v>0.07933288466472277</v>
       </c>
       <c r="E111" t="s">
         <v>67</v>
@@ -2476,13 +2476,13 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>102.9246113408304</v>
+        <v>85.23315400600768</v>
       </c>
       <c r="C112">
-        <v>102.8356973338008</v>
+        <v>85.15631507305359</v>
       </c>
       <c r="D112">
-        <v>0.08891400702960084</v>
+        <v>0.0768389329540895</v>
       </c>
       <c r="E112" t="s">
         <v>68</v>
@@ -2493,13 +2493,13 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>101.7277533677134</v>
+        <v>97.28785249768831</v>
       </c>
       <c r="C113">
-        <v>101.6345672427153</v>
+        <v>97.19987051384116</v>
       </c>
       <c r="D113">
-        <v>0.09318612499812673</v>
+        <v>0.0879819838471434</v>
       </c>
       <c r="E113" t="s">
         <v>69</v>
@@ -2510,13 +2510,13 @@
         <v>21</v>
       </c>
       <c r="B114">
-        <v>95.64820239929452</v>
+        <v>75.50930035213678</v>
       </c>
       <c r="C114">
-        <v>95.60052139139654</v>
+        <v>75.41423508089437</v>
       </c>
       <c r="D114">
-        <v>0.04768100789797813</v>
+        <v>0.09506527124240449</v>
       </c>
       <c r="E114" t="s">
         <v>63</v>
@@ -2527,13 +2527,13 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>93.96550537136601</v>
+        <v>61.93424235335238</v>
       </c>
       <c r="C115">
-        <v>93.89025651406405</v>
+        <v>61.85730390218247</v>
       </c>
       <c r="D115">
-        <v>0.07524885730195763</v>
+        <v>0.07693845116990872</v>
       </c>
       <c r="E115" t="s">
         <v>64</v>
@@ -2544,13 +2544,13 @@
         <v>21</v>
       </c>
       <c r="B116">
-        <v>97.67407262773919</v>
+        <v>92.3487582916725</v>
       </c>
       <c r="C116">
-        <v>98.57033096763369</v>
+        <v>92.23211076684602</v>
       </c>
       <c r="D116">
-        <v>-0.8962583398945014</v>
+        <v>0.116647524826476</v>
       </c>
       <c r="E116" t="s">
         <v>65</v>
@@ -2561,13 +2561,13 @@
         <v>21</v>
       </c>
       <c r="B117">
-        <v>93.1544987962383</v>
+        <v>72.17379592564417</v>
       </c>
       <c r="C117">
-        <v>93.10992093322707</v>
+        <v>72.08333887085365</v>
       </c>
       <c r="D117">
-        <v>0.04457786301122724</v>
+        <v>0.09045705479051946</v>
       </c>
       <c r="E117" t="s">
         <v>66</v>
@@ -2578,13 +2578,13 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>97.74233553079529</v>
+        <v>75.94409481257482</v>
       </c>
       <c r="C118">
-        <v>98.04059636573558</v>
+        <v>75.8482972416972</v>
       </c>
       <c r="D118">
-        <v>-0.2982608349402938</v>
+        <v>0.09579757087762175</v>
       </c>
       <c r="E118" t="s">
         <v>67</v>
@@ -2595,13 +2595,13 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>97.04268771214892</v>
+        <v>70.6174448253991</v>
       </c>
       <c r="C119">
-        <v>97.14675552170492</v>
+        <v>70.52877645990169</v>
       </c>
       <c r="D119">
-        <v>-0.1040678095559997</v>
+        <v>0.08866836549741208</v>
       </c>
       <c r="E119" t="s">
         <v>68</v>
@@ -2612,13 +2612,13 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>94.26565255392909</v>
+        <v>80.75226418172353</v>
       </c>
       <c r="C120">
-        <v>94.33663570943423</v>
+        <v>80.65033566461204</v>
       </c>
       <c r="D120">
-        <v>-0.07098315550514656</v>
+        <v>0.1019285171114888</v>
       </c>
       <c r="E120" t="s">
         <v>69</v>
@@ -2629,13 +2629,13 @@
         <v>22</v>
       </c>
       <c r="B121">
-        <v>102.5014492513059</v>
+        <v>91.29798187112559</v>
       </c>
       <c r="C121">
-        <v>102.4111892937343</v>
+        <v>91.21635293996619</v>
       </c>
       <c r="D121">
-        <v>0.09025995757161809</v>
+        <v>0.08162893115940051</v>
       </c>
       <c r="E121" t="s">
         <v>63</v>
@@ -2646,13 +2646,13 @@
         <v>22</v>
       </c>
       <c r="B122">
-        <v>102.7495067579277</v>
+        <v>83.42058544404867</v>
       </c>
       <c r="C122">
-        <v>102.6616780733299</v>
+        <v>83.34621642007366</v>
       </c>
       <c r="D122">
-        <v>0.08782868459783799</v>
+        <v>0.07436902397500944</v>
       </c>
       <c r="E122" t="s">
         <v>64</v>
@@ -2663,13 +2663,13 @@
         <v>22</v>
       </c>
       <c r="B123">
-        <v>102.4753341745071</v>
+        <v>99.94963949250752</v>
       </c>
       <c r="C123">
-        <v>102.3823636579091</v>
+        <v>99.86003168931548</v>
       </c>
       <c r="D123">
-        <v>0.09297051659795841</v>
+        <v>0.0896078031920382</v>
       </c>
       <c r="E123" t="s">
         <v>65</v>
@@ -2680,13 +2680,13 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>101.9242265925669</v>
+        <v>92.84592684474728</v>
       </c>
       <c r="C124">
-        <v>101.8331645411286</v>
+        <v>92.76290617631039</v>
       </c>
       <c r="D124">
-        <v>0.09106205143828561</v>
+        <v>0.08302066843688749</v>
       </c>
       <c r="E124" t="s">
         <v>66</v>
@@ -2697,13 +2697,13 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>103.2227426124319</v>
+        <v>88.13076165466164</v>
       </c>
       <c r="C125">
-        <v>103.1336930512006</v>
+        <v>88.0520172545196</v>
       </c>
       <c r="D125">
-        <v>0.08904956123133445</v>
+        <v>0.07874440014204254</v>
       </c>
       <c r="E125" t="s">
         <v>67</v>
@@ -2714,13 +2714,13 @@
         <v>22</v>
       </c>
       <c r="B126">
-        <v>103.2714544255207</v>
+        <v>85.4927219413932</v>
       </c>
       <c r="C126">
-        <v>103.1831907722486</v>
+        <v>85.41641135742789</v>
       </c>
       <c r="D126">
-        <v>0.08826365327203689</v>
+        <v>0.07631058396530932</v>
       </c>
       <c r="E126" t="s">
         <v>68</v>
@@ -2731,13 +2731,13 @@
         <v>22</v>
       </c>
       <c r="B127">
-        <v>101.876563743982</v>
+        <v>97.50758148668559</v>
       </c>
       <c r="C127">
-        <v>101.784097116044</v>
+        <v>97.42026012021527</v>
       </c>
       <c r="D127">
-        <v>0.09246662793799487</v>
+        <v>0.08732136647032007</v>
       </c>
       <c r="E127" t="s">
         <v>69</v>
@@ -2748,13 +2748,13 @@
         <v>23</v>
       </c>
       <c r="B128">
-        <v>102.4140746993041</v>
+        <v>91.2233763934936</v>
       </c>
       <c r="C128">
-        <v>102.323620435305</v>
+        <v>91.14157330796969</v>
       </c>
       <c r="D128">
-        <v>0.09045426399903533</v>
+        <v>0.08180308552390159</v>
       </c>
       <c r="E128" t="s">
         <v>63</v>
@@ -2765,13 +2765,13 @@
         <v>23</v>
       </c>
       <c r="B129">
-        <v>102.6175611192371</v>
+        <v>83.31326464095062</v>
       </c>
       <c r="C129">
-        <v>102.5295603877825</v>
+        <v>83.23876996720584</v>
       </c>
       <c r="D129">
-        <v>0.08800073145458498</v>
+        <v>0.07449467374478047</v>
       </c>
       <c r="E129" t="s">
         <v>64</v>
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>102.4335821809334</v>
+        <v>99.91487487478186</v>
       </c>
       <c r="C130">
-        <v>102.3403916079477</v>
+        <v>99.82503595455172</v>
       </c>
       <c r="D130">
-        <v>0.09319057298570499</v>
+        <v>0.08983892023013595</v>
       </c>
       <c r="E130" t="s">
         <v>65</v>
@@ -2799,13 +2799,13 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>101.8507953432165</v>
+        <v>92.75807495766831</v>
       </c>
       <c r="C131">
-        <v>101.7595407066255</v>
+        <v>92.67488917980671</v>
       </c>
       <c r="D131">
-        <v>0.09125463659098898</v>
+        <v>0.0831857778616012</v>
       </c>
       <c r="E131" t="s">
         <v>66</v>
@@ -2816,13 +2816,13 @@
         <v>23</v>
       </c>
       <c r="B132">
-        <v>103.1126080527711</v>
+        <v>88.06235784183525</v>
       </c>
       <c r="C132">
-        <v>103.0233662114269</v>
+        <v>87.98344052788859</v>
       </c>
       <c r="D132">
-        <v>0.08924184134411917</v>
+        <v>0.07891731394666124</v>
       </c>
       <c r="E132" t="s">
         <v>67</v>
@@ -2833,13 +2833,13 @@
         <v>23</v>
       </c>
       <c r="B133">
-        <v>103.1473430183639</v>
+        <v>85.4123716239386</v>
       </c>
       <c r="C133">
-        <v>103.0588942667672</v>
+        <v>85.33590531201416</v>
       </c>
       <c r="D133">
-        <v>0.08844875159674359</v>
+        <v>0.07646631192443465</v>
       </c>
       <c r="E133" t="s">
         <v>68</v>
@@ -2850,13 +2850,13 @@
         <v>23</v>
       </c>
       <c r="B134">
-        <v>101.8249290652489</v>
+        <v>97.43968579297501</v>
       </c>
       <c r="C134">
-        <v>101.7322579309781</v>
+        <v>97.35217003628092</v>
       </c>
       <c r="D134">
-        <v>0.09267113427078755</v>
+        <v>0.08751575669408851</v>
       </c>
       <c r="E134" t="s">
         <v>69</v>
@@ -2867,13 +2867,13 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>104.3507350405985</v>
+        <v>97.36265798951685</v>
       </c>
       <c r="C135">
-        <v>104.2804502711753</v>
+        <v>97.29722062103914</v>
       </c>
       <c r="D135">
-        <v>0.07028476942326733</v>
+        <v>0.06543736847770276</v>
       </c>
       <c r="E135" t="s">
         <v>63</v>
@@ -2884,13 +2884,13 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>105.1559611687937</v>
+        <v>92.06350190684641</v>
       </c>
       <c r="C136">
-        <v>105.0861560935237</v>
+        <v>92.0016913380222</v>
       </c>
       <c r="D136">
-        <v>0.06980507527001123</v>
+        <v>0.06181056882421387</v>
       </c>
       <c r="E136" t="s">
         <v>64</v>
@@ -2901,13 +2901,13 @@
         <v>24</v>
       </c>
       <c r="B137">
-        <v>103.584472676976</v>
+        <v>102.9739067916901</v>
       </c>
       <c r="C137">
-        <v>103.5136643032324</v>
+        <v>102.9046273091696</v>
       </c>
       <c r="D137">
-        <v>0.07080837374356008</v>
+        <v>0.06927948252048566</v>
       </c>
       <c r="E137" t="s">
         <v>65</v>
@@ -2918,13 +2918,13 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>103.9004943042871</v>
+        <v>99.54917259078626</v>
       </c>
       <c r="C138">
-        <v>103.8299102691146</v>
+        <v>99.48225199018705</v>
       </c>
       <c r="D138">
-        <v>0.07058403517248735</v>
+        <v>0.06692060059920379</v>
       </c>
       <c r="E138" t="s">
         <v>66</v>
@@ -2935,13 +2935,13 @@
         <v>24</v>
       </c>
       <c r="B139">
-        <v>104.9945122830247</v>
+        <v>94.12114404978661</v>
       </c>
       <c r="C139">
-        <v>104.9246009240009</v>
+        <v>94.05791200236007</v>
       </c>
       <c r="D139">
-        <v>0.06991135902374879</v>
+        <v>0.06323204742653843</v>
       </c>
       <c r="E139" t="s">
         <v>67</v>
@@ -2952,13 +2952,13 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>105.2360194841764</v>
+        <v>92.432403777673</v>
       </c>
       <c r="C140">
-        <v>105.1662591172353</v>
+        <v>92.3703284949944</v>
       </c>
       <c r="D140">
-        <v>0.06976036694116772</v>
+        <v>0.06207528267860596</v>
       </c>
       <c r="E140" t="s">
         <v>68</v>
@@ -2969,13 +2969,13 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>103.4909611943969</v>
+        <v>102.5597969437173</v>
       </c>
       <c r="C141">
-        <v>103.4201094593854</v>
+        <v>102.4908140007436</v>
       </c>
       <c r="D141">
-        <v>0.07085173501151587</v>
+        <v>0.06898294297366192</v>
       </c>
       <c r="E141" t="s">
         <v>69</v>
@@ -2986,13 +2986,13 @@
         <v>25</v>
       </c>
       <c r="B142">
-        <v>104.1383478355649</v>
+        <v>104.147771323011</v>
       </c>
       <c r="C142">
-        <v>105.1411904335369</v>
+        <v>105.1521606771947</v>
       </c>
       <c r="D142">
-        <v>-1.002842597971977</v>
+        <v>-1.004389354183729</v>
       </c>
       <c r="E142" t="s">
         <v>63</v>
@@ -3003,13 +3003,13 @@
         <v>25</v>
       </c>
       <c r="B143">
-        <v>83.80602452163981</v>
+        <v>83.8145234874172</v>
       </c>
       <c r="C143">
-        <v>83.70355322444031</v>
+        <v>83.71204149443503</v>
       </c>
       <c r="D143">
-        <v>0.1024712971995001</v>
+        <v>0.1024819929821774</v>
       </c>
       <c r="E143" t="s">
         <v>64</v>
@@ -3020,13 +3020,13 @@
         <v>25</v>
       </c>
       <c r="B144">
-        <v>116.3234621141064</v>
+        <v>116.3320685192221</v>
       </c>
       <c r="C144">
-        <v>133.4712790041389</v>
+        <v>133.4855542927207</v>
       </c>
       <c r="D144">
-        <v>-17.14781689003253</v>
+        <v>-17.15348577349859</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
@@ -3037,13 +3037,13 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>97.8047485808525</v>
+        <v>97.81474237675549</v>
       </c>
       <c r="C145">
-        <v>97.70481989202449</v>
+        <v>97.71486564988814</v>
       </c>
       <c r="D145">
-        <v>0.09992868882801531</v>
+        <v>0.09987672686735038</v>
       </c>
       <c r="E145" t="s">
         <v>66</v>
@@ -3054,13 +3054,13 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>102.2980982463725</v>
+        <v>102.3058948620488</v>
       </c>
       <c r="C146">
-        <v>108.2421207594155</v>
+        <v>108.2535141248661</v>
       </c>
       <c r="D146">
-        <v>-5.944022513043009</v>
+        <v>-5.947619262817383</v>
       </c>
       <c r="E146" t="s">
         <v>67</v>
@@ -3071,13 +3071,13 @@
         <v>25</v>
       </c>
       <c r="B147">
-        <v>97.51679529015789</v>
+        <v>97.52558993793478</v>
       </c>
       <c r="C147">
-        <v>99.06942163879438</v>
+        <v>99.07974236843837</v>
       </c>
       <c r="D147">
-        <v>-1.552626348636494</v>
+        <v>-1.554152430503592</v>
       </c>
       <c r="E147" t="s">
         <v>68</v>
@@ -3088,13 +3088,13 @@
         <v>25</v>
       </c>
       <c r="B148">
-        <v>110.4073853825261</v>
+        <v>110.417367758813</v>
       </c>
       <c r="C148">
-        <v>111.5977095552461</v>
+        <v>111.6093708510414</v>
       </c>
       <c r="D148">
-        <v>-1.190324172720011</v>
+        <v>-1.192003092228333</v>
       </c>
       <c r="E148" t="s">
         <v>69</v>
@@ -3105,13 +3105,13 @@
         <v>26</v>
       </c>
       <c r="B149">
-        <v>104.4102654916629</v>
+        <v>86.92124127858565</v>
       </c>
       <c r="C149">
-        <v>104.2975535277135</v>
+        <v>86.82326312635855</v>
       </c>
       <c r="D149">
-        <v>0.1127119639494083</v>
+        <v>0.09797815222709971</v>
       </c>
       <c r="E149" t="s">
         <v>63</v>
@@ -3122,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="B150">
-        <v>104.0139088705514</v>
+        <v>75.01159072882399</v>
       </c>
       <c r="C150">
-        <v>103.9079239567337</v>
+        <v>74.92789141620285</v>
       </c>
       <c r="D150">
-        <v>0.1059849138177356</v>
+        <v>0.08369931262113539</v>
       </c>
       <c r="E150" t="s">
         <v>64</v>
@@ -3139,13 +3139,13 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>105.6395785308202</v>
+        <v>100.8895759068823</v>
       </c>
       <c r="C151">
-        <v>105.5189273180302</v>
+        <v>100.7748317904294</v>
       </c>
       <c r="D151">
-        <v>0.1206512127900652</v>
+        <v>0.1147441164529397</v>
       </c>
       <c r="E151" t="s">
         <v>65</v>
@@ -3156,13 +3156,13 @@
         <v>26</v>
       </c>
       <c r="B152">
-        <v>102.7694033553193</v>
+        <v>85.96046271672296</v>
       </c>
       <c r="C152">
-        <v>102.656134878459</v>
+        <v>85.86372331766567</v>
       </c>
       <c r="D152">
-        <v>0.1132684768602843</v>
+        <v>0.09673939905728446</v>
       </c>
       <c r="E152" t="s">
         <v>66</v>
@@ -3173,13 +3173,13 @@
         <v>26</v>
       </c>
       <c r="B153">
-        <v>106.1835106747425</v>
+        <v>85.32664861938335</v>
       </c>
       <c r="C153">
-        <v>106.0725325691629</v>
+        <v>85.23049714258354</v>
       </c>
       <c r="D153">
-        <v>0.110978105579548</v>
+        <v>0.09615147679980396</v>
       </c>
       <c r="E153" t="s">
         <v>67</v>
@@ -3190,13 +3190,13 @@
         <v>26</v>
       </c>
       <c r="B154">
-        <v>105.9358623015307</v>
+        <v>80.98994465457615</v>
       </c>
       <c r="C154">
-        <v>105.8271920706346</v>
+        <v>80.89900034277123</v>
       </c>
       <c r="D154">
-        <v>0.108670230896152</v>
+        <v>0.09094431180491824</v>
       </c>
       <c r="E154" t="s">
         <v>68</v>
@@ -3207,13 +3207,13 @@
         <v>26</v>
       </c>
       <c r="B155">
-        <v>103.2692266182532</v>
+        <v>93.31047777482208</v>
       </c>
       <c r="C155">
-        <v>103.1519237721811</v>
+        <v>93.20491656666901</v>
       </c>
       <c r="D155">
-        <v>0.1173028460721497</v>
+        <v>0.1055612081530626</v>
       </c>
       <c r="E155" t="s">
         <v>69</v>
@@ -3224,13 +3224,13 @@
         <v>27</v>
       </c>
       <c r="B156">
-        <v>105.6049252129322</v>
+        <v>105.6142221069481</v>
       </c>
       <c r="C156">
-        <v>106.7187951710539</v>
+        <v>106.7297522461004</v>
       </c>
       <c r="D156">
-        <v>-1.113869958121725</v>
+        <v>-1.115530139152284</v>
       </c>
       <c r="E156" t="s">
         <v>63</v>
@@ -3241,13 +3241,13 @@
         <v>27</v>
       </c>
       <c r="B157">
-        <v>85.6613272638338</v>
+        <v>85.66985557630152</v>
       </c>
       <c r="C157">
-        <v>85.55855731867103</v>
+        <v>85.56707651828657</v>
       </c>
       <c r="D157">
-        <v>0.1027699451627626</v>
+        <v>0.1027790580149457</v>
       </c>
       <c r="E157" t="s">
         <v>64</v>
@@ -3258,13 +3258,13 @@
         <v>27</v>
       </c>
       <c r="B158">
-        <v>116.9036140281033</v>
+        <v>116.9118440911462</v>
       </c>
       <c r="C158">
-        <v>134.5215743901397</v>
+        <v>134.5357587031455</v>
       </c>
       <c r="D158">
-        <v>-17.6179603620364</v>
+        <v>-17.62391461199925</v>
       </c>
       <c r="E158" t="s">
         <v>65</v>
@@ -3275,13 +3275,13 @@
         <v>27</v>
       </c>
       <c r="B159">
-        <v>99.67227316684985</v>
+        <v>99.68228539671588</v>
       </c>
       <c r="C159">
-        <v>99.58081640647698</v>
+        <v>99.5908882128869</v>
       </c>
       <c r="D159">
-        <v>0.09145676037286421</v>
+        <v>0.0913971838289882</v>
       </c>
       <c r="E159" t="s">
         <v>66</v>
@@ -3292,13 +3292,13 @@
         <v>27</v>
       </c>
       <c r="B160">
-        <v>103.5424377144012</v>
+        <v>103.5499635993058</v>
       </c>
       <c r="C160">
-        <v>109.5593412227191</v>
+        <v>109.5706889355631</v>
       </c>
       <c r="D160">
-        <v>-6.01690350831791</v>
+        <v>-6.0207253362573</v>
       </c>
       <c r="E160" t="s">
         <v>67</v>
@@ -3309,13 +3309,13 @@
         <v>27</v>
       </c>
       <c r="B161">
-        <v>99.00617887021099</v>
+        <v>99.01485782473394</v>
       </c>
       <c r="C161">
-        <v>100.5872470905939</v>
+        <v>100.5975509989438</v>
       </c>
       <c r="D161">
-        <v>-1.581068220382903</v>
+        <v>-1.582693174209894</v>
       </c>
       <c r="E161" t="s">
         <v>68</v>
@@ -3326,13 +3326,13 @@
         <v>27</v>
       </c>
       <c r="B162">
-        <v>111.841950901682</v>
+        <v>111.8517950546726</v>
       </c>
       <c r="C162">
-        <v>113.240873819161</v>
+        <v>113.2525261665448</v>
       </c>
       <c r="D162">
-        <v>-1.398922917478913</v>
+        <v>-1.400731111872176</v>
       </c>
       <c r="E162" t="s">
         <v>69</v>
@@ -3343,13 +3343,13 @@
         <v>28</v>
       </c>
       <c r="B163">
-        <v>107.1079622228388</v>
+        <v>107.1131616707679</v>
       </c>
       <c r="C163">
-        <v>107.0449820681002</v>
+        <v>107.0501783706839</v>
       </c>
       <c r="D163">
-        <v>0.06298015473855401</v>
+        <v>0.06298330008401365</v>
       </c>
       <c r="E163" t="s">
         <v>63</v>
@@ -3360,13 +3360,13 @@
         <v>28</v>
       </c>
       <c r="B164">
-        <v>102.2492162480294</v>
+        <v>102.2541723235569</v>
       </c>
       <c r="C164">
-        <v>102.189184015697</v>
+        <v>102.1941370949359</v>
       </c>
       <c r="D164">
-        <v>0.06003223233238941</v>
+        <v>0.06003522862096133</v>
       </c>
       <c r="E164" t="s">
         <v>64</v>
@@ -3377,13 +3377,13 @@
         <v>28</v>
       </c>
       <c r="B165">
-        <v>112.206253924484</v>
+        <v>112.2117088705904</v>
       </c>
       <c r="C165">
-        <v>112.1401789703836</v>
+        <v>112.1456306146309</v>
       </c>
       <c r="D165">
-        <v>0.06607495410041508</v>
+        <v>0.06607825595955319</v>
       </c>
       <c r="E165" t="s">
         <v>65</v>
@@ -3394,13 +3394,13 @@
         <v>28</v>
       </c>
       <c r="B166">
-        <v>109.4199886240067</v>
+        <v>109.4253028171975</v>
       </c>
       <c r="C166">
-        <v>109.3556185806588</v>
+        <v>109.360929558478</v>
       </c>
       <c r="D166">
-        <v>0.06437004334789265</v>
+        <v>0.06437325871952737</v>
       </c>
       <c r="E166" t="s">
         <v>66</v>
@@ -3411,13 +3411,13 @@
         <v>28</v>
       </c>
       <c r="B167">
-        <v>103.8345139743774</v>
+        <v>103.8395505328191</v>
       </c>
       <c r="C167">
-        <v>103.7735068698799</v>
+        <v>103.7785403824858</v>
       </c>
       <c r="D167">
-        <v>0.06100710449744895</v>
+        <v>0.06101015033327428</v>
       </c>
       <c r="E167" t="s">
         <v>67</v>
@@ -3428,13 +3428,13 @@
         <v>28</v>
       </c>
       <c r="B168">
-        <v>102.3100056930851</v>
+        <v>102.3149658145373</v>
       </c>
       <c r="C168">
-        <v>102.2499244548089</v>
+        <v>102.2548815772578</v>
       </c>
       <c r="D168">
-        <v>0.06008123827622569</v>
+        <v>0.06008423727948298</v>
       </c>
       <c r="E168" t="s">
         <v>68</v>
@@ -3445,13 +3445,13 @@
         <v>28</v>
       </c>
       <c r="B169">
-        <v>112.1372619479288</v>
+        <v>112.1427123976534</v>
       </c>
       <c r="C169">
-        <v>112.0712414560099</v>
+        <v>112.0766886068753</v>
       </c>
       <c r="D169">
-        <v>0.06602049191890558</v>
+        <v>0.06602379077817488</v>
       </c>
       <c r="E169" t="s">
         <v>69</v>
@@ -3462,13 +3462,13 @@
         <v>29</v>
       </c>
       <c r="B170">
-        <v>104.9579119843815</v>
+        <v>104.967263841573</v>
       </c>
       <c r="C170">
-        <v>106.0207505520693</v>
+        <v>106.0317157059055</v>
       </c>
       <c r="D170">
-        <v>-1.062838567687791</v>
+        <v>-1.064451864332497</v>
       </c>
       <c r="E170" t="s">
         <v>63</v>
@@ -3479,13 +3479,13 @@
         <v>29</v>
       </c>
       <c r="B171">
-        <v>84.83976685403302</v>
+        <v>84.8482852329962</v>
       </c>
       <c r="C171">
-        <v>84.73710160533427</v>
+        <v>84.74560947083569</v>
       </c>
       <c r="D171">
-        <v>0.1026652486987416</v>
+        <v>0.1026757621605157</v>
       </c>
       <c r="E171" t="s">
         <v>64</v>
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="B172">
-        <v>116.6590410671116</v>
+        <v>116.6674483343186</v>
       </c>
       <c r="C172">
-        <v>134.0558448258811</v>
+        <v>134.0700713170076</v>
       </c>
       <c r="D172">
-        <v>-17.39680375876952</v>
+        <v>-17.40262298268892</v>
       </c>
       <c r="E172" t="s">
         <v>65</v>
@@ -3513,13 +3513,13 @@
         <v>29</v>
       </c>
       <c r="B173">
-        <v>98.85102403100562</v>
+        <v>98.86101965648449</v>
       </c>
       <c r="C173">
-        <v>98.75425653050213</v>
+        <v>98.76431936783334</v>
       </c>
       <c r="D173">
-        <v>0.09676750050348915</v>
+        <v>0.09670028865114944</v>
       </c>
       <c r="E173" t="s">
         <v>66</v>
@@ -3530,13 +3530,13 @@
         <v>29</v>
       </c>
       <c r="B174">
-        <v>102.9848632679722</v>
+        <v>102.9925321930304</v>
       </c>
       <c r="C174">
-        <v>108.9724093969097</v>
+        <v>108.9837792179766</v>
       </c>
       <c r="D174">
-        <v>-5.987546128937495</v>
+        <v>-5.991247024946233</v>
       </c>
       <c r="E174" t="s">
         <v>67</v>
@@ -3547,13 +3547,13 @@
         <v>29</v>
       </c>
       <c r="B175">
-        <v>98.34274012086618</v>
+        <v>98.35146904475539</v>
       </c>
       <c r="C175">
-        <v>99.9123383882679</v>
+        <v>99.92265180683195</v>
       </c>
       <c r="D175">
-        <v>-1.569598267401716</v>
+        <v>-1.57118276207656</v>
       </c>
       <c r="E175" t="s">
         <v>68</v>
@@ -3564,13 +3564,13 @@
         <v>29</v>
       </c>
       <c r="B176">
-        <v>111.2159499552103</v>
+        <v>111.2258543834898</v>
       </c>
       <c r="C176">
-        <v>112.5173183939743</v>
+        <v>112.5289771540084</v>
       </c>
       <c r="D176">
-        <v>-1.301368438763916</v>
+        <v>-1.303122770518556</v>
       </c>
       <c r="E176" t="s">
         <v>69</v>
@@ -3581,13 +3581,13 @@
         <v>30</v>
       </c>
       <c r="B177">
-        <v>105.4528327887368</v>
+        <v>105.4621442138925</v>
       </c>
       <c r="C177">
-        <v>106.5547324052203</v>
+        <v>106.5656917394603</v>
       </c>
       <c r="D177">
-        <v>-1.101899616483422</v>
+        <v>-1.103547525567819</v>
       </c>
       <c r="E177" t="s">
         <v>63</v>
@@ -3598,13 +3598,13 @@
         <v>30</v>
       </c>
       <c r="B178">
-        <v>85.46608841971141</v>
+        <v>85.47461408241288</v>
       </c>
       <c r="C178">
-        <v>85.36334274023008</v>
+        <v>85.37185930575104</v>
       </c>
       <c r="D178">
-        <v>0.1027456794813304</v>
+        <v>0.1027547766618397</v>
       </c>
       <c r="E178" t="s">
         <v>64</v>
@@ -3615,13 +3615,13 @@
         <v>30</v>
       </c>
       <c r="B179">
-        <v>116.8462131491031</v>
+        <v>116.854484600007</v>
       </c>
       <c r="C179">
-        <v>134.415906177119</v>
+        <v>134.4301013172646</v>
       </c>
       <c r="D179">
-        <v>-17.56969302801591</v>
+        <v>-17.57561671725766</v>
       </c>
       <c r="E179" t="s">
         <v>65</v>
@@ -3632,13 +3632,13 @@
         <v>30</v>
       </c>
       <c r="B180">
-        <v>99.47708336541847</v>
+        <v>99.48709370554194</v>
       </c>
       <c r="C180">
-        <v>99.38473078390709</v>
+        <v>99.3948005910128</v>
       </c>
       <c r="D180">
-        <v>0.09235258151137771</v>
+        <v>0.09229311452914146</v>
       </c>
       <c r="E180" t="s">
         <v>66</v>
@@ -3649,13 +3649,13 @@
         <v>30</v>
       </c>
       <c r="B181">
-        <v>103.4122869434186</v>
+        <v>103.4198430120148</v>
       </c>
       <c r="C181">
-        <v>109.4228292017821</v>
+        <v>109.4341826623514</v>
       </c>
       <c r="D181">
-        <v>-6.010542258363444</v>
+        <v>-6.014339650336623</v>
       </c>
       <c r="E181" t="s">
         <v>67</v>
@@ -3666,13 +3666,13 @@
         <v>30</v>
       </c>
       <c r="B182">
-        <v>98.85015245399266</v>
+        <v>98.85884467672408</v>
       </c>
       <c r="C182">
-        <v>100.4286626064006</v>
+        <v>100.4389691020234</v>
       </c>
       <c r="D182">
-        <v>-1.578510152407972</v>
+        <v>-1.580124425299374</v>
       </c>
       <c r="E182" t="s">
         <v>68</v>
@@ -3683,13 +3683,13 @@
         <v>30</v>
       </c>
       <c r="B183">
-        <v>111.6947923733483</v>
+        <v>111.7046523877544</v>
       </c>
       <c r="C183">
-        <v>113.0707656466028</v>
+        <v>113.0824198701634</v>
       </c>
       <c r="D183">
-        <v>-1.375973273254488</v>
+        <v>-1.377767482408984</v>
       </c>
       <c r="E183" t="s">
         <v>69</v>
@@ -3700,13 +3700,13 @@
         <v>31</v>
       </c>
       <c r="B184">
-        <v>105.4988639990026</v>
+        <v>105.5081683426393</v>
       </c>
       <c r="C184">
-        <v>106.6066999572787</v>
+        <v>106.6176570197133</v>
       </c>
       <c r="D184">
-        <v>-1.10783595827607</v>
+        <v>-1.109488677073998</v>
       </c>
       <c r="E184" t="s">
         <v>63</v>
@@ -3717,13 +3717,13 @@
         <v>31</v>
       </c>
       <c r="B185">
-        <v>85.54093804204811</v>
+        <v>85.549464957738</v>
       </c>
       <c r="C185">
-        <v>85.43818731043199</v>
+        <v>85.44670512285276</v>
       </c>
       <c r="D185">
-        <v>0.1027507316161262</v>
+        <v>0.1027598348852337</v>
       </c>
       <c r="E185" t="s">
         <v>64</v>
@@ -3734,13 +3734,13 @@
         <v>31</v>
       </c>
       <c r="B186">
-        <v>116.8491507728496</v>
+        <v>116.8574040311822</v>
       </c>
       <c r="C186">
-        <v>134.425272563136</v>
+        <v>134.4394592516861</v>
       </c>
       <c r="D186">
-        <v>-17.57612179028634</v>
+        <v>-17.58205522050382</v>
       </c>
       <c r="E186" t="s">
         <v>65</v>
@@ -3751,13 +3751,13 @@
         <v>31</v>
       </c>
       <c r="B187">
-        <v>99.55102220989978</v>
+        <v>99.56103328646149</v>
       </c>
       <c r="C187">
-        <v>99.45924986741812</v>
+        <v>99.46932046003782</v>
       </c>
       <c r="D187">
-        <v>0.09177234248166144</v>
+        <v>0.09171282642367373</v>
       </c>
       <c r="E187" t="s">
         <v>66</v>
@@ -3768,13 +3768,13 @@
         <v>31</v>
       </c>
       <c r="B188">
-        <v>103.4469867216055</v>
+        <v>103.4545293072684</v>
       </c>
       <c r="C188">
-        <v>109.4555301238295</v>
+        <v>109.4668788049111</v>
       </c>
       <c r="D188">
-        <v>-6.008543402224021</v>
+        <v>-6.012349497642717</v>
       </c>
       <c r="E188" t="s">
         <v>67</v>
@@ -3785,13 +3785,13 @@
         <v>31</v>
       </c>
       <c r="B189">
-        <v>98.89768078497382</v>
+        <v>98.90636644182156</v>
       </c>
       <c r="C189">
-        <v>100.4774362827739</v>
+        <v>100.487740280206</v>
       </c>
       <c r="D189">
-        <v>-1.579755497800051</v>
+        <v>-1.581373838384408</v>
       </c>
       <c r="E189" t="s">
         <v>68</v>
@@ -3802,13 +3802,13 @@
         <v>31</v>
       </c>
       <c r="B190">
-        <v>111.7391941380343</v>
+        <v>111.7490465777041</v>
       </c>
       <c r="C190">
-        <v>113.1263110717645</v>
+        <v>113.1379632883613</v>
       </c>
       <c r="D190">
-        <v>-1.387116933730226</v>
+        <v>-1.388916710657156</v>
       </c>
       <c r="E190" t="s">
         <v>69</v>
@@ -3819,13 +3819,13 @@
         <v>32</v>
       </c>
       <c r="B191">
-        <v>105.1226887835173</v>
+        <v>105.1302110875339</v>
       </c>
       <c r="C191">
-        <v>106.9530735360714</v>
+        <v>106.9638325329286</v>
       </c>
       <c r="D191">
-        <v>-1.830384752554011</v>
+        <v>-1.833621445394769</v>
       </c>
       <c r="E191" t="s">
         <v>63</v>
@@ -3836,13 +3836,13 @@
         <v>32</v>
       </c>
       <c r="B192">
-        <v>87.69407582018482</v>
+        <v>87.70268311615857</v>
       </c>
       <c r="C192">
-        <v>87.5902948695486</v>
+        <v>87.59889207940721</v>
       </c>
       <c r="D192">
-        <v>0.1037809506362208</v>
+        <v>0.1037910367513604</v>
       </c>
       <c r="E192" t="s">
         <v>64</v>
@@ -3853,13 +3853,13 @@
         <v>32</v>
       </c>
       <c r="B193">
-        <v>111.8142326225407</v>
+        <v>111.8200577776951</v>
       </c>
       <c r="C193">
-        <v>131.5530801685402</v>
+        <v>131.5666028794049</v>
       </c>
       <c r="D193">
-        <v>-19.73884754599956</v>
+        <v>-19.74654510170986</v>
       </c>
       <c r="E193" t="s">
         <v>65</v>
@@ -3870,13 +3870,13 @@
         <v>32</v>
       </c>
       <c r="B194">
-        <v>101.572623329851</v>
+        <v>101.5823370950647</v>
       </c>
       <c r="C194">
-        <v>101.5795424552437</v>
+        <v>101.5896497111403</v>
       </c>
       <c r="D194">
-        <v>-0.006919125392641945</v>
+        <v>-0.007312616075523692</v>
       </c>
       <c r="E194" t="s">
         <v>66</v>
@@ -3887,13 +3887,13 @@
         <v>32</v>
       </c>
       <c r="B195">
-        <v>102.5719181382452</v>
+        <v>102.5779568251579</v>
       </c>
       <c r="C195">
-        <v>108.2919092714632</v>
+        <v>108.3028693171664</v>
       </c>
       <c r="D195">
-        <v>-5.719991133218016</v>
+        <v>-5.724912492008499</v>
       </c>
       <c r="E195" t="s">
         <v>67</v>
@@ -3904,13 +3904,13 @@
         <v>32</v>
       </c>
       <c r="B196">
-        <v>99.09608559752451</v>
+        <v>99.10392989273316</v>
       </c>
       <c r="C196">
-        <v>100.4711801887106</v>
+        <v>100.48126004358</v>
       </c>
       <c r="D196">
-        <v>-1.375094591186141</v>
+        <v>-1.377330150846802</v>
       </c>
       <c r="E196" t="s">
         <v>68</v>
@@ -3921,13 +3921,13 @@
         <v>32</v>
       </c>
       <c r="B197">
-        <v>110.5981593242575</v>
+        <v>110.6052674789529</v>
       </c>
       <c r="C197">
-        <v>113.8696459906438</v>
+        <v>113.8811304605333</v>
       </c>
       <c r="D197">
-        <v>-3.27148666638638</v>
+        <v>-3.27586298158036</v>
       </c>
       <c r="E197" t="s">
         <v>69</v>
@@ -3938,13 +3938,13 @@
         <v>33</v>
       </c>
       <c r="B198">
-        <v>100.2418787728176</v>
+        <v>100.2515543070265</v>
       </c>
       <c r="C198">
-        <v>100.2732036551172</v>
+        <v>100.2832570915276</v>
       </c>
       <c r="D198">
-        <v>-0.03132488229957175</v>
+        <v>-0.03170278450110686</v>
       </c>
       <c r="E198" t="s">
         <v>63</v>
@@ -3955,13 +3955,13 @@
         <v>33</v>
       </c>
       <c r="B199">
-        <v>82.40934090868309</v>
+        <v>82.41740329615506</v>
       </c>
       <c r="C199">
-        <v>82.31172005902241</v>
+        <v>82.31977195828469</v>
       </c>
       <c r="D199">
-        <v>0.09762084966068585</v>
+        <v>0.09763133787036793</v>
       </c>
       <c r="E199" t="s">
         <v>64</v>
@@ -3972,13 +3972,13 @@
         <v>33</v>
       </c>
       <c r="B200">
-        <v>109.8313208786433</v>
+        <v>109.836519360732</v>
       </c>
       <c r="C200">
-        <v>122.9806413572697</v>
+        <v>122.9932385081858</v>
       </c>
       <c r="D200">
-        <v>-13.14932047862639</v>
+        <v>-13.15671914745377</v>
       </c>
       <c r="E200" t="s">
         <v>65</v>
@@ -3989,13 +3989,13 @@
         <v>33</v>
       </c>
       <c r="B201">
-        <v>95.51730432285693</v>
+        <v>95.52677134609246</v>
       </c>
       <c r="C201">
-        <v>95.40719743340033</v>
+        <v>95.41666710912106</v>
       </c>
       <c r="D201">
-        <v>0.1101068894566026</v>
+        <v>0.1101042369713952</v>
       </c>
       <c r="E201" t="s">
         <v>66</v>
@@ -4006,13 +4006,13 @@
         <v>33</v>
       </c>
       <c r="B202">
-        <v>99.93961840980975</v>
+        <v>99.94735926771963</v>
       </c>
       <c r="C202">
-        <v>101.3708897454307</v>
+        <v>101.3811067153263</v>
       </c>
       <c r="D202">
-        <v>-1.431271335620906</v>
+        <v>-1.433747447606706</v>
       </c>
       <c r="E202" t="s">
         <v>67</v>
@@ -4023,13 +4023,13 @@
         <v>33</v>
       </c>
       <c r="B203">
-        <v>94.14350842000616</v>
+        <v>94.15255462091564</v>
       </c>
       <c r="C203">
-        <v>94.16117947857694</v>
+        <v>94.17058759547831</v>
       </c>
       <c r="D203">
-        <v>-0.01767105857078377</v>
+        <v>-0.01803297456267217</v>
       </c>
       <c r="E203" t="s">
         <v>68</v>
@@ -4040,13 +4040,13 @@
         <v>33</v>
       </c>
       <c r="B204">
-        <v>106.1477189528232</v>
+        <v>106.1568314761728</v>
       </c>
       <c r="C204">
-        <v>106.8019017849316</v>
+        <v>106.8126453136098</v>
       </c>
       <c r="D204">
-        <v>-0.6541828321084182</v>
+        <v>-0.6558138374370515</v>
       </c>
       <c r="E204" t="s">
         <v>69</v>
@@ -4057,13 +4057,13 @@
         <v>34</v>
       </c>
       <c r="B205">
-        <v>104.997605517938</v>
+        <v>105.0069591327968</v>
       </c>
       <c r="C205">
-        <v>106.0637142263577</v>
+        <v>106.0746793310802</v>
       </c>
       <c r="D205">
-        <v>-1.066108708419691</v>
+        <v>-1.067720198283425</v>
       </c>
       <c r="E205" t="s">
         <v>63</v>
@@ -4074,13 +4074,13 @@
         <v>34</v>
       </c>
       <c r="B206">
-        <v>84.88251149200511</v>
+        <v>84.89102830353021</v>
       </c>
       <c r="C206">
-        <v>84.77984738789677</v>
+        <v>84.78835514689908</v>
       </c>
       <c r="D206">
-        <v>0.1026641041083423</v>
+        <v>0.102673156631127</v>
       </c>
       <c r="E206" t="s">
         <v>64</v>
@@ -4091,13 +4091,13 @@
         <v>34</v>
       </c>
       <c r="B207">
-        <v>116.6745974682617</v>
+        <v>116.6829911337087</v>
       </c>
       <c r="C207">
-        <v>134.0992696216449</v>
+        <v>134.1134961530067</v>
       </c>
       <c r="D207">
-        <v>-17.42467215338323</v>
+        <v>-17.43050501929807</v>
       </c>
       <c r="E207" t="s">
         <v>65</v>
@@ -4108,13 +4108,13 @@
         <v>34</v>
       </c>
       <c r="B208">
-        <v>98.89192877167487</v>
+        <v>98.90193245836481</v>
       </c>
       <c r="C208">
-        <v>98.7968458202424</v>
+        <v>98.80690858268554</v>
       </c>
       <c r="D208">
-        <v>0.09508295143247381</v>
+        <v>0.09502387567927428</v>
       </c>
       <c r="E208" t="s">
         <v>66</v>
@@ -4125,13 +4125,13 @@
         <v>34</v>
       </c>
       <c r="B209">
-        <v>103.0254899050612</v>
+        <v>103.0331345620705</v>
       </c>
       <c r="C209">
-        <v>109.0156831508581</v>
+        <v>109.0270529366639</v>
       </c>
       <c r="D209">
-        <v>-5.990193245796974</v>
+        <v>-5.993918374593434</v>
       </c>
       <c r="E209" t="s">
         <v>67</v>
@@ -4142,13 +4142,13 @@
         <v>34</v>
       </c>
       <c r="B210">
-        <v>98.38526354751922</v>
+        <v>98.39399432116453</v>
       </c>
       <c r="C210">
-        <v>99.9554086672258</v>
+        <v>99.96572201587858</v>
       </c>
       <c r="D210">
-        <v>-1.570145119706581</v>
+        <v>-1.571727694714056</v>
       </c>
       <c r="E210" t="s">
         <v>68</v>
@@ -4159,13 +4159,13 @@
         <v>34</v>
       </c>
       <c r="B211">
-        <v>111.2521561826648</v>
+        <v>111.2620622309635</v>
       </c>
       <c r="C211">
-        <v>112.5601955071123</v>
+        <v>112.5718542436862</v>
       </c>
       <c r="D211">
-        <v>-1.308039324447421</v>
+        <v>-1.30979201272271</v>
       </c>
       <c r="E211" t="s">
         <v>69</v>
@@ -4176,13 +4176,13 @@
         <v>35</v>
       </c>
       <c r="B212">
-        <v>105.1491722647487</v>
+        <v>105.1585120376129</v>
       </c>
       <c r="C212">
-        <v>106.2271887439795</v>
+        <v>106.2381520859866</v>
       </c>
       <c r="D212">
-        <v>-1.07801647923074</v>
+        <v>-1.079640048373747</v>
       </c>
       <c r="E212" t="s">
         <v>63</v>
@@ -4193,13 +4193,13 @@
         <v>35</v>
       </c>
       <c r="B213">
-        <v>85.0766784882375</v>
+        <v>85.08519839485569</v>
       </c>
       <c r="C213">
-        <v>84.97398580293675</v>
+        <v>84.98249664266839</v>
       </c>
       <c r="D213">
-        <v>0.1026926853007524</v>
+        <v>0.1027017521873006</v>
       </c>
       <c r="E213" t="s">
         <v>64</v>
@@ -4210,13 +4210,13 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>116.7317040193808</v>
+        <v>116.740057269207</v>
       </c>
       <c r="C214">
-        <v>134.2047492293683</v>
+        <v>134.2189654694051</v>
       </c>
       <c r="D214">
-        <v>-17.47304520998757</v>
+        <v>-17.47890820019815</v>
       </c>
       <c r="E214" t="s">
         <v>65</v>
@@ -4227,13 +4227,13 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>99.08690757287691</v>
+        <v>99.0969136341155</v>
       </c>
       <c r="C215">
-        <v>98.99274153824337</v>
+        <v>99.00280681718971</v>
       </c>
       <c r="D215">
-        <v>0.09416603463354534</v>
+        <v>0.09410681692578748</v>
       </c>
       <c r="E215" t="s">
         <v>66</v>
@@ -4244,13 +4244,13 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>103.1538154489844</v>
+        <v>103.1614308953446</v>
       </c>
       <c r="C216">
-        <v>109.1509978214199</v>
+        <v>109.1623623107847</v>
       </c>
       <c r="D216">
-        <v>-5.997182372435546</v>
+        <v>-6.000931415440135</v>
       </c>
       <c r="E216" t="s">
         <v>67</v>
@@ -4261,13 +4261,13 @@
         <v>35</v>
       </c>
       <c r="B217">
-        <v>98.53969432386062</v>
+        <v>98.54841244167834</v>
       </c>
       <c r="C217">
-        <v>100.1127415353614</v>
+        <v>100.1230527441903</v>
       </c>
       <c r="D217">
-        <v>-1.573047211500779</v>
+        <v>-1.574640302511924</v>
       </c>
       <c r="E217" t="s">
         <v>68</v>
@@ -4278,13 +4278,13 @@
         <v>35</v>
       </c>
       <c r="B218">
-        <v>111.3998949007002</v>
+        <v>111.409785847701</v>
       </c>
       <c r="C218">
-        <v>112.730422100051</v>
+        <v>112.7420795109943</v>
       </c>
       <c r="D218">
-        <v>-1.330527199350811</v>
+        <v>-1.332293663293314</v>
       </c>
       <c r="E218" t="s">
         <v>69</v>
@@ -4295,13 +4295,13 @@
         <v>36</v>
       </c>
       <c r="B219">
-        <v>104.1832137966851</v>
+        <v>104.1909162134904</v>
       </c>
       <c r="C219">
-        <v>105.901418558694</v>
+        <v>105.9121993854622</v>
       </c>
       <c r="D219">
-        <v>-1.718204762008924</v>
+        <v>-1.721283171971805</v>
       </c>
       <c r="E219" t="s">
         <v>63</v>
@@ -4312,13 +4312,13 @@
         <v>36</v>
       </c>
       <c r="B220">
-        <v>86.39731408808406</v>
+        <v>86.40590534634346</v>
       </c>
       <c r="C220">
-        <v>86.29378902549817</v>
+        <v>86.3023704296439</v>
       </c>
       <c r="D220">
-        <v>0.1035250625858879</v>
+        <v>0.1035349166995587</v>
       </c>
       <c r="E220" t="s">
         <v>64</v>
@@ -4329,13 +4329,13 @@
         <v>36</v>
       </c>
       <c r="B221">
-        <v>111.4285568509014</v>
+        <v>111.4347105174433</v>
       </c>
       <c r="C221">
-        <v>130.9236150342279</v>
+        <v>130.9372204946744</v>
       </c>
       <c r="D221">
-        <v>-19.49505818332655</v>
+        <v>-19.50250997723116</v>
       </c>
       <c r="E221" t="s">
         <v>65</v>
@@ -4346,13 +4346,13 @@
         <v>36</v>
       </c>
       <c r="B222">
-        <v>100.2973418086848</v>
+        <v>100.3072685546526</v>
       </c>
       <c r="C222">
-        <v>100.2749684723782</v>
+        <v>100.2850657030867</v>
       </c>
       <c r="D222">
-        <v>0.02237333630655769</v>
+        <v>0.0222028515658792</v>
       </c>
       <c r="E222" t="s">
         <v>66</v>
@@ -4363,13 +4363,13 @@
         <v>36</v>
       </c>
       <c r="B223">
-        <v>101.644865239721</v>
+        <v>101.6511616727377</v>
       </c>
       <c r="C223">
-        <v>107.4600838508705</v>
+        <v>107.4710918420468</v>
       </c>
       <c r="D223">
-        <v>-5.815218611149447</v>
+        <v>-5.819930169309075</v>
       </c>
       <c r="E223" t="s">
         <v>67</v>
@@ -4380,13 +4380,13 @@
         <v>36</v>
       </c>
       <c r="B224">
-        <v>98.06092566921488</v>
+        <v>98.06888120512849</v>
       </c>
       <c r="C224">
-        <v>99.49528268824609</v>
+        <v>99.50538995422433</v>
       </c>
       <c r="D224">
-        <v>-1.434357019031211</v>
+        <v>-1.436508749095836</v>
       </c>
       <c r="E224" t="s">
         <v>68</v>
@@ -4397,13 +4397,13 @@
         <v>36</v>
       </c>
       <c r="B225">
-        <v>109.803609637066</v>
+        <v>109.8117302328492</v>
       </c>
       <c r="C225">
-        <v>112.7332010098815</v>
+        <v>112.7447008231588</v>
       </c>
       <c r="D225">
-        <v>-2.929591372815494</v>
+        <v>-2.932970590309651</v>
       </c>
       <c r="E225" t="s">
         <v>69</v>
@@ -4414,13 +4414,13 @@
         <v>37</v>
       </c>
       <c r="B226">
-        <v>100.3765161161741</v>
+        <v>69.5211624520152</v>
       </c>
       <c r="C226">
-        <v>100.7995846244417</v>
+        <v>69.42839305339484</v>
       </c>
       <c r="D226">
-        <v>-0.4230685082676615</v>
+        <v>0.09276939862036215</v>
       </c>
       <c r="E226" t="s">
         <v>63</v>
@@ -4431,13 +4431,13 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>97.53257676845587</v>
+        <v>51.71112742135696</v>
       </c>
       <c r="C227">
-        <v>97.56101242915429</v>
+        <v>51.64497462184339</v>
       </c>
       <c r="D227">
-        <v>-0.02843566069842041</v>
+        <v>0.06615279951356712</v>
       </c>
       <c r="E227" t="s">
         <v>64</v>
@@ -4448,13 +4448,13 @@
         <v>37</v>
       </c>
       <c r="B228">
-        <v>103.5468219082129</v>
+        <v>94.49575189677564</v>
       </c>
       <c r="C228">
-        <v>107.3030062938209</v>
+        <v>94.82085572175666</v>
       </c>
       <c r="D228">
-        <v>-3.756184385608023</v>
+        <v>-0.3251038249810136</v>
       </c>
       <c r="E228" t="s">
         <v>65</v>
@@ -4465,13 +4465,13 @@
         <v>37</v>
       </c>
       <c r="B229">
-        <v>92.28975015654859</v>
+        <v>60.83119129215958</v>
       </c>
       <c r="C229">
-        <v>92.20760021382283</v>
+        <v>60.7517405710337</v>
       </c>
       <c r="D229">
-        <v>0.08214994272576348</v>
+        <v>0.07945072112588036</v>
       </c>
       <c r="E229" t="s">
         <v>66</v>
@@ -4482,13 +4482,13 @@
         <v>37</v>
       </c>
       <c r="B230">
-        <v>105.1675170341382</v>
+        <v>74.89680560774693</v>
       </c>
       <c r="C230">
-        <v>109.9377591870332</v>
+        <v>74.81079810980947</v>
       </c>
       <c r="D230">
-        <v>-4.770242152894951</v>
+        <v>0.08600749793745877</v>
       </c>
       <c r="E230" t="s">
         <v>67</v>
@@ -4499,13 +4499,13 @@
         <v>37</v>
       </c>
       <c r="B231">
-        <v>104.2486417335563</v>
+        <v>66.3038835470357</v>
       </c>
       <c r="C231">
-        <v>106.8605766912061</v>
+        <v>66.21579876703787</v>
       </c>
       <c r="D231">
-        <v>-2.611934957649893</v>
+        <v>0.08808477999782838</v>
       </c>
       <c r="E231" t="s">
         <v>68</v>
@@ -4516,13 +4516,13 @@
         <v>37</v>
       </c>
       <c r="B232">
-        <v>94.82482468912521</v>
+        <v>72.90800248519692</v>
       </c>
       <c r="C232">
-        <v>94.89533289876225</v>
+        <v>72.81046065619869</v>
       </c>
       <c r="D232">
-        <v>-0.07050820963704041</v>
+        <v>0.09754182899823149</v>
       </c>
       <c r="E232" t="s">
         <v>69</v>
@@ -4533,13 +4533,13 @@
         <v>38</v>
       </c>
       <c r="B233">
-        <v>102.2294011072405</v>
+        <v>83.73547505724004</v>
       </c>
       <c r="C233">
-        <v>103.4721051204377</v>
+        <v>83.63313243644494</v>
       </c>
       <c r="D233">
-        <v>-1.242704013197269</v>
+        <v>0.102342620795099</v>
       </c>
       <c r="E233" t="s">
         <v>63</v>
@@ -4550,13 +4550,13 @@
         <v>38</v>
       </c>
       <c r="B234">
-        <v>100.1294989024095</v>
+        <v>69.13575119807403</v>
       </c>
       <c r="C234">
-        <v>100.4639509872304</v>
+        <v>69.05274122104353</v>
       </c>
       <c r="D234">
-        <v>-0.3344520848209243</v>
+        <v>0.08300997703049973</v>
       </c>
       <c r="E234" t="s">
         <v>64</v>
@@ -4567,13 +4567,13 @@
         <v>38</v>
       </c>
       <c r="B235">
-        <v>102.7737124671302</v>
+        <v>101.6212263440549</v>
       </c>
       <c r="C235">
-        <v>107.9456395983277</v>
+        <v>101.7332180292197</v>
       </c>
       <c r="D235">
-        <v>-5.17192713119745</v>
+        <v>-0.1119916851648668</v>
       </c>
       <c r="E235" t="s">
         <v>65</v>
@@ -4584,13 +4584,13 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <v>100.0720819657586</v>
+        <v>80.2296467950093</v>
       </c>
       <c r="C236">
-        <v>100.7957183045757</v>
+        <v>80.13222919628015</v>
       </c>
       <c r="D236">
-        <v>-0.7236363388171156</v>
+        <v>0.09741759872915168</v>
       </c>
       <c r="E236" t="s">
         <v>66</v>
@@ -4601,13 +4601,13 @@
         <v>38</v>
       </c>
       <c r="B237">
-        <v>103.1222784383786</v>
+        <v>84.12560709515078</v>
       </c>
       <c r="C237">
-        <v>105.8210567232339</v>
+        <v>84.02247038036863</v>
       </c>
       <c r="D237">
-        <v>-2.698778284855237</v>
+        <v>0.1031367147821527</v>
       </c>
       <c r="E237" t="s">
         <v>67</v>
@@ -4618,13 +4618,13 @@
         <v>38</v>
       </c>
       <c r="B238">
-        <v>102.7096224719023</v>
+        <v>78.38674820609128</v>
       </c>
       <c r="C238">
-        <v>104.4253122015573</v>
+        <v>78.29124355059797</v>
       </c>
       <c r="D238">
-        <v>-1.715689729655011</v>
+        <v>0.09550465549331477</v>
       </c>
       <c r="E238" t="s">
         <v>68</v>
@@ -4635,13 +4635,13 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>101.1431442537347</v>
+        <v>89.464151433053</v>
       </c>
       <c r="C239">
-        <v>102.8088700180732</v>
+        <v>89.35447572410071</v>
       </c>
       <c r="D239">
-        <v>-1.665725764338546</v>
+        <v>0.1096757089522953</v>
       </c>
       <c r="E239" t="s">
         <v>69</v>
@@ -4652,13 +4652,13 @@
         <v>39</v>
       </c>
       <c r="B240">
-        <v>97.55601889271624</v>
+        <v>70.63790164901228</v>
       </c>
       <c r="C240">
-        <v>97.58275756300439</v>
+        <v>70.54256654361656</v>
       </c>
       <c r="D240">
-        <v>-0.0267386702881538</v>
+        <v>0.09533510539571921</v>
       </c>
       <c r="E240" t="s">
         <v>63</v>
@@ -4669,13 +4669,13 @@
         <v>39</v>
       </c>
       <c r="B241">
-        <v>94.84486444141822</v>
+        <v>54.68523115930078</v>
       </c>
       <c r="C241">
-        <v>94.77773314685145</v>
+        <v>54.61274288582321</v>
       </c>
       <c r="D241">
-        <v>0.06713129456677791</v>
+        <v>0.07248827347757469</v>
       </c>
       <c r="E241" t="s">
         <v>64</v>
@@ -4686,13 +4686,13 @@
         <v>39</v>
       </c>
       <c r="B242">
-        <v>100.8298629328187</v>
+        <v>91.58829091431336</v>
       </c>
       <c r="C242">
-        <v>102.8026134956058</v>
+        <v>91.61473821705998</v>
       </c>
       <c r="D242">
-        <v>-1.972750562787098</v>
+        <v>-0.02644730274661811</v>
       </c>
       <c r="E242" t="s">
         <v>65</v>
@@ -4703,13 +4703,13 @@
         <v>39</v>
       </c>
       <c r="B243">
-        <v>92.81058407104159</v>
+        <v>64.60896664212814</v>
       </c>
       <c r="C243">
-        <v>92.74999291500882</v>
+        <v>64.52239660797866</v>
       </c>
       <c r="D243">
-        <v>0.06059115603277121</v>
+        <v>0.0865700341494744</v>
       </c>
       <c r="E243" t="s">
         <v>66</v>
@@ -4720,13 +4720,13 @@
         <v>39</v>
       </c>
       <c r="B244">
-        <v>101.3636407400726</v>
+        <v>73.42317205469483</v>
       </c>
       <c r="C244">
-        <v>102.5074589427751</v>
+        <v>73.32393071213056</v>
       </c>
       <c r="D244">
-        <v>-1.143818202702505</v>
+        <v>0.09924134256426953</v>
       </c>
       <c r="E244" t="s">
         <v>67</v>
@@ -4737,13 +4737,13 @@
         <v>39</v>
       </c>
       <c r="B245">
-        <v>100.1792437555197</v>
+        <v>66.62567225146984</v>
       </c>
       <c r="C245">
-        <v>100.6944853155229</v>
+        <v>66.53597192212874</v>
       </c>
       <c r="D245">
-        <v>-0.515241560003119</v>
+        <v>0.08970032934109895</v>
       </c>
       <c r="E245" t="s">
         <v>68</v>
@@ -4754,13 +4754,13 @@
         <v>39</v>
       </c>
       <c r="B246">
-        <v>94.69357251026149</v>
+        <v>74.90313934624881</v>
       </c>
       <c r="C246">
-        <v>94.76597534989432</v>
+        <v>74.801813003614</v>
       </c>
       <c r="D246">
-        <v>-0.07240283963282934</v>
+        <v>0.1013263426348061</v>
       </c>
       <c r="E246" t="s">
         <v>69</v>
@@ -4771,13 +4771,13 @@
         <v>40</v>
       </c>
       <c r="B247">
-        <v>98.69554597971941</v>
+        <v>72.71517592459269</v>
       </c>
       <c r="C247">
-        <v>98.62627252356684</v>
+        <v>72.62119483135234</v>
       </c>
       <c r="D247">
-        <v>0.06927345615257252</v>
+        <v>0.09398109324034465</v>
       </c>
       <c r="E247" t="s">
         <v>63</v>
@@ -4788,13 +4788,13 @@
         <v>40</v>
       </c>
       <c r="B248">
-        <v>96.16959395033481</v>
+        <v>56.84493795825251</v>
       </c>
       <c r="C248">
-        <v>96.08066487729739</v>
+        <v>56.77366417876913</v>
       </c>
       <c r="D248">
-        <v>0.08892907303741993</v>
+        <v>0.0712737794833771</v>
       </c>
       <c r="E248" t="s">
         <v>64</v>
@@ -4805,13 +4805,13 @@
         <v>40</v>
       </c>
       <c r="B249">
-        <v>102.3082554638168</v>
+        <v>93.80223458552783</v>
       </c>
       <c r="C249">
-        <v>103.1932290203828</v>
+        <v>93.71636173038152</v>
       </c>
       <c r="D249">
-        <v>-0.8849735565660666</v>
+        <v>0.08587285514630594</v>
       </c>
       <c r="E249" t="s">
         <v>65</v>
@@ -4822,13 +4822,13 @@
         <v>40</v>
       </c>
       <c r="B250">
-        <v>91.96551360846544</v>
+        <v>65.75216184914154</v>
       </c>
       <c r="C250">
-        <v>91.86180833463781</v>
+        <v>65.66844350574652</v>
       </c>
       <c r="D250">
-        <v>0.1037052738276287</v>
+        <v>0.08371834339502016</v>
       </c>
       <c r="E250" t="s">
         <v>66</v>
@@ -4839,13 +4839,13 @@
         <v>40</v>
       </c>
       <c r="B251">
-        <v>104.4442634447755</v>
+        <v>76.28188462386893</v>
       </c>
       <c r="C251">
-        <v>105.2882276776264</v>
+        <v>76.18263610195383</v>
       </c>
       <c r="D251">
-        <v>-0.8439642328509507</v>
+        <v>0.0992485219151007</v>
       </c>
       <c r="E251" t="s">
         <v>67</v>
@@ -4856,13 +4856,13 @@
         <v>40</v>
       </c>
       <c r="B252">
-        <v>102.4800823929831</v>
+        <v>68.73197074151751</v>
       </c>
       <c r="C252">
-        <v>102.7164549359843</v>
+        <v>68.64345535038358</v>
       </c>
       <c r="D252">
-        <v>-0.2363725430011669</v>
+        <v>0.08851539113393869</v>
       </c>
       <c r="E252" t="s">
         <v>68</v>
@@ -4873,13 +4873,13 @@
         <v>40</v>
       </c>
       <c r="B253">
-        <v>94.77463638637404</v>
+        <v>76.94402380264111</v>
       </c>
       <c r="C253">
-        <v>94.72695081600537</v>
+        <v>76.84423452828818</v>
       </c>
       <c r="D253">
-        <v>0.04768557036867094</v>
+        <v>0.09978927435292917</v>
       </c>
       <c r="E253" t="s">
         <v>69</v>
@@ -4890,13 +4890,13 @@
         <v>41</v>
       </c>
       <c r="B254">
-        <v>100.6256491097889</v>
+        <v>74.23200579750389</v>
       </c>
       <c r="C254">
-        <v>100.6360390583657</v>
+        <v>74.13592319475448</v>
       </c>
       <c r="D254">
-        <v>-0.0103899485768153</v>
+        <v>0.09608260274940505</v>
       </c>
       <c r="E254" t="s">
         <v>63</v>
@@ -4907,13 +4907,13 @@
         <v>41</v>
       </c>
       <c r="B255">
-        <v>99.04917259345407</v>
+        <v>58.25831391885705</v>
       </c>
       <c r="C255">
-        <v>98.96840155582525</v>
+        <v>58.18504705617319</v>
       </c>
       <c r="D255">
-        <v>0.08077103762882132</v>
+        <v>0.07326686268385885</v>
       </c>
       <c r="E255" t="s">
         <v>64</v>
@@ -4924,13 +4924,13 @@
         <v>41</v>
       </c>
       <c r="B256">
-        <v>102.5241231844777</v>
+        <v>95.13740757903042</v>
       </c>
       <c r="C256">
-        <v>104.5741784919224</v>
+        <v>95.17042496672528</v>
       </c>
       <c r="D256">
-        <v>-2.050055307444723</v>
+        <v>-0.03301738769485496</v>
       </c>
       <c r="E256" t="s">
         <v>65</v>
@@ -4941,13 +4941,13 @@
         <v>41</v>
       </c>
       <c r="B257">
-        <v>94.71726128149932</v>
+        <v>68.26325208400755</v>
       </c>
       <c r="C257">
-        <v>94.64703895360701</v>
+        <v>68.17581978053957</v>
       </c>
       <c r="D257">
-        <v>0.07022232789230998</v>
+        <v>0.08743230346797759</v>
       </c>
       <c r="E257" t="s">
         <v>66</v>
@@ -4958,13 +4958,13 @@
         <v>41</v>
       </c>
       <c r="B258">
-        <v>105.868815597866</v>
+        <v>76.94860453353823</v>
       </c>
       <c r="C258">
-        <v>106.9374892292422</v>
+        <v>76.84869158070948</v>
       </c>
       <c r="D258">
-        <v>-1.068673631376271</v>
+        <v>0.09991295282874546</v>
       </c>
       <c r="E258" t="s">
         <v>67</v>
@@ -4975,13 +4975,13 @@
         <v>41</v>
       </c>
       <c r="B259">
-        <v>105.0466189391316</v>
+        <v>70.17507407437597</v>
       </c>
       <c r="C259">
-        <v>105.4916986506749</v>
+        <v>70.0846796378579</v>
       </c>
       <c r="D259">
-        <v>-0.4450797115432721</v>
+        <v>0.09039443651806778</v>
       </c>
       <c r="E259" t="s">
         <v>68</v>
@@ -4992,13 +4992,13 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>96.02025315965695</v>
+        <v>78.54505515660075</v>
       </c>
       <c r="C260">
-        <v>96.08539617565962</v>
+        <v>78.44292398439811</v>
       </c>
       <c r="D260">
-        <v>-0.06514301600267913</v>
+        <v>0.1021311722026468</v>
       </c>
       <c r="E260" t="s">
         <v>69</v>
@@ -5009,13 +5009,13 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>99.45270691600022</v>
+        <v>73.03929466835368</v>
       </c>
       <c r="C261">
-        <v>99.44859746239956</v>
+        <v>72.94360526266836</v>
       </c>
       <c r="D261">
-        <v>0.004109453600662505</v>
+        <v>0.09568940568532014</v>
       </c>
       <c r="E261" t="s">
         <v>63</v>
@@ -5026,13 +5026,13 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>97.54826870540779</v>
+        <v>56.96841047811881</v>
       </c>
       <c r="C262">
-        <v>97.46566660422596</v>
+        <v>56.89576665715194</v>
       </c>
       <c r="D262">
-        <v>0.08260210118183409</v>
+        <v>0.07264382096687427</v>
       </c>
       <c r="E262" t="s">
         <v>64</v>
@@ -5043,13 +5043,13 @@
         <v>42</v>
       </c>
       <c r="B263">
-        <v>101.8483636570298</v>
+        <v>94.20172728071479</v>
       </c>
       <c r="C263">
-        <v>103.7262934324435</v>
+        <v>94.22117876614473</v>
       </c>
       <c r="D263">
-        <v>-1.877929775413691</v>
+        <v>-0.01945148542993991</v>
       </c>
       <c r="E263" t="s">
         <v>65</v>
@@ -5060,13 +5060,13 @@
         <v>42</v>
       </c>
       <c r="B264">
-        <v>93.60063888169931</v>
+        <v>66.91772860809277</v>
       </c>
       <c r="C264">
-        <v>93.52104600042912</v>
+        <v>66.83097953712112</v>
       </c>
       <c r="D264">
-        <v>0.07959288127018738</v>
+        <v>0.08674907097164919</v>
       </c>
       <c r="E264" t="s">
         <v>66</v>
@@ -5077,13 +5077,13 @@
         <v>42</v>
       </c>
       <c r="B265">
-        <v>104.5772541298888</v>
+        <v>75.89737972053631</v>
       </c>
       <c r="C265">
-        <v>105.6296341809036</v>
+        <v>75.79766201640906</v>
       </c>
       <c r="D265">
-        <v>-1.052380051014765</v>
+        <v>0.09971770412724368</v>
       </c>
       <c r="E265" t="s">
         <v>67</v>
@@ -5094,13 +5094,13 @@
         <v>42</v>
       </c>
       <c r="B266">
-        <v>103.5924900772574</v>
+        <v>69.02462297827815</v>
       </c>
       <c r="C266">
-        <v>104.0276605327914</v>
+        <v>68.93455120574288</v>
       </c>
       <c r="D266">
-        <v>-0.4351704555340206</v>
+        <v>0.09007177253526777</v>
       </c>
       <c r="E266" t="s">
         <v>68</v>
@@ -5111,13 +5111,13 @@
         <v>42</v>
       </c>
       <c r="B267">
-        <v>95.08943150847577</v>
+        <v>77.30449868538994</v>
       </c>
       <c r="C267">
-        <v>95.1262775135523</v>
+        <v>77.20283768824427</v>
       </c>
       <c r="D267">
-        <v>-0.03684600507652647</v>
+        <v>0.1016609971456717</v>
       </c>
       <c r="E267" t="s">
         <v>69</v>
@@ -5128,13 +5128,13 @@
         <v>43</v>
       </c>
       <c r="B268">
-        <v>105.0469210890513</v>
+        <v>87.51195400482506</v>
       </c>
       <c r="C268">
-        <v>104.934854189452</v>
+        <v>87.41435981388619</v>
       </c>
       <c r="D268">
-        <v>0.1120668995993412</v>
+        <v>0.09759419093886379</v>
       </c>
       <c r="E268" t="s">
         <v>63</v>
@@ -5145,13 +5145,13 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>104.9209317049088</v>
+        <v>75.75233835867607</v>
       </c>
       <c r="C269">
-        <v>104.815488544885</v>
+        <v>75.66873904458072</v>
       </c>
       <c r="D269">
-        <v>0.1054431600237251</v>
+        <v>0.08359931409535193</v>
       </c>
       <c r="E269" t="s">
         <v>64</v>
@@ -5162,13 +5162,13 @@
         <v>43</v>
       </c>
       <c r="B270">
-        <v>105.9899624052343</v>
+        <v>101.2638837174825</v>
       </c>
       <c r="C270">
-        <v>105.8701124222063</v>
+        <v>101.1499070695939</v>
       </c>
       <c r="D270">
-        <v>0.1198499830279758</v>
+        <v>0.1139766478886912</v>
       </c>
       <c r="E270" t="s">
         <v>65</v>
@@ -5179,13 +5179,13 @@
         <v>43</v>
       </c>
       <c r="B271">
-        <v>103.3132132430596</v>
+        <v>86.68846734287982</v>
       </c>
       <c r="C271">
-        <v>103.2004943468681</v>
+        <v>86.59192859281353</v>
       </c>
       <c r="D271">
-        <v>0.1127188961914811</v>
+        <v>0.09653875006628709</v>
       </c>
       <c r="E271" t="s">
         <v>66</v>
@@ -5196,13 +5196,13 @@
         <v>43</v>
       </c>
       <c r="B272">
-        <v>106.9721578817352</v>
+        <v>85.81476792395239</v>
       </c>
       <c r="C272">
-        <v>106.8619024607075</v>
+        <v>85.71911959689712</v>
       </c>
       <c r="D272">
-        <v>0.1102554210277304</v>
+        <v>0.09564832705527238</v>
       </c>
       <c r="E272" t="s">
         <v>67</v>
@@ -5213,13 +5213,13 @@
         <v>43</v>
       </c>
       <c r="B273">
-        <v>106.8177712164456</v>
+        <v>81.55065737274444</v>
       </c>
       <c r="C273">
-        <v>106.7097761331666</v>
+        <v>81.4600903610278</v>
       </c>
       <c r="D273">
-        <v>0.1079950832789507</v>
+        <v>0.09056701171664372</v>
       </c>
       <c r="E273" t="s">
         <v>68</v>
@@ -5230,13 +5230,13 @@
         <v>43</v>
       </c>
       <c r="B274">
-        <v>103.675941103797</v>
+        <v>93.93521899761591</v>
       </c>
       <c r="C274">
-        <v>103.55926104372</v>
+        <v>93.83004763642423</v>
       </c>
       <c r="D274">
-        <v>0.1166800600770728</v>
+        <v>0.1051713611916796</v>
       </c>
       <c r="E274" t="s">
         <v>69</v>

--- a/outputs/bond_results_tier2_oas.xlsx
+++ b/outputs/bond_results_tier2_oas.xlsx
@@ -623,13 +623,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>62.55112430626606</v>
+        <v>63.34016979395761</v>
       </c>
       <c r="C3">
-        <v>62.47574730567867</v>
+        <v>63.26360245584787</v>
       </c>
       <c r="D3">
-        <v>0.0753770005873875</v>
+        <v>0.07656733810974004</v>
       </c>
       <c r="E3" t="s">
         <v>64</v>
@@ -640,13 +640,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>99.88602801317066</v>
+        <v>98.57419652161781</v>
       </c>
       <c r="C4">
-        <v>99.9094013158531</v>
+        <v>98.50691292023195</v>
       </c>
       <c r="D4">
-        <v>-0.02337330268244386</v>
+        <v>0.06728360138585288</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -657,13 +657,13 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>72.81859329746192</v>
+        <v>73.36227826110105</v>
       </c>
       <c r="C5">
-        <v>72.72898903587709</v>
+        <v>73.2719020451764</v>
       </c>
       <c r="D5">
-        <v>0.08960426158482448</v>
+        <v>0.09037621592464973</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -674,13 +674,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>81.32835344913367</v>
+        <v>80.90107005226439</v>
       </c>
       <c r="C6">
-        <v>81.22620470161775</v>
+        <v>80.79941649070467</v>
       </c>
       <c r="D6">
-        <v>0.1021487475159262</v>
+        <v>0.1016535615597149</v>
       </c>
       <c r="E6" t="s">
         <v>67</v>
@@ -691,13 +691,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>74.46635902185859</v>
+        <v>74.43596492462602</v>
       </c>
       <c r="C7">
-        <v>74.3737790519146</v>
+        <v>74.34339778604686</v>
       </c>
       <c r="D7">
-        <v>0.09257996994399775</v>
+        <v>0.09256713857915599</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
@@ -708,13 +708,13 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>83.22752315091005</v>
+        <v>83.2600690981117</v>
       </c>
       <c r="C8">
-        <v>83.12311314704344</v>
+        <v>83.15564520538081</v>
       </c>
       <c r="D8">
-        <v>0.1044100038666045</v>
+        <v>0.1044238927308925</v>
       </c>
       <c r="E8" t="s">
         <v>69</v>
@@ -742,13 +742,13 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>75.01159072882399</v>
+        <v>75.03330603065312</v>
       </c>
       <c r="C10">
-        <v>74.92789141620285</v>
+        <v>74.94956089270715</v>
       </c>
       <c r="D10">
-        <v>0.08369931262113539</v>
+        <v>0.08374513794596794</v>
       </c>
       <c r="E10" t="s">
         <v>64</v>
@@ -759,13 +759,13 @@
         <v>6</v>
       </c>
       <c r="B11">
-        <v>100.8895759068823</v>
+        <v>100.8512608725165</v>
       </c>
       <c r="C11">
-        <v>100.7748317904294</v>
+        <v>100.7365841588359</v>
       </c>
       <c r="D11">
-        <v>0.1147441164529397</v>
+        <v>0.1146767136805806</v>
       </c>
       <c r="E11" t="s">
         <v>65</v>
@@ -776,13 +776,13 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>85.96046271672296</v>
+        <v>85.99968940384476</v>
       </c>
       <c r="C12">
-        <v>85.86372331766567</v>
+        <v>85.90290791572096</v>
       </c>
       <c r="D12">
-        <v>0.09673939905728446</v>
+        <v>0.09678148812379561</v>
       </c>
       <c r="E12" t="s">
         <v>66</v>
@@ -793,13 +793,13 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>85.32664861938335</v>
+        <v>85.29564603735928</v>
       </c>
       <c r="C13">
-        <v>85.23049714258354</v>
+        <v>85.19952411315292</v>
       </c>
       <c r="D13">
-        <v>0.09615147679980396</v>
+        <v>0.09612192420635779</v>
       </c>
       <c r="E13" t="s">
         <v>67</v>
@@ -810,13 +810,13 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>80.98994465457615</v>
+        <v>80.97660266628367</v>
       </c>
       <c r="C14">
-        <v>80.89900034277123</v>
+        <v>80.8856624815361</v>
       </c>
       <c r="D14">
-        <v>0.09094431180491824</v>
+        <v>0.09094018474756638</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
@@ -827,13 +827,13 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>93.31047777482208</v>
+        <v>93.32446317713837</v>
       </c>
       <c r="C15">
-        <v>93.20491656666901</v>
+        <v>93.21889753467545</v>
       </c>
       <c r="D15">
-        <v>0.1055612081530626</v>
+        <v>0.1055656424629206</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -861,13 +861,13 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>72.15720106325075</v>
+        <v>73.16001507507673</v>
       </c>
       <c r="C17">
-        <v>72.06982043446787</v>
+        <v>73.07104842573644</v>
       </c>
       <c r="D17">
-        <v>0.08738062878288133</v>
+        <v>0.08896664934029275</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>123.1947224060987</v>
+        <v>122.1394919694088</v>
       </c>
       <c r="C18">
-        <v>131.5684974482242</v>
+        <v>129.1953121211816</v>
       </c>
       <c r="D18">
-        <v>-8.373775042125473</v>
+        <v>-7.05582015177275</v>
       </c>
       <c r="E18" t="s">
         <v>65</v>
@@ -895,13 +895,13 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>84.38312280669099</v>
+        <v>85.7943923699931</v>
       </c>
       <c r="C19">
-        <v>84.27871832441537</v>
+        <v>85.68822425377616</v>
       </c>
       <c r="D19">
-        <v>0.1044044822756263</v>
+        <v>0.1061681162169492</v>
       </c>
       <c r="E19" t="s">
         <v>66</v>
@@ -912,13 +912,13 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>101.0739672670428</v>
+        <v>100.4063255310315</v>
       </c>
       <c r="C20">
-        <v>103.7493911069637</v>
+        <v>102.4127438175135</v>
       </c>
       <c r="D20">
-        <v>-2.675423839920924</v>
+        <v>-2.006418286482003</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
@@ -929,13 +929,13 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>91.35313935204866</v>
+        <v>91.31870321484155</v>
       </c>
       <c r="C21">
-        <v>91.63397321133549</v>
+        <v>91.59955250823691</v>
       </c>
       <c r="D21">
-        <v>-0.2808338592868296</v>
+        <v>-0.280849293395363</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
@@ -946,13 +946,13 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>100.7371193000324</v>
+        <v>100.7741696367547</v>
       </c>
       <c r="C22">
-        <v>100.6852561861928</v>
+        <v>100.722289655168</v>
       </c>
       <c r="D22">
-        <v>0.05186311383967279</v>
+        <v>0.05187998158672258</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
@@ -980,13 +980,13 @@
         <v>8</v>
       </c>
       <c r="B24">
-        <v>72.32284012738599</v>
+        <v>73.32533869041558</v>
       </c>
       <c r="C24">
-        <v>72.23542814589148</v>
+        <v>73.23634164617658</v>
       </c>
       <c r="D24">
-        <v>0.08741198149451179</v>
+        <v>0.08899704423899379</v>
       </c>
       <c r="E24" t="s">
         <v>64</v>
@@ -997,13 +997,13 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>123.2815701511858</v>
+        <v>122.2386764833912</v>
       </c>
       <c r="C25">
-        <v>131.6775611695413</v>
+        <v>129.3079944035326</v>
       </c>
       <c r="D25">
-        <v>-8.395991018355446</v>
+        <v>-7.069317920141415</v>
       </c>
       <c r="E25" t="s">
         <v>65</v>
@@ -1014,13 +1014,13 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>84.54807156169649</v>
+        <v>85.95744130300061</v>
       </c>
       <c r="C26">
-        <v>84.44363624581592</v>
+        <v>85.85124637533804</v>
       </c>
       <c r="D26">
-        <v>0.1044353158805649</v>
+        <v>0.1061949276625711</v>
       </c>
       <c r="E26" t="s">
         <v>66</v>
@@ -1031,13 +1031,13 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>101.1981675639944</v>
+        <v>100.5348722761798</v>
       </c>
       <c r="C27">
-        <v>103.8840628139921</v>
+        <v>102.5502107518638</v>
       </c>
       <c r="D27">
-        <v>-2.685895249997685</v>
+        <v>-2.015338475683947</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
@@ -1048,13 +1048,13 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>91.49980348368406</v>
+        <v>91.46530491861044</v>
       </c>
       <c r="C28">
-        <v>91.78313723321827</v>
+        <v>91.74865411998088</v>
       </c>
       <c r="D28">
-        <v>-0.2833337495342079</v>
+        <v>-0.2833492013704415</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
@@ -1065,13 +1065,13 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>100.8892387842838</v>
+        <v>100.9263533288769</v>
       </c>
       <c r="C29">
-        <v>100.8375153602018</v>
+        <v>100.8746130156137</v>
       </c>
       <c r="D29">
-        <v>0.05172342408204145</v>
+        <v>0.05174031326323814</v>
       </c>
       <c r="E29" t="s">
         <v>69</v>
@@ -1099,13 +1099,13 @@
         <v>9</v>
       </c>
       <c r="B31">
-        <v>72.40796092102532</v>
+        <v>73.41037882937765</v>
       </c>
       <c r="C31">
-        <v>72.32054186128596</v>
+        <v>73.32137458039705</v>
       </c>
       <c r="D31">
-        <v>0.0874190597393607</v>
+        <v>0.08900424898060066</v>
       </c>
       <c r="E31" t="s">
         <v>64</v>
@@ -1116,13 +1116,13 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>123.3311600615986</v>
+        <v>122.2953547634925</v>
       </c>
       <c r="C32">
-        <v>131.7460478365371</v>
+        <v>129.3774353419545</v>
       </c>
       <c r="D32">
-        <v>-8.414887774938521</v>
+        <v>-7.082080578462083</v>
       </c>
       <c r="E32" t="s">
         <v>65</v>
@@ -1133,13 +1133,13 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>84.63247963118317</v>
+        <v>86.04141910664816</v>
       </c>
       <c r="C33">
-        <v>84.52803741034249</v>
+        <v>85.93521531143489</v>
       </c>
       <c r="D33">
-        <v>0.1044422208406814</v>
+        <v>0.1062037952132755</v>
       </c>
       <c r="E33" t="s">
         <v>66</v>
@@ -1150,13 +1150,13 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>101.2683335930186</v>
+        <v>100.6069685115668</v>
       </c>
       <c r="C34">
-        <v>103.960353938079</v>
+        <v>102.6271651829572</v>
       </c>
       <c r="D34">
-        <v>-2.692020345060413</v>
+        <v>-2.020196671390323</v>
       </c>
       <c r="E34" t="s">
         <v>67</v>
@@ -1167,13 +1167,13 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>91.57952192813079</v>
+        <v>91.54488030084367</v>
       </c>
       <c r="C35">
-        <v>91.86359828908215</v>
+        <v>91.82897216852442</v>
       </c>
       <c r="D35">
-        <v>-0.2840763609513601</v>
+        <v>-0.2840918676807433</v>
       </c>
       <c r="E35" t="s">
         <v>68</v>
@@ -1184,13 +1184,13 @@
         <v>9</v>
       </c>
       <c r="B36">
-        <v>100.9698128120773</v>
+        <v>101.0070792462293</v>
       </c>
       <c r="C36">
-        <v>100.9180376975664</v>
+        <v>100.9552871817401</v>
       </c>
       <c r="D36">
-        <v>0.05177511451091732</v>
+        <v>0.05179206448924845</v>
       </c>
       <c r="E36" t="s">
         <v>69</v>
@@ -1218,13 +1218,13 @@
         <v>10</v>
       </c>
       <c r="B38">
-        <v>79.01753819654715</v>
+        <v>78.84230452278327</v>
       </c>
       <c r="C38">
-        <v>78.93884863338364</v>
+        <v>78.76378348902765</v>
       </c>
       <c r="D38">
-        <v>0.07868956316350761</v>
+        <v>0.07852103375562081</v>
       </c>
       <c r="E38" t="s">
         <v>64</v>
@@ -1235,13 +1235,13 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>98.89597929644924</v>
+        <v>99.1137789381423</v>
       </c>
       <c r="C39">
-        <v>98.79667304354521</v>
+        <v>99.01426042210477</v>
       </c>
       <c r="D39">
-        <v>0.09930625290402872</v>
+        <v>0.09951851603753425</v>
       </c>
       <c r="E39" t="s">
         <v>65</v>
@@ -1252,13 +1252,13 @@
         <v>10</v>
       </c>
       <c r="B40">
-        <v>89.15278566485262</v>
+        <v>89.10696596051547</v>
       </c>
       <c r="C40">
-        <v>89.06364916649731</v>
+        <v>89.0178821029557</v>
       </c>
       <c r="D40">
-        <v>0.0891364983553018</v>
+        <v>0.08908385755977122</v>
       </c>
       <c r="E40" t="s">
         <v>66</v>
@@ -1269,13 +1269,13 @@
         <v>10</v>
       </c>
       <c r="B41">
-        <v>85.6407876441604</v>
+        <v>85.66500795065281</v>
       </c>
       <c r="C41">
-        <v>85.55517390949241</v>
+        <v>85.5793624016481</v>
       </c>
       <c r="D41">
-        <v>0.08561373466798727</v>
+        <v>0.08564554900470966</v>
       </c>
       <c r="E41" t="s">
         <v>67</v>
@@ -1286,13 +1286,13 @@
         <v>10</v>
       </c>
       <c r="B42">
-        <v>82.42394512894987</v>
+        <v>82.41010199890407</v>
       </c>
       <c r="C42">
-        <v>82.34167050512636</v>
+        <v>82.32783250958995</v>
       </c>
       <c r="D42">
-        <v>0.08227462382350836</v>
+        <v>0.08226948931411471</v>
       </c>
       <c r="E42" t="s">
         <v>68</v>
@@ -1303,13 +1303,13 @@
         <v>10</v>
       </c>
       <c r="B43">
-        <v>94.76646612471112</v>
+        <v>94.78117370857986</v>
       </c>
       <c r="C43">
-        <v>94.67150347292613</v>
+        <v>94.68620558363493</v>
       </c>
       <c r="D43">
-        <v>0.0949626517849822</v>
+        <v>0.09496812494492701</v>
       </c>
       <c r="E43" t="s">
         <v>69</v>
@@ -1337,13 +1337,13 @@
         <v>11</v>
       </c>
       <c r="B45">
-        <v>77.03818280215367</v>
+        <v>76.94096988038916</v>
       </c>
       <c r="C45">
-        <v>76.95635380539592</v>
+        <v>76.85923040090063</v>
       </c>
       <c r="D45">
-        <v>0.08182899675774991</v>
+        <v>0.08173947948853311</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
@@ -1354,13 +1354,13 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>99.74069203692518</v>
+        <v>99.86161452445853</v>
       </c>
       <c r="C46">
-        <v>99.63346682974144</v>
+        <v>99.75427432056182</v>
       </c>
       <c r="D46">
-        <v>0.1072252071837454</v>
+        <v>0.1073402038967117</v>
       </c>
       <c r="E46" t="s">
         <v>65</v>
@@ -1371,13 +1371,13 @@
         <v>11</v>
       </c>
       <c r="B47">
-        <v>87.69574114649237</v>
+        <v>87.6865299359411</v>
       </c>
       <c r="C47">
-        <v>87.60208901737445</v>
+        <v>87.59289384743944</v>
       </c>
       <c r="D47">
-        <v>0.09365212911791332</v>
+        <v>0.09363608850165406</v>
       </c>
       <c r="E47" t="s">
         <v>66</v>
@@ -1388,13 +1388,13 @@
         <v>11</v>
       </c>
       <c r="B48">
-        <v>85.2911519355945</v>
+        <v>85.29115221602724</v>
       </c>
       <c r="C48">
-        <v>85.20000823323899</v>
+        <v>85.20000042177021</v>
       </c>
       <c r="D48">
-        <v>0.0911437023555095</v>
+        <v>0.09115179425702991</v>
       </c>
       <c r="E48" t="s">
         <v>67</v>
@@ -1405,13 +1405,13 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <v>81.56129064794052</v>
+        <v>81.54503136638495</v>
       </c>
       <c r="C49">
-        <v>81.47432385688894</v>
+        <v>81.45807084730674</v>
       </c>
       <c r="D49">
-        <v>0.08696679105158012</v>
+        <v>0.0869605190782039</v>
       </c>
       <c r="E49" t="s">
         <v>68</v>
@@ -1422,13 +1422,13 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>94.13305533124489</v>
+        <v>94.15037749128069</v>
       </c>
       <c r="C50">
-        <v>94.03219659762779</v>
+        <v>94.049512049204</v>
       </c>
       <c r="D50">
-        <v>0.1008587336171018</v>
+        <v>0.1008654420766959</v>
       </c>
       <c r="E50" t="s">
         <v>69</v>
@@ -1456,13 +1456,13 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>82.44210559726139</v>
+        <v>82.81602187334356</v>
       </c>
       <c r="C52">
-        <v>82.34407796277968</v>
+        <v>82.71743114124133</v>
       </c>
       <c r="D52">
-        <v>0.09802763448170992</v>
+        <v>0.09859073210222391</v>
       </c>
       <c r="E52" t="s">
         <v>64</v>
@@ -1473,13 +1473,13 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>105.1128245192902</v>
+        <v>105.4908939437536</v>
       </c>
       <c r="C53">
-        <v>119.2978931893979</v>
+        <v>118.6865860639606</v>
       </c>
       <c r="D53">
-        <v>-14.18506867010773</v>
+        <v>-13.19569212020704</v>
       </c>
       <c r="E53" t="s">
         <v>65</v>
@@ -1490,13 +1490,13 @@
         <v>12</v>
       </c>
       <c r="B54">
-        <v>95.44010060775334</v>
+        <v>95.69715566890928</v>
       </c>
       <c r="C54">
-        <v>95.33616857135027</v>
+        <v>95.59405766849781</v>
       </c>
       <c r="D54">
-        <v>0.1039320364030658</v>
+        <v>0.1030980004114639</v>
       </c>
       <c r="E54" t="s">
         <v>66</v>
@@ -1507,13 +1507,13 @@
         <v>12</v>
       </c>
       <c r="B55">
-        <v>98.19477500788254</v>
+        <v>98.01465036988375</v>
       </c>
       <c r="C55">
-        <v>98.94121528148678</v>
+        <v>98.74748079725748</v>
       </c>
       <c r="D55">
-        <v>-0.7464402736042359</v>
+        <v>-0.7328304273737274</v>
       </c>
       <c r="E55" t="s">
         <v>67</v>
@@ -1524,13 +1524,13 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>92.5874634322206</v>
+        <v>92.55242456610313</v>
       </c>
       <c r="C56">
-        <v>92.50554732150455</v>
+        <v>92.47635164178874</v>
       </c>
       <c r="D56">
-        <v>0.08191611071605109</v>
+        <v>0.0760729243143885</v>
       </c>
       <c r="E56" t="s">
         <v>68</v>
@@ -1541,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>104.1750033034132</v>
+        <v>104.3386574389924</v>
       </c>
       <c r="C57">
-        <v>105.7540226638049</v>
+        <v>105.785783235108</v>
       </c>
       <c r="D57">
-        <v>-1.579019360391698</v>
+        <v>-1.447125796115543</v>
       </c>
       <c r="E57" t="s">
         <v>69</v>
@@ -1575,13 +1575,13 @@
         <v>13</v>
       </c>
       <c r="B59">
-        <v>83.3694309271886</v>
+        <v>83.71008709515908</v>
       </c>
       <c r="C59">
-        <v>83.27133504588286</v>
+        <v>83.61147406985656</v>
       </c>
       <c r="D59">
-        <v>0.09809588130573843</v>
+        <v>0.09861302530252658</v>
       </c>
       <c r="E59" t="s">
         <v>64</v>
@@ -1592,13 +1592,13 @@
         <v>13</v>
       </c>
       <c r="B60">
-        <v>105.2454230198436</v>
+        <v>105.5920839796043</v>
       </c>
       <c r="C60">
-        <v>119.7022230878312</v>
+        <v>119.1460400258675</v>
       </c>
       <c r="D60">
-        <v>-14.45680006798756</v>
+        <v>-13.5539560462632</v>
       </c>
       <c r="E60" t="s">
         <v>65</v>
@@ -1609,13 +1609,13 @@
         <v>13</v>
       </c>
       <c r="B61">
-        <v>96.34536974466447</v>
+        <v>96.58436819672279</v>
       </c>
       <c r="C61">
-        <v>96.24090065435361</v>
+        <v>96.48025477866942</v>
       </c>
       <c r="D61">
-        <v>0.1044690903108574</v>
+        <v>0.1041134180533732</v>
       </c>
       <c r="E61" t="s">
         <v>66</v>
@@ -1626,13 +1626,13 @@
         <v>13</v>
       </c>
       <c r="B62">
-        <v>98.8739916535918</v>
+        <v>98.7012646695962</v>
       </c>
       <c r="C62">
-        <v>99.52605539793429</v>
+        <v>99.34578045075077</v>
       </c>
       <c r="D62">
-        <v>-0.6520637443424846</v>
+        <v>-0.644515781154567</v>
       </c>
       <c r="E62" t="s">
         <v>67</v>
@@ -1643,13 +1643,13 @@
         <v>13</v>
       </c>
       <c r="B63">
-        <v>93.28706407228421</v>
+        <v>93.25223353613731</v>
       </c>
       <c r="C63">
-        <v>93.19645687702705</v>
+        <v>93.16602179118541</v>
       </c>
       <c r="D63">
-        <v>0.09060719525716365</v>
+        <v>0.08621174495189621</v>
       </c>
       <c r="E63" t="s">
         <v>68</v>
@@ -1660,13 +1660,13 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>104.6205569960759</v>
+        <v>104.7834777442241</v>
       </c>
       <c r="C64">
-        <v>106.5181559736313</v>
+        <v>106.5511506961706</v>
       </c>
       <c r="D64">
-        <v>-1.897598977555376</v>
+        <v>-1.767672951946466</v>
       </c>
       <c r="E64" t="s">
         <v>69</v>
@@ -1694,13 +1694,13 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>83.42497986085765</v>
+        <v>83.76372136600092</v>
       </c>
       <c r="C66">
-        <v>83.32688857018495</v>
+        <v>83.66511553908987</v>
       </c>
       <c r="D66">
-        <v>0.09809129067269851</v>
+        <v>0.09860582691105435</v>
       </c>
       <c r="E66" t="s">
         <v>64</v>
@@ -1711,13 +1711,13 @@
         <v>14</v>
       </c>
       <c r="B67">
-        <v>105.2261459876978</v>
+        <v>105.568653199339</v>
       </c>
       <c r="C67">
-        <v>119.7261618004958</v>
+        <v>119.17311512392</v>
       </c>
       <c r="D67">
-        <v>-14.50001581279803</v>
+        <v>-13.60446192458103</v>
       </c>
       <c r="E67" t="s">
         <v>65</v>
@@ -1728,13 +1728,13 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>96.39878114013763</v>
+        <v>96.63674048862968</v>
       </c>
       <c r="C68">
-        <v>96.29404369846223</v>
+        <v>96.5323188200731</v>
       </c>
       <c r="D68">
-        <v>0.1047374416753968</v>
+        <v>0.1044216685565829</v>
       </c>
       <c r="E68" t="s">
         <v>66</v>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="B69">
-        <v>98.92087215249826</v>
+        <v>98.74873191723651</v>
       </c>
       <c r="C69">
-        <v>99.56161114980507</v>
+        <v>99.38212623982817</v>
       </c>
       <c r="D69">
-        <v>-0.6407389973068121</v>
+        <v>-0.6333943225916556</v>
       </c>
       <c r="E69" t="s">
         <v>67</v>
@@ -1762,13 +1762,13 @@
         <v>14</v>
       </c>
       <c r="B70">
-        <v>93.32996133861703</v>
+        <v>93.29527137514538</v>
       </c>
       <c r="C70">
-        <v>93.23830829230479</v>
+        <v>93.20783841120564</v>
       </c>
       <c r="D70">
-        <v>0.09165304631223137</v>
+        <v>0.0874329639397331</v>
       </c>
       <c r="E70" t="s">
         <v>68</v>
@@ -1779,13 +1779,13 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>104.6331796025454</v>
+        <v>104.7954459734264</v>
       </c>
       <c r="C71">
-        <v>106.5627999419577</v>
+        <v>106.5958213787489</v>
       </c>
       <c r="D71">
-        <v>-1.929620339412224</v>
+        <v>-1.800375405322569</v>
       </c>
       <c r="E71" t="s">
         <v>69</v>
@@ -1813,13 +1813,13 @@
         <v>15</v>
       </c>
       <c r="B73">
-        <v>58.03336271275611</v>
+        <v>58.62966561048167</v>
       </c>
       <c r="C73">
-        <v>57.96018511178455</v>
+        <v>58.55562741866084</v>
       </c>
       <c r="D73">
-        <v>0.07317760097156167</v>
+        <v>0.07403819182083282</v>
       </c>
       <c r="E73" t="s">
         <v>64</v>
@@ -1830,13 +1830,13 @@
         <v>15</v>
       </c>
       <c r="B74">
-        <v>91.04101077344455</v>
+        <v>90.05768349388133</v>
       </c>
       <c r="C74">
-        <v>90.92876116645532</v>
+        <v>89.94253343742584</v>
       </c>
       <c r="D74">
-        <v>0.1122496069892378</v>
+        <v>0.1151500564554908</v>
       </c>
       <c r="E74" t="s">
         <v>65</v>
@@ -1847,13 +1847,13 @@
         <v>15</v>
       </c>
       <c r="B75">
-        <v>67.94005089009451</v>
+        <v>68.30858423561104</v>
       </c>
       <c r="C75">
-        <v>67.85325367027372</v>
+        <v>68.22127810194947</v>
       </c>
       <c r="D75">
-        <v>0.08679721982079514</v>
+        <v>0.08730613366157058</v>
       </c>
       <c r="E75" t="s">
         <v>66</v>
@@ -1864,13 +1864,13 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>74.03763430324058</v>
+        <v>73.76176750007559</v>
       </c>
       <c r="C76">
-        <v>73.94206790641491</v>
+        <v>73.66657683770188</v>
       </c>
       <c r="D76">
-        <v>0.09556639682567436</v>
+        <v>0.09519066237371021</v>
       </c>
       <c r="E76" t="s">
         <v>67</v>
@@ -1881,13 +1881,13 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>68.12929791451522</v>
+        <v>68.1142835451779</v>
       </c>
       <c r="C77">
-        <v>68.04196017714062</v>
+        <v>68.02695054345531</v>
       </c>
       <c r="D77">
-        <v>0.08733773737459671</v>
+        <v>0.08733300172258396</v>
       </c>
       <c r="E77" t="s">
         <v>68</v>
@@ -1898,13 +1898,13 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>77.18175437109248</v>
+        <v>77.19752762486092</v>
       </c>
       <c r="C78">
-        <v>77.0820975852088</v>
+        <v>77.09786578828293</v>
       </c>
       <c r="D78">
-        <v>0.09965678588368121</v>
+        <v>0.09966183657799377</v>
       </c>
       <c r="E78" t="s">
         <v>69</v>
@@ -1932,13 +1932,13 @@
         <v>16</v>
       </c>
       <c r="B80">
-        <v>74.52274330135653</v>
+        <v>74.55419715792451</v>
       </c>
       <c r="C80">
-        <v>74.4390000592737</v>
+        <v>74.47039489372681</v>
       </c>
       <c r="D80">
-        <v>0.08374324208283213</v>
+        <v>0.08380226419770054</v>
       </c>
       <c r="E80" t="s">
         <v>64</v>
@@ -1949,13 +1949,13 @@
         <v>16</v>
       </c>
       <c r="B81">
-        <v>100.6335600020557</v>
+        <v>100.5810528613585</v>
       </c>
       <c r="C81">
-        <v>100.5183447762463</v>
+        <v>100.4659238567334</v>
       </c>
       <c r="D81">
-        <v>0.1152152258094219</v>
+        <v>0.1151290046250892</v>
       </c>
       <c r="E81" t="s">
         <v>65</v>
@@ -1966,13 +1966,13 @@
         <v>16</v>
       </c>
       <c r="B82">
-        <v>85.47598766225333</v>
+        <v>85.5207596547053</v>
       </c>
       <c r="C82">
-        <v>85.37914416970932</v>
+        <v>85.42386762148477</v>
       </c>
       <c r="D82">
-        <v>0.0968434925440107</v>
+        <v>0.0968920332205272</v>
       </c>
       <c r="E82" t="s">
         <v>66</v>
@@ -1983,13 +1983,13 @@
         <v>16</v>
       </c>
       <c r="B83">
-        <v>85.00137954412477</v>
+        <v>84.96623674114498</v>
       </c>
       <c r="C83">
-        <v>84.90492278015843</v>
+        <v>84.86981408036499</v>
       </c>
       <c r="D83">
-        <v>0.09645676396634428</v>
+        <v>0.09642266077999295</v>
       </c>
       <c r="E83" t="s">
         <v>67</v>
@@ -2000,13 +2000,13 @@
         <v>16</v>
       </c>
       <c r="B84">
-        <v>80.6181396484771</v>
+        <v>80.60364191457228</v>
       </c>
       <c r="C84">
-        <v>80.52697109104169</v>
+        <v>80.51247804431407</v>
       </c>
       <c r="D84">
-        <v>0.09116855743540953</v>
+        <v>0.09116387025821382</v>
       </c>
       <c r="E84" t="s">
         <v>68</v>
@@ -2017,13 +2017,13 @@
         <v>16</v>
       </c>
       <c r="B85">
-        <v>92.89137999020053</v>
+        <v>92.90662244133209</v>
       </c>
       <c r="C85">
-        <v>92.78559395993679</v>
+        <v>92.80083138432894</v>
       </c>
       <c r="D85">
-        <v>0.1057860302637437</v>
+        <v>0.1057910570031453</v>
       </c>
       <c r="E85" t="s">
         <v>69</v>
@@ -2051,13 +2051,13 @@
         <v>17</v>
       </c>
       <c r="B87">
-        <v>87.40730075026894</v>
+        <v>88.09343694273259</v>
       </c>
       <c r="C87">
-        <v>87.30356668987594</v>
+        <v>87.98996855023987</v>
       </c>
       <c r="D87">
-        <v>0.103734060393009</v>
+        <v>0.1034683924927293</v>
       </c>
       <c r="E87" t="s">
         <v>64</v>
@@ -2068,13 +2068,13 @@
         <v>17</v>
       </c>
       <c r="B88">
-        <v>111.7205180043511</v>
+        <v>112.4103568497599</v>
       </c>
       <c r="C88">
-        <v>131.3979710671924</v>
+        <v>130.2055060833671</v>
       </c>
       <c r="D88">
-        <v>-19.67745306284131</v>
+        <v>-17.79514923360723</v>
       </c>
       <c r="E88" t="s">
         <v>65</v>
@@ -2085,13 +2085,13 @@
         <v>17</v>
       </c>
       <c r="B89">
-        <v>101.2925319955577</v>
+        <v>101.7237194586253</v>
       </c>
       <c r="C89">
-        <v>101.2928398897354</v>
+        <v>101.7582080332541</v>
       </c>
       <c r="D89">
-        <v>-0.0003078941776522015</v>
+        <v>-0.0344885746287531</v>
       </c>
       <c r="E89" t="s">
         <v>66</v>
@@ -2102,13 +2102,13 @@
         <v>17</v>
       </c>
       <c r="B90">
-        <v>102.3533590157611</v>
+        <v>102.1888761625142</v>
       </c>
       <c r="C90">
-        <v>108.0958413912315</v>
+        <v>107.7366201313917</v>
       </c>
       <c r="D90">
-        <v>-5.742482375470317</v>
+        <v>-5.547743968877569</v>
       </c>
       <c r="E90" t="s">
         <v>67</v>
@@ -2119,13 +2119,13 @@
         <v>17</v>
       </c>
       <c r="B91">
-        <v>98.85607177674574</v>
+        <v>98.72159344539568</v>
       </c>
       <c r="C91">
-        <v>100.2469798380881</v>
+        <v>100.2111485123645</v>
       </c>
       <c r="D91">
-        <v>-1.390908061342316</v>
+        <v>-1.489555066968776</v>
       </c>
       <c r="E91" t="s">
         <v>68</v>
@@ -2136,13 +2136,13 @@
         <v>17</v>
       </c>
       <c r="B92">
-        <v>110.4284727252258</v>
+        <v>110.6291481348876</v>
       </c>
       <c r="C92">
-        <v>113.6163865913574</v>
+        <v>113.6552054974807</v>
       </c>
       <c r="D92">
-        <v>-3.187913866131609</v>
+        <v>-3.026057362593079</v>
       </c>
       <c r="E92" t="s">
         <v>69</v>
@@ -2170,13 +2170,13 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>87.80575262223469</v>
+        <v>88.4777508710103</v>
       </c>
       <c r="C94">
-        <v>87.70194630143386</v>
+        <v>88.37418992314157</v>
       </c>
       <c r="D94">
-        <v>0.1038063208008282</v>
+        <v>0.1035609478687292</v>
       </c>
       <c r="E94" t="s">
         <v>64</v>
@@ -2187,13 +2187,13 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>111.8434402356179</v>
+        <v>112.531105728568</v>
       </c>
       <c r="C95">
-        <v>131.5887529707466</v>
+        <v>130.4228390065322</v>
       </c>
       <c r="D95">
-        <v>-19.74531273512872</v>
+        <v>-17.89173327796421</v>
       </c>
       <c r="E95" t="s">
         <v>65</v>
@@ -2204,13 +2204,13 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>101.6817180019322</v>
+        <v>102.106614920987</v>
       </c>
       <c r="C96">
-        <v>101.6924472356592</v>
+        <v>102.1496411407902</v>
       </c>
       <c r="D96">
-        <v>-0.01072923372707635</v>
+        <v>-0.04302621980319543</v>
       </c>
       <c r="E96" t="s">
         <v>66</v>
@@ -2221,13 +2221,13 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>102.6387658809387</v>
+        <v>102.4686903782579</v>
       </c>
       <c r="C97">
-        <v>108.3506427544998</v>
+        <v>107.9980610761059</v>
       </c>
       <c r="D97">
-        <v>-5.71187687356101</v>
+        <v>-5.529370697848051</v>
       </c>
       <c r="E97" t="s">
         <v>67</v>
@@ -2238,13 +2238,13 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>99.17365945398458</v>
+        <v>99.0358033995456</v>
       </c>
       <c r="C98">
-        <v>100.5464117099415</v>
+        <v>100.510222208397</v>
       </c>
       <c r="D98">
-        <v>-1.372752255956897</v>
+        <v>-1.474418808851425</v>
       </c>
       <c r="E98" t="s">
         <v>68</v>
@@ -2255,13 +2255,13 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>110.6546454799219</v>
+        <v>110.8857823769716</v>
       </c>
       <c r="C99">
-        <v>113.9634360361408</v>
+        <v>114.002589482156</v>
       </c>
       <c r="D99">
-        <v>-3.308790556218938</v>
+        <v>-3.116807105184421</v>
       </c>
       <c r="E99" t="s">
         <v>69</v>
@@ -2289,13 +2289,13 @@
         <v>19</v>
       </c>
       <c r="B101">
-        <v>61.74925750099757</v>
+        <v>62.12921944468621</v>
       </c>
       <c r="C101">
-        <v>61.67237646482638</v>
+        <v>62.05180049707972</v>
       </c>
       <c r="D101">
-        <v>0.07688103617119424</v>
+        <v>0.07741894760649615</v>
       </c>
       <c r="E101" t="s">
         <v>64</v>
@@ -2306,13 +2306,13 @@
         <v>19</v>
       </c>
       <c r="B102">
-        <v>92.26619357357418</v>
+        <v>91.66866334057599</v>
       </c>
       <c r="C102">
-        <v>92.14959007695178</v>
+        <v>91.55205331912201</v>
       </c>
       <c r="D102">
-        <v>0.1166034966224032</v>
+        <v>0.1166100214539796</v>
       </c>
       <c r="E102" t="s">
         <v>65</v>
@@ -2323,13 +2323,13 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>71.98898681556766</v>
+        <v>72.22093641283</v>
       </c>
       <c r="C103">
-        <v>71.89857142871456</v>
+        <v>72.13021348822164</v>
       </c>
       <c r="D103">
-        <v>0.09041538685309547</v>
+        <v>0.0907229246083574</v>
       </c>
       <c r="E103" t="s">
         <v>66</v>
@@ -2340,13 +2340,13 @@
         <v>19</v>
       </c>
       <c r="B104">
-        <v>75.82828646862804</v>
+        <v>75.6593362731233</v>
       </c>
       <c r="C104">
-        <v>75.73242640347435</v>
+        <v>75.56369560601223</v>
       </c>
       <c r="D104">
-        <v>0.09586006515368695</v>
+        <v>0.09564066711106989</v>
       </c>
       <c r="E104" t="s">
         <v>67</v>
@@ -2357,13 +2357,13 @@
         <v>19</v>
       </c>
       <c r="B105">
-        <v>70.4802307198062</v>
+        <v>70.46670906536259</v>
       </c>
       <c r="C105">
-        <v>70.39153828796204</v>
+        <v>70.37802101674168</v>
       </c>
       <c r="D105">
-        <v>0.08869243184416575</v>
+        <v>0.0886880486209094</v>
       </c>
       <c r="E105" t="s">
         <v>68</v>
@@ -2374,13 +2374,13 @@
         <v>19</v>
       </c>
       <c r="B106">
-        <v>80.59464889908031</v>
+        <v>80.60894348029684</v>
       </c>
       <c r="C106">
-        <v>80.49271022341516</v>
+        <v>80.50700020038066</v>
       </c>
       <c r="D106">
-        <v>0.1019386756651528</v>
+        <v>0.1019432799161848</v>
       </c>
       <c r="E106" t="s">
         <v>69</v>
@@ -2408,13 +2408,13 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>83.06603804171542</v>
+        <v>82.7405810609059</v>
       </c>
       <c r="C108">
-        <v>82.99124706397902</v>
+        <v>82.66608455455045</v>
       </c>
       <c r="D108">
-        <v>0.07479097773639864</v>
+        <v>0.07449650635544458</v>
       </c>
       <c r="E108" t="s">
         <v>64</v>
@@ -2425,13 +2425,13 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>99.84671822037885</v>
+        <v>100.239816013662</v>
       </c>
       <c r="C109">
-        <v>99.75631977431951</v>
+        <v>100.149060144737</v>
       </c>
       <c r="D109">
-        <v>0.09039844605933922</v>
+        <v>0.09075586892494414</v>
       </c>
       <c r="E109" t="s">
         <v>65</v>
@@ -2442,13 +2442,13 @@
         <v>20</v>
       </c>
       <c r="B110">
-        <v>92.55703404105563</v>
+        <v>92.46342322845922</v>
       </c>
       <c r="C110">
-        <v>92.4734550782</v>
+        <v>92.3799359772775</v>
       </c>
       <c r="D110">
-        <v>0.0835789628556256</v>
+        <v>0.0834872511817224</v>
       </c>
       <c r="E110" t="s">
         <v>66</v>
@@ -2459,13 +2459,13 @@
         <v>20</v>
       </c>
       <c r="B111">
-        <v>87.91269018384962</v>
+        <v>87.9672865899357</v>
       </c>
       <c r="C111">
-        <v>87.8333572991849</v>
+        <v>87.88789729118727</v>
       </c>
       <c r="D111">
-        <v>0.07933288466472277</v>
+        <v>0.07938929874842415</v>
       </c>
       <c r="E111" t="s">
         <v>67</v>
@@ -2476,13 +2476,13 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>85.23315400600768</v>
+        <v>85.2206801228694</v>
       </c>
       <c r="C112">
-        <v>85.15631507305359</v>
+        <v>85.1438456007137</v>
       </c>
       <c r="D112">
-        <v>0.0768389329540895</v>
+        <v>0.07683452215569275</v>
       </c>
       <c r="E112" t="s">
         <v>68</v>
@@ -2493,13 +2493,13 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>97.28785249768831</v>
+        <v>97.30106152300198</v>
       </c>
       <c r="C113">
-        <v>97.19987051384116</v>
+        <v>97.21307484893022</v>
       </c>
       <c r="D113">
-        <v>0.0879819838471434</v>
+        <v>0.08798667407175742</v>
       </c>
       <c r="E113" t="s">
         <v>69</v>
@@ -2527,13 +2527,13 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>61.93424235335238</v>
+        <v>62.30704397272733</v>
       </c>
       <c r="C115">
-        <v>61.85730390218247</v>
+        <v>62.22957820102193</v>
       </c>
       <c r="D115">
-        <v>0.07693845116990872</v>
+        <v>0.07746577170539837</v>
       </c>
       <c r="E115" t="s">
         <v>64</v>
@@ -2544,13 +2544,13 @@
         <v>21</v>
       </c>
       <c r="B116">
-        <v>92.3487582916725</v>
+        <v>91.76339687258108</v>
       </c>
       <c r="C116">
-        <v>92.23211076684602</v>
+        <v>91.64691531459009</v>
       </c>
       <c r="D116">
-        <v>0.116647524826476</v>
+        <v>0.1164815579909941</v>
       </c>
       <c r="E116" t="s">
         <v>65</v>
@@ -2561,13 +2561,13 @@
         <v>21</v>
       </c>
       <c r="B117">
-        <v>72.17379592564417</v>
+        <v>72.40119521270989</v>
       </c>
       <c r="C117">
-        <v>72.08333887085365</v>
+        <v>72.31043733729425</v>
       </c>
       <c r="D117">
-        <v>0.09045705479051946</v>
+        <v>0.0907578754156475</v>
       </c>
       <c r="E117" t="s">
         <v>66</v>
@@ -2578,13 +2578,13 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>75.94409481257482</v>
+        <v>75.77855007483015</v>
       </c>
       <c r="C118">
-        <v>75.8482972416972</v>
+        <v>75.68296686672701</v>
       </c>
       <c r="D118">
-        <v>0.09579757087762175</v>
+        <v>0.09558320810313603</v>
       </c>
       <c r="E118" t="s">
         <v>67</v>
@@ -2595,13 +2595,13 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>70.6174448253991</v>
+        <v>70.6039173400095</v>
       </c>
       <c r="C119">
-        <v>70.52877645990169</v>
+        <v>70.51525327021781</v>
       </c>
       <c r="D119">
-        <v>0.08866836549741208</v>
+        <v>0.08866406979169028</v>
       </c>
       <c r="E119" t="s">
         <v>68</v>
@@ -2612,13 +2612,13 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>80.75226418172353</v>
+        <v>80.76654629441867</v>
       </c>
       <c r="C120">
-        <v>80.65033566461204</v>
+        <v>80.66461326857325</v>
       </c>
       <c r="D120">
-        <v>0.1019285171114888</v>
+        <v>0.1019330258454261</v>
       </c>
       <c r="E120" t="s">
         <v>69</v>
@@ -2646,13 +2646,13 @@
         <v>22</v>
       </c>
       <c r="B122">
-        <v>83.42058544404867</v>
+        <v>83.07916072168442</v>
       </c>
       <c r="C122">
-        <v>83.34621642007366</v>
+        <v>83.00509851919202</v>
       </c>
       <c r="D122">
-        <v>0.07436902397500944</v>
+        <v>0.07406220249239936</v>
       </c>
       <c r="E122" t="s">
         <v>64</v>
@@ -2663,13 +2663,13 @@
         <v>22</v>
       </c>
       <c r="B123">
-        <v>99.94963949250752</v>
+        <v>100.3610188602472</v>
       </c>
       <c r="C123">
-        <v>99.86003168931548</v>
+        <v>100.271039656744</v>
       </c>
       <c r="D123">
-        <v>0.0896078031920382</v>
+        <v>0.0899792035032192</v>
       </c>
       <c r="E123" t="s">
         <v>65</v>
@@ -2680,13 +2680,13 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>92.84592684474728</v>
+        <v>92.74827540115585</v>
       </c>
       <c r="C124">
-        <v>92.76290617631039</v>
+        <v>92.66534950349538</v>
       </c>
       <c r="D124">
-        <v>0.08302066843688749</v>
+        <v>0.08292589766047342</v>
       </c>
       <c r="E124" t="s">
         <v>66</v>
@@ -2697,13 +2697,13 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>88.13076165466164</v>
+        <v>88.187882694179</v>
       </c>
       <c r="C125">
-        <v>88.0520172545196</v>
+        <v>88.10907992223278</v>
       </c>
       <c r="D125">
-        <v>0.07874440014204254</v>
+        <v>0.07880277194621499</v>
       </c>
       <c r="E125" t="s">
         <v>67</v>
@@ -2714,13 +2714,13 @@
         <v>22</v>
       </c>
       <c r="B126">
-        <v>85.4927219413932</v>
+        <v>85.48030382718271</v>
       </c>
       <c r="C126">
-        <v>85.41641135742789</v>
+        <v>85.40399747218811</v>
       </c>
       <c r="D126">
-        <v>0.07631058396530932</v>
+        <v>0.0763063549945997</v>
       </c>
       <c r="E126" t="s">
         <v>68</v>
@@ -2731,13 +2731,13 @@
         <v>22</v>
       </c>
       <c r="B127">
-        <v>97.50758148668559</v>
+        <v>97.52070080594902</v>
       </c>
       <c r="C127">
-        <v>97.42026012021527</v>
+        <v>97.4333749497074</v>
       </c>
       <c r="D127">
-        <v>0.08732136647032007</v>
+        <v>0.0873258562416197</v>
       </c>
       <c r="E127" t="s">
         <v>69</v>
@@ -2765,13 +2765,13 @@
         <v>23</v>
       </c>
       <c r="B129">
-        <v>83.31326464095062</v>
+        <v>82.97632936546883</v>
       </c>
       <c r="C129">
-        <v>83.23876996720584</v>
+        <v>82.90213808149691</v>
       </c>
       <c r="D129">
-        <v>0.07449467374478047</v>
+        <v>0.07419128397191344</v>
       </c>
       <c r="E129" t="s">
         <v>64</v>
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>99.91487487478186</v>
+        <v>100.3211289242305</v>
       </c>
       <c r="C130">
-        <v>99.82503595455172</v>
+        <v>100.2309224742214</v>
       </c>
       <c r="D130">
-        <v>0.08983892023013595</v>
+        <v>0.09020645000911998</v>
       </c>
       <c r="E130" t="s">
         <v>65</v>
@@ -2799,13 +2799,13 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>92.75807495766831</v>
+        <v>92.66156102281985</v>
       </c>
       <c r="C131">
-        <v>92.67488917980671</v>
+        <v>92.57846915662761</v>
       </c>
       <c r="D131">
-        <v>0.0831857778616012</v>
+        <v>0.08309186619224818</v>
       </c>
       <c r="E131" t="s">
         <v>66</v>
@@ -2816,13 +2816,13 @@
         <v>23</v>
       </c>
       <c r="B132">
-        <v>88.06235784183525</v>
+        <v>88.11876766943557</v>
       </c>
       <c r="C132">
-        <v>87.98344052788859</v>
+        <v>88.03979253793726</v>
       </c>
       <c r="D132">
-        <v>0.07891731394666124</v>
+        <v>0.0789751314983107</v>
       </c>
       <c r="E132" t="s">
         <v>67</v>
@@ -2833,13 +2833,13 @@
         <v>23</v>
       </c>
       <c r="B133">
-        <v>85.4123716239386</v>
+        <v>85.39993447582671</v>
       </c>
       <c r="C133">
-        <v>85.33590531201416</v>
+        <v>85.32347245677165</v>
       </c>
       <c r="D133">
-        <v>0.07646631192443465</v>
+        <v>0.07646201905505734</v>
       </c>
       <c r="E133" t="s">
         <v>68</v>
@@ -2850,13 +2850,13 @@
         <v>23</v>
       </c>
       <c r="B134">
-        <v>97.43968579297501</v>
+        <v>97.4528361250083</v>
       </c>
       <c r="C134">
-        <v>97.35217003628092</v>
+        <v>97.36531580827452</v>
       </c>
       <c r="D134">
-        <v>0.08751575669408851</v>
+        <v>0.08752031673378724</v>
       </c>
       <c r="E134" t="s">
         <v>69</v>
@@ -2884,13 +2884,13 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>92.06350190684641</v>
+        <v>91.49322888121138</v>
       </c>
       <c r="C136">
-        <v>92.0016913380222</v>
+        <v>91.4318065639886</v>
       </c>
       <c r="D136">
-        <v>0.06181056882421387</v>
+        <v>0.06142231722277813</v>
       </c>
       <c r="E136" t="s">
         <v>64</v>
@@ -2901,13 +2901,13 @@
         <v>24</v>
       </c>
       <c r="B137">
-        <v>102.9739067916901</v>
+        <v>103.6169386761022</v>
       </c>
       <c r="C137">
-        <v>102.9046273091696</v>
+        <v>103.5472208539859</v>
       </c>
       <c r="D137">
-        <v>0.06927948252048566</v>
+        <v>0.06971782211631705</v>
       </c>
       <c r="E137" t="s">
         <v>65</v>
@@ -2918,13 +2918,13 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>99.54917259078626</v>
+        <v>99.57986588588044</v>
       </c>
       <c r="C138">
-        <v>99.48225199018705</v>
+        <v>99.51292652809559</v>
       </c>
       <c r="D138">
-        <v>0.06692060059920379</v>
+        <v>0.06693935778484672</v>
       </c>
       <c r="E138" t="s">
         <v>66</v>
@@ -2935,13 +2935,13 @@
         <v>24</v>
       </c>
       <c r="B139">
-        <v>94.12114404978661</v>
+        <v>94.01758127709289</v>
       </c>
       <c r="C139">
-        <v>94.05791200236007</v>
+        <v>93.95441765585701</v>
       </c>
       <c r="D139">
-        <v>0.06323204742653843</v>
+        <v>0.06316362123587282</v>
       </c>
       <c r="E139" t="s">
         <v>67</v>
@@ -2952,13 +2952,13 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>92.432403777673</v>
+        <v>92.20714379804932</v>
       </c>
       <c r="C140">
-        <v>92.3703284949944</v>
+        <v>92.14521993696627</v>
       </c>
       <c r="D140">
-        <v>0.06207528267860596</v>
+        <v>0.06192386108304504</v>
       </c>
       <c r="E140" t="s">
         <v>68</v>
@@ -2969,13 +2969,13 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>102.5597969437173</v>
+        <v>102.810370837046</v>
       </c>
       <c r="C141">
-        <v>102.4908140007436</v>
+        <v>102.7412192030358</v>
       </c>
       <c r="D141">
-        <v>0.06898294297366192</v>
+        <v>0.06915163401019697</v>
       </c>
       <c r="E141" t="s">
         <v>69</v>
@@ -3003,13 +3003,13 @@
         <v>25</v>
       </c>
       <c r="B143">
-        <v>83.8145234874172</v>
+        <v>84.70057067636557</v>
       </c>
       <c r="C143">
-        <v>83.71204149443503</v>
+        <v>84.59788484862258</v>
       </c>
       <c r="D143">
-        <v>0.1024819929821774</v>
+        <v>0.1026858277429881</v>
       </c>
       <c r="E143" t="s">
         <v>64</v>
@@ -3020,13 +3020,13 @@
         <v>25</v>
       </c>
       <c r="B144">
-        <v>116.3320685192221</v>
+        <v>116.7680028816017</v>
       </c>
       <c r="C144">
-        <v>133.4855542927207</v>
+        <v>131.8276762695843</v>
       </c>
       <c r="D144">
-        <v>-17.15348577349859</v>
+        <v>-15.05967338798263</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
@@ -3037,13 +3037,13 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>97.81474237675549</v>
+        <v>98.53490924684324</v>
       </c>
       <c r="C145">
-        <v>97.71486564988814</v>
+        <v>98.45372470160355</v>
       </c>
       <c r="D145">
-        <v>0.09987672686735038</v>
+        <v>0.08118454523969376</v>
       </c>
       <c r="E145" t="s">
         <v>66</v>
@@ -3054,13 +3054,13 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>102.3058948620488</v>
+        <v>102.2558915492363</v>
       </c>
       <c r="C146">
-        <v>108.2535141248661</v>
+        <v>107.6599818003886</v>
       </c>
       <c r="D146">
-        <v>-5.947619262817383</v>
+        <v>-5.404090251152326</v>
       </c>
       <c r="E146" t="s">
         <v>67</v>
@@ -3071,13 +3071,13 @@
         <v>25</v>
       </c>
       <c r="B147">
-        <v>97.52558993793478</v>
+        <v>97.4915205804718</v>
       </c>
       <c r="C147">
-        <v>99.07974236843837</v>
+        <v>99.04569063777764</v>
       </c>
       <c r="D147">
-        <v>-1.554152430503592</v>
+        <v>-1.554170057305839</v>
       </c>
       <c r="E147" t="s">
         <v>68</v>
@@ -3088,13 +3088,13 @@
         <v>25</v>
       </c>
       <c r="B148">
-        <v>110.417367758813</v>
+        <v>110.4544347417514</v>
       </c>
       <c r="C148">
-        <v>111.6093708510414</v>
+        <v>111.6464184910672</v>
       </c>
       <c r="D148">
-        <v>-1.192003092228333</v>
+        <v>-1.191983749315739</v>
       </c>
       <c r="E148" t="s">
         <v>69</v>
@@ -3122,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="B150">
-        <v>75.01159072882399</v>
+        <v>75.03330603065312</v>
       </c>
       <c r="C150">
-        <v>74.92789141620285</v>
+        <v>74.94956089270715</v>
       </c>
       <c r="D150">
-        <v>0.08369931262113539</v>
+        <v>0.08374513794596794</v>
       </c>
       <c r="E150" t="s">
         <v>64</v>
@@ -3139,13 +3139,13 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>100.8895759068823</v>
+        <v>100.8512608725165</v>
       </c>
       <c r="C151">
-        <v>100.7748317904294</v>
+        <v>100.7365841588359</v>
       </c>
       <c r="D151">
-        <v>0.1147441164529397</v>
+        <v>0.1146767136805806</v>
       </c>
       <c r="E151" t="s">
         <v>65</v>
@@ -3156,13 +3156,13 @@
         <v>26</v>
       </c>
       <c r="B152">
-        <v>85.96046271672296</v>
+        <v>85.99968940384476</v>
       </c>
       <c r="C152">
-        <v>85.86372331766567</v>
+        <v>85.90290791572096</v>
       </c>
       <c r="D152">
-        <v>0.09673939905728446</v>
+        <v>0.09678148812379561</v>
       </c>
       <c r="E152" t="s">
         <v>66</v>
@@ -3173,13 +3173,13 @@
         <v>26</v>
       </c>
       <c r="B153">
-        <v>85.32664861938335</v>
+        <v>85.29564603735928</v>
       </c>
       <c r="C153">
-        <v>85.23049714258354</v>
+        <v>85.19952411315292</v>
       </c>
       <c r="D153">
-        <v>0.09615147679980396</v>
+        <v>0.09612192420635779</v>
       </c>
       <c r="E153" t="s">
         <v>67</v>
@@ -3190,13 +3190,13 @@
         <v>26</v>
       </c>
       <c r="B154">
-        <v>80.98994465457615</v>
+        <v>80.97660266628367</v>
       </c>
       <c r="C154">
-        <v>80.89900034277123</v>
+        <v>80.8856624815361</v>
       </c>
       <c r="D154">
-        <v>0.09094431180491824</v>
+        <v>0.09094018474756638</v>
       </c>
       <c r="E154" t="s">
         <v>68</v>
@@ -3207,13 +3207,13 @@
         <v>26</v>
       </c>
       <c r="B155">
-        <v>93.31047777482208</v>
+        <v>93.32446317713837</v>
       </c>
       <c r="C155">
-        <v>93.20491656666901</v>
+        <v>93.21889753467545</v>
       </c>
       <c r="D155">
-        <v>0.1055612081530626</v>
+        <v>0.1055656424629206</v>
       </c>
       <c r="E155" t="s">
         <v>69</v>
@@ -3241,13 +3241,13 @@
         <v>27</v>
       </c>
       <c r="B157">
-        <v>85.66985557630152</v>
+        <v>86.53754708334621</v>
       </c>
       <c r="C157">
-        <v>85.56707651828657</v>
+        <v>86.43458548617131</v>
       </c>
       <c r="D157">
-        <v>0.1027790580149457</v>
+        <v>0.1029615971748967</v>
       </c>
       <c r="E157" t="s">
         <v>64</v>
@@ -3258,13 +3258,13 @@
         <v>27</v>
       </c>
       <c r="B158">
-        <v>116.9118440911462</v>
+        <v>117.4395760410046</v>
       </c>
       <c r="C158">
-        <v>134.5357587031455</v>
+        <v>132.9281332431088</v>
       </c>
       <c r="D158">
-        <v>-17.62391461199925</v>
+        <v>-15.48855720210413</v>
       </c>
       <c r="E158" t="s">
         <v>65</v>
@@ -3275,13 +3275,13 @@
         <v>27</v>
       </c>
       <c r="B159">
-        <v>99.68228539671588</v>
+        <v>100.3608659510788</v>
       </c>
       <c r="C159">
-        <v>99.5908882128869</v>
+        <v>100.2862588728537</v>
       </c>
       <c r="D159">
-        <v>0.0913971838289882</v>
+        <v>0.07460707822507118</v>
       </c>
       <c r="E159" t="s">
         <v>66</v>
@@ -3292,13 +3292,13 @@
         <v>27</v>
       </c>
       <c r="B160">
-        <v>103.5499635993058</v>
+        <v>103.5175162502674</v>
       </c>
       <c r="C160">
-        <v>109.5706889355631</v>
+        <v>109.0151510604717</v>
       </c>
       <c r="D160">
-        <v>-6.0207253362573</v>
+        <v>-5.497634810204246</v>
       </c>
       <c r="E160" t="s">
         <v>67</v>
@@ -3309,13 +3309,13 @@
         <v>27</v>
       </c>
       <c r="B161">
-        <v>99.01485782473394</v>
+        <v>98.97846808482694</v>
       </c>
       <c r="C161">
-        <v>100.5975509989438</v>
+        <v>100.561178463188</v>
       </c>
       <c r="D161">
-        <v>-1.582693174209894</v>
+        <v>-1.582710378361043</v>
       </c>
       <c r="E161" t="s">
         <v>68</v>
@@ -3326,13 +3326,13 @@
         <v>27</v>
       </c>
       <c r="B162">
-        <v>111.8517950546726</v>
+        <v>111.8911175003948</v>
       </c>
       <c r="C162">
-        <v>113.2525261665448</v>
+        <v>113.2918298168946</v>
       </c>
       <c r="D162">
-        <v>-1.400731111872176</v>
+        <v>-1.400712316499806</v>
       </c>
       <c r="E162" t="s">
         <v>69</v>
@@ -3360,13 +3360,13 @@
         <v>28</v>
       </c>
       <c r="B164">
-        <v>102.2541723235569</v>
+        <v>101.6404779934821</v>
       </c>
       <c r="C164">
-        <v>102.1941370949359</v>
+        <v>101.5808129258797</v>
       </c>
       <c r="D164">
-        <v>0.06003522862096133</v>
+        <v>0.05966506760239554</v>
       </c>
       <c r="E164" t="s">
         <v>64</v>
@@ -3377,13 +3377,13 @@
         <v>28</v>
       </c>
       <c r="B165">
-        <v>112.2117088705904</v>
+        <v>112.891201342487</v>
       </c>
       <c r="C165">
-        <v>112.1456306146309</v>
+        <v>112.8247126566915</v>
       </c>
       <c r="D165">
-        <v>0.06607825595955319</v>
+        <v>0.06648868579547695</v>
       </c>
       <c r="E165" t="s">
         <v>65</v>
@@ -3394,13 +3394,13 @@
         <v>28</v>
       </c>
       <c r="B166">
-        <v>109.4253028171975</v>
+        <v>109.5172216686943</v>
       </c>
       <c r="C166">
-        <v>109.360929558478</v>
+        <v>109.4527953225148</v>
       </c>
       <c r="D166">
-        <v>0.06437325871952737</v>
+        <v>0.06442634617948784</v>
       </c>
       <c r="E166" t="s">
         <v>66</v>
@@ -3411,13 +3411,13 @@
         <v>28</v>
       </c>
       <c r="B167">
-        <v>103.8395505328191</v>
+        <v>103.6686387128907</v>
       </c>
       <c r="C167">
-        <v>103.7785403824858</v>
+        <v>103.6077293167873</v>
       </c>
       <c r="D167">
-        <v>0.06101015033327428</v>
+        <v>0.06090939610341195</v>
       </c>
       <c r="E167" t="s">
         <v>67</v>
@@ -3428,13 +3428,13 @@
         <v>28</v>
       </c>
       <c r="B168">
-        <v>102.3149658145373</v>
+        <v>102.0121620062219</v>
       </c>
       <c r="C168">
-        <v>102.2548815772578</v>
+        <v>101.9522582306181</v>
       </c>
       <c r="D168">
-        <v>0.06008423727948298</v>
+        <v>0.05990377560382854</v>
       </c>
       <c r="E168" t="s">
         <v>68</v>
@@ -3445,13 +3445,13 @@
         <v>28</v>
       </c>
       <c r="B169">
-        <v>112.1427123976534</v>
+        <v>112.4760219885739</v>
       </c>
       <c r="C169">
-        <v>112.0766886068753</v>
+        <v>112.4097991930996</v>
       </c>
       <c r="D169">
-        <v>0.06602379077817488</v>
+        <v>0.06622279547433152</v>
       </c>
       <c r="E169" t="s">
         <v>69</v>
@@ -3479,13 +3479,13 @@
         <v>29</v>
       </c>
       <c r="B171">
-        <v>84.8482852329962</v>
+        <v>85.72352273391978</v>
       </c>
       <c r="C171">
-        <v>84.74560947083569</v>
+        <v>85.62075419029819</v>
       </c>
       <c r="D171">
-        <v>0.1026757621605157</v>
+        <v>0.1027685436215933</v>
       </c>
       <c r="E171" t="s">
         <v>64</v>
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="B172">
-        <v>116.6674483343186</v>
+        <v>117.15612018446</v>
       </c>
       <c r="C172">
-        <v>134.0700713170076</v>
+        <v>132.440966800427</v>
       </c>
       <c r="D172">
-        <v>-17.40262298268892</v>
+        <v>-15.28484661596701</v>
       </c>
       <c r="E172" t="s">
         <v>65</v>
@@ -3513,13 +3513,13 @@
         <v>29</v>
       </c>
       <c r="B173">
-        <v>98.86101965648449</v>
+        <v>99.55581604294302</v>
       </c>
       <c r="C173">
-        <v>98.76431936783334</v>
+        <v>99.47896701547667</v>
       </c>
       <c r="D173">
-        <v>0.09670028865114944</v>
+        <v>0.07684902746635203</v>
       </c>
       <c r="E173" t="s">
         <v>66</v>
@@ -3530,13 +3530,13 @@
         <v>29</v>
       </c>
       <c r="B174">
-        <v>102.9925321930304</v>
+        <v>102.9582459691921</v>
       </c>
       <c r="C174">
-        <v>108.9837792179766</v>
+        <v>108.411413571443</v>
       </c>
       <c r="D174">
-        <v>-5.991247024946233</v>
+        <v>-5.453167602250886</v>
       </c>
       <c r="E174" t="s">
         <v>67</v>
@@ -3547,13 +3547,13 @@
         <v>29</v>
       </c>
       <c r="B175">
-        <v>98.35146904475539</v>
+        <v>98.31569337078608</v>
       </c>
       <c r="C175">
-        <v>99.92265180683195</v>
+        <v>99.88689377110822</v>
       </c>
       <c r="D175">
-        <v>-1.57118276207656</v>
+        <v>-1.571200400322141</v>
       </c>
       <c r="E175" t="s">
         <v>68</v>
@@ -3564,13 +3564,13 @@
         <v>29</v>
       </c>
       <c r="B176">
-        <v>111.2258543834898</v>
+        <v>111.264634386855</v>
       </c>
       <c r="C176">
-        <v>112.5289771540084</v>
+        <v>112.5677378500025</v>
       </c>
       <c r="D176">
-        <v>-1.303122770518556</v>
+        <v>-1.303103463147551</v>
       </c>
       <c r="E176" t="s">
         <v>69</v>
@@ -3598,13 +3598,13 @@
         <v>30</v>
       </c>
       <c r="B178">
-        <v>85.47461408241288</v>
+        <v>86.34417815012064</v>
       </c>
       <c r="C178">
-        <v>85.37185930575104</v>
+        <v>86.2412072697642</v>
       </c>
       <c r="D178">
-        <v>0.1027547766618397</v>
+        <v>0.1029708803564375</v>
       </c>
       <c r="E178" t="s">
         <v>64</v>
@@ -3615,13 +3615,13 @@
         <v>30</v>
       </c>
       <c r="B179">
-        <v>116.854484600007</v>
+        <v>117.3733539858309</v>
       </c>
       <c r="C179">
-        <v>134.4301013172646</v>
+        <v>132.8171994681665</v>
       </c>
       <c r="D179">
-        <v>-17.57561671725766</v>
+        <v>-15.44384548233558</v>
       </c>
       <c r="E179" t="s">
         <v>65</v>
@@ -3632,13 +3632,13 @@
         <v>30</v>
       </c>
       <c r="B180">
-        <v>99.48709370554194</v>
+        <v>100.1703367972787</v>
       </c>
       <c r="C180">
-        <v>99.3948005910128</v>
+        <v>100.0950424292397</v>
       </c>
       <c r="D180">
-        <v>0.09229311452914146</v>
+        <v>0.07529436803898193</v>
       </c>
       <c r="E180" t="s">
         <v>66</v>
@@ -3649,13 +3649,13 @@
         <v>30</v>
       </c>
       <c r="B181">
-        <v>103.4198430120148</v>
+        <v>103.3855566066302</v>
       </c>
       <c r="C181">
-        <v>109.4341826623514</v>
+        <v>108.8743931008523</v>
       </c>
       <c r="D181">
-        <v>-6.014339650336623</v>
+        <v>-5.488836494222042</v>
       </c>
       <c r="E181" t="s">
         <v>67</v>
@@ -3666,13 +3666,13 @@
         <v>30</v>
       </c>
       <c r="B182">
-        <v>98.85884467672408</v>
+        <v>98.82254942219464</v>
       </c>
       <c r="C182">
-        <v>100.4389691020234</v>
+        <v>100.4026911728416</v>
       </c>
       <c r="D182">
-        <v>-1.580124425299374</v>
+        <v>-1.580141750646916</v>
       </c>
       <c r="E182" t="s">
         <v>68</v>
@@ -3683,13 +3683,13 @@
         <v>30</v>
       </c>
       <c r="B183">
-        <v>111.7046523877544</v>
+        <v>111.7439004975998</v>
       </c>
       <c r="C183">
-        <v>113.0824198701634</v>
+        <v>113.121649043632</v>
       </c>
       <c r="D183">
-        <v>-1.377767482408984</v>
+        <v>-1.377748546032208</v>
       </c>
       <c r="E183" t="s">
         <v>69</v>
@@ -3717,13 +3717,13 @@
         <v>31</v>
       </c>
       <c r="B185">
-        <v>85.549464957738</v>
+        <v>86.41780368610782</v>
       </c>
       <c r="C185">
-        <v>85.44670512285276</v>
+        <v>86.31485895303523</v>
       </c>
       <c r="D185">
-        <v>0.1027598348852337</v>
+        <v>0.1029447330725901</v>
       </c>
       <c r="E185" t="s">
         <v>64</v>
@@ -3734,13 +3734,13 @@
         <v>31</v>
       </c>
       <c r="B186">
-        <v>116.8574040311822</v>
+        <v>117.3800091106238</v>
       </c>
       <c r="C186">
-        <v>134.4394592516861</v>
+        <v>132.8302541874102</v>
       </c>
       <c r="D186">
-        <v>-17.58205522050382</v>
+        <v>-15.45024507678647</v>
       </c>
       <c r="E186" t="s">
         <v>65</v>
@@ -3751,13 +3751,13 @@
         <v>31</v>
       </c>
       <c r="B187">
-        <v>99.56103328646149</v>
+        <v>100.2408231170837</v>
       </c>
       <c r="C187">
-        <v>99.46932046003782</v>
+        <v>100.1659877017172</v>
       </c>
       <c r="D187">
-        <v>0.09171282642367373</v>
+        <v>0.07483541536652183</v>
       </c>
       <c r="E187" t="s">
         <v>66</v>
@@ -3768,13 +3768,13 @@
         <v>31</v>
       </c>
       <c r="B188">
-        <v>103.4545293072684</v>
+        <v>103.4210590439385</v>
       </c>
       <c r="C188">
-        <v>109.4668788049111</v>
+        <v>108.9102306379113</v>
       </c>
       <c r="D188">
-        <v>-6.012349497642717</v>
+        <v>-5.489171593972827</v>
       </c>
       <c r="E188" t="s">
         <v>67</v>
@@ -3785,13 +3785,13 @@
         <v>31</v>
       </c>
       <c r="B189">
-        <v>98.90636644182156</v>
+        <v>98.87007257556054</v>
       </c>
       <c r="C189">
-        <v>100.487740280206</v>
+        <v>100.4514636765529</v>
       </c>
       <c r="D189">
-        <v>-1.581373838384408</v>
+        <v>-1.58139110099232</v>
       </c>
       <c r="E189" t="s">
         <v>68</v>
@@ -3802,13 +3802,13 @@
         <v>31</v>
       </c>
       <c r="B190">
-        <v>111.7490465777041</v>
+        <v>111.7882827558781</v>
       </c>
       <c r="C190">
-        <v>113.1379632883613</v>
+        <v>113.1771806018561</v>
       </c>
       <c r="D190">
-        <v>-1.388916710657156</v>
+        <v>-1.388897845977993</v>
       </c>
       <c r="E190" t="s">
         <v>69</v>
@@ -3836,13 +3836,13 @@
         <v>32</v>
       </c>
       <c r="B192">
-        <v>87.70268311615857</v>
+        <v>88.37996965298456</v>
       </c>
       <c r="C192">
-        <v>87.59889207940721</v>
+        <v>88.27641810002426</v>
       </c>
       <c r="D192">
-        <v>0.1037910367513604</v>
+        <v>0.1035515529602975</v>
       </c>
       <c r="E192" t="s">
         <v>64</v>
@@ -3853,13 +3853,13 @@
         <v>32</v>
       </c>
       <c r="B193">
-        <v>111.8200577776951</v>
+        <v>112.5082991899775</v>
       </c>
       <c r="C193">
-        <v>131.5666028794049</v>
+        <v>130.3905936522783</v>
       </c>
       <c r="D193">
-        <v>-19.74654510170986</v>
+        <v>-17.88229446230072</v>
       </c>
       <c r="E193" t="s">
         <v>65</v>
@@ -3870,13 +3870,13 @@
         <v>32</v>
       </c>
       <c r="B194">
-        <v>101.5823370950647</v>
+        <v>102.0099144027356</v>
       </c>
       <c r="C194">
-        <v>101.5896497111403</v>
+        <v>102.0500632157068</v>
       </c>
       <c r="D194">
-        <v>-0.007312616075523692</v>
+        <v>-0.04014881297121065</v>
       </c>
       <c r="E194" t="s">
         <v>66</v>
@@ -3887,13 +3887,13 @@
         <v>32</v>
       </c>
       <c r="B195">
-        <v>102.5779568251579</v>
+        <v>102.4089852254025</v>
       </c>
       <c r="C195">
-        <v>108.3028693171664</v>
+        <v>107.9476431985694</v>
       </c>
       <c r="D195">
-        <v>-5.724912492008499</v>
+        <v>-5.538657973166877</v>
       </c>
       <c r="E195" t="s">
         <v>67</v>
@@ -3904,13 +3904,13 @@
         <v>32</v>
       </c>
       <c r="B196">
-        <v>99.10392989273316</v>
+        <v>98.96680657247764</v>
       </c>
       <c r="C196">
-        <v>100.48126004358</v>
+        <v>100.4451193848135</v>
       </c>
       <c r="D196">
-        <v>-1.377330150846802</v>
+        <v>-1.478312812335901</v>
       </c>
       <c r="E196" t="s">
         <v>68</v>
@@ -3921,13 +3921,13 @@
         <v>32</v>
       </c>
       <c r="B197">
-        <v>110.6052674789529</v>
+        <v>110.8281971563678</v>
       </c>
       <c r="C197">
-        <v>113.8811304605333</v>
+        <v>113.9202483179308</v>
       </c>
       <c r="D197">
-        <v>-3.27586298158036</v>
+        <v>-3.092051161562964</v>
       </c>
       <c r="E197" t="s">
         <v>69</v>
@@ -3955,13 +3955,13 @@
         <v>33</v>
       </c>
       <c r="B199">
-        <v>82.41740329615506</v>
+        <v>83.01759279083697</v>
       </c>
       <c r="C199">
-        <v>82.31977195828469</v>
+        <v>82.91905840016518</v>
       </c>
       <c r="D199">
-        <v>0.09763133787036793</v>
+        <v>0.09853439067178726</v>
       </c>
       <c r="E199" t="s">
         <v>64</v>
@@ -3972,13 +3972,13 @@
         <v>33</v>
       </c>
       <c r="B200">
-        <v>109.836519360732</v>
+        <v>110.4909582200297</v>
       </c>
       <c r="C200">
-        <v>122.9932385081858</v>
+        <v>121.971864466515</v>
       </c>
       <c r="D200">
-        <v>-13.15671914745377</v>
+        <v>-11.48090624648525</v>
       </c>
       <c r="E200" t="s">
         <v>65</v>
@@ -3989,13 +3989,13 @@
         <v>33</v>
       </c>
       <c r="B201">
-        <v>95.52677134609246</v>
+        <v>95.93085475631266</v>
       </c>
       <c r="C201">
-        <v>95.41666710912106</v>
+        <v>95.82111757671146</v>
       </c>
       <c r="D201">
-        <v>0.1101042369713952</v>
+        <v>0.109737179601197</v>
       </c>
       <c r="E201" t="s">
         <v>66</v>
@@ -4006,13 +4006,13 @@
         <v>33</v>
       </c>
       <c r="B202">
-        <v>99.94735926771963</v>
+        <v>99.69517966618709</v>
       </c>
       <c r="C202">
-        <v>101.3811067153263</v>
+        <v>101.0720867508607</v>
       </c>
       <c r="D202">
-        <v>-1.433747447606706</v>
+        <v>-1.37690708467359</v>
       </c>
       <c r="E202" t="s">
         <v>67</v>
@@ -4023,13 +4023,13 @@
         <v>33</v>
       </c>
       <c r="B203">
-        <v>94.15255462091564</v>
+        <v>94.10062666447276</v>
       </c>
       <c r="C203">
-        <v>94.17058759547831</v>
+        <v>94.13760623991004</v>
       </c>
       <c r="D203">
-        <v>-0.01803297456267217</v>
+        <v>-0.03697957543728592</v>
       </c>
       <c r="E203" t="s">
         <v>68</v>
@@ -4040,13 +4040,13 @@
         <v>33</v>
       </c>
       <c r="B204">
-        <v>106.1568314761728</v>
+        <v>106.2747977500569</v>
       </c>
       <c r="C204">
-        <v>106.8126453136098</v>
+        <v>106.8481653624873</v>
       </c>
       <c r="D204">
-        <v>-0.6558138374370515</v>
+        <v>-0.5733676124303315</v>
       </c>
       <c r="E204" t="s">
         <v>69</v>
@@ -4074,13 +4074,13 @@
         <v>34</v>
       </c>
       <c r="B206">
-        <v>84.89102830353021</v>
+        <v>85.76634807683101</v>
       </c>
       <c r="C206">
-        <v>84.78835514689908</v>
+        <v>85.66342041098771</v>
       </c>
       <c r="D206">
-        <v>0.102673156631127</v>
+        <v>0.1029276658432963</v>
       </c>
       <c r="E206" t="s">
         <v>64</v>
@@ -4091,13 +4091,13 @@
         <v>34</v>
       </c>
       <c r="B207">
-        <v>116.6829911337087</v>
+        <v>117.1740499654675</v>
       </c>
       <c r="C207">
-        <v>134.1134961530067</v>
+        <v>132.484486644743</v>
       </c>
       <c r="D207">
-        <v>-17.43050501929807</v>
+        <v>-15.31043667927551</v>
       </c>
       <c r="E207" t="s">
         <v>65</v>
@@ -4108,13 +4108,13 @@
         <v>34</v>
       </c>
       <c r="B208">
-        <v>98.90193245836481</v>
+        <v>99.59902561656907</v>
       </c>
       <c r="C208">
-        <v>98.80690858268554</v>
+        <v>99.52162242895643</v>
       </c>
       <c r="D208">
-        <v>0.09502387567927428</v>
+        <v>0.07740318761263154</v>
       </c>
       <c r="E208" t="s">
         <v>66</v>
@@ -4125,13 +4125,13 @@
         <v>34</v>
       </c>
       <c r="B209">
-        <v>103.0331345620705</v>
+        <v>102.9932848950403</v>
       </c>
       <c r="C209">
-        <v>109.0270529366639</v>
+        <v>108.4546186964635</v>
       </c>
       <c r="D209">
-        <v>-5.993918374593434</v>
+        <v>-5.461333801423223</v>
       </c>
       <c r="E209" t="s">
         <v>67</v>
@@ -4142,13 +4142,13 @@
         <v>34</v>
       </c>
       <c r="B210">
-        <v>98.39399432116453</v>
+        <v>98.35818617008668</v>
       </c>
       <c r="C210">
-        <v>99.96572201587858</v>
+        <v>99.92993145636204</v>
       </c>
       <c r="D210">
-        <v>-1.571727694714056</v>
+        <v>-1.571745286275359</v>
       </c>
       <c r="E210" t="s">
         <v>68</v>
@@ -4159,13 +4159,13 @@
         <v>34</v>
       </c>
       <c r="B211">
-        <v>111.2620622309635</v>
+        <v>111.3008667056348</v>
       </c>
       <c r="C211">
-        <v>112.5718542436862</v>
+        <v>112.6106394642517</v>
       </c>
       <c r="D211">
-        <v>-1.30979201272271</v>
+        <v>-1.30977275861683</v>
       </c>
       <c r="E211" t="s">
         <v>69</v>
@@ -4193,13 +4193,13 @@
         <v>35</v>
       </c>
       <c r="B213">
-        <v>85.08519839485569</v>
+        <v>85.95858949542053</v>
       </c>
       <c r="C213">
-        <v>84.98249664266839</v>
+        <v>85.85562295432966</v>
       </c>
       <c r="D213">
-        <v>0.1027017521873006</v>
+        <v>0.1029665410908649</v>
       </c>
       <c r="E213" t="s">
         <v>64</v>
@@ -4210,13 +4210,13 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>116.740057269207</v>
+        <v>117.2405895448511</v>
       </c>
       <c r="C214">
-        <v>134.2189654694051</v>
+        <v>132.5953715839819</v>
       </c>
       <c r="D214">
-        <v>-17.47890820019815</v>
+        <v>-15.35478203913075</v>
       </c>
       <c r="E214" t="s">
         <v>65</v>
@@ -4227,13 +4227,13 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>99.0969136341155</v>
+        <v>99.78941264715112</v>
       </c>
       <c r="C215">
-        <v>99.00280681718971</v>
+        <v>99.71272027241788</v>
       </c>
       <c r="D215">
-        <v>0.09410681692578748</v>
+        <v>0.07669237473324131</v>
       </c>
       <c r="E215" t="s">
         <v>66</v>
@@ -4244,13 +4244,13 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>103.1614308953446</v>
+        <v>103.123441485865</v>
       </c>
       <c r="C216">
-        <v>109.1623623107847</v>
+        <v>108.5941246781992</v>
       </c>
       <c r="D216">
-        <v>-6.000931415440135</v>
+        <v>-5.470683192334121</v>
       </c>
       <c r="E216" t="s">
         <v>67</v>
@@ -4261,13 +4261,13 @@
         <v>35</v>
       </c>
       <c r="B217">
-        <v>98.54841244167834</v>
+        <v>98.51240815358987</v>
       </c>
       <c r="C217">
-        <v>100.1230527441903</v>
+        <v>100.0870659758306</v>
       </c>
       <c r="D217">
-        <v>-1.574640302511924</v>
+        <v>-1.574657822240752</v>
       </c>
       <c r="E217" t="s">
         <v>68</v>
@@ -4278,13 +4278,13 @@
         <v>35</v>
       </c>
       <c r="B218">
-        <v>111.409785847701</v>
+        <v>111.4487749142889</v>
       </c>
       <c r="C218">
-        <v>112.7420795109943</v>
+        <v>112.7810494110643</v>
       </c>
       <c r="D218">
-        <v>-1.332293663293314</v>
+        <v>-1.332274496775412</v>
       </c>
       <c r="E218" t="s">
         <v>69</v>
@@ -4312,13 +4312,13 @@
         <v>36</v>
       </c>
       <c r="B220">
-        <v>86.40590534634346</v>
+        <v>87.12956428925909</v>
       </c>
       <c r="C220">
-        <v>86.3023704296439</v>
+        <v>87.02633173787028</v>
       </c>
       <c r="D220">
-        <v>0.1035349166995587</v>
+        <v>0.1032325513888139</v>
       </c>
       <c r="E220" t="s">
         <v>64</v>
@@ -4329,13 +4329,13 @@
         <v>36</v>
       </c>
       <c r="B221">
-        <v>111.4347105174433</v>
+        <v>112.1273843228207</v>
       </c>
       <c r="C221">
-        <v>130.9372204946744</v>
+        <v>129.6739624731269</v>
       </c>
       <c r="D221">
-        <v>-19.50250997723116</v>
+        <v>-17.54657815030625</v>
       </c>
       <c r="E221" t="s">
         <v>65</v>
@@ -4346,13 +4346,13 @@
         <v>36</v>
       </c>
       <c r="B222">
-        <v>100.3072685546526</v>
+        <v>100.7607052622287</v>
       </c>
       <c r="C222">
-        <v>100.2850657030867</v>
+        <v>100.771568272601</v>
       </c>
       <c r="D222">
-        <v>0.0222028515658792</v>
+        <v>-0.01086301037221915</v>
       </c>
       <c r="E222" t="s">
         <v>66</v>
@@ -4363,13 +4363,13 @@
         <v>36</v>
       </c>
       <c r="B223">
-        <v>101.6511616727377</v>
+        <v>101.5031003717643</v>
       </c>
       <c r="C223">
-        <v>107.4710918420468</v>
+        <v>107.0946637938006</v>
       </c>
       <c r="D223">
-        <v>-5.819930169309075</v>
+        <v>-5.591563422036245</v>
       </c>
       <c r="E223" t="s">
         <v>67</v>
@@ -4380,13 +4380,13 @@
         <v>36</v>
       </c>
       <c r="B224">
-        <v>98.06888120512849</v>
+        <v>97.94474346038729</v>
       </c>
       <c r="C224">
-        <v>99.50538995422433</v>
+        <v>99.47095990724364</v>
       </c>
       <c r="D224">
-        <v>-1.436508749095836</v>
+        <v>-1.526216446856353</v>
       </c>
       <c r="E224" t="s">
         <v>68</v>
@@ -4397,13 +4397,13 @@
         <v>36</v>
       </c>
       <c r="B225">
-        <v>109.8117302328492</v>
+        <v>109.9872496374156</v>
       </c>
       <c r="C225">
-        <v>112.7447008231588</v>
+        <v>112.7821334621789</v>
       </c>
       <c r="D225">
-        <v>-2.932970590309651</v>
+        <v>-2.794883824763332</v>
       </c>
       <c r="E225" t="s">
         <v>69</v>
@@ -4431,13 +4431,13 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>51.71112742135696</v>
+        <v>52.57274240609772</v>
       </c>
       <c r="C227">
-        <v>51.64497462184339</v>
+        <v>52.50524818271919</v>
       </c>
       <c r="D227">
-        <v>0.06615279951356712</v>
+        <v>0.06749422337853872</v>
       </c>
       <c r="E227" t="s">
         <v>64</v>
@@ -4448,13 +4448,13 @@
         <v>37</v>
       </c>
       <c r="B228">
-        <v>94.49575189677564</v>
+        <v>92.93957232988635</v>
       </c>
       <c r="C228">
-        <v>94.82085572175666</v>
+        <v>93.03930859795503</v>
       </c>
       <c r="D228">
-        <v>-0.3251038249810136</v>
+        <v>-0.09973626806868197</v>
       </c>
       <c r="E228" t="s">
         <v>65</v>
@@ -4465,13 +4465,13 @@
         <v>37</v>
       </c>
       <c r="B229">
-        <v>60.83119129215958</v>
+        <v>61.83336279724793</v>
       </c>
       <c r="C229">
-        <v>60.7517405710337</v>
+        <v>61.75239789702831</v>
       </c>
       <c r="D229">
-        <v>0.07945072112588036</v>
+        <v>0.08096490021961955</v>
       </c>
       <c r="E229" t="s">
         <v>66</v>
@@ -4482,13 +4482,13 @@
         <v>37</v>
       </c>
       <c r="B230">
-        <v>74.89680560774693</v>
+        <v>74.03336382962043</v>
       </c>
       <c r="C230">
-        <v>74.81079810980947</v>
+        <v>73.9423051108738</v>
       </c>
       <c r="D230">
-        <v>0.08600749793745877</v>
+        <v>0.09105871874662341</v>
       </c>
       <c r="E230" t="s">
         <v>67</v>
@@ -4499,13 +4499,13 @@
         <v>37</v>
       </c>
       <c r="B231">
-        <v>66.3038835470357</v>
+        <v>66.28567489207899</v>
       </c>
       <c r="C231">
-        <v>66.21579876703787</v>
+        <v>66.19759653616585</v>
       </c>
       <c r="D231">
-        <v>0.08808477999782838</v>
+        <v>0.08807835591314017</v>
       </c>
       <c r="E231" t="s">
         <v>68</v>
@@ -4516,13 +4516,13 @@
         <v>37</v>
       </c>
       <c r="B232">
-        <v>72.90800248519692</v>
+        <v>72.92720628461076</v>
       </c>
       <c r="C232">
-        <v>72.81046065619869</v>
+        <v>72.82965743833533</v>
       </c>
       <c r="D232">
-        <v>0.09754182899823149</v>
+        <v>0.09754884627542992</v>
       </c>
       <c r="E232" t="s">
         <v>69</v>
@@ -4550,13 +4550,13 @@
         <v>38</v>
       </c>
       <c r="B234">
-        <v>69.13575119807403</v>
+        <v>69.46946295903537</v>
       </c>
       <c r="C234">
-        <v>69.05274122104353</v>
+        <v>69.38595847290168</v>
       </c>
       <c r="D234">
-        <v>0.08300997703049973</v>
+        <v>0.0835044861336911</v>
       </c>
       <c r="E234" t="s">
         <v>64</v>
@@ -4567,13 +4567,13 @@
         <v>38</v>
       </c>
       <c r="B235">
-        <v>101.6212263440549</v>
+        <v>101.1603374926111</v>
       </c>
       <c r="C235">
-        <v>101.7332180292197</v>
+        <v>101.1920368626699</v>
       </c>
       <c r="D235">
-        <v>-0.1119916851648668</v>
+        <v>-0.03169937005878865</v>
       </c>
       <c r="E235" t="s">
         <v>65</v>
@@ -4584,13 +4584,13 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <v>80.2296467950093</v>
+        <v>80.49032382565409</v>
       </c>
       <c r="C236">
-        <v>80.13222919628015</v>
+        <v>80.39255996767662</v>
       </c>
       <c r="D236">
-        <v>0.09741759872915168</v>
+        <v>0.09776385797746912</v>
       </c>
       <c r="E236" t="s">
         <v>66</v>
@@ -4601,13 +4601,13 @@
         <v>38</v>
       </c>
       <c r="B237">
-        <v>84.12560709515078</v>
+        <v>83.93336995706368</v>
       </c>
       <c r="C237">
-        <v>84.02247038036863</v>
+        <v>83.8304820691905</v>
       </c>
       <c r="D237">
-        <v>0.1031367147821527</v>
+        <v>0.1028878878731803</v>
       </c>
       <c r="E237" t="s">
         <v>67</v>
@@ -4618,13 +4618,13 @@
         <v>38</v>
       </c>
       <c r="B238">
-        <v>78.38674820609128</v>
+        <v>78.36744574419701</v>
       </c>
       <c r="C238">
-        <v>78.29124355059797</v>
+        <v>78.27194782940619</v>
       </c>
       <c r="D238">
-        <v>0.09550465549331477</v>
+        <v>0.09549791479082614</v>
       </c>
       <c r="E238" t="s">
         <v>68</v>
@@ -4635,13 +4635,13 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>89.464151433053</v>
+        <v>89.4846598163634</v>
       </c>
       <c r="C239">
-        <v>89.35447572410071</v>
+        <v>89.37497680136057</v>
       </c>
       <c r="D239">
-        <v>0.1096757089522953</v>
+        <v>0.1096830150028296</v>
       </c>
       <c r="E239" t="s">
         <v>69</v>
@@ -4669,13 +4669,13 @@
         <v>39</v>
       </c>
       <c r="B241">
-        <v>54.68523115930078</v>
+        <v>55.51028185650235</v>
       </c>
       <c r="C241">
-        <v>54.61274288582321</v>
+        <v>55.43658791677076</v>
       </c>
       <c r="D241">
-        <v>0.07248827347757469</v>
+        <v>0.07369393973158367</v>
       </c>
       <c r="E241" t="s">
         <v>64</v>
@@ -4686,13 +4686,13 @@
         <v>39</v>
       </c>
       <c r="B242">
-        <v>91.58829091431336</v>
+        <v>90.23792828637869</v>
       </c>
       <c r="C242">
-        <v>91.61473821705998</v>
+        <v>90.17373517203087</v>
       </c>
       <c r="D242">
-        <v>-0.02644730274661811</v>
+        <v>0.06419311434781605</v>
       </c>
       <c r="E242" t="s">
         <v>65</v>
@@ -4703,13 +4703,13 @@
         <v>39</v>
       </c>
       <c r="B243">
-        <v>64.60896664212814</v>
+        <v>65.13976994441839</v>
       </c>
       <c r="C243">
-        <v>64.52239660797866</v>
+        <v>65.05243318031826</v>
       </c>
       <c r="D243">
-        <v>0.0865700341494744</v>
+        <v>0.08733676410012947</v>
       </c>
       <c r="E243" t="s">
         <v>66</v>
@@ -4720,13 +4720,13 @@
         <v>39</v>
       </c>
       <c r="B244">
-        <v>73.42317205469483</v>
+        <v>73.01351488936983</v>
       </c>
       <c r="C244">
-        <v>73.32393071213056</v>
+        <v>72.91476148078323</v>
       </c>
       <c r="D244">
-        <v>0.09924134256426953</v>
+        <v>0.09875340858660309</v>
       </c>
       <c r="E244" t="s">
         <v>67</v>
@@ -4737,13 +4737,13 @@
         <v>39</v>
       </c>
       <c r="B245">
-        <v>66.62567225146984</v>
+        <v>66.62065759952431</v>
       </c>
       <c r="C245">
-        <v>66.53597192212874</v>
+        <v>66.53095951198064</v>
       </c>
       <c r="D245">
-        <v>0.08970032934109895</v>
+        <v>0.08969808754366682</v>
       </c>
       <c r="E245" t="s">
         <v>68</v>
@@ -4754,13 +4754,13 @@
         <v>39</v>
       </c>
       <c r="B246">
-        <v>74.90313934624881</v>
+        <v>74.90844222888016</v>
       </c>
       <c r="C246">
-        <v>74.801813003614</v>
+        <v>74.80711342118029</v>
       </c>
       <c r="D246">
-        <v>0.1013263426348061</v>
+        <v>0.101328807699872</v>
       </c>
       <c r="E246" t="s">
         <v>69</v>
@@ -4788,13 +4788,13 @@
         <v>40</v>
       </c>
       <c r="B248">
-        <v>56.84493795825251</v>
+        <v>56.81866350555578</v>
       </c>
       <c r="C248">
-        <v>56.77366417876913</v>
+        <v>56.74739786617018</v>
       </c>
       <c r="D248">
-        <v>0.0712737794833771</v>
+        <v>0.07126563938560082</v>
       </c>
       <c r="E248" t="s">
         <v>64</v>
@@ -4805,13 +4805,13 @@
         <v>40</v>
       </c>
       <c r="B249">
-        <v>93.80223458552783</v>
+        <v>93.83024832029375</v>
       </c>
       <c r="C249">
-        <v>93.71636173038152</v>
+        <v>93.74440591860316</v>
       </c>
       <c r="D249">
-        <v>0.08587285514630594</v>
+        <v>0.08584240169058432</v>
       </c>
       <c r="E249" t="s">
         <v>65</v>
@@ -4822,13 +4822,13 @@
         <v>40</v>
       </c>
       <c r="B250">
-        <v>65.75216184914154</v>
+        <v>66.29958684637261</v>
       </c>
       <c r="C250">
-        <v>65.66844350574652</v>
+        <v>66.21507996087939</v>
       </c>
       <c r="D250">
-        <v>0.08371834339502016</v>
+        <v>0.08450688549321228</v>
       </c>
       <c r="E250" t="s">
         <v>66</v>
@@ -4839,13 +4839,13 @@
         <v>40</v>
       </c>
       <c r="B251">
-        <v>76.28188462386893</v>
+        <v>75.84065756987954</v>
       </c>
       <c r="C251">
-        <v>76.18263610195383</v>
+        <v>75.74197598715867</v>
       </c>
       <c r="D251">
-        <v>0.0992485219151007</v>
+        <v>0.09868158272087157</v>
       </c>
       <c r="E251" t="s">
         <v>67</v>
@@ -4856,13 +4856,13 @@
         <v>40</v>
       </c>
       <c r="B252">
-        <v>68.73197074151751</v>
+        <v>68.7180383385724</v>
       </c>
       <c r="C252">
-        <v>68.64345535038358</v>
+        <v>68.62952640985246</v>
       </c>
       <c r="D252">
-        <v>0.08851539113393869</v>
+        <v>0.08851192871993874</v>
       </c>
       <c r="E252" t="s">
         <v>68</v>
@@ -4873,13 +4873,13 @@
         <v>40</v>
       </c>
       <c r="B253">
-        <v>76.94402380264111</v>
+        <v>76.95854921509101</v>
       </c>
       <c r="C253">
-        <v>76.84423452828818</v>
+        <v>76.85875628002988</v>
       </c>
       <c r="D253">
-        <v>0.09978927435292917</v>
+        <v>0.09979293506113152</v>
       </c>
       <c r="E253" t="s">
         <v>69</v>
@@ -4907,13 +4907,13 @@
         <v>41</v>
       </c>
       <c r="B255">
-        <v>58.25831391885705</v>
+        <v>59.08499106589221</v>
       </c>
       <c r="C255">
-        <v>58.18504705617319</v>
+        <v>59.01051782737053</v>
       </c>
       <c r="D255">
-        <v>0.07326686268385885</v>
+        <v>0.07447323852168353</v>
       </c>
       <c r="E255" t="s">
         <v>64</v>
@@ -4924,13 +4924,13 @@
         <v>41</v>
       </c>
       <c r="B256">
-        <v>95.13740757903042</v>
+        <v>93.79797673531549</v>
       </c>
       <c r="C256">
-        <v>95.17042496672528</v>
+        <v>93.73474782164487</v>
       </c>
       <c r="D256">
-        <v>-0.03301738769485496</v>
+        <v>0.06322891367061345</v>
       </c>
       <c r="E256" t="s">
         <v>65</v>
@@ -4941,13 +4941,13 @@
         <v>41</v>
       </c>
       <c r="B257">
-        <v>68.26325208400755</v>
+        <v>68.78137536874499</v>
       </c>
       <c r="C257">
-        <v>68.17581978053957</v>
+        <v>68.69319877626873</v>
       </c>
       <c r="D257">
-        <v>0.08743230346797759</v>
+        <v>0.08817659247625897</v>
       </c>
       <c r="E257" t="s">
         <v>66</v>
@@ -4958,13 +4958,13 @@
         <v>41</v>
       </c>
       <c r="B258">
-        <v>76.94860453353823</v>
+        <v>76.54924046614649</v>
       </c>
       <c r="C258">
-        <v>76.84869158070948</v>
+        <v>76.44984369036951</v>
       </c>
       <c r="D258">
-        <v>0.09991295282874546</v>
+        <v>0.09939677577698092</v>
       </c>
       <c r="E258" t="s">
         <v>67</v>
@@ -4975,13 +4975,13 @@
         <v>41</v>
       </c>
       <c r="B259">
-        <v>70.17507407437597</v>
+        <v>70.16686730370051</v>
       </c>
       <c r="C259">
-        <v>70.0846796378579</v>
+        <v>70.07647663633074</v>
       </c>
       <c r="D259">
-        <v>0.09039443651806778</v>
+        <v>0.09039066736977475</v>
       </c>
       <c r="E259" t="s">
         <v>68</v>
@@ -4992,13 +4992,13 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>78.54505515660075</v>
+        <v>78.5537726526433</v>
       </c>
       <c r="C260">
-        <v>78.44292398439811</v>
+        <v>78.45163734979944</v>
       </c>
       <c r="D260">
-        <v>0.1021311722026468</v>
+        <v>0.1021353028438625</v>
       </c>
       <c r="E260" t="s">
         <v>69</v>
@@ -5026,13 +5026,13 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>56.96841047811881</v>
+        <v>57.79406301453413</v>
       </c>
       <c r="C262">
-        <v>56.89576665715194</v>
+        <v>57.72020180738556</v>
       </c>
       <c r="D262">
-        <v>0.07264382096687427</v>
+        <v>0.07386120714856759</v>
       </c>
       <c r="E262" t="s">
         <v>64</v>
@@ -5043,13 +5043,13 @@
         <v>42</v>
       </c>
       <c r="B263">
-        <v>94.20172728071479</v>
+        <v>92.83546057218308</v>
       </c>
       <c r="C263">
-        <v>94.22117876614473</v>
+        <v>92.76774379750741</v>
       </c>
       <c r="D263">
-        <v>-0.01945148542993991</v>
+        <v>0.06771677467567372</v>
       </c>
       <c r="E263" t="s">
         <v>65</v>
@@ -5060,13 +5060,13 @@
         <v>42</v>
       </c>
       <c r="B264">
-        <v>66.91772860809277</v>
+        <v>67.46909398364262</v>
       </c>
       <c r="C264">
-        <v>66.83097953712112</v>
+        <v>67.38155239894357</v>
       </c>
       <c r="D264">
-        <v>0.08674907097164919</v>
+        <v>0.08754158469905349</v>
       </c>
       <c r="E264" t="s">
         <v>66</v>
@@ -5077,13 +5077,13 @@
         <v>42</v>
       </c>
       <c r="B265">
-        <v>75.89737972053631</v>
+        <v>75.46868259097019</v>
       </c>
       <c r="C265">
-        <v>75.79766201640906</v>
+        <v>75.3694901057757</v>
       </c>
       <c r="D265">
-        <v>0.09971770412724368</v>
+        <v>0.09919248519449297</v>
       </c>
       <c r="E265" t="s">
         <v>67</v>
@@ -5094,13 +5094,13 @@
         <v>42</v>
       </c>
       <c r="B266">
-        <v>69.02462297827815</v>
+        <v>69.01260707975149</v>
       </c>
       <c r="C266">
-        <v>68.93455120574288</v>
+        <v>68.92253908523882</v>
       </c>
       <c r="D266">
-        <v>0.09007177253526777</v>
+        <v>0.09006799451266545</v>
       </c>
       <c r="E266" t="s">
         <v>68</v>
@@ -5111,13 +5111,13 @@
         <v>42</v>
       </c>
       <c r="B267">
-        <v>77.30449868538994</v>
+        <v>77.31705977085593</v>
       </c>
       <c r="C267">
-        <v>77.20283768824427</v>
+        <v>77.21539475757577</v>
       </c>
       <c r="D267">
-        <v>0.1016609971456717</v>
+        <v>0.1016650132801686</v>
       </c>
       <c r="E267" t="s">
         <v>69</v>
@@ -5145,13 +5145,13 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>75.75233835867607</v>
+        <v>75.75929263848215</v>
       </c>
       <c r="C269">
-        <v>75.66873904458072</v>
+        <v>75.67566767583897</v>
       </c>
       <c r="D269">
-        <v>0.08359931409535193</v>
+        <v>0.08362496264318509</v>
       </c>
       <c r="E269" t="s">
         <v>64</v>
@@ -5162,13 +5162,13 @@
         <v>43</v>
       </c>
       <c r="B270">
-        <v>101.2638837174825</v>
+        <v>101.2469639478213</v>
       </c>
       <c r="C270">
-        <v>101.1499070695939</v>
+        <v>101.1330262668271</v>
       </c>
       <c r="D270">
-        <v>0.1139766478886912</v>
+        <v>0.1139376809941979</v>
       </c>
       <c r="E270" t="s">
         <v>65</v>
@@ -5179,13 +5179,13 @@
         <v>43</v>
       </c>
       <c r="B271">
-        <v>86.68846734287982</v>
+        <v>86.71924780469705</v>
       </c>
       <c r="C271">
-        <v>86.59192859281353</v>
+        <v>86.62267642989329</v>
       </c>
       <c r="D271">
-        <v>0.09653875006628709</v>
+        <v>0.09657137480375866</v>
       </c>
       <c r="E271" t="s">
         <v>66</v>
@@ -5196,13 +5196,13 @@
         <v>43</v>
       </c>
       <c r="B272">
-        <v>85.81476792395239</v>
+        <v>85.79006265579724</v>
       </c>
       <c r="C272">
-        <v>85.71911959689712</v>
+        <v>85.69443736009275</v>
       </c>
       <c r="D272">
-        <v>0.09564832705527238</v>
+        <v>0.09562529570449385</v>
       </c>
       <c r="E272" t="s">
         <v>67</v>
@@ -5213,13 +5213,13 @@
         <v>43</v>
       </c>
       <c r="B273">
-        <v>81.55065737274444</v>
+        <v>81.53909667549561</v>
       </c>
       <c r="C273">
-        <v>81.4600903610278</v>
+        <v>81.44853333175729</v>
       </c>
       <c r="D273">
-        <v>0.09056701171664372</v>
+        <v>0.09056334373832442</v>
       </c>
       <c r="E273" t="s">
         <v>68</v>
@@ -5230,13 +5230,13 @@
         <v>43</v>
       </c>
       <c r="B274">
-        <v>93.93521899761591</v>
+        <v>93.94733232105281</v>
       </c>
       <c r="C274">
-        <v>93.83004763642423</v>
+        <v>93.84215698391375</v>
       </c>
       <c r="D274">
-        <v>0.1051713611916796</v>
+        <v>0.1051753371390589</v>
       </c>
       <c r="E274" t="s">
         <v>69</v>
@@ -5264,13 +5264,13 @@
         <v>44</v>
       </c>
       <c r="B276">
-        <v>99.51527079742749</v>
+        <v>99.11632237310315</v>
       </c>
       <c r="C276">
-        <v>95.04997009851439</v>
+        <v>94.49590042321695</v>
       </c>
       <c r="D276">
-        <v>4.465300698913097</v>
+        <v>4.620421949886193</v>
       </c>
       <c r="E276" t="s">
         <v>64</v>
@@ -5281,13 +5281,13 @@
         <v>44</v>
       </c>
       <c r="B277">
-        <v>104.3889487482931</v>
+        <v>104.8091197718228</v>
       </c>
       <c r="C277">
-        <v>106.6090103361114</v>
+        <v>107.235146293222</v>
       </c>
       <c r="D277">
-        <v>-2.220061587818236</v>
+        <v>-2.426026521399265</v>
       </c>
       <c r="E277" t="s">
         <v>65</v>
@@ -5298,13 +5298,13 @@
         <v>44</v>
       </c>
       <c r="B278">
-        <v>103.5609526407742</v>
+        <v>103.6791865867935</v>
       </c>
       <c r="C278">
-        <v>102.9673002535509</v>
+        <v>102.9265904751754</v>
       </c>
       <c r="D278">
-        <v>0.59365238722323</v>
+        <v>0.7525961116181037</v>
       </c>
       <c r="E278" t="s">
         <v>66</v>
@@ -5315,13 +5315,13 @@
         <v>44</v>
       </c>
       <c r="B279">
-        <v>99.80760335902156</v>
+        <v>99.64498293093904</v>
       </c>
       <c r="C279">
-        <v>97.2355169738895</v>
+        <v>97.21682098443644</v>
       </c>
       <c r="D279">
-        <v>2.572086385132053</v>
+        <v>2.428161946502598</v>
       </c>
       <c r="E279" t="s">
         <v>67</v>
@@ -5332,13 +5332,13 @@
         <v>44</v>
       </c>
       <c r="B280">
-        <v>99.08768731646236</v>
+        <v>98.85286363195742</v>
       </c>
       <c r="C280">
-        <v>95.44783676713506</v>
+        <v>95.32951893576747</v>
       </c>
       <c r="D280">
-        <v>3.639850549327306</v>
+        <v>3.523344696189952</v>
       </c>
       <c r="E280" t="s">
         <v>68</v>
@@ -5349,13 +5349,13 @@
         <v>44</v>
       </c>
       <c r="B281">
-        <v>104.8394082482462</v>
+        <v>105.0884528911797</v>
       </c>
       <c r="C281">
-        <v>106.1605563051736</v>
+        <v>106.2918637736107</v>
       </c>
       <c r="D281">
-        <v>-1.321148056927399</v>
+        <v>-1.203410882431029</v>
       </c>
       <c r="E281" t="s">
         <v>69</v>
@@ -5383,13 +5383,13 @@
         <v>45</v>
       </c>
       <c r="B283">
-        <v>97.9961175953152</v>
+        <v>97.46043858892209</v>
       </c>
       <c r="C283">
-        <v>92.12140045928801</v>
+        <v>91.63906387035831</v>
       </c>
       <c r="D283">
-        <v>5.874717136027186</v>
+        <v>5.821374718563774</v>
       </c>
       <c r="E283" t="s">
         <v>64</v>
@@ -5400,13 +5400,13 @@
         <v>45</v>
       </c>
       <c r="B284">
-        <v>105.2810829582148</v>
+        <v>105.8615299091998</v>
       </c>
       <c r="C284">
-        <v>106.0246480797973</v>
+        <v>106.5861496022455</v>
       </c>
       <c r="D284">
-        <v>-0.7435651215825203</v>
+        <v>-0.7246196930456676</v>
       </c>
       <c r="E284" t="s">
         <v>65</v>
@@ -5417,13 +5417,13 @@
         <v>45</v>
       </c>
       <c r="B285">
-        <v>103.5774202608119</v>
+        <v>103.6765046182746</v>
       </c>
       <c r="C285">
-        <v>100.8834619450059</v>
+        <v>100.778632370508</v>
       </c>
       <c r="D285">
-        <v>2.693958315806015</v>
+        <v>2.897872247766628</v>
       </c>
       <c r="E285" t="s">
         <v>66</v>
@@ -5434,13 +5434,13 @@
         <v>45</v>
       </c>
       <c r="B286">
-        <v>98.85954632053668</v>
+        <v>98.69872929295749</v>
       </c>
       <c r="C286">
-        <v>95.39425031277501</v>
+        <v>95.44796581280207</v>
       </c>
       <c r="D286">
-        <v>3.465296007761665</v>
+        <v>3.250763480155427</v>
       </c>
       <c r="E286" t="s">
         <v>67</v>
@@ -5451,13 +5451,13 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>97.76091852274479</v>
+        <v>97.49709102857767</v>
       </c>
       <c r="C287">
-        <v>93.21395155760256</v>
+        <v>93.18149306610117</v>
       </c>
       <c r="D287">
-        <v>4.546966965142232</v>
+        <v>4.315597962476502</v>
       </c>
       <c r="E287" t="s">
         <v>68</v>
@@ -5468,13 +5468,13 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>105.5347417797663</v>
+        <v>105.8210589522465</v>
       </c>
       <c r="C288">
-        <v>104.7676893661906</v>
+        <v>104.8033278077167</v>
       </c>
       <c r="D288">
-        <v>0.7670524135757546</v>
+        <v>1.017731144529876</v>
       </c>
       <c r="E288" t="s">
         <v>69</v>
@@ -5502,13 +5502,13 @@
         <v>46</v>
       </c>
       <c r="B290">
-        <v>97.65489751817806</v>
+        <v>97.27418181643762</v>
       </c>
       <c r="C290">
-        <v>91.344436322275</v>
+        <v>90.8084862826731</v>
       </c>
       <c r="D290">
-        <v>6.310461195903059</v>
+        <v>6.465695533764517</v>
       </c>
       <c r="E290" t="s">
         <v>64</v>
@@ -5519,13 +5519,13 @@
         <v>46</v>
       </c>
       <c r="B291">
-        <v>102.2255705194341</v>
+        <v>102.6256651703413</v>
       </c>
       <c r="C291">
-        <v>102.3645906790227</v>
+        <v>102.9695215118075</v>
       </c>
       <c r="D291">
-        <v>-0.1390201595885827</v>
+        <v>-0.3438563414661786</v>
       </c>
       <c r="E291" t="s">
         <v>65</v>
@@ -5536,13 +5536,13 @@
         <v>46</v>
       </c>
       <c r="B292">
-        <v>101.4719515543709</v>
+        <v>101.5897405024566</v>
       </c>
       <c r="C292">
-        <v>98.92306292065564</v>
+        <v>98.88831728328095</v>
       </c>
       <c r="D292">
-        <v>2.548888633715279</v>
+        <v>2.701423219175638</v>
       </c>
       <c r="E292" t="s">
         <v>66</v>
@@ -5553,13 +5553,13 @@
         <v>46</v>
       </c>
       <c r="B293">
-        <v>97.90768844290409</v>
+        <v>97.74737134148074</v>
       </c>
       <c r="C293">
-        <v>93.40278542318539</v>
+        <v>93.37993831057555</v>
       </c>
       <c r="D293">
-        <v>4.504903019718697</v>
+        <v>4.36743303090519</v>
       </c>
       <c r="E293" t="s">
         <v>67</v>
@@ -5570,13 +5570,13 @@
         <v>46</v>
       </c>
       <c r="B294">
-        <v>97.23359000519416</v>
+        <v>97.00438399857136</v>
       </c>
       <c r="C294">
-        <v>91.69997918963946</v>
+        <v>91.58051855812424</v>
       </c>
       <c r="D294">
-        <v>5.533610815554695</v>
+        <v>5.423865440447116</v>
       </c>
       <c r="E294" t="s">
         <v>68</v>
@@ -5587,13 +5587,13 @@
         <v>46</v>
       </c>
       <c r="B295">
-        <v>102.6685079948128</v>
+        <v>102.9110974299847</v>
       </c>
       <c r="C295">
-        <v>101.9649588704356</v>
+        <v>102.0976667196148</v>
       </c>
       <c r="D295">
-        <v>0.7035491243772043</v>
+        <v>0.8134307103699143</v>
       </c>
       <c r="E295" t="s">
         <v>69</v>
@@ -5621,13 +5621,13 @@
         <v>47</v>
       </c>
       <c r="B297">
-        <v>104.5567339958388</v>
+        <v>104.5136016749318</v>
       </c>
       <c r="C297">
-        <v>92.54615646655762</v>
+        <v>92.04200289654152</v>
       </c>
       <c r="D297">
-        <v>12.01057752928122</v>
+        <v>12.4715987783903</v>
       </c>
       <c r="E297" t="s">
         <v>64</v>
@@ -5638,13 +5638,13 @@
         <v>47</v>
       </c>
       <c r="B298">
-        <v>104.9286563340331</v>
+        <v>104.9719599462407</v>
       </c>
       <c r="C298">
-        <v>105.825270430989</v>
+        <v>106.4090111597488</v>
       </c>
       <c r="D298">
-        <v>-0.8966140969558865</v>
+        <v>-1.437051213508141</v>
       </c>
       <c r="E298" t="s">
         <v>65</v>
@@ -5655,13 +5655,13 @@
         <v>47</v>
       </c>
       <c r="B299">
-        <v>104.8967477163994</v>
+        <v>104.9183342872409</v>
       </c>
       <c r="C299">
-        <v>101.060670348169</v>
+        <v>100.9595262287203</v>
       </c>
       <c r="D299">
-        <v>3.83607736823042</v>
+        <v>3.958808058520674</v>
       </c>
       <c r="E299" t="s">
         <v>66</v>
@@ -5672,13 +5672,13 @@
         <v>47</v>
       </c>
       <c r="B300">
-        <v>104.5492285712636</v>
+        <v>104.5218702022862</v>
       </c>
       <c r="C300">
-        <v>95.54802751886486</v>
+        <v>95.596142725826</v>
       </c>
       <c r="D300">
-        <v>9.001201052398713</v>
+        <v>8.925727476460182</v>
       </c>
       <c r="E300" t="s">
         <v>67</v>
@@ -5689,13 +5689,13 @@
         <v>47</v>
       </c>
       <c r="B301">
-        <v>104.4953386961058</v>
+        <v>104.4598537859175</v>
       </c>
       <c r="C301">
-        <v>93.4682232377552</v>
+        <v>93.42704540143572</v>
       </c>
       <c r="D301">
-        <v>11.02711545835064</v>
+        <v>11.0328083844818</v>
       </c>
       <c r="E301" t="s">
         <v>68</v>
@@ -5706,13 +5706,13 @@
         <v>47</v>
       </c>
       <c r="B302">
-        <v>104.9903062256608</v>
+        <v>105.0259713300242</v>
       </c>
       <c r="C302">
-        <v>104.7697320289855</v>
+        <v>104.8153944636724</v>
       </c>
       <c r="D302">
-        <v>0.2205741966752583</v>
+        <v>0.2105768663518006</v>
       </c>
       <c r="E302" t="s">
         <v>69</v>
@@ -5740,13 +5740,13 @@
         <v>48</v>
       </c>
       <c r="B304">
-        <v>97.75803088557709</v>
+        <v>97.22538534570931</v>
       </c>
       <c r="C304">
-        <v>91.19634782932248</v>
+        <v>91.16273749842786</v>
       </c>
       <c r="D304">
-        <v>6.561683056254608</v>
+        <v>6.062647847281454</v>
       </c>
       <c r="E304" t="s">
         <v>64</v>
@@ -5757,13 +5757,13 @@
         <v>48</v>
       </c>
       <c r="B305">
-        <v>102.5456494674216</v>
+        <v>103.1074418699661</v>
       </c>
       <c r="C305">
-        <v>104.2311938623516</v>
+        <v>104.2671038578026</v>
       </c>
       <c r="D305">
-        <v>-1.68554439493002</v>
+        <v>-1.1596619878365</v>
       </c>
       <c r="E305" t="s">
         <v>65</v>
@@ -5774,13 +5774,13 @@
         <v>48</v>
       </c>
       <c r="B306">
-        <v>101.7322741090132</v>
+        <v>101.8171002477665</v>
       </c>
       <c r="C306">
-        <v>99.619256137965</v>
+        <v>99.55016430866641</v>
       </c>
       <c r="D306">
-        <v>2.113017971048237</v>
+        <v>2.266935939100094</v>
       </c>
       <c r="E306" t="s">
         <v>66</v>
@@ -5791,13 +5791,13 @@
         <v>48</v>
       </c>
       <c r="B307">
-        <v>98.04520144097199</v>
+        <v>97.90552527824964</v>
       </c>
       <c r="C307">
-        <v>94.18945723996777</v>
+        <v>94.22833862989678</v>
       </c>
       <c r="D307">
-        <v>3.855744201004228</v>
+        <v>3.677186648352858</v>
       </c>
       <c r="E307" t="s">
         <v>67</v>
@@ -5808,13 +5808,13 @@
         <v>48</v>
       </c>
       <c r="B308">
-        <v>97.33799767053974</v>
+        <v>97.10732050090984</v>
       </c>
       <c r="C308">
-        <v>92.3026073164876</v>
+        <v>92.29017205396615</v>
       </c>
       <c r="D308">
-        <v>5.03539035405214</v>
+        <v>4.81714844694369</v>
       </c>
       <c r="E308" t="s">
         <v>68</v>
@@ -5825,13 +5825,13 @@
         <v>48</v>
       </c>
       <c r="B309">
-        <v>102.9881547568737</v>
+        <v>103.232801771354</v>
       </c>
       <c r="C309">
-        <v>102.9751005955365</v>
+        <v>102.9882889394677</v>
       </c>
       <c r="D309">
-        <v>0.01305416133722304</v>
+        <v>0.244512831886297</v>
       </c>
       <c r="E309" t="s">
         <v>69</v>
@@ -5859,13 +5859,13 @@
         <v>49</v>
       </c>
       <c r="B311">
-        <v>100.4695873910087</v>
+        <v>100.1812055975771</v>
       </c>
       <c r="C311">
-        <v>89.04481367165511</v>
+        <v>88.65249775377731</v>
       </c>
       <c r="D311">
-        <v>11.42477371935364</v>
+        <v>11.52870784379978</v>
       </c>
       <c r="E311" t="s">
         <v>64</v>
@@ -5876,13 +5876,13 @@
         <v>49</v>
       </c>
       <c r="B312">
-        <v>103.4526982539322</v>
+        <v>103.7504973718391</v>
       </c>
       <c r="C312">
-        <v>105.1298970734496</v>
+        <v>105.5958689510879</v>
       </c>
       <c r="D312">
-        <v>-1.677198819517386</v>
+        <v>-1.84537157924882</v>
       </c>
       <c r="E312" t="s">
         <v>65</v>
@@ -5893,13 +5893,13 @@
         <v>49</v>
       </c>
       <c r="B313">
-        <v>103.0838139976804</v>
+        <v>103.2019929364598</v>
       </c>
       <c r="C313">
-        <v>98.54152873344309</v>
+        <v>98.4416594737264</v>
       </c>
       <c r="D313">
-        <v>4.542285264237293</v>
+        <v>4.760333462733385</v>
       </c>
       <c r="E313" t="s">
         <v>66</v>
@@ -5910,13 +5910,13 @@
         <v>49</v>
       </c>
       <c r="B314">
-        <v>100.5181388222082</v>
+        <v>100.3660554533129</v>
       </c>
       <c r="C314">
-        <v>93.37096803330924</v>
+        <v>93.42653318652474</v>
       </c>
       <c r="D314">
-        <v>7.147170788899004</v>
+        <v>6.939522266788131</v>
       </c>
       <c r="E314" t="s">
         <v>67</v>
@@ -5927,13 +5927,13 @@
         <v>49</v>
       </c>
       <c r="B315">
-        <v>100.083810073087</v>
+        <v>99.87922410687767</v>
       </c>
       <c r="C315">
-        <v>90.83580266136184</v>
+        <v>90.81591536819387</v>
       </c>
       <c r="D315">
-        <v>9.248007411725155</v>
+        <v>9.063308738683801</v>
       </c>
       <c r="E315" t="s">
         <v>68</v>
@@ -5944,13 +5944,13 @@
         <v>49</v>
       </c>
       <c r="B316">
-        <v>103.8514610951452</v>
+        <v>104.064183527667</v>
       </c>
       <c r="C316">
-        <v>103.0343445217546</v>
+        <v>103.0556090869436</v>
       </c>
       <c r="D316">
-        <v>0.8171165733906491</v>
+        <v>1.008574440723379</v>
       </c>
       <c r="E316" t="s">
         <v>69</v>
@@ -5978,13 +5978,13 @@
         <v>50</v>
       </c>
       <c r="B318">
-        <v>96.73421748474941</v>
+        <v>96.19575743644889</v>
       </c>
       <c r="C318">
-        <v>90.88949512383789</v>
+        <v>90.44136571499315</v>
       </c>
       <c r="D318">
-        <v>5.844722360911518</v>
+        <v>5.754391721455733</v>
       </c>
       <c r="E318" t="s">
         <v>64</v>
@@ -5995,13 +5995,13 @@
         <v>50</v>
       </c>
       <c r="B319">
-        <v>104.7741665047963</v>
+        <v>105.3621636633655</v>
       </c>
       <c r="C319">
-        <v>105.5278498991754</v>
+        <v>106.0530960342612</v>
       </c>
       <c r="D319">
-        <v>-0.7536833943790242</v>
+        <v>-0.6909323708957089</v>
       </c>
       <c r="E319" t="s">
         <v>65</v>
@@ -6012,13 +6012,13 @@
         <v>50</v>
       </c>
       <c r="B320">
-        <v>102.7663222370925</v>
+        <v>102.8364888534832</v>
       </c>
       <c r="C320">
-        <v>99.91300706244543</v>
+        <v>99.80328547895101</v>
       </c>
       <c r="D320">
-        <v>2.853315174647022</v>
+        <v>3.033203374532192</v>
       </c>
       <c r="E320" t="s">
         <v>66</v>
@@ -6029,13 +6029,13 @@
         <v>50</v>
       </c>
       <c r="B321">
-        <v>97.80020626629396</v>
+        <v>97.6691334928914</v>
       </c>
       <c r="C321">
-        <v>94.50604123461331</v>
+        <v>94.56785577700826</v>
       </c>
       <c r="D321">
-        <v>3.294165031680649</v>
+        <v>3.101277715883143</v>
       </c>
       <c r="E321" t="s">
         <v>67</v>
@@ -6046,13 +6046,13 @@
         <v>50</v>
       </c>
       <c r="B322">
-        <v>96.58185907713542</v>
+        <v>96.34887052537348</v>
       </c>
       <c r="C322">
-        <v>92.20651515057573</v>
+        <v>92.18726699712664</v>
       </c>
       <c r="D322">
-        <v>4.375343926559694</v>
+        <v>4.161603528246843</v>
       </c>
       <c r="E322" t="s">
         <v>68</v>
@@ -6063,13 +6063,13 @@
         <v>50</v>
       </c>
       <c r="B323">
-        <v>104.939088966752</v>
+        <v>105.1932007752908</v>
       </c>
       <c r="C323">
-        <v>104.0034535332947</v>
+        <v>104.0239457139039</v>
       </c>
       <c r="D323">
-        <v>0.9356354334573211</v>
+        <v>1.169255061386878</v>
       </c>
       <c r="E323" t="s">
         <v>69</v>
@@ -6097,13 +6097,13 @@
         <v>51</v>
       </c>
       <c r="B325">
-        <v>102.5693891448442</v>
+        <v>102.3901845142014</v>
       </c>
       <c r="C325">
-        <v>96.53475413633566</v>
+        <v>95.99719959402552</v>
       </c>
       <c r="D325">
-        <v>6.034635008508531</v>
+        <v>6.392984920175905</v>
       </c>
       <c r="E325" t="s">
         <v>64</v>
@@ -6114,13 +6114,13 @@
         <v>51</v>
       </c>
       <c r="B326">
-        <v>104.1246002298358</v>
+        <v>104.3068404573883</v>
       </c>
       <c r="C326">
-        <v>104.5231890831979</v>
+        <v>105.1099770259277</v>
       </c>
       <c r="D326">
-        <v>-0.3985888533620425</v>
+        <v>-0.8031365685393865</v>
       </c>
       <c r="E326" t="s">
         <v>65</v>
@@ -6131,13 +6131,13 @@
         <v>51</v>
       </c>
       <c r="B327">
-        <v>103.990470790756</v>
+        <v>104.0811965450515</v>
       </c>
       <c r="C327">
-        <v>102.534376568907</v>
+        <v>102.6059846882894</v>
       </c>
       <c r="D327">
-        <v>1.456094221849</v>
+        <v>1.47521185676203</v>
       </c>
       <c r="E327" t="s">
         <v>66</v>
@@ -6148,13 +6148,13 @@
         <v>51</v>
       </c>
       <c r="B328">
-        <v>102.5381886657457</v>
+        <v>102.4245197488043</v>
       </c>
       <c r="C328">
-        <v>97.58848417621684</v>
+        <v>97.4560168516914</v>
       </c>
       <c r="D328">
-        <v>4.949704489528813</v>
+        <v>4.968502897112927</v>
       </c>
       <c r="E328" t="s">
         <v>67</v>
@@ -6165,13 +6165,13 @@
         <v>51</v>
       </c>
       <c r="B329">
-        <v>102.3143782720726</v>
+        <v>102.1672095927148</v>
       </c>
       <c r="C329">
-        <v>96.37822731993201</v>
+        <v>96.14393109250211</v>
       </c>
       <c r="D329">
-        <v>5.936150952140565</v>
+        <v>6.023278500212641</v>
       </c>
       <c r="E329" t="s">
         <v>68</v>
@@ -6182,13 +6182,13 @@
         <v>51</v>
       </c>
       <c r="B330">
-        <v>104.3841229443364</v>
+        <v>104.5344850182434</v>
       </c>
       <c r="C330">
-        <v>104.6926201713064</v>
+        <v>104.948104533828</v>
       </c>
       <c r="D330">
-        <v>-0.3084972269699904</v>
+        <v>-0.4136195155846423</v>
       </c>
       <c r="E330" t="s">
         <v>69</v>
@@ -6216,13 +6216,13 @@
         <v>52</v>
       </c>
       <c r="B332">
-        <v>102.4724893292097</v>
+        <v>102.2934539975734</v>
       </c>
       <c r="C332">
-        <v>96.35106641146771</v>
+        <v>95.81418402392239</v>
       </c>
       <c r="D332">
-        <v>6.121422917741981</v>
+        <v>6.479269973650986</v>
       </c>
       <c r="E332" t="s">
         <v>64</v>
@@ -6233,13 +6233,13 @@
         <v>52</v>
       </c>
       <c r="B333">
-        <v>104.0262311681752</v>
+        <v>104.2082992289185</v>
       </c>
       <c r="C333">
-        <v>104.3305201568943</v>
+        <v>104.9165865190259</v>
       </c>
       <c r="D333">
-        <v>-0.3042889887190796</v>
+        <v>-0.7082872901074211</v>
       </c>
       <c r="E333" t="s">
         <v>65</v>
@@ -6250,13 +6250,13 @@
         <v>52</v>
       </c>
       <c r="B334">
-        <v>103.8922284444636</v>
+        <v>103.9828684879155</v>
       </c>
       <c r="C334">
-        <v>102.3437134491517</v>
+        <v>102.4151712133323</v>
       </c>
       <c r="D334">
-        <v>1.548514995311905</v>
+        <v>1.567697274583224</v>
       </c>
       <c r="E334" t="s">
         <v>66</v>
@@ -6267,13 +6267,13 @@
         <v>52</v>
       </c>
       <c r="B335">
-        <v>102.4413183259684</v>
+        <v>102.3277567948386</v>
       </c>
       <c r="C335">
-        <v>97.40382673883738</v>
+        <v>97.2715882677836</v>
       </c>
       <c r="D335">
-        <v>5.037491587131029</v>
+        <v>5.05616852705505</v>
       </c>
       <c r="E335" t="s">
         <v>67</v>
@@ -6284,13 +6284,13 @@
         <v>52</v>
       </c>
       <c r="B336">
-        <v>102.2177193714593</v>
+        <v>102.0706897259596</v>
       </c>
       <c r="C336">
-        <v>96.19491978588395</v>
+        <v>95.96097932810657</v>
       </c>
       <c r="D336">
-        <v>6.022799585575299</v>
+        <v>6.109710397852979</v>
       </c>
       <c r="E336" t="s">
         <v>68</v>
@@ -6301,13 +6301,13 @@
         <v>52</v>
       </c>
       <c r="B337">
-        <v>104.2855087052072</v>
+        <v>104.4357287283779</v>
       </c>
       <c r="C337">
-        <v>104.4995546813235</v>
+        <v>104.7546602675912</v>
       </c>
       <c r="D337">
-        <v>-0.21404597611631</v>
+        <v>-0.3189315392133238</v>
       </c>
       <c r="E337" t="s">
         <v>69</v>
@@ -6335,13 +6335,13 @@
         <v>53</v>
       </c>
       <c r="B339">
-        <v>99.60019526064582</v>
+        <v>99.30099003129841</v>
       </c>
       <c r="C339">
-        <v>93.31617970552955</v>
+        <v>92.7789031504378</v>
       </c>
       <c r="D339">
-        <v>6.28401555511627</v>
+        <v>6.522086880860613</v>
       </c>
       <c r="E339" t="s">
         <v>64</v>
@@ -6352,13 +6352,13 @@
         <v>53</v>
       </c>
       <c r="B340">
-        <v>102.7866935572146</v>
+        <v>103.096401609571</v>
       </c>
       <c r="C340">
-        <v>102.9470037236309</v>
+        <v>103.5442045044892</v>
       </c>
       <c r="D340">
-        <v>-0.1603101664162381</v>
+        <v>-0.4478028949182402</v>
       </c>
       <c r="E340" t="s">
         <v>65</v>
@@ -6369,13 +6369,13 @@
         <v>53</v>
       </c>
       <c r="B341">
-        <v>102.3745838274864</v>
+        <v>102.4917747241591</v>
       </c>
       <c r="C341">
-        <v>100.2116806783557</v>
+        <v>100.2232924912705</v>
       </c>
       <c r="D341">
-        <v>2.16290314913077</v>
+        <v>2.268482232888616</v>
       </c>
       <c r="E341" t="s">
         <v>66</v>
@@ -6386,13 +6386,13 @@
         <v>53</v>
       </c>
       <c r="B342">
-        <v>99.66936175274516</v>
+        <v>99.51743017110232</v>
       </c>
       <c r="C342">
-        <v>94.88150568603582</v>
+        <v>94.81109255053009</v>
       </c>
       <c r="D342">
-        <v>4.787856066709338</v>
+        <v>4.706337620572228</v>
       </c>
       <c r="E342" t="s">
         <v>67</v>
@@ -6403,13 +6403,13 @@
         <v>53</v>
       </c>
       <c r="B343">
-        <v>99.20460448818741</v>
+        <v>98.99843617019444</v>
       </c>
       <c r="C343">
-        <v>93.40658335906356</v>
+        <v>93.23752496848046</v>
       </c>
       <c r="D343">
-        <v>5.798021129123853</v>
+        <v>5.760911201713981</v>
       </c>
       <c r="E343" t="s">
         <v>68</v>
@@ -6420,13 +6420,13 @@
         <v>53</v>
       </c>
       <c r="B344">
-        <v>103.1965683580116</v>
+        <v>103.4114794590763</v>
       </c>
       <c r="C344">
-        <v>102.8457126163961</v>
+        <v>103.0321097523068</v>
       </c>
       <c r="D344">
-        <v>0.3508557416155327</v>
+        <v>0.3793697067695376</v>
       </c>
       <c r="E344" t="s">
         <v>69</v>
@@ -6454,13 +6454,13 @@
         <v>54</v>
       </c>
       <c r="B346">
-        <v>102.6662889604787</v>
+        <v>102.4869150308295</v>
       </c>
       <c r="C346">
-        <v>96.71844186120352</v>
+        <v>96.1802151641286</v>
       </c>
       <c r="D346">
-        <v>5.94784709927518</v>
+        <v>6.30669986670091</v>
       </c>
       <c r="E346" t="s">
         <v>64</v>
@@ -6471,13 +6471,13 @@
         <v>54</v>
       </c>
       <c r="B347">
-        <v>104.2229692914965</v>
+        <v>104.4053816858582</v>
       </c>
       <c r="C347">
-        <v>104.7158580095015</v>
+        <v>105.3033675328296</v>
       </c>
       <c r="D347">
-        <v>-0.492888718004977</v>
+        <v>-0.8979858469713804</v>
       </c>
       <c r="E347" t="s">
         <v>65</v>
@@ -6488,13 +6488,13 @@
         <v>54</v>
       </c>
       <c r="B348">
-        <v>104.0887131370484</v>
+        <v>104.1795246021874</v>
       </c>
       <c r="C348">
-        <v>102.7250396886622</v>
+        <v>102.7967981632465</v>
       </c>
       <c r="D348">
-        <v>1.363673448386166</v>
+        <v>1.382726438940864</v>
       </c>
       <c r="E348" t="s">
         <v>66</v>
@@ -6505,13 +6505,13 @@
         <v>54</v>
       </c>
       <c r="B349">
-        <v>102.6350590055229</v>
+        <v>102.52128270277</v>
       </c>
       <c r="C349">
-        <v>97.77314161359637</v>
+        <v>97.64044543559912</v>
       </c>
       <c r="D349">
-        <v>4.861917391926525</v>
+        <v>4.880837267170847</v>
       </c>
       <c r="E349" t="s">
         <v>67</v>
@@ -6522,13 +6522,13 @@
         <v>54</v>
       </c>
       <c r="B350">
-        <v>102.4110371726859</v>
+        <v>102.26372945947</v>
       </c>
       <c r="C350">
-        <v>96.56153485398005</v>
+        <v>96.32688285689767</v>
       </c>
       <c r="D350">
-        <v>5.849502318705845</v>
+        <v>5.936846602572317</v>
       </c>
       <c r="E350" t="s">
         <v>68</v>
@@ -6539,13 +6539,13 @@
         <v>54</v>
       </c>
       <c r="B351">
-        <v>104.4827371834657</v>
+        <v>104.6332413081089</v>
       </c>
       <c r="C351">
-        <v>104.8856856612893</v>
+        <v>105.1415488000647</v>
       </c>
       <c r="D351">
-        <v>-0.4029484778235854</v>
+        <v>-0.5083074919558754</v>
       </c>
       <c r="E351" t="s">
         <v>69</v>
@@ -6573,13 +6573,13 @@
         <v>55</v>
       </c>
       <c r="B353">
-        <v>102.8198231993877</v>
+        <v>102.6242949942016</v>
       </c>
       <c r="C353">
-        <v>102.8088985866758</v>
+        <v>102.6133911563739</v>
       </c>
       <c r="D353">
-        <v>0.01092461271188938</v>
+        <v>0.01090383782771198</v>
       </c>
       <c r="E353" t="s">
         <v>64</v>
@@ -6590,13 +6590,13 @@
         <v>55</v>
       </c>
       <c r="B354">
-        <v>104.1496454190348</v>
+        <v>104.348079846679</v>
       </c>
       <c r="C354">
-        <v>104.1385795126281</v>
+        <v>104.3369928566018</v>
       </c>
       <c r="D354">
-        <v>0.01106590640671357</v>
+        <v>0.01108699007720304</v>
       </c>
       <c r="E354" t="s">
         <v>65</v>
@@ -6607,13 +6607,13 @@
         <v>55</v>
       </c>
       <c r="B355">
-        <v>104.0350695871731</v>
+        <v>104.1102578808078</v>
       </c>
       <c r="C355">
-        <v>104.0240158544558</v>
+        <v>104.0991961593295</v>
       </c>
       <c r="D355">
-        <v>0.01105373271735743</v>
+        <v>0.0110617214783133</v>
       </c>
       <c r="E355" t="s">
         <v>66</v>
@@ -6624,13 +6624,13 @@
         <v>55</v>
       </c>
       <c r="B356">
-        <v>102.7931144482502</v>
+        <v>102.6973211422739</v>
       </c>
       <c r="C356">
-        <v>102.7821926733448</v>
+        <v>102.6864095454133</v>
       </c>
       <c r="D356">
-        <v>0.01092177490538404</v>
+        <v>0.01091159686055221</v>
       </c>
       <c r="E356" t="s">
         <v>67</v>
@@ -6641,13 +6641,13 @@
         <v>55</v>
       </c>
       <c r="B357">
-        <v>102.601489741369</v>
+        <v>102.4754517070361</v>
       </c>
       <c r="C357">
-        <v>102.5905883266009</v>
+        <v>102.464563683817</v>
       </c>
       <c r="D357">
-        <v>0.01090141476812789</v>
+        <v>0.01088802321909554</v>
       </c>
       <c r="E357" t="s">
         <v>68</v>
@@ -6658,13 +6658,13 @@
         <v>55</v>
       </c>
       <c r="B358">
-        <v>104.3712733144297</v>
+        <v>104.4996430840696</v>
       </c>
       <c r="C358">
-        <v>104.360183860045</v>
+        <v>104.4885399903888</v>
       </c>
       <c r="D358">
-        <v>0.01108945438467401</v>
+        <v>0.01110309368075946</v>
       </c>
       <c r="E358" t="s">
         <v>69</v>
@@ -6692,13 +6692,13 @@
         <v>56</v>
       </c>
       <c r="B360">
-        <v>96.90933687386934</v>
+        <v>96.73602857100462</v>
       </c>
       <c r="C360">
-        <v>96.86133476431516</v>
+        <v>96.68811260865532</v>
       </c>
       <c r="D360">
-        <v>0.04800210955417583</v>
+        <v>0.04791596234930751</v>
       </c>
       <c r="E360" t="s">
         <v>64</v>
@@ -6709,13 +6709,13 @@
         <v>56</v>
       </c>
       <c r="B361">
-        <v>105.7358604375961</v>
+        <v>105.9253527640014</v>
       </c>
       <c r="C361">
-        <v>105.6833096445418</v>
+        <v>105.8727074850219</v>
       </c>
       <c r="D361">
-        <v>0.05255079305426591</v>
+        <v>0.05264527897955418</v>
       </c>
       <c r="E361" t="s">
         <v>65</v>
@@ -6726,13 +6726,13 @@
         <v>56</v>
       </c>
       <c r="B362">
-        <v>103.3462206739145</v>
+        <v>103.2833657715376</v>
       </c>
       <c r="C362">
-        <v>103.2949059473374</v>
+        <v>103.232084997649</v>
       </c>
       <c r="D362">
-        <v>0.0513147265771039</v>
+        <v>0.05128077388856411</v>
       </c>
       <c r="E362" t="s">
         <v>66</v>
@@ -6743,13 +6743,13 @@
         <v>56</v>
       </c>
       <c r="B363">
-        <v>98.29972201269233</v>
+        <v>98.33739647562983</v>
       </c>
       <c r="C363">
-        <v>98.25099896929063</v>
+        <v>98.28865213330114</v>
       </c>
       <c r="D363">
-        <v>0.04872304340169364</v>
+        <v>0.04874434232868907</v>
       </c>
       <c r="E363" t="s">
         <v>67</v>
@@ -6760,13 +6760,13 @@
         <v>56</v>
       </c>
       <c r="B364">
-        <v>97.04211285052223</v>
+        <v>97.03657660912498</v>
       </c>
       <c r="C364">
-        <v>96.99403786294221</v>
+        <v>96.98850213466766</v>
       </c>
       <c r="D364">
-        <v>0.04807498758002282</v>
+        <v>0.04807447445732294</v>
       </c>
       <c r="E364" t="s">
         <v>68</v>
@@ -6777,13 +6777,13 @@
         <v>56</v>
       </c>
       <c r="B365">
-        <v>105.5898406930666</v>
+        <v>105.5954657722516</v>
       </c>
       <c r="C365">
-        <v>105.5373696937649</v>
+        <v>105.5429942515933</v>
       </c>
       <c r="D365">
-        <v>0.05247099930170407</v>
+        <v>0.05247152065831528</v>
       </c>
       <c r="E365" t="s">
         <v>69</v>
@@ -6811,13 +6811,13 @@
         <v>57</v>
       </c>
       <c r="B367">
-        <v>95.74553054938541</v>
+        <v>95.54628523598248</v>
       </c>
       <c r="C367">
-        <v>95.70202247348386</v>
+        <v>95.50287031314511</v>
       </c>
       <c r="D367">
-        <v>0.04350807590154204</v>
+        <v>0.04341492283737125</v>
       </c>
       <c r="E367" t="s">
         <v>64</v>
@@ -6828,13 +6828,13 @@
         <v>57</v>
       </c>
       <c r="B368">
-        <v>103.4639849949931</v>
+        <v>103.6802279755579</v>
       </c>
       <c r="C368">
-        <v>103.4168382342616</v>
+        <v>103.6329800386192</v>
       </c>
       <c r="D368">
-        <v>0.04714676073153612</v>
+        <v>0.04724793693874574</v>
       </c>
       <c r="E368" t="s">
         <v>65</v>
@@ -6845,13 +6845,13 @@
         <v>57</v>
       </c>
       <c r="B369">
-        <v>101.5452787110711</v>
+        <v>101.4853918780544</v>
       </c>
       <c r="C369">
-        <v>101.4990375156714</v>
+        <v>101.4391793180302</v>
       </c>
       <c r="D369">
-        <v>0.04624119539978722</v>
+        <v>0.04621256002427288</v>
       </c>
       <c r="E369" t="s">
         <v>66</v>
@@ -6862,13 +6862,13 @@
         <v>57</v>
       </c>
       <c r="B370">
-        <v>96.80479345518198</v>
+        <v>96.8422760858582</v>
       </c>
       <c r="C370">
-        <v>96.76078501261122</v>
+        <v>96.79824948434175</v>
       </c>
       <c r="D370">
-        <v>0.04400844257075676</v>
+        <v>0.04402660151644966</v>
       </c>
       <c r="E370" t="s">
         <v>67</v>
@@ -6879,13 +6879,13 @@
         <v>57</v>
       </c>
       <c r="B371">
-        <v>95.70463952161548</v>
+        <v>95.70326182543559</v>
       </c>
       <c r="C371">
-        <v>95.66114970595771</v>
+        <v>95.65977205319282</v>
       </c>
       <c r="D371">
-        <v>0.04348981565776455</v>
+        <v>0.04348977224276496</v>
       </c>
       <c r="E371" t="s">
         <v>68</v>
@@ -6896,13 +6896,13 @@
         <v>57</v>
       </c>
       <c r="B372">
-        <v>103.5081329994673</v>
+        <v>103.5095180256864</v>
       </c>
       <c r="C372">
-        <v>103.460966444945</v>
+        <v>103.4623514275182</v>
       </c>
       <c r="D372">
-        <v>0.04716655452223506</v>
+        <v>0.04716659816817526</v>
       </c>
       <c r="E372" t="s">
         <v>69</v>
@@ -6930,13 +6930,13 @@
         <v>58</v>
       </c>
       <c r="B374">
-        <v>97.45659133719549</v>
+        <v>96.94056297665911</v>
       </c>
       <c r="C374">
-        <v>97.42415451844994</v>
+        <v>96.90829790944079</v>
       </c>
       <c r="D374">
-        <v>0.03243681874555193</v>
+        <v>0.03226506721831868</v>
       </c>
       <c r="E374" t="s">
         <v>64</v>
@@ -6947,13 +6947,13 @@
         <v>58</v>
       </c>
       <c r="B375">
-        <v>102.037149641433</v>
+        <v>102.5803078553577</v>
       </c>
       <c r="C375">
-        <v>102.0031882594186</v>
+        <v>102.5461656920919</v>
       </c>
       <c r="D375">
-        <v>0.03396138201442511</v>
+        <v>0.03414216326586939</v>
       </c>
       <c r="E375" t="s">
         <v>65</v>
@@ -6964,13 +6964,13 @@
         <v>58</v>
       </c>
       <c r="B376">
-        <v>101.279811366006</v>
+        <v>101.3682520262212</v>
       </c>
       <c r="C376">
-        <v>101.2461020515432</v>
+        <v>101.3345132757435</v>
       </c>
       <c r="D376">
-        <v>0.03370931446281134</v>
+        <v>0.03373875047766717</v>
       </c>
       <c r="E376" t="s">
         <v>66</v>
@@ -6981,13 +6981,13 @@
         <v>58</v>
       </c>
       <c r="B377">
-        <v>97.71188135784485</v>
+        <v>97.5705180436503</v>
       </c>
       <c r="C377">
-        <v>97.67935957002736</v>
+        <v>97.53804330627992</v>
       </c>
       <c r="D377">
-        <v>0.03252178781748682</v>
+        <v>0.03247473737037865</v>
       </c>
       <c r="E377" t="s">
         <v>67</v>
@@ -6998,13 +6998,13 @@
         <v>58</v>
       </c>
       <c r="B378">
-        <v>97.03622845099271</v>
+        <v>96.80734762739243</v>
       </c>
       <c r="C378">
-        <v>97.0039315430994</v>
+        <v>96.77512689870554</v>
       </c>
       <c r="D378">
-        <v>0.0322969078933113</v>
+        <v>0.03222072868689452</v>
       </c>
       <c r="E378" t="s">
         <v>68</v>
@@ -7015,13 +7015,13 @@
         <v>58</v>
       </c>
       <c r="B379">
-        <v>102.4791766184484</v>
+        <v>102.7214673011411</v>
       </c>
       <c r="C379">
-        <v>102.4450681150466</v>
+        <v>102.6872781552825</v>
       </c>
       <c r="D379">
-        <v>0.03410850340188176</v>
+        <v>0.03418914585866162</v>
       </c>
       <c r="E379" t="s">
         <v>69</v>
@@ -7049,13 +7049,13 @@
         <v>59</v>
       </c>
       <c r="B381">
-        <v>98.39009767741442</v>
+        <v>98.01993211035413</v>
       </c>
       <c r="C381">
-        <v>98.35893758556499</v>
+        <v>97.98888924974392</v>
       </c>
       <c r="D381">
-        <v>0.03116009184942925</v>
+        <v>0.03104286061021355</v>
       </c>
       <c r="E381" t="s">
         <v>64</v>
@@ -7066,13 +7066,13 @@
         <v>59</v>
       </c>
       <c r="B382">
-        <v>102.7446711855695</v>
+        <v>103.1326794064792</v>
       </c>
       <c r="C382">
-        <v>102.7121320025953</v>
+        <v>103.1000173415068</v>
       </c>
       <c r="D382">
-        <v>0.03253918297420455</v>
+        <v>0.03266206497239921</v>
       </c>
       <c r="E382" t="s">
         <v>65</v>
@@ -7083,13 +7083,13 @@
         <v>59</v>
       </c>
       <c r="B383">
-        <v>102.0525599909961</v>
+        <v>102.1725853422724</v>
       </c>
       <c r="C383">
-        <v>102.0202399992708</v>
+        <v>102.1402273385819</v>
       </c>
       <c r="D383">
-        <v>0.03231999172528788</v>
+        <v>0.03235800369051844</v>
       </c>
       <c r="E383" t="s">
         <v>66</v>
@@ -7100,13 +7100,13 @@
         <v>59</v>
       </c>
       <c r="B384">
-        <v>98.60670832398981</v>
+        <v>98.44511886653196</v>
       </c>
       <c r="C384">
-        <v>98.57547963166331</v>
+        <v>98.41394134950113</v>
       </c>
       <c r="D384">
-        <v>0.0312286923264935</v>
+        <v>0.03117751703082661</v>
       </c>
       <c r="E384" t="s">
         <v>67</v>
@@ -7117,13 +7117,13 @@
         <v>59</v>
       </c>
       <c r="B385">
-        <v>97.96567519535067</v>
+        <v>97.73711499023969</v>
       </c>
       <c r="C385">
-        <v>97.93464951787669</v>
+        <v>97.70616169766171</v>
       </c>
       <c r="D385">
-        <v>0.031025677473977</v>
+        <v>0.0309532925779763</v>
       </c>
       <c r="E385" t="s">
         <v>68</v>
@@ -7134,13 +7134,13 @@
         <v>59</v>
       </c>
       <c r="B386">
-        <v>103.1897979942853</v>
+        <v>103.4311094080434</v>
       </c>
       <c r="C386">
-        <v>103.1571178398864</v>
+        <v>103.3983528304475</v>
       </c>
       <c r="D386">
-        <v>0.03268015439888927</v>
+        <v>0.03275657759587602</v>
       </c>
       <c r="E386" t="s">
         <v>69</v>
@@ -7168,13 +7168,13 @@
         <v>60</v>
       </c>
       <c r="B388">
-        <v>98.76583642143494</v>
+        <v>98.26954336279434</v>
       </c>
       <c r="C388">
-        <v>98.73490143325083</v>
+        <v>98.23876382127544</v>
       </c>
       <c r="D388">
-        <v>0.03093498818411433</v>
+        <v>0.03077954151889628</v>
       </c>
       <c r="E388" t="s">
         <v>64</v>
@@ -7185,13 +7185,13 @@
         <v>60</v>
       </c>
       <c r="B389">
-        <v>103.0792849860917</v>
+        <v>103.5998687995258</v>
       </c>
       <c r="C389">
-        <v>103.0469989590746</v>
+        <v>103.5674197176032</v>
       </c>
       <c r="D389">
-        <v>0.03228602701712191</v>
+        <v>0.03244908192259288</v>
       </c>
       <c r="E389" t="s">
         <v>65</v>
@@ -7202,13 +7202,13 @@
         <v>60</v>
       </c>
       <c r="B390">
-        <v>102.3996396786317</v>
+        <v>102.4946344841521</v>
       </c>
       <c r="C390">
-        <v>102.3675665270411</v>
+        <v>102.4625315787186</v>
       </c>
       <c r="D390">
-        <v>0.03207315159059476</v>
+        <v>0.03210290543350425</v>
       </c>
       <c r="E390" t="s">
         <v>66</v>
@@ -7219,13 +7219,13 @@
         <v>60</v>
       </c>
       <c r="B391">
-        <v>98.97483679759441</v>
+        <v>98.82924840178424</v>
       </c>
       <c r="C391">
-        <v>98.94383634725861</v>
+        <v>98.79829355198673</v>
       </c>
       <c r="D391">
-        <v>0.0310004503357959</v>
+        <v>0.03095484979751006</v>
       </c>
       <c r="E391" t="s">
         <v>67</v>
@@ -7236,13 +7236,13 @@
         <v>60</v>
       </c>
       <c r="B392">
-        <v>98.34013089148243</v>
+        <v>98.11138764668571</v>
       </c>
       <c r="C392">
-        <v>98.30932924085731</v>
+        <v>98.08065764198425</v>
       </c>
       <c r="D392">
-        <v>0.03080165062512208</v>
+        <v>0.03073000470146781</v>
       </c>
       <c r="E392" t="s">
         <v>68</v>
@@ -7253,13 +7253,13 @@
         <v>60</v>
       </c>
       <c r="B393">
-        <v>103.5255058853759</v>
+        <v>103.7668719561599</v>
       </c>
       <c r="C393">
-        <v>103.4930800950687</v>
+        <v>103.7343705662646</v>
       </c>
       <c r="D393">
-        <v>0.03242579030721515</v>
+        <v>0.03250138989530171</v>
       </c>
       <c r="E393" t="s">
         <v>69</v>
@@ -7287,13 +7287,13 @@
         <v>61</v>
       </c>
       <c r="B395">
-        <v>99.05242581475973</v>
+        <v>98.57258321127158</v>
       </c>
       <c r="C395">
-        <v>99.02267447658477</v>
+        <v>98.54297599838627</v>
       </c>
       <c r="D395">
-        <v>0.02975133817496101</v>
+        <v>0.02960721288530976</v>
       </c>
       <c r="E395" t="s">
         <v>64</v>
@@ -7304,13 +7304,13 @@
         <v>61</v>
       </c>
       <c r="B396">
-        <v>103.1668953051401</v>
+        <v>103.669102612936</v>
       </c>
       <c r="C396">
-        <v>103.1359081469212</v>
+        <v>103.6379646119757</v>
       </c>
       <c r="D396">
-        <v>0.03098715821887765</v>
+        <v>0.03113800096026864</v>
       </c>
       <c r="E396" t="s">
         <v>65</v>
@@ -7321,13 +7321,13 @@
         <v>61</v>
       </c>
       <c r="B397">
-        <v>102.539384557055</v>
+        <v>102.6372586905028</v>
       </c>
       <c r="C397">
-        <v>102.5085858776575</v>
+        <v>102.6064306136784</v>
       </c>
       <c r="D397">
-        <v>0.03079867939752035</v>
+        <v>0.03082807682436339</v>
       </c>
       <c r="E397" t="s">
         <v>66</v>
@@ -7338,13 +7338,13 @@
         <v>61</v>
       </c>
       <c r="B398">
-        <v>99.23224191188497</v>
+        <v>99.08561061872874</v>
       </c>
       <c r="C398">
-        <v>99.20243656423503</v>
+        <v>99.05584931318228</v>
       </c>
       <c r="D398">
-        <v>0.02980534764994047</v>
+        <v>0.02976130554645806</v>
       </c>
       <c r="E398" t="s">
         <v>67</v>
@@ -7355,13 +7355,13 @@
         <v>61</v>
       </c>
       <c r="B399">
-        <v>98.62777153068382</v>
+        <v>98.40135323230989</v>
       </c>
       <c r="C399">
-        <v>98.59814774146196</v>
+        <v>98.37179744997738</v>
       </c>
       <c r="D399">
-        <v>0.02962378922185849</v>
+        <v>0.02955578233250833</v>
       </c>
       <c r="E399" t="s">
         <v>68</v>
@@ -7372,13 +7372,13 @@
         <v>61</v>
       </c>
       <c r="B400">
-        <v>103.6110933579421</v>
+        <v>103.849499098109</v>
       </c>
       <c r="C400">
-        <v>103.5799727806134</v>
+        <v>103.8183069133487</v>
       </c>
       <c r="D400">
-        <v>0.03112057732877815</v>
+        <v>0.03119218476028607</v>
       </c>
       <c r="E400" t="s">
         <v>69</v>
@@ -7406,13 +7406,13 @@
         <v>62</v>
       </c>
       <c r="B402">
-        <v>102.267124598571</v>
+        <v>102.0349963696122</v>
       </c>
       <c r="C402">
-        <v>102.2500364445528</v>
+        <v>102.0179470026719</v>
       </c>
       <c r="D402">
-        <v>0.01708815401825348</v>
+        <v>0.01704936694034132</v>
       </c>
       <c r="E402" t="s">
         <v>64</v>
@@ -7423,13 +7423,13 @@
         <v>62</v>
       </c>
       <c r="B403">
-        <v>104.4246944710765</v>
+        <v>104.6622592307138</v>
       </c>
       <c r="C403">
-        <v>104.4072458015316</v>
+        <v>104.6447708656829</v>
       </c>
       <c r="D403">
-        <v>0.01744866954490476</v>
+        <v>0.01748836503084306</v>
       </c>
       <c r="E403" t="s">
         <v>65</v>
@@ -7440,13 +7440,13 @@
         <v>62</v>
       </c>
       <c r="B404">
-        <v>104.2056411158236</v>
+        <v>104.3150231921995</v>
       </c>
       <c r="C404">
-        <v>104.1882290486325</v>
+        <v>104.2975928479933</v>
       </c>
       <c r="D404">
-        <v>0.01741206719115951</v>
+        <v>0.01743034420617562</v>
       </c>
       <c r="E404" t="s">
         <v>66</v>
@@ -7457,13 +7457,13 @@
         <v>62</v>
       </c>
       <c r="B405">
-        <v>102.2560912686474</v>
+        <v>102.1180378861747</v>
       </c>
       <c r="C405">
-        <v>102.239004958225</v>
+        <v>102.1009746435512</v>
       </c>
       <c r="D405">
-        <v>0.01708631042245656</v>
+        <v>0.01706324262354997</v>
       </c>
       <c r="E405" t="s">
         <v>67</v>
@@ -7474,13 +7474,13 @@
         <v>62</v>
       </c>
       <c r="B406">
-        <v>101.9441348839087</v>
+        <v>101.7631399171323</v>
       </c>
       <c r="C406">
-        <v>101.9271006993162</v>
+        <v>101.7461359755909</v>
       </c>
       <c r="D406">
-        <v>0.01703418459248951</v>
+        <v>0.01700394154143225</v>
       </c>
       <c r="E406" t="s">
         <v>68</v>
@@ -7491,13 +7491,13 @@
         <v>62</v>
       </c>
       <c r="B407">
-        <v>104.7555433454067</v>
+        <v>104.9418605728712</v>
       </c>
       <c r="C407">
-        <v>104.7380393932229</v>
+        <v>104.9243254883222</v>
       </c>
       <c r="D407">
-        <v>0.01750395218387268</v>
+        <v>0.01753508454908115</v>
       </c>
       <c r="E407" t="s">
         <v>69</v>

--- a/outputs/bond_results_tier2_oas.xlsx
+++ b/outputs/bond_results_tier2_oas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="81">
   <si>
     <t>bond_id</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>shock</t>
-  </si>
-  <si>
-    <t>Test_change_coupon_type</t>
   </si>
   <si>
     <t>VCBH2230004</t>
@@ -203,6 +200,42 @@
   </si>
   <si>
     <t>TCBL2326005</t>
+  </si>
+  <si>
+    <t>VCB12501</t>
+  </si>
+  <si>
+    <t>VBA12505</t>
+  </si>
+  <si>
+    <t>OCB12501</t>
+  </si>
+  <si>
+    <t>MSB12503</t>
+  </si>
+  <si>
+    <t>PGB12401</t>
+  </si>
+  <si>
+    <t>VPBB2427001</t>
+  </si>
+  <si>
+    <t>HDBL2427010</t>
+  </si>
+  <si>
+    <t>OCBL2427024</t>
+  </si>
+  <si>
+    <t>VBA12503</t>
+  </si>
+  <si>
+    <t>ABBL2426004</t>
+  </si>
+  <si>
+    <t>MSBL2427010</t>
+  </si>
+  <si>
+    <t>ABBL2426002</t>
   </si>
   <si>
     <t>0</t>
@@ -581,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E407"/>
+  <dimension ref="A1:E484"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -606,16 +639,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>78.71632465393753</v>
+        <v>105.3558548807097</v>
       </c>
       <c r="C2">
-        <v>78.61800974190142</v>
+        <v>104.7076704773811</v>
       </c>
       <c r="D2">
-        <v>0.0983149120361162</v>
+        <v>0.6481844033285853</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -623,16 +656,16 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>63.34016979395761</v>
+        <v>100.982680879905</v>
       </c>
       <c r="C3">
-        <v>63.26360245584787</v>
+        <v>100.37691030739</v>
       </c>
       <c r="D3">
-        <v>0.07656733810974004</v>
+        <v>0.6057705725150129</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -640,16 +673,16 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>98.57419652161781</v>
+        <v>110.4266770409442</v>
       </c>
       <c r="C4">
-        <v>98.50691292023195</v>
+        <v>109.7300240556283</v>
       </c>
       <c r="D4">
-        <v>0.06728360138585288</v>
+        <v>0.6966529853158647</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -657,16 +690,16 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>73.36227826110105</v>
+        <v>106.0926527800007</v>
       </c>
       <c r="C5">
-        <v>73.2719020451764</v>
+        <v>105.4378121698606</v>
       </c>
       <c r="D5">
-        <v>0.09037621592464973</v>
+        <v>0.6548406101400985</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -674,16 +707,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>80.90107005226439</v>
+        <v>103.8722132048805</v>
       </c>
       <c r="C6">
-        <v>80.79941649070467</v>
+        <v>103.2385454779229</v>
       </c>
       <c r="D6">
-        <v>0.1016535615597149</v>
+        <v>0.6336677269576114</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -691,16 +724,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>74.43596492462602</v>
+        <v>102.3204628280584</v>
       </c>
       <c r="C7">
-        <v>74.34339778604686</v>
+        <v>101.7016501559655</v>
       </c>
       <c r="D7">
-        <v>0.09256713857915599</v>
+        <v>0.6188126720928437</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -708,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>83.2600690981117</v>
+        <v>108.7533334921368</v>
       </c>
       <c r="C8">
-        <v>83.15564520538081</v>
+        <v>108.0726958682296</v>
       </c>
       <c r="D8">
-        <v>0.1044238927308925</v>
+        <v>0.6806376239072023</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -725,16 +758,16 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>86.92124127858565</v>
+        <v>97.09202204277855</v>
       </c>
       <c r="C9">
-        <v>86.82326312635855</v>
+        <v>96.46447335079897</v>
       </c>
       <c r="D9">
-        <v>0.09797815222709971</v>
+        <v>0.6275486919795839</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -742,16 +775,16 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>75.03330603065312</v>
+        <v>74.98336789213303</v>
       </c>
       <c r="C10">
-        <v>74.94956089270715</v>
+        <v>74.46186728625193</v>
       </c>
       <c r="D10">
-        <v>0.08374513794596794</v>
+        <v>0.5215006058811014</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -759,16 +792,16 @@
         <v>6</v>
       </c>
       <c r="B11">
-        <v>100.8512608725165</v>
+        <v>121.9771603385987</v>
       </c>
       <c r="C11">
-        <v>100.7365841588359</v>
+        <v>127.5809789885077</v>
       </c>
       <c r="D11">
-        <v>0.1146767136805806</v>
+        <v>-5.603818649909002</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -776,16 +809,16 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>85.99968940384476</v>
+        <v>87.35671737834541</v>
       </c>
       <c r="C12">
-        <v>85.90290791572096</v>
+        <v>86.73733347184252</v>
       </c>
       <c r="D12">
-        <v>0.09678148812379561</v>
+        <v>0.6193839065028897</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -793,16 +826,16 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>85.29564603735928</v>
+        <v>101.0067712390315</v>
       </c>
       <c r="C13">
-        <v>85.19952411315292</v>
+        <v>102.2768156427455</v>
       </c>
       <c r="D13">
-        <v>0.09612192420635779</v>
+        <v>-1.270044403714067</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -810,16 +843,16 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>80.97660266628367</v>
+        <v>92.26266140219298</v>
       </c>
       <c r="C14">
-        <v>80.8856624815361</v>
+        <v>92.00448874252361</v>
       </c>
       <c r="D14">
-        <v>0.09094018474756638</v>
+        <v>0.2581726596693699</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -827,16 +860,16 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>93.32446317713837</v>
+        <v>101.8308889718141</v>
       </c>
       <c r="C15">
-        <v>93.21889753467545</v>
+        <v>101.1683488599022</v>
       </c>
       <c r="D15">
-        <v>0.1055656424629206</v>
+        <v>0.6625401119118948</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -844,16 +877,16 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>96.0873820711391</v>
+        <v>97.24203766476884</v>
       </c>
       <c r="C16">
-        <v>96.0395235455366</v>
+        <v>96.61493084370302</v>
       </c>
       <c r="D16">
-        <v>0.04785852560250703</v>
+        <v>0.6271068210658228</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -861,16 +894,16 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>73.16001507507673</v>
+        <v>75.14835691251052</v>
       </c>
       <c r="C17">
-        <v>73.07104842573644</v>
+        <v>74.62668540787804</v>
       </c>
       <c r="D17">
-        <v>0.08896664934029275</v>
+        <v>0.5216715046324794</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -878,16 +911,16 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>122.1394919694088</v>
+        <v>122.0792850475169</v>
       </c>
       <c r="C18">
-        <v>129.1953121211816</v>
+        <v>127.6962238025228</v>
       </c>
       <c r="D18">
-        <v>-7.05582015177275</v>
+        <v>-5.616938755005847</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -895,16 +928,16 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>85.7943923699931</v>
+        <v>87.51936197340409</v>
       </c>
       <c r="C19">
-        <v>85.68822425377616</v>
+        <v>86.89982305694788</v>
       </c>
       <c r="D19">
-        <v>0.1061681162169492</v>
+        <v>0.6195389164562073</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -912,16 +945,16 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>100.4063255310315</v>
+        <v>101.1359492865264</v>
       </c>
       <c r="C20">
-        <v>102.4127438175135</v>
+        <v>102.4147705121433</v>
       </c>
       <c r="D20">
-        <v>-2.006418286482003</v>
+        <v>-1.278821225616866</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -929,16 +962,16 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>91.31870321484155</v>
+        <v>92.40906601624079</v>
       </c>
       <c r="C21">
-        <v>91.59955250823691</v>
+        <v>92.15339378994757</v>
       </c>
       <c r="D21">
-        <v>-0.280849293395363</v>
+        <v>0.2556722262932141</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -946,16 +979,16 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>100.7741696367547</v>
+        <v>101.9829483280458</v>
       </c>
       <c r="C22">
-        <v>100.722289655168</v>
+        <v>101.3205000901741</v>
       </c>
       <c r="D22">
-        <v>0.05187998158672258</v>
+        <v>0.6624482378716721</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -963,16 +996,16 @@
         <v>8</v>
       </c>
       <c r="B23">
-        <v>96.23755522659482</v>
+        <v>97.32391319075778</v>
       </c>
       <c r="C23">
-        <v>96.19016607626369</v>
+        <v>96.69763981395224</v>
       </c>
       <c r="D23">
-        <v>0.04738915033112789</v>
+        <v>0.6262733768055426</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -980,16 +1013,16 @@
         <v>8</v>
       </c>
       <c r="B24">
-        <v>73.32533869041558</v>
+        <v>75.23490206800538</v>
       </c>
       <c r="C24">
-        <v>73.23634164617658</v>
+        <v>74.71310215842735</v>
       </c>
       <c r="D24">
-        <v>0.08899704423899379</v>
+        <v>0.5217999095780357</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -997,16 +1030,16 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>122.2386764833912</v>
+        <v>122.1253997184364</v>
       </c>
       <c r="C25">
-        <v>129.3079944035326</v>
+        <v>127.7689456516105</v>
       </c>
       <c r="D25">
-        <v>-7.069317920141415</v>
+        <v>-5.64354593317411</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1014,16 +1047,16 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>85.95744130300061</v>
+        <v>87.60680211223351</v>
       </c>
       <c r="C26">
-        <v>85.85124637533804</v>
+        <v>86.9871449150418</v>
       </c>
       <c r="D26">
-        <v>0.1061949276625711</v>
+        <v>0.6196571971917137</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1031,16 +1064,16 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>100.5348722761798</v>
+        <v>101.2011677910479</v>
       </c>
       <c r="C27">
-        <v>102.5502107518638</v>
+        <v>102.492667279295</v>
       </c>
       <c r="D27">
-        <v>-2.015338475683947</v>
+        <v>-1.291499488247112</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1048,16 +1081,16 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>91.46530491861044</v>
+        <v>92.48671988015364</v>
       </c>
       <c r="C28">
-        <v>91.74865411998088</v>
+        <v>92.23442082606128</v>
       </c>
       <c r="D28">
-        <v>-0.2833492013704415</v>
+        <v>0.2522990540923615</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1065,16 +1098,16 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>100.9263533288769</v>
+        <v>102.0670451692874</v>
       </c>
       <c r="C29">
-        <v>100.8746130156137</v>
+        <v>101.4049420949977</v>
       </c>
       <c r="D29">
-        <v>0.05174031326323814</v>
+        <v>0.6621030742896892</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1082,16 +1115,16 @@
         <v>9</v>
       </c>
       <c r="B30">
-        <v>96.31805870373194</v>
+        <v>103.3468779311886</v>
       </c>
       <c r="C30">
-        <v>96.27068090419684</v>
+        <v>102.7705452561677</v>
       </c>
       <c r="D30">
-        <v>0.04737779953509857</v>
+        <v>0.5763326750209359</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1099,16 +1132,16 @@
         <v>9</v>
       </c>
       <c r="B31">
-        <v>73.41037882937765</v>
+        <v>98.65607638568575</v>
       </c>
       <c r="C31">
-        <v>73.32137458039705</v>
+        <v>98.11205071062247</v>
       </c>
       <c r="D31">
-        <v>0.08900424898060066</v>
+        <v>0.5440256750632813</v>
       </c>
       <c r="E31" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1116,16 +1149,16 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>122.2953547634925</v>
+        <v>108.5151943918809</v>
       </c>
       <c r="C32">
-        <v>129.3774353419545</v>
+        <v>107.9032075278587</v>
       </c>
       <c r="D32">
-        <v>-7.082080578462083</v>
+        <v>0.6119868640222137</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1133,16 +1166,16 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>86.04141910664816</v>
+        <v>105.1104787047452</v>
       </c>
       <c r="C33">
-        <v>85.93521531143489</v>
+        <v>104.5237488143508</v>
       </c>
       <c r="D33">
-        <v>0.1062037952132755</v>
+        <v>0.5867298903944373</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1150,16 +1183,16 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>100.6069685115668</v>
+        <v>100.7484503929038</v>
       </c>
       <c r="C34">
-        <v>102.6271651829572</v>
+        <v>100.1884863704874</v>
       </c>
       <c r="D34">
-        <v>-2.020196671390323</v>
+        <v>0.5599640224164091</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1167,16 +1200,16 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>91.54488030084367</v>
+        <v>99.20249025595857</v>
       </c>
       <c r="C35">
-        <v>91.82897216852442</v>
+        <v>98.65325605970187</v>
       </c>
       <c r="D35">
-        <v>-0.2840918676807433</v>
+        <v>0.5492341962566911</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1184,16 +1217,16 @@
         <v>9</v>
       </c>
       <c r="B36">
-        <v>101.0070792462293</v>
+        <v>107.8308061572943</v>
       </c>
       <c r="C36">
-        <v>100.9552871817401</v>
+        <v>107.2251303710519</v>
       </c>
       <c r="D36">
-        <v>0.05179206448924845</v>
+        <v>0.6056757862424007</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1201,16 +1234,16 @@
         <v>10</v>
       </c>
       <c r="B37">
-        <v>88.37446227582153</v>
+        <v>102.6211328490372</v>
       </c>
       <c r="C37">
-        <v>88.28607311972657</v>
+        <v>102.0129371990874</v>
       </c>
       <c r="D37">
-        <v>0.08838915609496212</v>
+        <v>0.6081956499497636</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1218,16 +1251,16 @@
         <v>10</v>
       </c>
       <c r="B38">
-        <v>78.84230452278327</v>
+        <v>97.67869643262148</v>
       </c>
       <c r="C38">
-        <v>78.76378348902765</v>
+        <v>97.10818450217566</v>
       </c>
       <c r="D38">
-        <v>0.07852103375562081</v>
+        <v>0.5705119304458179</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1235,16 +1268,16 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>99.1137789381423</v>
+        <v>108.1366894136391</v>
       </c>
       <c r="C39">
-        <v>99.01426042210477</v>
+        <v>107.4864107167657</v>
       </c>
       <c r="D39">
-        <v>0.09951851603753425</v>
+        <v>0.650278696873329</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1252,16 +1285,16 @@
         <v>10</v>
       </c>
       <c r="B40">
-        <v>89.10696596051547</v>
+        <v>104.2227211759986</v>
       </c>
       <c r="C40">
-        <v>89.0178821029557</v>
+        <v>103.6046012065446</v>
       </c>
       <c r="D40">
-        <v>0.08908385755977122</v>
+        <v>0.6181199694539714</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1269,16 +1302,16 @@
         <v>10</v>
       </c>
       <c r="B41">
-        <v>85.66500795065281</v>
+        <v>100.1518980561162</v>
       </c>
       <c r="C41">
-        <v>85.5793624016481</v>
+        <v>99.56057806900918</v>
       </c>
       <c r="D41">
-        <v>0.08564554900470966</v>
+        <v>0.5913199871070276</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1286,16 +1319,16 @@
         <v>10</v>
       </c>
       <c r="B42">
-        <v>82.41010199890407</v>
+        <v>98.49349071246742</v>
       </c>
       <c r="C42">
-        <v>82.32783250958995</v>
+        <v>97.91491282849415</v>
       </c>
       <c r="D42">
-        <v>0.08226948931411471</v>
+        <v>0.5785778839732671</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1303,16 +1336,16 @@
         <v>10</v>
       </c>
       <c r="B43">
-        <v>94.78117370857986</v>
+        <v>107.1281530642702</v>
       </c>
       <c r="C43">
-        <v>94.68620558363493</v>
+        <v>106.4876211729209</v>
       </c>
       <c r="D43">
-        <v>0.09496812494492701</v>
+        <v>0.6405318913493403</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1320,16 +1353,16 @@
         <v>11</v>
       </c>
       <c r="B44">
-        <v>87.61504534942506</v>
+        <v>99.75967981559688</v>
       </c>
       <c r="C44">
-        <v>87.52139258207693</v>
+        <v>99.33504620677651</v>
       </c>
       <c r="D44">
-        <v>0.09365276734813222</v>
+        <v>0.4246336088203719</v>
       </c>
       <c r="E44" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1337,16 +1370,16 @@
         <v>11</v>
       </c>
       <c r="B45">
-        <v>76.94096988038916</v>
+        <v>84.47340366894805</v>
       </c>
       <c r="C45">
-        <v>76.85923040090063</v>
+        <v>83.89993147352837</v>
       </c>
       <c r="D45">
-        <v>0.08173947948853311</v>
+        <v>0.5734721954196829</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1354,16 +1387,16 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>99.86161452445853</v>
+        <v>105.6356808278303</v>
       </c>
       <c r="C46">
-        <v>99.75427432056182</v>
+        <v>117.9927480839997</v>
       </c>
       <c r="D46">
-        <v>0.1073402038967117</v>
+        <v>-12.35706725616946</v>
       </c>
       <c r="E46" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1371,16 +1404,16 @@
         <v>11</v>
       </c>
       <c r="B47">
-        <v>87.6865299359411</v>
+        <v>97.06312051428455</v>
       </c>
       <c r="C47">
-        <v>87.59289384743944</v>
+        <v>96.4254393517364</v>
       </c>
       <c r="D47">
-        <v>0.09363608850165406</v>
+        <v>0.637681162548148</v>
       </c>
       <c r="E47" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1388,16 +1421,16 @@
         <v>11</v>
       </c>
       <c r="B48">
-        <v>85.29115221602724</v>
+        <v>98.54547550556917</v>
       </c>
       <c r="C48">
-        <v>85.20000042177021</v>
+        <v>98.89084709266055</v>
       </c>
       <c r="D48">
-        <v>0.09115179425702991</v>
+        <v>-0.3453715870913783</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1405,16 +1438,16 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <v>81.54503136638495</v>
+        <v>93.46633087547875</v>
       </c>
       <c r="C49">
-        <v>81.45807084730674</v>
+        <v>92.88012891705121</v>
       </c>
       <c r="D49">
-        <v>0.0869605190782039</v>
+        <v>0.5862019584275373</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1422,16 +1455,16 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>94.15037749128069</v>
+        <v>104.9303996278008</v>
       </c>
       <c r="C50">
-        <v>94.049512049204</v>
+        <v>106.2500600533418</v>
       </c>
       <c r="D50">
-        <v>0.1008654420766959</v>
+        <v>-1.319660425540988</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1439,16 +1472,16 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>98.85693377104015</v>
+        <v>100.459684164911</v>
       </c>
       <c r="C51">
-        <v>98.90208347664061</v>
+        <v>100.0639128115468</v>
       </c>
       <c r="D51">
-        <v>-0.0451497056004655</v>
+        <v>0.3957713533641964</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1456,16 +1489,16 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>82.81602187334356</v>
+        <v>85.3648078199769</v>
       </c>
       <c r="C52">
-        <v>82.71743114124133</v>
+        <v>84.79130881591067</v>
       </c>
       <c r="D52">
-        <v>0.09859073210222391</v>
+        <v>0.5734990040662353</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1473,16 +1506,16 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>105.4908939437536</v>
+        <v>105.7226258548094</v>
       </c>
       <c r="C53">
-        <v>118.6865860639606</v>
+        <v>118.4714978045451</v>
       </c>
       <c r="D53">
-        <v>-13.19569212020704</v>
+        <v>-12.74887194973572</v>
       </c>
       <c r="E53" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1490,16 +1523,16 @@
         <v>12</v>
       </c>
       <c r="B54">
-        <v>95.69715566890928</v>
+        <v>97.93953988240595</v>
       </c>
       <c r="C54">
-        <v>95.59405766849781</v>
+        <v>97.3093517209676</v>
       </c>
       <c r="D54">
-        <v>0.1030980004114639</v>
+        <v>0.6301881614383547</v>
       </c>
       <c r="E54" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1507,16 +1540,16 @@
         <v>12</v>
       </c>
       <c r="B55">
-        <v>98.01465036988375</v>
+        <v>99.22760723515724</v>
       </c>
       <c r="C55">
-        <v>98.74748079725748</v>
+        <v>99.49731002121098</v>
       </c>
       <c r="D55">
-        <v>-0.7328304273737274</v>
+        <v>-0.2697027860537418</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1524,16 +1557,16 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>92.55242456610313</v>
+        <v>94.1716454903549</v>
       </c>
       <c r="C56">
-        <v>92.47635164178874</v>
+        <v>93.57282722301071</v>
       </c>
       <c r="D56">
-        <v>0.0760729243143885</v>
+        <v>0.5988182673441997</v>
       </c>
       <c r="E56" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1541,16 +1574,16 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>104.3386574389924</v>
+        <v>105.3495730475823</v>
       </c>
       <c r="C57">
-        <v>105.785783235108</v>
+        <v>107.0190058827796</v>
       </c>
       <c r="D57">
-        <v>-1.447125796115543</v>
+        <v>-1.669432835197284</v>
       </c>
       <c r="E57" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1558,16 +1591,16 @@
         <v>13</v>
       </c>
       <c r="B58">
-        <v>99.58824786548189</v>
+        <v>100.5343170218006</v>
       </c>
       <c r="C58">
-        <v>99.62765858831003</v>
+        <v>100.143264225699</v>
       </c>
       <c r="D58">
-        <v>-0.03941072282813707</v>
+        <v>0.3910527961016328</v>
       </c>
       <c r="E58" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1575,16 +1608,16 @@
         <v>13</v>
       </c>
       <c r="B59">
-        <v>83.71008709515908</v>
+        <v>85.45327224852259</v>
       </c>
       <c r="C59">
-        <v>83.61147406985656</v>
+        <v>84.87973460032437</v>
       </c>
       <c r="D59">
-        <v>0.09861302530252658</v>
+        <v>0.5735376481982257</v>
       </c>
       <c r="E59" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1592,16 +1625,16 @@
         <v>13</v>
       </c>
       <c r="B60">
-        <v>105.5920839796043</v>
+        <v>105.7155621618096</v>
       </c>
       <c r="C60">
-        <v>119.1460400258675</v>
+        <v>118.5367212442669</v>
       </c>
       <c r="D60">
-        <v>-13.5539560462632</v>
+        <v>-12.82115908245729</v>
       </c>
       <c r="E60" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1609,16 +1642,16 @@
         <v>13</v>
       </c>
       <c r="B61">
-        <v>96.58436819672279</v>
+        <v>98.02794300383574</v>
       </c>
       <c r="C61">
-        <v>96.48025477866942</v>
+        <v>97.39816694748393</v>
       </c>
       <c r="D61">
-        <v>0.1041134180533732</v>
+        <v>0.6297760563518153</v>
       </c>
       <c r="E61" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1626,16 +1659,16 @@
         <v>13</v>
       </c>
       <c r="B62">
-        <v>98.7012646695962</v>
+        <v>99.30242585294116</v>
       </c>
       <c r="C62">
-        <v>99.34578045075077</v>
+        <v>99.56905616827829</v>
       </c>
       <c r="D62">
-        <v>-0.644515781154567</v>
+        <v>-0.2666303153371388</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1643,16 +1676,16 @@
         <v>13</v>
       </c>
       <c r="B63">
-        <v>93.25223353613731</v>
+        <v>94.24958314182035</v>
       </c>
       <c r="C63">
-        <v>93.16602179118541</v>
+        <v>93.64946477492761</v>
       </c>
       <c r="D63">
-        <v>0.08621174495189621</v>
+        <v>0.6001183668927439</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1660,16 +1693,16 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>104.7834777442241</v>
+        <v>105.383987243085</v>
       </c>
       <c r="C64">
-        <v>106.5511506961706</v>
+        <v>107.101295319296</v>
       </c>
       <c r="D64">
-        <v>-1.767672951946466</v>
+        <v>-1.717308076210941</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1677,16 +1710,16 @@
         <v>14</v>
       </c>
       <c r="B65">
-        <v>99.63313074564924</v>
+        <v>96.96584320856537</v>
       </c>
       <c r="C65">
-        <v>99.67081786330752</v>
+        <v>96.33427139565985</v>
       </c>
       <c r="D65">
-        <v>-0.03768711765827959</v>
+        <v>0.6315718129055199</v>
       </c>
       <c r="E65" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1694,16 +1727,16 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>83.76372136600092</v>
+        <v>92.35900983721749</v>
       </c>
       <c r="C66">
-        <v>83.66511553908987</v>
+        <v>91.77168337289662</v>
       </c>
       <c r="D66">
-        <v>0.09860582691105435</v>
+        <v>0.5873264643208671</v>
       </c>
       <c r="E66" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1711,16 +1744,16 @@
         <v>14</v>
       </c>
       <c r="B67">
-        <v>105.568653199339</v>
+        <v>102.1960799416092</v>
       </c>
       <c r="C67">
-        <v>119.17311512392</v>
+        <v>102.063345073874</v>
       </c>
       <c r="D67">
-        <v>-13.60446192458103</v>
+        <v>0.1327348677351665</v>
       </c>
       <c r="E67" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1728,16 +1761,16 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>96.63674048862968</v>
+        <v>95.59094180739297</v>
       </c>
       <c r="C68">
-        <v>96.5323188200731</v>
+        <v>94.97210770622337</v>
       </c>
       <c r="D68">
-        <v>0.1044216685565829</v>
+        <v>0.6188341011695968</v>
       </c>
       <c r="E68" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1745,16 +1778,16 @@
         <v>14</v>
       </c>
       <c r="B69">
-        <v>98.74873191723651</v>
+        <v>97.42770346846758</v>
       </c>
       <c r="C69">
-        <v>99.38212623982817</v>
+        <v>97.10747034180359</v>
       </c>
       <c r="D69">
-        <v>-0.6333943225916556</v>
+        <v>0.3202331266639931</v>
       </c>
       <c r="E69" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1762,16 +1795,16 @@
         <v>14</v>
       </c>
       <c r="B70">
-        <v>93.29527137514538</v>
+        <v>95.58576678952241</v>
       </c>
       <c r="C70">
-        <v>93.20783841120564</v>
+        <v>95.12670160266114</v>
       </c>
       <c r="D70">
-        <v>0.0874329639397331</v>
+        <v>0.4590651868612667</v>
       </c>
       <c r="E70" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1779,16 +1812,16 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>104.7954459734264</v>
+        <v>98.39549893398768</v>
       </c>
       <c r="C71">
-        <v>106.5958213787489</v>
+        <v>97.80969234567802</v>
       </c>
       <c r="D71">
-        <v>-1.800375405322569</v>
+        <v>0.5858065883096657</v>
       </c>
       <c r="E71" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1796,16 +1829,16 @@
         <v>15</v>
       </c>
       <c r="B72">
-        <v>72.50690857839989</v>
+        <v>104.9301936203262</v>
       </c>
       <c r="C72">
-        <v>72.41361652806917</v>
+        <v>104.2798834142228</v>
       </c>
       <c r="D72">
-        <v>0.0932920503307173</v>
+        <v>0.6503102061034127</v>
       </c>
       <c r="E72" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1813,16 +1846,16 @@
         <v>15</v>
       </c>
       <c r="B73">
-        <v>58.62966561048167</v>
+        <v>100.4135097417488</v>
       </c>
       <c r="C73">
-        <v>58.55562741866084</v>
+        <v>99.80640050269325</v>
       </c>
       <c r="D73">
-        <v>0.07403819182083282</v>
+        <v>0.6071092390555748</v>
       </c>
       <c r="E73" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1830,16 +1863,16 @@
         <v>15</v>
       </c>
       <c r="B74">
-        <v>90.05768349388133</v>
+        <v>110.1631545527275</v>
       </c>
       <c r="C74">
-        <v>89.94253343742584</v>
+        <v>109.4634261233845</v>
       </c>
       <c r="D74">
-        <v>0.1151500564554908</v>
+        <v>0.6997284293429544</v>
       </c>
       <c r="E74" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1847,16 +1880,16 @@
         <v>15</v>
       </c>
       <c r="B75">
-        <v>68.30858423561104</v>
+        <v>105.7255113974568</v>
       </c>
       <c r="C75">
-        <v>68.22127810194947</v>
+        <v>105.0685509442034</v>
       </c>
       <c r="D75">
-        <v>0.08730613366157058</v>
+        <v>0.6569604532534612</v>
       </c>
       <c r="E75" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1864,16 +1897,16 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>73.76176750007559</v>
+        <v>103.3626740092489</v>
       </c>
       <c r="C76">
-        <v>73.66657683770188</v>
+        <v>102.7270219318692</v>
       </c>
       <c r="D76">
-        <v>0.09519066237371021</v>
+        <v>0.635652077379703</v>
       </c>
       <c r="E76" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1881,16 +1914,16 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>68.1142835451779</v>
+        <v>101.7624126345919</v>
       </c>
       <c r="C77">
-        <v>68.02695054345531</v>
+        <v>101.1419143925872</v>
       </c>
       <c r="D77">
-        <v>0.08733300172258396</v>
+        <v>0.6204982420047571</v>
       </c>
       <c r="E77" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1898,16 +1931,16 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>77.19752762486092</v>
+        <v>108.4687352075977</v>
       </c>
       <c r="C78">
-        <v>77.09786578828293</v>
+        <v>107.785487216688</v>
       </c>
       <c r="D78">
-        <v>0.09966183657799377</v>
+        <v>0.683247990909706</v>
       </c>
       <c r="E78" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1915,16 +1948,16 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>86.52724841860909</v>
+        <v>105.6910962016474</v>
       </c>
       <c r="C79">
-        <v>86.42904522660545</v>
+        <v>107.187755861152</v>
       </c>
       <c r="D79">
-        <v>0.0982031920036377</v>
+        <v>-1.496659659504573</v>
       </c>
       <c r="E79" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1932,16 +1965,16 @@
         <v>16</v>
       </c>
       <c r="B80">
-        <v>74.55419715792451</v>
+        <v>89.92747435918419</v>
       </c>
       <c r="C80">
-        <v>74.47039489372681</v>
+        <v>89.31949099262198</v>
       </c>
       <c r="D80">
-        <v>0.08380226419770054</v>
+        <v>0.607983366562209</v>
       </c>
       <c r="E80" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1949,16 +1982,16 @@
         <v>16</v>
       </c>
       <c r="B81">
-        <v>100.5810528613585</v>
+        <v>112.6738017709954</v>
       </c>
       <c r="C81">
-        <v>100.4659238567334</v>
+        <v>129.3209812822326</v>
       </c>
       <c r="D81">
-        <v>0.1151290046250892</v>
+        <v>-16.64717951123716</v>
       </c>
       <c r="E81" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1966,16 +1999,16 @@
         <v>16</v>
       </c>
       <c r="B82">
-        <v>85.5207596547053</v>
+        <v>103.1865205756935</v>
       </c>
       <c r="C82">
-        <v>85.42386762148477</v>
+        <v>102.7078429815126</v>
       </c>
       <c r="D82">
-        <v>0.0968920332205272</v>
+        <v>0.4786775941809509</v>
       </c>
       <c r="E82" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1983,16 +2016,16 @@
         <v>16</v>
       </c>
       <c r="B83">
-        <v>84.96623674114498</v>
+        <v>102.7445071093657</v>
       </c>
       <c r="C83">
-        <v>84.86981408036499</v>
+        <v>107.8516598929049</v>
       </c>
       <c r="D83">
-        <v>0.09642266077999295</v>
+        <v>-5.107152783539235</v>
       </c>
       <c r="E83" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2000,16 +2033,16 @@
         <v>16</v>
       </c>
       <c r="B84">
-        <v>80.60364191457228</v>
+        <v>99.53223723056801</v>
       </c>
       <c r="C84">
-        <v>80.51247804431407</v>
+        <v>100.654873157534</v>
       </c>
       <c r="D84">
-        <v>0.09116387025821382</v>
+        <v>-1.122635926965984</v>
       </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2017,16 +2050,16 @@
         <v>16</v>
       </c>
       <c r="B85">
-        <v>92.90662244133209</v>
+        <v>111.4091418980142</v>
       </c>
       <c r="C85">
-        <v>92.80083138432894</v>
+        <v>114.1585941643218</v>
       </c>
       <c r="D85">
-        <v>0.1057910570031453</v>
+        <v>-2.749452266307628</v>
       </c>
       <c r="E85" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2034,16 +2067,16 @@
         <v>17</v>
       </c>
       <c r="B86">
-        <v>104.9060519405605</v>
+        <v>105.9520133189514</v>
       </c>
       <c r="C86">
-        <v>106.7151637579515</v>
+        <v>107.488465944757</v>
       </c>
       <c r="D86">
-        <v>-1.809111817391042</v>
+        <v>-1.536452625805666</v>
       </c>
       <c r="E86" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2051,16 +2084,16 @@
         <v>17</v>
       </c>
       <c r="B87">
-        <v>88.09343694273259</v>
+        <v>90.28850647214784</v>
       </c>
       <c r="C87">
-        <v>87.98996855023987</v>
+        <v>89.68037551862515</v>
       </c>
       <c r="D87">
-        <v>0.1034683924927293</v>
+        <v>0.6081309535226893</v>
       </c>
       <c r="E87" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2068,16 +2101,16 @@
         <v>17</v>
       </c>
       <c r="B88">
-        <v>112.4103568497599</v>
+        <v>112.7706827637671</v>
       </c>
       <c r="C88">
-        <v>130.2055060833671</v>
+        <v>129.523757392709</v>
       </c>
       <c r="D88">
-        <v>-17.79514923360723</v>
+        <v>-16.7530746289419</v>
       </c>
       <c r="E88" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2085,16 +2118,16 @@
         <v>17</v>
       </c>
       <c r="B89">
-        <v>101.7237194586253</v>
+        <v>103.5461732996801</v>
       </c>
       <c r="C89">
-        <v>101.7582080332541</v>
+        <v>103.0753521559928</v>
       </c>
       <c r="D89">
-        <v>-0.0344885746287531</v>
+        <v>0.4708211436872887</v>
       </c>
       <c r="E89" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2102,16 +2135,16 @@
         <v>17</v>
       </c>
       <c r="B90">
-        <v>102.1888761625142</v>
+        <v>102.9976039036995</v>
       </c>
       <c r="C90">
-        <v>107.7366201313917</v>
+        <v>108.0946229222276</v>
       </c>
       <c r="D90">
-        <v>-5.547743968877569</v>
+        <v>-5.097019018528073</v>
       </c>
       <c r="E90" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2119,16 +2152,16 @@
         <v>17</v>
       </c>
       <c r="B91">
-        <v>98.72159344539568</v>
+        <v>99.8223082751081</v>
       </c>
       <c r="C91">
-        <v>100.2111485123645</v>
+        <v>100.9331577224844</v>
       </c>
       <c r="D91">
-        <v>-1.489555066968776</v>
+        <v>-1.110849447376282</v>
       </c>
       <c r="E91" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2136,16 +2169,16 @@
         <v>17</v>
       </c>
       <c r="B92">
-        <v>110.6291481348876</v>
+        <v>111.6121381943773</v>
       </c>
       <c r="C92">
-        <v>113.6552054974807</v>
+        <v>114.4844576936109</v>
       </c>
       <c r="D92">
-        <v>-3.026057362593079</v>
+        <v>-2.872319499233598</v>
       </c>
       <c r="E92" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2153,16 +2186,16 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>105.1937845505193</v>
+        <v>96.39449188967073</v>
       </c>
       <c r="C93">
-        <v>107.0370347979289</v>
+        <v>95.85556422492522</v>
       </c>
       <c r="D93">
-        <v>-1.843250247409628</v>
+        <v>0.5389276647455148</v>
       </c>
       <c r="E93" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2170,16 +2203,16 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>88.4777508710103</v>
+        <v>91.23498591742947</v>
       </c>
       <c r="C94">
-        <v>88.37418992314157</v>
+        <v>90.68112678015068</v>
       </c>
       <c r="D94">
-        <v>0.1035609478687292</v>
+        <v>0.553859137278792</v>
       </c>
       <c r="E94" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2187,16 +2220,16 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>112.531105728568</v>
+        <v>101.5405205252423</v>
       </c>
       <c r="C95">
-        <v>130.4228390065322</v>
+        <v>102.0462437022581</v>
       </c>
       <c r="D95">
-        <v>-17.89173327796421</v>
+        <v>-0.5057231770157387</v>
       </c>
       <c r="E95" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2204,16 +2237,16 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>102.106614920987</v>
+        <v>96.38873197328107</v>
       </c>
       <c r="C96">
-        <v>102.1496411407902</v>
+        <v>95.86956788125727</v>
       </c>
       <c r="D96">
-        <v>-0.04302621980319543</v>
+        <v>0.5191640920238001</v>
       </c>
       <c r="E96" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2221,16 +2254,16 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>102.4686903782579</v>
+        <v>95.23487463733677</v>
       </c>
       <c r="C97">
-        <v>107.9980610761059</v>
+        <v>95.03867722588078</v>
       </c>
       <c r="D97">
-        <v>-5.529370697848051</v>
+        <v>0.1961974114559979</v>
       </c>
       <c r="E97" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2238,16 +2271,16 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>99.0358033995456</v>
+        <v>93.44037894514869</v>
       </c>
       <c r="C98">
-        <v>100.510222208397</v>
+        <v>93.04630396644799</v>
       </c>
       <c r="D98">
-        <v>-1.474418808851425</v>
+        <v>0.3940749787007007</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2255,16 +2288,16 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>110.8857823769716</v>
+        <v>99.35907751108259</v>
       </c>
       <c r="C99">
-        <v>114.002589482156</v>
+        <v>99.03302538181734</v>
       </c>
       <c r="D99">
-        <v>-3.116807105184421</v>
+        <v>0.3260521292652498</v>
       </c>
       <c r="E99" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2272,16 +2305,16 @@
         <v>19</v>
       </c>
       <c r="B100">
-        <v>75.36246684023007</v>
+        <v>103.0259518121573</v>
       </c>
       <c r="C100">
-        <v>75.26738390657738</v>
+        <v>102.5037262463386</v>
       </c>
       <c r="D100">
-        <v>0.09508293365269083</v>
+        <v>0.5222255658187294</v>
       </c>
       <c r="E100" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2289,16 +2322,16 @@
         <v>19</v>
       </c>
       <c r="B101">
-        <v>62.12921944468621</v>
+        <v>98.86783474514039</v>
       </c>
       <c r="C101">
-        <v>62.05180049707972</v>
+        <v>98.37036464076621</v>
       </c>
       <c r="D101">
-        <v>0.07741894760649615</v>
+        <v>0.4974701043741732</v>
       </c>
       <c r="E101" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2306,16 +2339,16 @@
         <v>19</v>
       </c>
       <c r="B102">
-        <v>91.66866334057599</v>
+        <v>107.5106671378903</v>
       </c>
       <c r="C102">
-        <v>91.55205331912201</v>
+        <v>106.9616936217664</v>
       </c>
       <c r="D102">
-        <v>0.1166100214539796</v>
+        <v>0.5489735161238229</v>
       </c>
       <c r="E102" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2323,16 +2356,16 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>72.22093641283</v>
+        <v>104.7620285751465</v>
       </c>
       <c r="C103">
-        <v>72.13021348822164</v>
+        <v>104.2302698645163</v>
       </c>
       <c r="D103">
-        <v>0.0907229246083574</v>
+        <v>0.5317587106301858</v>
       </c>
       <c r="E103" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2340,16 +2373,16 @@
         <v>19</v>
       </c>
       <c r="B104">
-        <v>75.6593362731233</v>
+        <v>100.5345727428424</v>
       </c>
       <c r="C104">
-        <v>75.56369560601223</v>
+        <v>100.0264653140974</v>
       </c>
       <c r="D104">
-        <v>0.09564066711106989</v>
+        <v>0.5081074287450207</v>
       </c>
       <c r="E104" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2357,16 +2390,16 @@
         <v>19</v>
       </c>
       <c r="B105">
-        <v>70.46670906536259</v>
+        <v>99.18795817553655</v>
       </c>
       <c r="C105">
-        <v>70.37802101674168</v>
+        <v>98.68790073048936</v>
       </c>
       <c r="D105">
-        <v>0.0886880486209094</v>
+        <v>0.5000574450471902</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2374,16 +2407,16 @@
         <v>19</v>
       </c>
       <c r="B106">
-        <v>80.60894348029684</v>
+        <v>107.1273812882631</v>
       </c>
       <c r="C106">
-        <v>80.50700020038066</v>
+        <v>106.5814201717498</v>
       </c>
       <c r="D106">
-        <v>0.1019432799161848</v>
+        <v>0.5459611165133111</v>
       </c>
       <c r="E106" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2391,16 +2424,16 @@
         <v>20</v>
       </c>
       <c r="B107">
-        <v>91.056720256291</v>
+        <v>96.5502087156966</v>
       </c>
       <c r="C107">
-        <v>90.97449995735786</v>
+        <v>96.01029855599296</v>
       </c>
       <c r="D107">
-        <v>0.08222029893313731</v>
+        <v>0.5399101597036378</v>
       </c>
       <c r="E107" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2408,16 +2441,16 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>82.7405810609059</v>
+        <v>91.45779533792198</v>
       </c>
       <c r="C108">
-        <v>82.66608455455045</v>
+        <v>90.90265997459892</v>
       </c>
       <c r="D108">
-        <v>0.07449650635544458</v>
+        <v>0.5551353633230605</v>
       </c>
       <c r="E108" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2425,16 +2458,16 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>100.239816013662</v>
+        <v>101.6211128321928</v>
       </c>
       <c r="C109">
-        <v>100.149060144737</v>
+        <v>102.123693797026</v>
       </c>
       <c r="D109">
-        <v>0.09075586892494414</v>
+        <v>-0.5025809648332142</v>
       </c>
       <c r="E109" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2442,16 +2475,16 @@
         <v>20</v>
       </c>
       <c r="B110">
-        <v>92.46342322845922</v>
+        <v>96.54087456339856</v>
       </c>
       <c r="C110">
-        <v>92.3799359772775</v>
+        <v>96.0239094960413</v>
       </c>
       <c r="D110">
-        <v>0.0834872511817224</v>
+        <v>0.5169650673572619</v>
       </c>
       <c r="E110" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2459,16 +2492,16 @@
         <v>20</v>
       </c>
       <c r="B111">
-        <v>87.9672865899357</v>
+        <v>95.41553314921848</v>
       </c>
       <c r="C111">
-        <v>87.88789729118727</v>
+        <v>95.20340219329766</v>
       </c>
       <c r="D111">
-        <v>0.07938929874842415</v>
+        <v>0.2121309559208129</v>
       </c>
       <c r="E111" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2476,16 +2509,16 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>85.2206801228694</v>
+        <v>93.64309479746723</v>
       </c>
       <c r="C112">
-        <v>85.1438456007137</v>
+        <v>93.23741161327297</v>
       </c>
       <c r="D112">
-        <v>0.07683452215569275</v>
+        <v>0.4056831841942596</v>
       </c>
       <c r="E112" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2493,16 +2526,16 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>97.30106152300198</v>
+        <v>99.47099657233142</v>
       </c>
       <c r="C113">
-        <v>97.21307484893022</v>
+        <v>99.14880152895786</v>
       </c>
       <c r="D113">
-        <v>0.08798667407175742</v>
+        <v>0.3221950433735543</v>
       </c>
       <c r="E113" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2510,16 +2543,16 @@
         <v>21</v>
       </c>
       <c r="B114">
-        <v>75.50930035213678</v>
+        <v>103.2669744583758</v>
       </c>
       <c r="C114">
-        <v>75.41423508089437</v>
+        <v>102.7486956698823</v>
       </c>
       <c r="D114">
-        <v>0.09506527124240449</v>
+        <v>0.5182787884935607</v>
       </c>
       <c r="E114" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2527,16 +2560,16 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>62.30704397272733</v>
+        <v>99.2293188045691</v>
       </c>
       <c r="C115">
-        <v>62.22957820102193</v>
+        <v>98.73504271277227</v>
       </c>
       <c r="D115">
-        <v>0.07746577170539837</v>
+        <v>0.4942760917968343</v>
       </c>
       <c r="E115" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2544,16 +2577,16 @@
         <v>21</v>
       </c>
       <c r="B116">
-        <v>91.76339687258108</v>
+        <v>107.6181994960786</v>
       </c>
       <c r="C116">
-        <v>91.64691531459009</v>
+        <v>107.074010984486</v>
       </c>
       <c r="D116">
-        <v>0.1164815579909941</v>
+        <v>0.54418851159258</v>
       </c>
       <c r="E116" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2561,16 +2594,16 @@
         <v>21</v>
       </c>
       <c r="B117">
-        <v>72.40119521270989</v>
+        <v>104.9659743818114</v>
       </c>
       <c r="C117">
-        <v>72.31043733729425</v>
+        <v>104.4383490254191</v>
       </c>
       <c r="D117">
-        <v>0.0907578754156475</v>
+        <v>0.5276253563922495</v>
       </c>
       <c r="E117" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2578,16 +2611,16 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>75.77855007483015</v>
+        <v>100.8345476257628</v>
       </c>
       <c r="C118">
-        <v>75.68296686672701</v>
+        <v>100.3300603519827</v>
       </c>
       <c r="D118">
-        <v>0.09558320810313603</v>
+        <v>0.5044872737801711</v>
       </c>
       <c r="E118" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2595,16 +2628,16 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>70.6039173400095</v>
+        <v>99.52790528815818</v>
       </c>
       <c r="C119">
-        <v>70.51525327021781</v>
+        <v>99.03121404751963</v>
       </c>
       <c r="D119">
-        <v>0.08866406979169028</v>
+        <v>0.4966912406385546</v>
       </c>
       <c r="E119" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2612,16 +2645,16 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>80.76654629441867</v>
+        <v>107.2597309314777</v>
       </c>
       <c r="C120">
-        <v>80.66461326857325</v>
+        <v>106.7183535300381</v>
       </c>
       <c r="D120">
-        <v>0.1019330258454261</v>
+        <v>0.5413774014396751</v>
       </c>
       <c r="E120" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2629,16 +2662,16 @@
         <v>22</v>
       </c>
       <c r="B121">
-        <v>91.29798187112559</v>
+        <v>103.1811256474387</v>
       </c>
       <c r="C121">
-        <v>91.21635293996619</v>
+        <v>102.6617244885836</v>
       </c>
       <c r="D121">
-        <v>0.08162893115940051</v>
+        <v>0.5194011588550893</v>
       </c>
       <c r="E121" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2646,16 +2679,16 @@
         <v>22</v>
       </c>
       <c r="B122">
-        <v>83.07916072168442</v>
+        <v>99.1027995549628</v>
       </c>
       <c r="C122">
-        <v>83.00509851919202</v>
+        <v>98.60763605842179</v>
       </c>
       <c r="D122">
-        <v>0.07406220249239936</v>
+        <v>0.4951634965410108</v>
       </c>
       <c r="E122" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2663,16 +2696,16 @@
         <v>22</v>
       </c>
       <c r="B123">
-        <v>100.3610188602472</v>
+        <v>107.5772124486722</v>
       </c>
       <c r="C123">
-        <v>100.271039656744</v>
+        <v>107.0316402348795</v>
       </c>
       <c r="D123">
-        <v>0.0899792035032192</v>
+        <v>0.5455722137926244</v>
       </c>
       <c r="E123" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2680,16 +2713,16 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>92.74827540115585</v>
+        <v>104.8955618680646</v>
       </c>
       <c r="C124">
-        <v>92.66534950349538</v>
+        <v>104.3667433326011</v>
       </c>
       <c r="D124">
-        <v>0.08292589766047342</v>
+        <v>0.5288185354634862</v>
       </c>
       <c r="E124" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2697,16 +2730,16 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>88.187882694179</v>
+        <v>100.7258485158245</v>
       </c>
       <c r="C125">
-        <v>88.10907992223278</v>
+        <v>100.2203534442194</v>
       </c>
       <c r="D125">
-        <v>0.07880277194621499</v>
+        <v>0.5054950716050968</v>
       </c>
       <c r="E125" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2714,16 +2747,16 @@
         <v>22</v>
       </c>
       <c r="B126">
-        <v>85.48030382718271</v>
+        <v>99.40598900056899</v>
       </c>
       <c r="C126">
-        <v>85.40399747218811</v>
+        <v>98.90836807128431</v>
       </c>
       <c r="D126">
-        <v>0.0763063549945997</v>
+        <v>0.4976209292846789</v>
       </c>
       <c r="E126" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2731,16 +2764,16 @@
         <v>22</v>
       </c>
       <c r="B127">
-        <v>97.52070080594902</v>
+        <v>107.2132715339136</v>
       </c>
       <c r="C127">
-        <v>97.4333749497074</v>
+        <v>106.6705610766879</v>
       </c>
       <c r="D127">
-        <v>0.0873258562416197</v>
+        <v>0.5427104572256383</v>
       </c>
       <c r="E127" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2748,16 +2781,16 @@
         <v>23</v>
       </c>
       <c r="B128">
-        <v>91.2233763934936</v>
+        <v>104.9820809018199</v>
       </c>
       <c r="C128">
-        <v>91.14157330796969</v>
+        <v>104.5789390814983</v>
       </c>
       <c r="D128">
-        <v>0.08180308552390159</v>
+        <v>0.4031418203215793</v>
       </c>
       <c r="E128" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2765,16 +2798,16 @@
         <v>23</v>
       </c>
       <c r="B129">
-        <v>82.97632936546883</v>
+        <v>101.3872765313642</v>
       </c>
       <c r="C129">
-        <v>82.90213808149691</v>
+        <v>100.9980460161356</v>
       </c>
       <c r="D129">
-        <v>0.07419128397191344</v>
+        <v>0.3892305152285616</v>
       </c>
       <c r="E129" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2782,16 +2815,16 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>100.3211289242305</v>
+        <v>108.7435355122258</v>
       </c>
       <c r="C130">
-        <v>100.2309224742214</v>
+        <v>108.3258312752621</v>
       </c>
       <c r="D130">
-        <v>0.09020645000911998</v>
+        <v>0.4177042369637007</v>
       </c>
       <c r="E130" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2799,16 +2832,16 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>92.66156102281985</v>
+        <v>106.9709235982506</v>
       </c>
       <c r="C131">
-        <v>92.57846915662761</v>
+        <v>106.5601246719702</v>
       </c>
       <c r="D131">
-        <v>0.08309186619224818</v>
+        <v>0.4107989262803784</v>
       </c>
       <c r="E131" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2816,16 +2849,16 @@
         <v>23</v>
       </c>
       <c r="B132">
-        <v>88.11876766943557</v>
+        <v>102.3153405318526</v>
       </c>
       <c r="C132">
-        <v>88.03979253793726</v>
+        <v>101.9224766094945</v>
       </c>
       <c r="D132">
-        <v>0.0789751314983107</v>
+        <v>0.3928639223581598</v>
       </c>
       <c r="E132" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2833,16 +2866,16 @@
         <v>23</v>
       </c>
       <c r="B133">
-        <v>85.39993447582671</v>
+        <v>101.2021448291184</v>
       </c>
       <c r="C133">
-        <v>85.32347245677165</v>
+        <v>100.8135923438329</v>
       </c>
       <c r="D133">
-        <v>0.07646201905505734</v>
+        <v>0.3885524852855156</v>
       </c>
       <c r="E133" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2850,16 +2883,16 @@
         <v>23</v>
       </c>
       <c r="B134">
-        <v>97.4528361250083</v>
+        <v>108.9418942019189</v>
       </c>
       <c r="C134">
-        <v>97.36531580827452</v>
+        <v>108.5234627421785</v>
       </c>
       <c r="D134">
-        <v>0.08752031673378724</v>
+        <v>0.4184314597403755</v>
       </c>
       <c r="E134" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2867,16 +2900,16 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>97.36265798951685</v>
+        <v>105.1337687318547</v>
       </c>
       <c r="C135">
-        <v>97.29722062103914</v>
+        <v>105.6444319532208</v>
       </c>
       <c r="D135">
-        <v>0.06543736847770276</v>
+        <v>-0.5106632213661157</v>
       </c>
       <c r="E135" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2884,16 +2917,16 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>91.49322888121138</v>
+        <v>86.61709188685803</v>
       </c>
       <c r="C136">
-        <v>91.4318065639886</v>
+        <v>86.01252161910652</v>
       </c>
       <c r="D136">
-        <v>0.06142231722277813</v>
+        <v>0.6045702677515123</v>
       </c>
       <c r="E136" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2901,16 +2934,16 @@
         <v>24</v>
       </c>
       <c r="B137">
-        <v>103.6169386761022</v>
+        <v>117.0707937507844</v>
       </c>
       <c r="C137">
-        <v>103.5472208539859</v>
+        <v>130.7540156268476</v>
       </c>
       <c r="D137">
-        <v>0.06971782211631705</v>
+        <v>-13.68322187606316</v>
       </c>
       <c r="E137" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2918,16 +2951,16 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>99.57986588588044</v>
+        <v>100.1401096044012</v>
       </c>
       <c r="C138">
-        <v>99.51292652809559</v>
+        <v>99.48676682831503</v>
       </c>
       <c r="D138">
-        <v>0.06693935778484672</v>
+        <v>0.6533427760861343</v>
       </c>
       <c r="E138" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2935,16 +2968,16 @@
         <v>24</v>
       </c>
       <c r="B139">
-        <v>94.01758127709289</v>
+        <v>102.9616122957066</v>
       </c>
       <c r="C139">
-        <v>93.95441765585701</v>
+        <v>107.7297523925515</v>
       </c>
       <c r="D139">
-        <v>0.06316362123587282</v>
+        <v>-4.768140096844903</v>
       </c>
       <c r="E139" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2952,16 +2985,16 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>92.20714379804932</v>
+        <v>98.41276532471677</v>
       </c>
       <c r="C140">
-        <v>92.14521993696627</v>
+        <v>99.5095556982418</v>
       </c>
       <c r="D140">
-        <v>0.06192386108304504</v>
+        <v>-1.096790373525025</v>
       </c>
       <c r="E140" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2969,16 +3002,16 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>102.810370837046</v>
+        <v>111.4986652915005</v>
       </c>
       <c r="C141">
-        <v>102.7412192030358</v>
+        <v>112.1688800144051</v>
       </c>
       <c r="D141">
-        <v>0.06915163401019697</v>
+        <v>-0.6702147229045892</v>
       </c>
       <c r="E141" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2986,16 +3019,16 @@
         <v>25</v>
       </c>
       <c r="B142">
-        <v>104.147771323011</v>
+        <v>105.3558548807097</v>
       </c>
       <c r="C142">
-        <v>105.1521606771947</v>
+        <v>104.7076704773811</v>
       </c>
       <c r="D142">
-        <v>-1.004389354183729</v>
+        <v>0.6481844033285853</v>
       </c>
       <c r="E142" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3003,16 +3036,16 @@
         <v>25</v>
       </c>
       <c r="B143">
-        <v>84.70057067636557</v>
+        <v>100.982680879905</v>
       </c>
       <c r="C143">
-        <v>84.59788484862258</v>
+        <v>100.37691030739</v>
       </c>
       <c r="D143">
-        <v>0.1026858277429881</v>
+        <v>0.6057705725150129</v>
       </c>
       <c r="E143" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3020,16 +3053,16 @@
         <v>25</v>
       </c>
       <c r="B144">
-        <v>116.7680028816017</v>
+        <v>110.4266770409442</v>
       </c>
       <c r="C144">
-        <v>131.8276762695843</v>
+        <v>109.7300240556283</v>
       </c>
       <c r="D144">
-        <v>-15.05967338798263</v>
+        <v>0.6966529853158647</v>
       </c>
       <c r="E144" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3037,16 +3070,16 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>98.53490924684324</v>
+        <v>106.0926527800007</v>
       </c>
       <c r="C145">
-        <v>98.45372470160355</v>
+        <v>105.4378121698606</v>
       </c>
       <c r="D145">
-        <v>0.08118454523969376</v>
+        <v>0.6548406101400985</v>
       </c>
       <c r="E145" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3054,16 +3087,16 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>102.2558915492363</v>
+        <v>103.8722132048805</v>
       </c>
       <c r="C146">
-        <v>107.6599818003886</v>
+        <v>103.2385454779229</v>
       </c>
       <c r="D146">
-        <v>-5.404090251152326</v>
+        <v>0.6336677269576114</v>
       </c>
       <c r="E146" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3071,16 +3104,16 @@
         <v>25</v>
       </c>
       <c r="B147">
-        <v>97.4915205804718</v>
+        <v>102.3204628280584</v>
       </c>
       <c r="C147">
-        <v>99.04569063777764</v>
+        <v>101.7016501559655</v>
       </c>
       <c r="D147">
-        <v>-1.554170057305839</v>
+        <v>0.6188126720928437</v>
       </c>
       <c r="E147" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3088,16 +3121,16 @@
         <v>25</v>
       </c>
       <c r="B148">
-        <v>110.4544347417514</v>
+        <v>108.7533334921368</v>
       </c>
       <c r="C148">
-        <v>111.6464184910672</v>
+        <v>108.0726958682296</v>
       </c>
       <c r="D148">
-        <v>-1.191983749315739</v>
+        <v>0.6806376239072023</v>
       </c>
       <c r="E148" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3105,16 +3138,16 @@
         <v>26</v>
       </c>
       <c r="B149">
-        <v>86.92124127858565</v>
+        <v>106.5390647498675</v>
       </c>
       <c r="C149">
-        <v>86.82326312635855</v>
+        <v>107.1829235086548</v>
       </c>
       <c r="D149">
-        <v>0.09797815222709971</v>
+        <v>-0.6438587587872888</v>
       </c>
       <c r="E149" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3122,16 +3155,16 @@
         <v>26</v>
       </c>
       <c r="B150">
-        <v>75.03330603065312</v>
+        <v>88.40906572734661</v>
       </c>
       <c r="C150">
-        <v>74.94956089270715</v>
+        <v>87.80298702343943</v>
       </c>
       <c r="D150">
-        <v>0.08374513794596794</v>
+        <v>0.6060787039071869</v>
       </c>
       <c r="E150" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3139,16 +3172,16 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>100.8512608725165</v>
+        <v>117.6823174252359</v>
       </c>
       <c r="C151">
-        <v>100.7365841588359</v>
+        <v>131.8452075294254</v>
       </c>
       <c r="D151">
-        <v>0.1146767136805806</v>
+        <v>-14.16289010418947</v>
       </c>
       <c r="E151" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3156,16 +3189,16 @@
         <v>26</v>
       </c>
       <c r="B152">
-        <v>85.99968940384476</v>
+        <v>101.9081579043105</v>
       </c>
       <c r="C152">
-        <v>85.90290791572096</v>
+        <v>101.2708435006611</v>
       </c>
       <c r="D152">
-        <v>0.09678148812379561</v>
+        <v>0.6373144036494125</v>
       </c>
       <c r="E152" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3173,16 +3206,16 @@
         <v>26</v>
       </c>
       <c r="B153">
-        <v>85.29564603735928</v>
+        <v>104.1540583955288</v>
       </c>
       <c r="C153">
-        <v>85.19952411315292</v>
+        <v>109.0560449050354</v>
       </c>
       <c r="D153">
-        <v>0.09612192420635779</v>
+        <v>-4.901986509506571</v>
       </c>
       <c r="E153" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3190,16 +3223,16 @@
         <v>26</v>
       </c>
       <c r="B154">
-        <v>80.97660266628367</v>
+        <v>99.84164659308904</v>
       </c>
       <c r="C154">
-        <v>80.8856624815361</v>
+        <v>100.987072177127</v>
       </c>
       <c r="D154">
-        <v>0.09094018474756638</v>
+        <v>-1.145425584037923</v>
       </c>
       <c r="E154" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3207,16 +3240,16 @@
         <v>26</v>
       </c>
       <c r="B155">
-        <v>93.32446317713837</v>
+        <v>112.8707601362442</v>
       </c>
       <c r="C155">
-        <v>93.21889753467545</v>
+        <v>113.7740574900079</v>
       </c>
       <c r="D155">
-        <v>0.1055656424629206</v>
+        <v>-0.9032973537637048</v>
       </c>
       <c r="E155" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3224,16 +3257,16 @@
         <v>27</v>
       </c>
       <c r="B156">
-        <v>105.6142221069481</v>
+        <v>107.6461793592309</v>
       </c>
       <c r="C156">
-        <v>106.7297522461004</v>
+        <v>107.285096956593</v>
       </c>
       <c r="D156">
-        <v>-1.115530139152284</v>
+        <v>0.3610824026379476</v>
       </c>
       <c r="E156" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3241,16 +3274,16 @@
         <v>27</v>
       </c>
       <c r="B157">
-        <v>86.53754708334621</v>
+        <v>102.4441543004597</v>
       </c>
       <c r="C157">
-        <v>86.43458548617131</v>
+        <v>102.1010602253517</v>
       </c>
       <c r="D157">
-        <v>0.1029615971748967</v>
+        <v>0.3430940751080556</v>
       </c>
       <c r="E157" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3258,16 +3291,16 @@
         <v>27</v>
       </c>
       <c r="B158">
-        <v>117.4395760410046</v>
+        <v>113.121828017844</v>
       </c>
       <c r="C158">
-        <v>132.9281332431088</v>
+        <v>112.7418009633613</v>
       </c>
       <c r="D158">
-        <v>-15.48855720210413</v>
+        <v>0.3800270544826958</v>
       </c>
       <c r="E158" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3275,16 +3308,16 @@
         <v>27</v>
       </c>
       <c r="B159">
-        <v>100.3608659510788</v>
+        <v>110.1218113734224</v>
       </c>
       <c r="C159">
-        <v>100.2862588728537</v>
+        <v>109.7522493600073</v>
       </c>
       <c r="D159">
-        <v>0.07460707822507118</v>
+        <v>0.3695620134151056</v>
       </c>
       <c r="E159" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3292,16 +3325,16 @@
         <v>27</v>
       </c>
       <c r="B160">
-        <v>103.5175162502674</v>
+        <v>104.1462707958864</v>
       </c>
       <c r="C160">
-        <v>109.0151510604717</v>
+        <v>103.7972090403469</v>
       </c>
       <c r="D160">
-        <v>-5.497634810204246</v>
+        <v>0.3490617555395374</v>
       </c>
       <c r="E160" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3309,16 +3342,16 @@
         <v>27</v>
       </c>
       <c r="B161">
-        <v>98.97846808482694</v>
+        <v>102.5178876465319</v>
       </c>
       <c r="C161">
-        <v>100.561178463188</v>
+        <v>102.1744625092805</v>
       </c>
       <c r="D161">
-        <v>-1.582710378361043</v>
+        <v>0.3434251372514296</v>
       </c>
       <c r="E161" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3326,16 +3359,16 @@
         <v>27</v>
       </c>
       <c r="B162">
-        <v>111.8911175003948</v>
+        <v>113.0377776299338</v>
       </c>
       <c r="C162">
-        <v>113.2918298168946</v>
+        <v>112.6581206717255</v>
       </c>
       <c r="D162">
-        <v>-1.400712316499806</v>
+        <v>0.3796569582082299</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3343,16 +3376,16 @@
         <v>28</v>
       </c>
       <c r="B163">
-        <v>107.1131616707679</v>
+        <v>105.9020486966781</v>
       </c>
       <c r="C163">
-        <v>107.0501783706839</v>
+        <v>106.4805430156471</v>
       </c>
       <c r="D163">
-        <v>0.06298330008401365</v>
+        <v>-0.5784943189689926</v>
       </c>
       <c r="E163" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3360,16 +3393,16 @@
         <v>28</v>
       </c>
       <c r="B164">
-        <v>101.6404779934821</v>
+        <v>87.59290546173884</v>
       </c>
       <c r="C164">
-        <v>101.5808129258797</v>
+        <v>86.98734113411388</v>
       </c>
       <c r="D164">
-        <v>0.05966506760239554</v>
+        <v>0.6055643276249612</v>
       </c>
       <c r="E164" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3377,16 +3410,16 @@
         <v>28</v>
       </c>
       <c r="B165">
-        <v>112.891201342487</v>
+        <v>117.4163994397888</v>
       </c>
       <c r="C165">
-        <v>112.8247126566915</v>
+        <v>131.3413840695506</v>
       </c>
       <c r="D165">
-        <v>0.06648868579547695</v>
+        <v>-13.92498462976184</v>
       </c>
       <c r="E165" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3394,16 +3427,16 @@
         <v>28</v>
       </c>
       <c r="B166">
-        <v>109.5172216686943</v>
+        <v>101.1112052854226</v>
       </c>
       <c r="C166">
-        <v>109.4527953225148</v>
+        <v>100.4632526748275</v>
       </c>
       <c r="D166">
-        <v>0.06442634617948784</v>
+        <v>0.6479526105950697</v>
       </c>
       <c r="E166" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3411,16 +3444,16 @@
         <v>28</v>
       </c>
       <c r="B167">
-        <v>103.6686387128907</v>
+        <v>103.6127985659323</v>
       </c>
       <c r="C167">
-        <v>103.6077293167873</v>
+        <v>108.4434270421651</v>
       </c>
       <c r="D167">
-        <v>0.06090939610341195</v>
+        <v>-4.830628476232803</v>
       </c>
       <c r="E167" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3428,16 +3461,16 @@
         <v>28</v>
       </c>
       <c r="B168">
-        <v>102.0121620062219</v>
+        <v>99.18680690119518</v>
       </c>
       <c r="C168">
-        <v>101.9522582306181</v>
+        <v>100.3076061080089</v>
       </c>
       <c r="D168">
-        <v>0.05990377560382854</v>
+        <v>-1.120799206813729</v>
       </c>
       <c r="E168" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3445,16 +3478,16 @@
         <v>28</v>
       </c>
       <c r="B169">
-        <v>112.4760219885739</v>
+        <v>112.2565676273563</v>
       </c>
       <c r="C169">
-        <v>112.4097991930996</v>
+        <v>113.0465328813153</v>
       </c>
       <c r="D169">
-        <v>0.06622279547433152</v>
+        <v>-0.7899652539590392</v>
       </c>
       <c r="E169" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3462,16 +3495,16 @@
         <v>29</v>
       </c>
       <c r="B170">
-        <v>104.967263841573</v>
+        <v>106.3884880287113</v>
       </c>
       <c r="C170">
-        <v>106.0317157059055</v>
+        <v>107.0189289356389</v>
       </c>
       <c r="D170">
-        <v>-1.064451864332497</v>
+        <v>-0.6304409069276318</v>
       </c>
       <c r="E170" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3479,16 +3512,16 @@
         <v>29</v>
       </c>
       <c r="B171">
-        <v>85.72352273391978</v>
+        <v>88.21661903383058</v>
       </c>
       <c r="C171">
-        <v>85.62075419029819</v>
+        <v>87.61067451758818</v>
       </c>
       <c r="D171">
-        <v>0.1027685436215933</v>
+        <v>0.6059445162424026</v>
       </c>
       <c r="E171" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3496,16 +3529,16 @@
         <v>29</v>
       </c>
       <c r="B172">
-        <v>117.15612018446</v>
+        <v>117.6158797617971</v>
       </c>
       <c r="C172">
-        <v>132.440966800427</v>
+        <v>131.730830317801</v>
       </c>
       <c r="D172">
-        <v>-15.28484661596701</v>
+        <v>-14.1149505560039</v>
       </c>
       <c r="E172" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3513,16 +3546,16 @@
         <v>29</v>
       </c>
       <c r="B173">
-        <v>99.55581604294302</v>
+        <v>101.7200491169819</v>
       </c>
       <c r="C173">
-        <v>99.47896701547667</v>
+        <v>101.080673750896</v>
       </c>
       <c r="D173">
-        <v>0.07684902746635203</v>
+        <v>0.6393753660859289</v>
       </c>
       <c r="E173" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3530,16 +3563,16 @@
         <v>29</v>
       </c>
       <c r="B174">
-        <v>102.9582459691921</v>
+        <v>104.0237977068182</v>
       </c>
       <c r="C174">
-        <v>108.411413571443</v>
+        <v>108.9143155541741</v>
       </c>
       <c r="D174">
-        <v>-5.453167602250886</v>
+        <v>-4.890517847355895</v>
       </c>
       <c r="E174" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3547,16 +3580,16 @@
         <v>29</v>
       </c>
       <c r="B175">
-        <v>98.31569337078608</v>
+        <v>99.68709983570174</v>
       </c>
       <c r="C175">
-        <v>99.88689377110822</v>
+        <v>100.8286666908097</v>
       </c>
       <c r="D175">
-        <v>-1.571200400322141</v>
+        <v>-1.141566855107968</v>
       </c>
       <c r="E175" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3564,16 +3597,16 @@
         <v>29</v>
       </c>
       <c r="B176">
-        <v>111.264634386855</v>
+        <v>112.7251828293014</v>
       </c>
       <c r="C176">
-        <v>112.5677378500025</v>
+        <v>113.6039242985326</v>
       </c>
       <c r="D176">
-        <v>-1.303103463147551</v>
+        <v>-0.8787414692311586</v>
       </c>
       <c r="E176" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3581,16 +3614,16 @@
         <v>30</v>
       </c>
       <c r="B177">
-        <v>105.4621442138925</v>
+        <v>106.4611419597932</v>
       </c>
       <c r="C177">
-        <v>106.5656917394603</v>
+        <v>107.0883065282618</v>
       </c>
       <c r="D177">
-        <v>-1.103547525567819</v>
+        <v>-0.6271645684685865</v>
       </c>
       <c r="E177" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3598,16 +3631,16 @@
         <v>30</v>
       </c>
       <c r="B178">
-        <v>86.34417815012064</v>
+        <v>88.30647508761884</v>
       </c>
       <c r="C178">
-        <v>86.2412072697642</v>
+        <v>87.70044046440394</v>
       </c>
       <c r="D178">
-        <v>0.1029708803564375</v>
+        <v>0.6060346232148959</v>
       </c>
       <c r="E178" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3615,16 +3648,16 @@
         <v>30</v>
       </c>
       <c r="B179">
-        <v>117.3733539858309</v>
+        <v>117.6648298586729</v>
       </c>
       <c r="C179">
-        <v>132.8171994681665</v>
+        <v>131.7647730788656</v>
       </c>
       <c r="D179">
-        <v>-15.44384548233558</v>
+        <v>-14.09994322019271</v>
       </c>
       <c r="E179" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3632,16 +3665,16 @@
         <v>30</v>
       </c>
       <c r="B180">
-        <v>100.1703367972787</v>
+        <v>101.8070679644262</v>
       </c>
       <c r="C180">
-        <v>100.0950424292397</v>
+        <v>101.1678622482765</v>
       </c>
       <c r="D180">
-        <v>0.07529436803898193</v>
+        <v>0.6392057161497462</v>
       </c>
       <c r="E180" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3649,16 +3682,16 @@
         <v>30</v>
       </c>
       <c r="B181">
-        <v>103.3855566066302</v>
+        <v>104.0941788105774</v>
       </c>
       <c r="C181">
-        <v>108.8743931008523</v>
+        <v>108.968692766</v>
       </c>
       <c r="D181">
-        <v>-5.488836494222042</v>
+        <v>-4.874513955422614</v>
       </c>
       <c r="E181" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3666,16 +3699,16 @@
         <v>30</v>
       </c>
       <c r="B182">
-        <v>98.82254942219464</v>
+        <v>99.76062784569142</v>
       </c>
       <c r="C182">
-        <v>100.4026911728416</v>
+        <v>100.8948970091872</v>
       </c>
       <c r="D182">
-        <v>-1.580141750646916</v>
+        <v>-1.134269163495745</v>
       </c>
       <c r="E182" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3683,16 +3716,16 @@
         <v>30</v>
       </c>
       <c r="B183">
-        <v>111.7439004975998</v>
+        <v>112.7969589791084</v>
       </c>
       <c r="C183">
-        <v>113.121649043632</v>
+        <v>113.6767697460643</v>
       </c>
       <c r="D183">
-        <v>-1.377748546032208</v>
+        <v>-0.8798107669558419</v>
       </c>
       <c r="E183" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3700,16 +3733,16 @@
         <v>31</v>
       </c>
       <c r="B184">
-        <v>105.5081683426393</v>
+        <v>105.8678373555347</v>
       </c>
       <c r="C184">
-        <v>106.6176570197133</v>
+        <v>107.4194055373493</v>
       </c>
       <c r="D184">
-        <v>-1.109488677073998</v>
+        <v>-1.551568181814631</v>
       </c>
       <c r="E184" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3717,16 +3750,16 @@
         <v>31</v>
       </c>
       <c r="B185">
-        <v>86.41780368610782</v>
+        <v>90.19535847822243</v>
       </c>
       <c r="C185">
-        <v>86.31485895303523</v>
+        <v>89.5873137976117</v>
       </c>
       <c r="D185">
-        <v>0.1029447330725901</v>
+        <v>0.6080446806107318</v>
       </c>
       <c r="E185" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3734,16 +3767,16 @@
         <v>31</v>
       </c>
       <c r="B186">
-        <v>117.3800091106238</v>
+        <v>112.7061143959258</v>
       </c>
       <c r="C186">
-        <v>132.8302541874102</v>
+        <v>129.4930982679804</v>
       </c>
       <c r="D186">
-        <v>-15.45024507678647</v>
+        <v>-16.78698387205459</v>
       </c>
       <c r="E186" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3751,16 +3784,16 @@
         <v>31</v>
       </c>
       <c r="B187">
-        <v>100.2408231170837</v>
+        <v>103.451738668126</v>
       </c>
       <c r="C187">
-        <v>100.1659877017172</v>
+        <v>102.9816747870638</v>
       </c>
       <c r="D187">
-        <v>0.07483541536652183</v>
+        <v>0.4700638810622877</v>
       </c>
       <c r="E187" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3768,16 +3801,16 @@
         <v>31</v>
       </c>
       <c r="B188">
-        <v>103.4210590439385</v>
+        <v>102.9066200521853</v>
       </c>
       <c r="C188">
-        <v>108.9102306379113</v>
+        <v>108.0465484067921</v>
       </c>
       <c r="D188">
-        <v>-5.489171593972827</v>
+        <v>-5.139928354606781</v>
       </c>
       <c r="E188" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3785,16 +3818,16 @@
         <v>31</v>
       </c>
       <c r="B189">
-        <v>98.87007257556054</v>
+        <v>99.73980198192226</v>
       </c>
       <c r="C189">
-        <v>100.4514636765529</v>
+        <v>100.8713249018983</v>
       </c>
       <c r="D189">
-        <v>-1.58139110099232</v>
+        <v>-1.131522919976035</v>
       </c>
       <c r="E189" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3802,16 +3835,16 @@
         <v>31</v>
       </c>
       <c r="B190">
-        <v>111.7882827558781</v>
+        <v>111.5331373492351</v>
       </c>
       <c r="C190">
-        <v>113.1771806018561</v>
+        <v>114.407229325213</v>
       </c>
       <c r="D190">
-        <v>-1.388897845977993</v>
+        <v>-2.874091975977862</v>
       </c>
       <c r="E190" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3819,16 +3852,16 @@
         <v>32</v>
       </c>
       <c r="B191">
-        <v>105.1302110875339</v>
+        <v>101.2109594074407</v>
       </c>
       <c r="C191">
-        <v>106.9638325329286</v>
+        <v>100.7272690971983</v>
       </c>
       <c r="D191">
-        <v>-1.833621445394769</v>
+        <v>0.4836903102423804</v>
       </c>
       <c r="E191" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3836,16 +3869,16 @@
         <v>32</v>
       </c>
       <c r="B192">
-        <v>88.37996965298456</v>
+        <v>84.73265649112531</v>
       </c>
       <c r="C192">
-        <v>88.27641810002426</v>
+        <v>84.15889721620151</v>
       </c>
       <c r="D192">
-        <v>0.1035515529602975</v>
+        <v>0.5737592749238019</v>
       </c>
       <c r="E192" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3853,16 +3886,16 @@
         <v>32</v>
       </c>
       <c r="B193">
-        <v>112.5082991899775</v>
+        <v>110.7282581580203</v>
       </c>
       <c r="C193">
-        <v>130.3905936522783</v>
+        <v>121.1663249578575</v>
       </c>
       <c r="D193">
-        <v>-17.88229446230072</v>
+        <v>-10.4380667998372</v>
       </c>
       <c r="E193" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3870,16 +3903,16 @@
         <v>32</v>
       </c>
       <c r="B194">
-        <v>102.0099144027356</v>
+        <v>97.36132046486374</v>
       </c>
       <c r="C194">
-        <v>102.0500632157068</v>
+        <v>96.70611163008975</v>
       </c>
       <c r="D194">
-        <v>-0.04014881297121065</v>
+        <v>0.6552088347739868</v>
       </c>
       <c r="E194" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3887,16 +3920,16 @@
         <v>32</v>
       </c>
       <c r="B195">
-        <v>102.4089852254025</v>
+        <v>100.287975467911</v>
       </c>
       <c r="C195">
-        <v>107.9476431985694</v>
+        <v>101.1879986841238</v>
       </c>
       <c r="D195">
-        <v>-5.538657973166877</v>
+        <v>-0.9000232162128157</v>
       </c>
       <c r="E195" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3904,16 +3937,16 @@
         <v>32</v>
       </c>
       <c r="B196">
-        <v>98.96680657247764</v>
+        <v>95.02287124585354</v>
       </c>
       <c r="C196">
-        <v>100.4451193848135</v>
+        <v>94.55407070171111</v>
       </c>
       <c r="D196">
-        <v>-1.478312812335901</v>
+        <v>0.4688005441424252</v>
       </c>
       <c r="E196" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3921,16 +3954,16 @@
         <v>32</v>
       </c>
       <c r="B197">
-        <v>110.8281971563678</v>
+        <v>107.2079243485411</v>
       </c>
       <c r="C197">
-        <v>113.9202483179308</v>
+        <v>107.3216076404596</v>
       </c>
       <c r="D197">
-        <v>-3.092051161562964</v>
+        <v>-0.1136832919185906</v>
       </c>
       <c r="E197" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3938,16 +3971,16 @@
         <v>33</v>
       </c>
       <c r="B198">
-        <v>100.2515543070265</v>
+        <v>105.9376625652953</v>
       </c>
       <c r="C198">
-        <v>100.2832570915276</v>
+        <v>106.5280696222834</v>
       </c>
       <c r="D198">
-        <v>-0.03170278450110686</v>
+        <v>-0.5904070569881554</v>
       </c>
       <c r="E198" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3955,16 +3988,16 @@
         <v>33</v>
       </c>
       <c r="B199">
-        <v>83.01759279083697</v>
+        <v>87.64146856799961</v>
       </c>
       <c r="C199">
-        <v>82.91905840016518</v>
+        <v>87.03597901353646</v>
       </c>
       <c r="D199">
-        <v>0.09853439067178726</v>
+        <v>0.6054895544631478</v>
       </c>
       <c r="E199" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3972,16 +4005,16 @@
         <v>33</v>
       </c>
       <c r="B200">
-        <v>110.4909582200297</v>
+        <v>117.4157538138765</v>
       </c>
       <c r="C200">
-        <v>121.971864466515</v>
+        <v>131.3877919758922</v>
       </c>
       <c r="D200">
-        <v>-11.48090624648525</v>
+        <v>-13.97203816201564</v>
       </c>
       <c r="E200" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3989,16 +4022,16 @@
         <v>33</v>
       </c>
       <c r="B201">
-        <v>95.93085475631266</v>
+        <v>101.1558787628018</v>
       </c>
       <c r="C201">
-        <v>95.82111757671146</v>
+        <v>100.5103387382006</v>
       </c>
       <c r="D201">
-        <v>0.109737179601197</v>
+        <v>0.6455400246011749</v>
       </c>
       <c r="E201" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4006,16 +4039,16 @@
         <v>33</v>
       </c>
       <c r="B202">
-        <v>99.69517966618709</v>
+        <v>103.6364035611164</v>
       </c>
       <c r="C202">
-        <v>101.0720867508607</v>
+        <v>108.4915780931489</v>
       </c>
       <c r="D202">
-        <v>-1.37690708467359</v>
+        <v>-4.855174532032478</v>
       </c>
       <c r="E202" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4023,16 +4056,16 @@
         <v>33</v>
       </c>
       <c r="B203">
-        <v>94.10062666447276</v>
+        <v>99.22672413180003</v>
       </c>
       <c r="C203">
-        <v>94.13760623991004</v>
+        <v>100.3561119243204</v>
       </c>
       <c r="D203">
-        <v>-0.03697957543728592</v>
+        <v>-1.12938779252039</v>
       </c>
       <c r="E203" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4040,16 +4073,16 @@
         <v>33</v>
       </c>
       <c r="B204">
-        <v>106.2747977500569</v>
+        <v>112.2869088697365</v>
       </c>
       <c r="C204">
-        <v>106.8481653624873</v>
+        <v>113.0930080844926</v>
       </c>
       <c r="D204">
-        <v>-0.5733676124303315</v>
+        <v>-0.8060992147560597</v>
       </c>
       <c r="E204" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4057,16 +4090,16 @@
         <v>34</v>
       </c>
       <c r="B205">
-        <v>105.0069591327968</v>
+        <v>106.0877850029822</v>
       </c>
       <c r="C205">
-        <v>106.0746793310802</v>
+        <v>106.6914984756032</v>
       </c>
       <c r="D205">
-        <v>-1.067720198283425</v>
+        <v>-0.6037134726210525</v>
       </c>
       <c r="E205" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4074,16 +4107,16 @@
         <v>34</v>
       </c>
       <c r="B206">
-        <v>85.76634807683101</v>
+        <v>87.8328178516486</v>
       </c>
       <c r="C206">
-        <v>85.66342041098771</v>
+        <v>87.22716839541468</v>
       </c>
       <c r="D206">
-        <v>0.1029276658432963</v>
+        <v>0.6056494562339196</v>
       </c>
       <c r="E206" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4091,16 +4124,16 @@
         <v>34</v>
       </c>
       <c r="B207">
-        <v>117.1740499654675</v>
+        <v>117.4825963838085</v>
       </c>
       <c r="C207">
-        <v>132.484486644743</v>
+        <v>131.5021176296377</v>
       </c>
       <c r="D207">
-        <v>-15.31043667927551</v>
+        <v>-14.01952124582924</v>
       </c>
       <c r="E207" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4108,16 +4141,16 @@
         <v>34</v>
       </c>
       <c r="B208">
-        <v>99.59902561656907</v>
+        <v>101.3439060179116</v>
       </c>
       <c r="C208">
-        <v>99.52162242895643</v>
+        <v>100.7004171474718</v>
       </c>
       <c r="D208">
-        <v>0.07740318761263154</v>
+        <v>0.6434888704397821</v>
       </c>
       <c r="E208" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4125,16 +4158,16 @@
         <v>34</v>
       </c>
       <c r="B209">
-        <v>102.9932848950403</v>
+        <v>103.7649703755126</v>
       </c>
       <c r="C209">
-        <v>108.4546186964635</v>
+        <v>108.6320795758631</v>
       </c>
       <c r="D209">
-        <v>-5.461333801423223</v>
+        <v>-4.867109200350498</v>
       </c>
       <c r="E209" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4142,16 +4175,16 @@
         <v>34</v>
       </c>
       <c r="B210">
-        <v>98.35818617008668</v>
+        <v>99.37963687521497</v>
       </c>
       <c r="C210">
-        <v>99.92993145636204</v>
+        <v>100.5131845532095</v>
       </c>
       <c r="D210">
-        <v>-1.571745286275359</v>
+        <v>-1.133547677994557</v>
       </c>
       <c r="E210" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4159,16 +4192,16 @@
         <v>34</v>
       </c>
       <c r="B211">
-        <v>111.3008667056348</v>
+        <v>112.4332555517243</v>
       </c>
       <c r="C211">
-        <v>112.6106394642517</v>
+        <v>113.2633948149246</v>
       </c>
       <c r="D211">
-        <v>-1.30977275861683</v>
+        <v>-0.8301392632003228</v>
       </c>
       <c r="E211" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4176,16 +4209,16 @@
         <v>35</v>
       </c>
       <c r="B212">
-        <v>105.1585120376129</v>
+        <v>105.0098354058642</v>
       </c>
       <c r="C212">
-        <v>106.2381520859866</v>
+        <v>106.4045267740081</v>
       </c>
       <c r="D212">
-        <v>-1.079640048373747</v>
+        <v>-1.394691368143853</v>
       </c>
       <c r="E212" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4193,16 +4226,16 @@
         <v>35</v>
       </c>
       <c r="B213">
-        <v>85.95858949542053</v>
+        <v>88.98846219177031</v>
       </c>
       <c r="C213">
-        <v>85.85562295432966</v>
+        <v>88.38086752305824</v>
       </c>
       <c r="D213">
-        <v>0.1029665410908649</v>
+        <v>0.6075946687120677</v>
       </c>
       <c r="E213" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4210,16 +4243,16 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>117.2405895448511</v>
+        <v>112.4170631901193</v>
       </c>
       <c r="C214">
-        <v>132.5953715839819</v>
+        <v>128.7920604544455</v>
       </c>
       <c r="D214">
-        <v>-15.35478203913075</v>
+        <v>-16.37499726432618</v>
       </c>
       <c r="E214" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4227,16 +4260,16 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>99.78941264715112</v>
+        <v>102.2485550519221</v>
       </c>
       <c r="C215">
-        <v>99.71272027241788</v>
+        <v>101.7479483572522</v>
       </c>
       <c r="D215">
-        <v>0.07669237473324131</v>
+        <v>0.5006066946698695</v>
       </c>
       <c r="E215" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4244,16 +4277,16 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>103.123441485865</v>
+        <v>102.0923766068834</v>
       </c>
       <c r="C216">
-        <v>108.5941246781992</v>
+        <v>107.2224329736193</v>
       </c>
       <c r="D216">
-        <v>-5.470683192334121</v>
+        <v>-5.130056366735872</v>
       </c>
       <c r="E216" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4261,16 +4294,16 @@
         <v>35</v>
       </c>
       <c r="B217">
-        <v>98.51240815358987</v>
+        <v>98.78270234742038</v>
       </c>
       <c r="C217">
-        <v>100.0870659758306</v>
+        <v>99.93347387660417</v>
       </c>
       <c r="D217">
-        <v>-1.574657822240752</v>
+        <v>-1.150771529183785</v>
       </c>
       <c r="E217" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4278,16 +4311,16 @@
         <v>35</v>
       </c>
       <c r="B218">
-        <v>111.4487749142889</v>
+        <v>110.8511471409183</v>
       </c>
       <c r="C218">
-        <v>112.7810494110643</v>
+        <v>113.3062424147636</v>
       </c>
       <c r="D218">
-        <v>-1.332274496775412</v>
+        <v>-2.455095273845302</v>
       </c>
       <c r="E218" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4295,16 +4328,16 @@
         <v>36</v>
       </c>
       <c r="B219">
-        <v>104.1909162134904</v>
+        <v>101.3452001617955</v>
       </c>
       <c r="C219">
-        <v>105.9121993854622</v>
+        <v>101.2096260302166</v>
       </c>
       <c r="D219">
-        <v>-1.721283171971805</v>
+        <v>0.1355741315789203</v>
       </c>
       <c r="E219" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4312,16 +4345,16 @@
         <v>36</v>
       </c>
       <c r="B220">
-        <v>87.12956428925909</v>
+        <v>95.44497590215515</v>
       </c>
       <c r="C220">
-        <v>87.02633173787028</v>
+        <v>95.07099973539198</v>
       </c>
       <c r="D220">
-        <v>0.1032325513888139</v>
+        <v>0.3739761667631711</v>
       </c>
       <c r="E220" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4329,16 +4362,16 @@
         <v>36</v>
       </c>
       <c r="B221">
-        <v>112.1273843228207</v>
+        <v>107.6068594577746</v>
       </c>
       <c r="C221">
-        <v>129.6739624731269</v>
+        <v>109.6615852107704</v>
       </c>
       <c r="D221">
-        <v>-17.54657815030625</v>
+        <v>-2.054725752995807</v>
       </c>
       <c r="E221" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4346,16 +4379,16 @@
         <v>36</v>
       </c>
       <c r="B222">
-        <v>100.7607052622287</v>
+        <v>96.83627442643602</v>
       </c>
       <c r="C222">
-        <v>100.771568272601</v>
+        <v>96.23196251934372</v>
       </c>
       <c r="D222">
-        <v>-0.01086301037221915</v>
+        <v>0.6043119070922955</v>
       </c>
       <c r="E222" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4363,16 +4396,16 @@
         <v>36</v>
       </c>
       <c r="B223">
-        <v>101.5031003717643</v>
+        <v>102.5714198113921</v>
       </c>
       <c r="C223">
-        <v>107.0946637938006</v>
+        <v>105.9356575983073</v>
       </c>
       <c r="D223">
-        <v>-5.591563422036245</v>
+        <v>-3.364237786915183</v>
       </c>
       <c r="E223" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4380,16 +4413,16 @@
         <v>36</v>
       </c>
       <c r="B224">
-        <v>97.94474346038729</v>
+        <v>100.5679680396554</v>
       </c>
       <c r="C224">
-        <v>99.47095990724364</v>
+        <v>102.5834549297922</v>
       </c>
       <c r="D224">
-        <v>-1.526216446856353</v>
+        <v>-2.015486890136785</v>
       </c>
       <c r="E224" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4397,16 +4430,16 @@
         <v>36</v>
       </c>
       <c r="B225">
-        <v>109.9872496374156</v>
+        <v>100.4896036767218</v>
       </c>
       <c r="C225">
-        <v>112.7821334621789</v>
+        <v>99.98664037558441</v>
       </c>
       <c r="D225">
-        <v>-2.794883824763332</v>
+        <v>0.502963301137342</v>
       </c>
       <c r="E225" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4414,16 +4447,16 @@
         <v>37</v>
       </c>
       <c r="B226">
-        <v>69.5211624520152</v>
+        <v>102.8644263439805</v>
       </c>
       <c r="C226">
-        <v>69.42839305339484</v>
+        <v>103.9055276742207</v>
       </c>
       <c r="D226">
-        <v>0.09276939862036215</v>
+        <v>-1.041101330240139</v>
       </c>
       <c r="E226" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4431,16 +4464,16 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>52.57274240609772</v>
+        <v>97.55880623240368</v>
       </c>
       <c r="C227">
-        <v>52.50524818271919</v>
+        <v>97.50273601787009</v>
       </c>
       <c r="D227">
-        <v>0.06749422337853872</v>
+        <v>0.05607021453359096</v>
       </c>
       <c r="E227" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4448,16 +4481,16 @@
         <v>37</v>
       </c>
       <c r="B228">
-        <v>92.93957232988635</v>
+        <v>106.5415526033861</v>
       </c>
       <c r="C228">
-        <v>93.03930859795503</v>
+        <v>111.5351698730767</v>
       </c>
       <c r="D228">
-        <v>-0.09973626806868197</v>
+        <v>-4.993617269690574</v>
       </c>
       <c r="E228" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4465,16 +4498,16 @@
         <v>37</v>
       </c>
       <c r="B229">
-        <v>61.83336279724793</v>
+        <v>103.2086923685813</v>
       </c>
       <c r="C229">
-        <v>61.75239789702831</v>
+        <v>103.8061140515717</v>
       </c>
       <c r="D229">
-        <v>0.08096490021961955</v>
+        <v>-0.5974216829903867</v>
       </c>
       <c r="E229" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4482,16 +4515,16 @@
         <v>37</v>
       </c>
       <c r="B230">
-        <v>74.03336382962043</v>
+        <v>100.7738320818957</v>
       </c>
       <c r="C230">
-        <v>73.9423051108738</v>
+        <v>102.9549036330078</v>
       </c>
       <c r="D230">
-        <v>0.09105871874662341</v>
+        <v>-2.181071551112126</v>
       </c>
       <c r="E230" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4499,16 +4532,16 @@
         <v>37</v>
       </c>
       <c r="B231">
-        <v>66.28567489207899</v>
+        <v>99.33056755922163</v>
       </c>
       <c r="C231">
-        <v>66.19759653616585</v>
+        <v>100.5254874430886</v>
       </c>
       <c r="D231">
-        <v>0.08807835591314017</v>
+        <v>-1.194919883866959</v>
       </c>
       <c r="E231" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4516,16 +4549,16 @@
         <v>37</v>
       </c>
       <c r="B232">
-        <v>72.92720628461076</v>
+        <v>105.8285634018814</v>
       </c>
       <c r="C232">
-        <v>72.82965743833533</v>
+        <v>107.6877935161804</v>
       </c>
       <c r="D232">
-        <v>0.09754884627542992</v>
+        <v>-1.859230114298967</v>
       </c>
       <c r="E232" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4533,16 +4566,16 @@
         <v>38</v>
       </c>
       <c r="B233">
-        <v>83.73547505724004</v>
+        <v>98.72796802994131</v>
       </c>
       <c r="C233">
-        <v>83.63313243644494</v>
+        <v>98.18950272471395</v>
       </c>
       <c r="D233">
-        <v>0.102342620795099</v>
+        <v>0.538465305227362</v>
       </c>
       <c r="E233" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4550,16 +4583,16 @@
         <v>38</v>
       </c>
       <c r="B234">
-        <v>69.46946295903537</v>
+        <v>94.48101526809587</v>
       </c>
       <c r="C234">
-        <v>69.38595847290168</v>
+        <v>93.94004029616416</v>
       </c>
       <c r="D234">
-        <v>0.0835044861336911</v>
+        <v>0.5409749719317176</v>
       </c>
       <c r="E234" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4567,16 +4600,16 @@
         <v>38</v>
       </c>
       <c r="B235">
-        <v>101.1603374926111</v>
+        <v>103.5410583824289</v>
       </c>
       <c r="C235">
-        <v>101.1920368626699</v>
+        <v>104.1169132421271</v>
       </c>
       <c r="D235">
-        <v>-0.03169937005878865</v>
+        <v>-0.5758548596982251</v>
       </c>
       <c r="E235" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4584,16 +4617,16 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <v>80.49032382565409</v>
+        <v>96.51465363164267</v>
       </c>
       <c r="C236">
-        <v>80.39255996767662</v>
+        <v>95.90967439675617</v>
       </c>
       <c r="D236">
-        <v>0.09776385797746912</v>
+        <v>0.6049792348864997</v>
       </c>
       <c r="E236" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4601,16 +4634,16 @@
         <v>38</v>
       </c>
       <c r="B237">
-        <v>83.93336995706368</v>
+        <v>99.66310499468425</v>
       </c>
       <c r="C237">
-        <v>83.8304820691905</v>
+        <v>100.1569870647923</v>
       </c>
       <c r="D237">
-        <v>0.1028878878731803</v>
+        <v>-0.4938820701080147</v>
       </c>
       <c r="E237" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4618,16 +4651,16 @@
         <v>38</v>
       </c>
       <c r="B238">
-        <v>78.36744574419701</v>
+        <v>98.01106096023457</v>
       </c>
       <c r="C238">
-        <v>78.27194782940619</v>
+        <v>98.04292309161994</v>
       </c>
       <c r="D238">
-        <v>0.09549791479082614</v>
+        <v>-0.03186213138536687</v>
       </c>
       <c r="E238" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4635,16 +4668,16 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>89.4846598163634</v>
+        <v>99.1598828108886</v>
       </c>
       <c r="C239">
-        <v>89.37497680136057</v>
+        <v>98.62862416488846</v>
       </c>
       <c r="D239">
-        <v>0.1096830150028296</v>
+        <v>0.5312586460001398</v>
       </c>
       <c r="E239" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4652,16 +4685,16 @@
         <v>39</v>
       </c>
       <c r="B240">
-        <v>70.63790164901228</v>
+        <v>99.65346006922225</v>
       </c>
       <c r="C240">
-        <v>70.54256654361656</v>
+        <v>99.02294529643999</v>
       </c>
       <c r="D240">
-        <v>0.09533510539571921</v>
+        <v>0.6305147727822629</v>
       </c>
       <c r="E240" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4669,16 +4702,16 @@
         <v>39</v>
       </c>
       <c r="B241">
-        <v>55.51028185650235</v>
+        <v>92.17663871807326</v>
       </c>
       <c r="C241">
-        <v>55.43658791677076</v>
+        <v>91.58125660082047</v>
       </c>
       <c r="D241">
-        <v>0.07369393973158367</v>
+        <v>0.5953821172527967</v>
       </c>
       <c r="E241" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4686,16 +4719,16 @@
         <v>39</v>
       </c>
       <c r="B242">
-        <v>90.23792828637869</v>
+        <v>108.2195140073742</v>
       </c>
       <c r="C242">
-        <v>90.17373517203087</v>
+        <v>108.7837016478832</v>
       </c>
       <c r="D242">
-        <v>0.06419311434781605</v>
+        <v>-0.5641876405090329</v>
       </c>
       <c r="E242" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4703,16 +4736,16 @@
         <v>39</v>
       </c>
       <c r="B243">
-        <v>65.13976994441839</v>
+        <v>95.83066605496424</v>
       </c>
       <c r="C243">
-        <v>65.05243318031826</v>
+        <v>95.18588325589796</v>
       </c>
       <c r="D243">
-        <v>0.08733676410012947</v>
+        <v>0.6447827990662773</v>
       </c>
       <c r="E243" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4720,16 +4753,16 @@
         <v>39</v>
       </c>
       <c r="B244">
-        <v>73.01351488936983</v>
+        <v>101.7459049703129</v>
       </c>
       <c r="C244">
-        <v>72.91476148078323</v>
+        <v>101.9861911545237</v>
       </c>
       <c r="D244">
-        <v>0.09875340858660309</v>
+        <v>-0.2402861842107455</v>
       </c>
       <c r="E244" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4737,16 +4770,16 @@
         <v>39</v>
       </c>
       <c r="B245">
-        <v>66.62065759952431</v>
+        <v>98.8532824854918</v>
       </c>
       <c r="C245">
-        <v>66.53095951198064</v>
+        <v>98.60402961333612</v>
       </c>
       <c r="D245">
-        <v>0.08969808754366682</v>
+        <v>0.2492528721556795</v>
       </c>
       <c r="E245" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4754,16 +4787,16 @@
         <v>39</v>
       </c>
       <c r="B246">
-        <v>74.90844222888016</v>
+        <v>100.2832866618493</v>
       </c>
       <c r="C246">
-        <v>74.80711342118029</v>
+        <v>99.65955910708799</v>
       </c>
       <c r="D246">
-        <v>0.101328807699872</v>
+        <v>0.6237275547613166</v>
       </c>
       <c r="E246" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4771,16 +4804,16 @@
         <v>40</v>
       </c>
       <c r="B247">
-        <v>72.71517592459269</v>
+        <v>101.5746061952531</v>
       </c>
       <c r="C247">
-        <v>72.62119483135234</v>
+        <v>101.0402539813729</v>
       </c>
       <c r="D247">
-        <v>0.09398109324034465</v>
+        <v>0.5343522138801688</v>
       </c>
       <c r="E247" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4788,16 +4821,16 @@
         <v>40</v>
       </c>
       <c r="B248">
-        <v>56.81866350555578</v>
+        <v>96.97465975018615</v>
       </c>
       <c r="C248">
-        <v>56.74739786617018</v>
+        <v>96.42081235376762</v>
       </c>
       <c r="D248">
-        <v>0.07126563938560082</v>
+        <v>0.5538473964185329</v>
       </c>
       <c r="E248" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4805,16 +4838,16 @@
         <v>40</v>
       </c>
       <c r="B249">
-        <v>93.83024832029375</v>
+        <v>106.4561343560524</v>
       </c>
       <c r="C249">
-        <v>93.74440591860316</v>
+        <v>107.1588496156677</v>
       </c>
       <c r="D249">
-        <v>0.08584240169058432</v>
+        <v>-0.7027152596153456</v>
       </c>
       <c r="E249" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4822,16 +4855,16 @@
         <v>40</v>
       </c>
       <c r="B250">
-        <v>66.29958684637261</v>
+        <v>98.51955503038057</v>
       </c>
       <c r="C250">
-        <v>66.21507996087939</v>
+        <v>97.9180662479089</v>
       </c>
       <c r="D250">
-        <v>0.08450688549321228</v>
+        <v>0.6014887824716766</v>
       </c>
       <c r="E250" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4839,16 +4872,16 @@
         <v>40</v>
       </c>
       <c r="B251">
-        <v>75.84065756987954</v>
+        <v>103.1896804497157</v>
       </c>
       <c r="C251">
-        <v>75.74197598715867</v>
+        <v>103.6847297401642</v>
       </c>
       <c r="D251">
-        <v>0.09868158272087157</v>
+        <v>-0.4950492904485486</v>
       </c>
       <c r="E251" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4856,16 +4889,16 @@
         <v>40</v>
       </c>
       <c r="B252">
-        <v>68.7180383385724</v>
+        <v>101.3966072781227</v>
       </c>
       <c r="C252">
-        <v>68.62952640985246</v>
+        <v>101.4110230447896</v>
       </c>
       <c r="D252">
-        <v>0.08851192871993874</v>
+        <v>-0.01441576666694289</v>
       </c>
       <c r="E252" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4873,16 +4906,16 @@
         <v>40</v>
       </c>
       <c r="B253">
-        <v>76.95854921509101</v>
+        <v>101.3677523342438</v>
       </c>
       <c r="C253">
-        <v>76.85875628002988</v>
+        <v>100.862125163503</v>
       </c>
       <c r="D253">
-        <v>0.09979293506113152</v>
+        <v>0.5056271707408229</v>
       </c>
       <c r="E253" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4890,16 +4923,16 @@
         <v>41</v>
       </c>
       <c r="B254">
-        <v>74.23200579750389</v>
+        <v>100.4397053831024</v>
       </c>
       <c r="C254">
-        <v>74.13592319475448</v>
+        <v>99.88141767126187</v>
       </c>
       <c r="D254">
-        <v>0.09608260274940505</v>
+        <v>0.5582877118405349</v>
       </c>
       <c r="E254" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4907,16 +4940,16 @@
         <v>41</v>
       </c>
       <c r="B255">
-        <v>59.08499106589221</v>
+        <v>95.44126955369026</v>
       </c>
       <c r="C255">
-        <v>59.01051782737053</v>
+        <v>94.88013960335661</v>
       </c>
       <c r="D255">
-        <v>0.07447323852168353</v>
+        <v>0.5611299503336511</v>
       </c>
       <c r="E255" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4924,16 +4957,16 @@
         <v>41</v>
       </c>
       <c r="B256">
-        <v>93.79797673531549</v>
+        <v>105.8628959849609</v>
       </c>
       <c r="C256">
-        <v>93.73474782164487</v>
+        <v>106.4303101720841</v>
       </c>
       <c r="D256">
-        <v>0.06322891367061345</v>
+        <v>-0.5674141871232621</v>
       </c>
       <c r="E256" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4941,16 +4974,16 @@
         <v>41</v>
       </c>
       <c r="B257">
-        <v>68.78137536874499</v>
+        <v>97.55359396479471</v>
       </c>
       <c r="C257">
-        <v>68.69319877626873</v>
+        <v>96.9411517487268</v>
       </c>
       <c r="D257">
-        <v>0.08817659247625897</v>
+        <v>0.6124422160679188</v>
       </c>
       <c r="E257" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4958,16 +4991,16 @@
         <v>41</v>
       </c>
       <c r="B258">
-        <v>76.54924046614649</v>
+        <v>101.8531825852408</v>
       </c>
       <c r="C258">
-        <v>76.44984369036951</v>
+        <v>102.2948432506539</v>
       </c>
       <c r="D258">
-        <v>0.09939677577698092</v>
+        <v>-0.4416606654130675</v>
       </c>
       <c r="E258" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4975,16 +5008,16 @@
         <v>41</v>
       </c>
       <c r="B259">
-        <v>70.16686730370051</v>
+        <v>99.89988286091032</v>
       </c>
       <c r="C259">
-        <v>70.07647663633074</v>
+        <v>99.88118449091186</v>
       </c>
       <c r="D259">
-        <v>0.09039066736977475</v>
+        <v>0.01869836999846086</v>
       </c>
       <c r="E259" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4992,16 +5025,16 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>78.5537726526433</v>
+        <v>100.6217014659889</v>
       </c>
       <c r="C260">
-        <v>78.45163734979944</v>
+        <v>100.0838478029232</v>
       </c>
       <c r="D260">
-        <v>0.1021353028438625</v>
+        <v>0.537853663065718</v>
       </c>
       <c r="E260" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5009,16 +5042,16 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>73.03929466835368</v>
+        <v>105.9907078222752</v>
       </c>
       <c r="C261">
-        <v>72.94360526266836</v>
+        <v>105.3462795264987</v>
       </c>
       <c r="D261">
-        <v>0.09568940568532014</v>
+        <v>0.6444282957764784</v>
       </c>
       <c r="E261" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5026,16 +5059,16 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>57.79406301453413</v>
+        <v>101.8571747030051</v>
       </c>
       <c r="C262">
-        <v>57.72020180738556</v>
+        <v>101.2539382553499</v>
       </c>
       <c r="D262">
-        <v>0.07386120714856759</v>
+        <v>0.6032364476551493</v>
       </c>
       <c r="E262" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5043,16 +5076,16 @@
         <v>42</v>
       </c>
       <c r="B263">
-        <v>92.83546057218308</v>
+        <v>110.7949447016465</v>
       </c>
       <c r="C263">
-        <v>92.76774379750741</v>
+        <v>110.1035067689157</v>
       </c>
       <c r="D263">
-        <v>0.06771677467567372</v>
+        <v>0.6914379327308069</v>
       </c>
       <c r="E263" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5060,16 +5093,16 @@
         <v>42</v>
       </c>
       <c r="B264">
-        <v>67.46909398364262</v>
+        <v>106.6210873083253</v>
       </c>
       <c r="C264">
-        <v>67.38155239894357</v>
+        <v>105.9700255148211</v>
       </c>
       <c r="D264">
-        <v>0.08754158469905349</v>
+        <v>0.6510617935042688</v>
       </c>
       <c r="E264" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5077,16 +5110,16 @@
         <v>42</v>
       </c>
       <c r="B265">
-        <v>75.46868259097019</v>
+        <v>104.6562267648006</v>
       </c>
       <c r="C265">
-        <v>75.3694901057757</v>
+        <v>104.0260646054306</v>
       </c>
       <c r="D265">
-        <v>0.09919248519449297</v>
+        <v>0.6301621593700304</v>
       </c>
       <c r="E265" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5094,16 +5127,16 @@
         <v>42</v>
       </c>
       <c r="B266">
-        <v>69.01260707975149</v>
+        <v>103.1843336651142</v>
       </c>
       <c r="C266">
-        <v>68.92253908523882</v>
+        <v>102.5685669673432</v>
       </c>
       <c r="D266">
-        <v>0.09006799451266545</v>
+        <v>0.6157666977710079</v>
       </c>
       <c r="E266" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5111,16 +5144,16 @@
         <v>42</v>
       </c>
       <c r="B267">
-        <v>77.31705977085593</v>
+        <v>109.145846150704</v>
       </c>
       <c r="C267">
-        <v>77.21539475757577</v>
+        <v>108.469742283445</v>
       </c>
       <c r="D267">
-        <v>0.1016650132801686</v>
+        <v>0.6761038672590445</v>
       </c>
       <c r="E267" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5128,16 +5161,16 @@
         <v>43</v>
       </c>
       <c r="B268">
-        <v>87.51195400482506</v>
+        <v>102.0884128831003</v>
       </c>
       <c r="C268">
-        <v>87.41435981388619</v>
+        <v>100.6593702253672</v>
       </c>
       <c r="D268">
-        <v>0.09759419093886379</v>
+        <v>1.429042657733092</v>
       </c>
       <c r="E268" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5145,16 +5178,16 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>75.75929263848215</v>
+        <v>99.430603137932</v>
       </c>
       <c r="C269">
-        <v>75.67566767583897</v>
+        <v>94.8263948515426</v>
       </c>
       <c r="D269">
-        <v>0.08362496264318509</v>
+        <v>4.604208286389394</v>
       </c>
       <c r="E269" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5162,16 +5195,16 @@
         <v>43</v>
       </c>
       <c r="B270">
-        <v>101.2469639478213</v>
+        <v>104.8172666772694</v>
       </c>
       <c r="C270">
-        <v>101.1330262668271</v>
+        <v>106.8603008051049</v>
       </c>
       <c r="D270">
-        <v>0.1139376809941979</v>
+        <v>-2.043034127835512</v>
       </c>
       <c r="E270" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5179,16 +5212,16 @@
         <v>43</v>
       </c>
       <c r="B271">
-        <v>86.71924780469705</v>
+        <v>103.8635251733502</v>
       </c>
       <c r="C271">
-        <v>86.62267642989329</v>
+        <v>103.0012187306053</v>
       </c>
       <c r="D271">
-        <v>0.09657137480375866</v>
+        <v>0.8623064427449236</v>
       </c>
       <c r="E271" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5196,16 +5229,16 @@
         <v>43</v>
       </c>
       <c r="B272">
-        <v>85.79006265579724</v>
+        <v>99.79642749958649</v>
       </c>
       <c r="C272">
-        <v>85.69443736009275</v>
+        <v>97.16990811870947</v>
       </c>
       <c r="D272">
-        <v>0.09562529570449385</v>
+        <v>2.626519380877014</v>
       </c>
       <c r="E272" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5213,16 +5246,16 @@
         <v>43</v>
       </c>
       <c r="B273">
-        <v>81.53909667549561</v>
+        <v>99.01331025637252</v>
       </c>
       <c r="C273">
-        <v>81.44853333175729</v>
+        <v>95.32951894740241</v>
       </c>
       <c r="D273">
-        <v>0.09056334373832442</v>
+        <v>3.683791308970115</v>
       </c>
       <c r="E273" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5230,16 +5263,16 @@
         <v>43</v>
       </c>
       <c r="B274">
-        <v>93.94733232105281</v>
+        <v>105.2590204085171</v>
       </c>
       <c r="C274">
-        <v>93.84215698391375</v>
+        <v>106.2918637866056</v>
       </c>
       <c r="D274">
-        <v>0.1051753371390589</v>
+        <v>-1.032843378088515</v>
       </c>
       <c r="E274" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5247,16 +5280,16 @@
         <v>44</v>
       </c>
       <c r="B275">
-        <v>101.9229831929245</v>
+        <v>101.7999226818687</v>
       </c>
       <c r="C275">
-        <v>100.6593702130711</v>
+        <v>98.8130851614342</v>
       </c>
       <c r="D275">
-        <v>1.263612979853349</v>
+        <v>2.986837520434506</v>
       </c>
       <c r="E275" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5264,16 +5297,16 @@
         <v>44</v>
       </c>
       <c r="B276">
-        <v>99.11632237310315</v>
+        <v>97.90339012020901</v>
       </c>
       <c r="C276">
-        <v>94.49590042321695</v>
+        <v>92.02091591348467</v>
       </c>
       <c r="D276">
-        <v>4.620421949886193</v>
+        <v>5.882474206724339</v>
       </c>
       <c r="E276" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5281,16 +5314,16 @@
         <v>44</v>
       </c>
       <c r="B277">
-        <v>104.8091197718228</v>
+        <v>105.8583340199091</v>
       </c>
       <c r="C277">
-        <v>107.235146293222</v>
+        <v>106.1398485349762</v>
       </c>
       <c r="D277">
-        <v>-2.426026521399265</v>
+        <v>-0.2815145150671299</v>
       </c>
       <c r="E277" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5298,16 +5331,16 @@
         <v>44</v>
       </c>
       <c r="B278">
-        <v>103.6791865867935</v>
+        <v>103.9460166893339</v>
       </c>
       <c r="C278">
-        <v>102.9265904751754</v>
+        <v>100.8819306925373</v>
       </c>
       <c r="D278">
-        <v>0.7525961116181037</v>
+        <v>3.064085996796649</v>
       </c>
       <c r="E278" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5315,16 +5348,16 @@
         <v>44</v>
       </c>
       <c r="B279">
-        <v>99.64498293093904</v>
+        <v>98.89915203365861</v>
       </c>
       <c r="C279">
-        <v>97.21682098443644</v>
+        <v>95.38298389033673</v>
       </c>
       <c r="D279">
-        <v>2.428161946502598</v>
+        <v>3.516168143321877</v>
       </c>
       <c r="E279" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5332,16 +5365,16 @@
         <v>44</v>
       </c>
       <c r="B280">
-        <v>98.85286363195742</v>
+        <v>97.71694507833753</v>
       </c>
       <c r="C280">
-        <v>95.32951893576747</v>
+        <v>93.18149303522408</v>
       </c>
       <c r="D280">
-        <v>3.523344696189952</v>
+        <v>4.535452043113452</v>
       </c>
       <c r="E280" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5349,16 +5382,16 @@
         <v>44</v>
       </c>
       <c r="B281">
-        <v>105.0884528911797</v>
+        <v>106.0604592961932</v>
       </c>
       <c r="C281">
-        <v>106.2918637736107</v>
+        <v>104.8033277727152</v>
       </c>
       <c r="D281">
-        <v>-1.203410882431029</v>
+        <v>1.257131523477966</v>
       </c>
       <c r="E281" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5366,16 +5399,16 @@
         <v>45</v>
       </c>
       <c r="B282">
-        <v>101.5705047436691</v>
+        <v>100.0841198349331</v>
       </c>
       <c r="C282">
-        <v>98.81308519430915</v>
+        <v>96.7210159412984</v>
       </c>
       <c r="D282">
-        <v>2.757419549359994</v>
+        <v>3.363103893634658</v>
       </c>
       <c r="E282" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5383,16 +5416,16 @@
         <v>45</v>
       </c>
       <c r="B283">
-        <v>97.46043858892209</v>
+        <v>97.58409086816143</v>
       </c>
       <c r="C283">
-        <v>91.63906387035831</v>
+        <v>91.14954815630996</v>
       </c>
       <c r="D283">
-        <v>5.821374718563774</v>
+        <v>6.434542711851464</v>
       </c>
       <c r="E283" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5400,16 +5433,16 @@
         <v>45</v>
       </c>
       <c r="B284">
-        <v>105.8615299091998</v>
+        <v>102.6481976110865</v>
       </c>
       <c r="C284">
-        <v>106.5861496022455</v>
+        <v>102.6395299556676</v>
       </c>
       <c r="D284">
-        <v>-0.7246196930456676</v>
+        <v>0.008667655418904019</v>
       </c>
       <c r="E284" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5417,16 +5450,16 @@
         <v>45</v>
       </c>
       <c r="B285">
-        <v>103.6765046182746</v>
+        <v>101.7771225837014</v>
       </c>
       <c r="C285">
-        <v>100.778632370508</v>
+        <v>98.98584481263987</v>
       </c>
       <c r="D285">
-        <v>2.897872247766628</v>
+        <v>2.791277771061516</v>
       </c>
       <c r="E285" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5434,16 +5467,16 @@
         <v>45</v>
       </c>
       <c r="B286">
-        <v>98.69872929295749</v>
+        <v>97.90439530796371</v>
       </c>
       <c r="C286">
-        <v>95.44796581280207</v>
+        <v>93.36124283021518</v>
       </c>
       <c r="D286">
-        <v>3.250763480155427</v>
+        <v>4.543152477748535</v>
       </c>
       <c r="E286" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5451,16 +5484,16 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>97.49709102857767</v>
+        <v>97.16945134710316</v>
       </c>
       <c r="C287">
-        <v>93.18149306610117</v>
+        <v>91.60584984557967</v>
       </c>
       <c r="D287">
-        <v>4.315597962476502</v>
+        <v>5.563601501523493</v>
       </c>
       <c r="E287" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5468,16 +5501,16 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>105.8210589522465</v>
+        <v>103.0862159275932</v>
       </c>
       <c r="C288">
-        <v>104.8033278077167</v>
+        <v>102.1252244071716</v>
       </c>
       <c r="D288">
-        <v>1.017731144529876</v>
+        <v>0.9609915204216577</v>
       </c>
       <c r="E288" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5485,16 +5518,16 @@
         <v>46</v>
       </c>
       <c r="B289">
-        <v>99.91410117101903</v>
+        <v>104.7573792101507</v>
       </c>
       <c r="C289">
-        <v>96.69459713292947</v>
+        <v>98.94832188364116</v>
       </c>
       <c r="D289">
-        <v>3.219504038089553</v>
+        <v>5.809057326509546</v>
       </c>
       <c r="E289" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5502,16 +5535,16 @@
         <v>46</v>
       </c>
       <c r="B290">
-        <v>97.27418181643762</v>
+        <v>104.5410658285326</v>
       </c>
       <c r="C290">
-        <v>90.8084862826731</v>
+        <v>92.41013040969534</v>
       </c>
       <c r="D290">
-        <v>6.465695533764517</v>
+        <v>12.1309354188373</v>
       </c>
       <c r="E290" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5519,16 +5552,16 @@
         <v>46</v>
       </c>
       <c r="B291">
-        <v>102.6256651703413</v>
+        <v>104.9741401812275</v>
       </c>
       <c r="C291">
-        <v>102.9695215118075</v>
+        <v>105.9812431249225</v>
       </c>
       <c r="D291">
-        <v>-0.3438563414661786</v>
+        <v>-1.007102943694989</v>
       </c>
       <c r="E291" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5536,16 +5569,16 @@
         <v>46</v>
       </c>
       <c r="B292">
-        <v>101.5897405024566</v>
+        <v>104.9336698515257</v>
       </c>
       <c r="C292">
-        <v>98.88831728328095</v>
+        <v>101.0560846709772</v>
       </c>
       <c r="D292">
-        <v>2.701423219175638</v>
+        <v>3.877585180548536</v>
       </c>
       <c r="E292" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5553,16 +5586,16 @@
         <v>46</v>
       </c>
       <c r="B293">
-        <v>97.74737134148074</v>
+        <v>104.5363815295667</v>
       </c>
       <c r="C293">
-        <v>93.37993831057555</v>
+        <v>95.53543150213487</v>
       </c>
       <c r="D293">
-        <v>4.36743303090519</v>
+        <v>9.00095002743187</v>
       </c>
       <c r="E293" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5570,16 +5603,16 @@
         <v>46</v>
       </c>
       <c r="B294">
-        <v>97.00438399857136</v>
+        <v>104.4746628354562</v>
       </c>
       <c r="C294">
-        <v>91.58051855812424</v>
+        <v>93.42704540696154</v>
       </c>
       <c r="D294">
-        <v>5.423865440447116</v>
+        <v>11.04761742849462</v>
       </c>
       <c r="E294" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5587,16 +5620,16 @@
         <v>46</v>
       </c>
       <c r="B295">
-        <v>102.9110974299847</v>
+        <v>105.0408606368335</v>
       </c>
       <c r="C295">
-        <v>102.0976667196148</v>
+        <v>104.8153944699362</v>
       </c>
       <c r="D295">
-        <v>0.8134307103699143</v>
+        <v>0.2254661668973057</v>
       </c>
       <c r="E295" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5604,16 +5637,16 @@
         <v>47</v>
       </c>
       <c r="B296">
-        <v>104.7425300861989</v>
+        <v>100.2857364474321</v>
       </c>
       <c r="C296">
-        <v>98.94832187775796</v>
+        <v>97.49091864322085</v>
       </c>
       <c r="D296">
-        <v>5.794208208440978</v>
+        <v>2.794817804211291</v>
       </c>
       <c r="E296" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5621,16 +5654,16 @@
         <v>47</v>
       </c>
       <c r="B297">
-        <v>104.5136016749318</v>
+        <v>97.383190434131</v>
       </c>
       <c r="C297">
-        <v>92.04200289654152</v>
+        <v>91.16273755169847</v>
       </c>
       <c r="D297">
-        <v>12.4715987783903</v>
+        <v>6.220452882432525</v>
       </c>
       <c r="E297" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5638,16 +5671,16 @@
         <v>47</v>
       </c>
       <c r="B298">
-        <v>104.9719599462407</v>
+        <v>103.2747940375442</v>
       </c>
       <c r="C298">
-        <v>106.4090111597488</v>
+        <v>104.2671039189707</v>
       </c>
       <c r="D298">
-        <v>-1.437051213508141</v>
+        <v>-0.9923098814265217</v>
       </c>
       <c r="E298" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5655,16 +5688,16 @@
         <v>47</v>
       </c>
       <c r="B299">
-        <v>104.9183342872409</v>
+        <v>101.9959781660138</v>
       </c>
       <c r="C299">
-        <v>100.9595262287203</v>
+        <v>99.61334573305484</v>
       </c>
       <c r="D299">
-        <v>3.958808058520674</v>
+        <v>2.382632432958999</v>
       </c>
       <c r="E299" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5672,16 +5705,16 @@
         <v>47</v>
       </c>
       <c r="B300">
-        <v>104.5218702022862</v>
+        <v>98.05570404119017</v>
       </c>
       <c r="C300">
-        <v>95.596142725826</v>
+        <v>94.18852051560056</v>
       </c>
       <c r="D300">
-        <v>8.925727476460182</v>
+        <v>3.86718352558961</v>
       </c>
       <c r="E300" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5689,16 +5722,16 @@
         <v>47</v>
       </c>
       <c r="B301">
-        <v>104.4598537859175</v>
+        <v>97.26493396002394</v>
       </c>
       <c r="C301">
-        <v>93.42704540143572</v>
+        <v>92.29017210793464</v>
       </c>
       <c r="D301">
-        <v>11.0328083844818</v>
+        <v>4.974761852089301</v>
       </c>
       <c r="E301" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5706,16 +5739,16 @@
         <v>47</v>
       </c>
       <c r="B302">
-        <v>105.0259713300242</v>
+        <v>103.4003574087385</v>
       </c>
       <c r="C302">
-        <v>104.8153944636724</v>
+        <v>102.9882889998444</v>
       </c>
       <c r="D302">
-        <v>0.2105768663518006</v>
+        <v>0.4120684088940578</v>
       </c>
       <c r="E302" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5723,16 +5756,16 @@
         <v>48</v>
       </c>
       <c r="B303">
-        <v>100.1232279134955</v>
+        <v>102.0585715374192</v>
       </c>
       <c r="C303">
-        <v>97.49091858613812</v>
+        <v>96.73657358217316</v>
       </c>
       <c r="D303">
-        <v>2.632309327357419</v>
+        <v>5.321997955246019</v>
       </c>
       <c r="E303" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5740,16 +5773,16 @@
         <v>48</v>
       </c>
       <c r="B304">
-        <v>97.22538534570931</v>
+        <v>100.3847808367394</v>
       </c>
       <c r="C304">
-        <v>91.16273749842786</v>
+        <v>89.08045558949024</v>
       </c>
       <c r="D304">
-        <v>6.062647847281454</v>
+        <v>11.3043252472492</v>
       </c>
       <c r="E304" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5757,16 +5790,16 @@
         <v>48</v>
       </c>
       <c r="B305">
-        <v>103.1074418699661</v>
+        <v>103.7602706051475</v>
       </c>
       <c r="C305">
-        <v>104.2671038578026</v>
+        <v>105.0844951852933</v>
       </c>
       <c r="D305">
-        <v>-1.1596619878365</v>
+        <v>-1.324224580145767</v>
       </c>
       <c r="E305" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5774,16 +5807,16 @@
         <v>48</v>
       </c>
       <c r="B306">
-        <v>101.8171002477665</v>
+        <v>103.3181555155236</v>
       </c>
       <c r="C306">
-        <v>99.55016430866641</v>
+        <v>98.57034220795936</v>
       </c>
       <c r="D306">
-        <v>2.266935939100094</v>
+        <v>4.747813307564229</v>
       </c>
       <c r="E306" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5791,16 +5824,16 @@
         <v>48</v>
       </c>
       <c r="B307">
-        <v>97.90552527824964</v>
+        <v>100.4685013135554</v>
       </c>
       <c r="C307">
-        <v>94.22833862989678</v>
+        <v>93.34531525257884</v>
       </c>
       <c r="D307">
-        <v>3.677186648352858</v>
+        <v>7.123186060976579</v>
       </c>
       <c r="E307" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5808,16 +5841,16 @@
         <v>48</v>
       </c>
       <c r="B308">
-        <v>97.10732050090984</v>
+        <v>99.98536234822487</v>
       </c>
       <c r="C308">
-        <v>92.29017205396615</v>
+        <v>90.815915381094</v>
       </c>
       <c r="D308">
-        <v>4.81714844694369</v>
+        <v>9.169446967130867</v>
       </c>
       <c r="E308" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5825,16 +5858,16 @@
         <v>48</v>
       </c>
       <c r="B309">
-        <v>103.232801771354</v>
+        <v>104.1747689825064</v>
       </c>
       <c r="C309">
-        <v>102.9882889394677</v>
+        <v>103.0556091016367</v>
       </c>
       <c r="D309">
-        <v>0.244512831886297</v>
+        <v>1.119159880869645</v>
       </c>
       <c r="E309" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5842,16 +5875,16 @@
         <v>49</v>
       </c>
       <c r="B310">
-        <v>101.9502325061552</v>
+        <v>100.9173609991365</v>
       </c>
       <c r="C310">
-        <v>96.73657356840648</v>
+        <v>97.91949908951956</v>
       </c>
       <c r="D310">
-        <v>5.213658937748676</v>
+        <v>2.997861909616972</v>
       </c>
       <c r="E310" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5859,16 +5892,16 @@
         <v>49</v>
       </c>
       <c r="B311">
-        <v>100.1812055975771</v>
+        <v>96.67335904073622</v>
       </c>
       <c r="C311">
-        <v>88.65249775377731</v>
+        <v>90.8386784507727</v>
       </c>
       <c r="D311">
-        <v>11.52870784379978</v>
+        <v>5.834680589963511</v>
       </c>
       <c r="E311" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5876,16 +5909,16 @@
         <v>49</v>
       </c>
       <c r="B312">
-        <v>103.7504973718391</v>
+        <v>105.3544459903274</v>
       </c>
       <c r="C312">
-        <v>105.5958689510879</v>
+        <v>105.5852606224958</v>
       </c>
       <c r="D312">
-        <v>-1.84537157924882</v>
+        <v>-0.2308146321683751</v>
       </c>
       <c r="E312" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5893,16 +5926,16 @@
         <v>49</v>
       </c>
       <c r="B313">
-        <v>103.2019929364598</v>
+        <v>103.1296990276786</v>
       </c>
       <c r="C313">
-        <v>98.4416594737264</v>
+        <v>99.91494484209505</v>
       </c>
       <c r="D313">
-        <v>4.760333462733385</v>
+        <v>3.214754185583544</v>
       </c>
       <c r="E313" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5910,16 +5943,16 @@
         <v>49</v>
       </c>
       <c r="B314">
-        <v>100.3660554533129</v>
+        <v>97.88168136884839</v>
       </c>
       <c r="C314">
-        <v>93.42653318652474</v>
+        <v>94.49754764399198</v>
       </c>
       <c r="D314">
-        <v>6.939522266788131</v>
+        <v>3.384133724856412</v>
       </c>
       <c r="E314" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5927,16 +5960,16 @@
         <v>49</v>
       </c>
       <c r="B315">
-        <v>99.87922410687767</v>
+        <v>96.58427374453667</v>
       </c>
       <c r="C315">
-        <v>90.81591536819387</v>
+        <v>92.18726691718007</v>
       </c>
       <c r="D315">
-        <v>9.063308738683801</v>
+        <v>4.397006827356606</v>
       </c>
       <c r="E315" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5944,16 +5977,16 @@
         <v>49</v>
       </c>
       <c r="B316">
-        <v>104.064183527667</v>
+        <v>105.4509096738266</v>
       </c>
       <c r="C316">
-        <v>103.0556090869436</v>
+        <v>104.0239456230154</v>
       </c>
       <c r="D316">
-        <v>1.008574440723379</v>
+        <v>1.426964050811264</v>
       </c>
       <c r="E316" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5961,16 +5994,16 @@
         <v>50</v>
       </c>
       <c r="B317">
-        <v>100.6710591156055</v>
+        <v>103.4185324129656</v>
       </c>
       <c r="C317">
-        <v>97.91949917476222</v>
+        <v>100.4741530670275</v>
       </c>
       <c r="D317">
-        <v>2.751559940843308</v>
+        <v>2.944379345938103</v>
       </c>
       <c r="E317" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5978,16 +6011,16 @@
         <v>50</v>
       </c>
       <c r="B318">
-        <v>96.19575743644889</v>
+        <v>102.5165133112589</v>
       </c>
       <c r="C318">
-        <v>90.44136571499315</v>
+        <v>96.26451836385711</v>
       </c>
       <c r="D318">
-        <v>5.754391721455733</v>
+        <v>6.251994947401826</v>
       </c>
       <c r="E318" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5995,16 +6028,16 @@
         <v>50</v>
       </c>
       <c r="B319">
-        <v>105.3621636633655</v>
+        <v>104.3284881722269</v>
       </c>
       <c r="C319">
-        <v>106.0530960342612</v>
+        <v>104.8744832587372</v>
       </c>
       <c r="D319">
-        <v>-0.6909323708957089</v>
+        <v>-0.5459950865102741</v>
       </c>
       <c r="E319" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6012,16 +6045,16 @@
         <v>50</v>
       </c>
       <c r="B320">
-        <v>102.8364888534832</v>
+        <v>104.1581323601268</v>
       </c>
       <c r="C320">
-        <v>99.80328547895101</v>
+        <v>102.6747395349171</v>
       </c>
       <c r="D320">
-        <v>3.033203374532192</v>
+        <v>1.483392825209663</v>
       </c>
       <c r="E320" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -6029,16 +6062,16 @@
         <v>50</v>
       </c>
       <c r="B321">
-        <v>97.6691334928914</v>
+        <v>102.4970466839698</v>
       </c>
       <c r="C321">
-        <v>94.56785577700826</v>
+        <v>97.45698362387361</v>
       </c>
       <c r="D321">
-        <v>3.101277715883143</v>
+        <v>5.04006306009623</v>
       </c>
       <c r="E321" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -6046,16 +6079,16 @@
         <v>50</v>
       </c>
       <c r="B322">
-        <v>96.34887052537348</v>
+        <v>102.2408248267436</v>
       </c>
       <c r="C322">
-        <v>92.18726699712664</v>
+        <v>96.17056964434163</v>
       </c>
       <c r="D322">
-        <v>4.161603528246843</v>
+        <v>6.070255182401937</v>
       </c>
       <c r="E322" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6063,16 +6096,16 @@
         <v>50</v>
       </c>
       <c r="B323">
-        <v>105.1932007752908</v>
+        <v>104.6098059613266</v>
       </c>
       <c r="C323">
-        <v>104.0239457139039</v>
+        <v>104.9762708372295</v>
       </c>
       <c r="D323">
-        <v>1.169255061386878</v>
+        <v>-0.3664648759029916</v>
       </c>
       <c r="E323" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -6080,16 +6113,16 @@
         <v>51</v>
       </c>
       <c r="B324">
-        <v>103.3440692082781</v>
+        <v>103.3205754532984</v>
       </c>
       <c r="C324">
-        <v>100.4467652356561</v>
+        <v>100.2855385457775</v>
       </c>
       <c r="D324">
-        <v>2.89730397262197</v>
+        <v>3.035036907520976</v>
       </c>
       <c r="E324" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6097,16 +6130,16 @@
         <v>51</v>
       </c>
       <c r="B325">
-        <v>102.3901845142014</v>
+        <v>102.4194107347153</v>
       </c>
       <c r="C325">
-        <v>95.99719959402552</v>
+        <v>96.0807235600938</v>
       </c>
       <c r="D325">
-        <v>6.392984920175905</v>
+        <v>6.338687174621541</v>
       </c>
       <c r="E325" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6114,16 +6147,16 @@
         <v>51</v>
       </c>
       <c r="B326">
-        <v>104.3068404573883</v>
+        <v>104.2296693119165</v>
       </c>
       <c r="C326">
-        <v>105.1099770259277</v>
+        <v>104.6808606087796</v>
       </c>
       <c r="D326">
-        <v>-0.8031365685393865</v>
+        <v>-0.4511912968630725</v>
       </c>
       <c r="E326" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6131,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="B327">
-        <v>104.0811965450515</v>
+        <v>104.059474859072</v>
       </c>
       <c r="C327">
-        <v>102.6059846882894</v>
+        <v>102.4833611683356</v>
       </c>
       <c r="D327">
-        <v>1.47521185676203</v>
+        <v>1.576113690736449</v>
       </c>
       <c r="E327" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6148,16 +6181,16 @@
         <v>51</v>
       </c>
       <c r="B328">
-        <v>102.4245197488043</v>
+        <v>102.3999625460134</v>
       </c>
       <c r="C328">
-        <v>97.4560168516914</v>
+        <v>97.27207411251487</v>
       </c>
       <c r="D328">
-        <v>4.968502897112927</v>
+        <v>5.127888433498569</v>
       </c>
       <c r="E328" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6165,16 +6198,16 @@
         <v>51</v>
       </c>
       <c r="B329">
-        <v>102.1672095927148</v>
+        <v>102.1439833794689</v>
       </c>
       <c r="C329">
-        <v>96.14393109250211</v>
+        <v>95.98711526522727</v>
       </c>
       <c r="D329">
-        <v>6.023278500212641</v>
+        <v>6.156868114241604</v>
       </c>
       <c r="E329" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6182,16 +6215,16 @@
         <v>51</v>
       </c>
       <c r="B330">
-        <v>104.5344850182434</v>
+        <v>104.5107206397284</v>
       </c>
       <c r="C330">
-        <v>104.948104533828</v>
+        <v>104.7822951307219</v>
       </c>
       <c r="D330">
-        <v>-0.4136195155846423</v>
+        <v>-0.271574490993487</v>
       </c>
       <c r="E330" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6199,16 +6232,16 @@
         <v>52</v>
       </c>
       <c r="B331">
-        <v>103.2464375334023</v>
+        <v>101.3089326795153</v>
       </c>
       <c r="C331">
-        <v>100.2586674664994</v>
+        <v>98.0363496602218</v>
       </c>
       <c r="D331">
-        <v>2.987770066902868</v>
+        <v>3.272583019293521</v>
       </c>
       <c r="E331" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6216,16 +6249,16 @@
         <v>52</v>
       </c>
       <c r="B332">
-        <v>102.2934539975734</v>
+        <v>99.52980599075127</v>
       </c>
       <c r="C332">
-        <v>95.81418402392239</v>
+        <v>93.0855308232242</v>
       </c>
       <c r="D332">
-        <v>6.479269973650986</v>
+        <v>6.444275167527067</v>
       </c>
       <c r="E332" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6233,16 +6266,16 @@
         <v>52</v>
       </c>
       <c r="B333">
-        <v>104.2082992289185</v>
+        <v>103.1198618192454</v>
       </c>
       <c r="C333">
-        <v>104.9165865190259</v>
+        <v>103.2567862460836</v>
       </c>
       <c r="D333">
-        <v>-0.7082872901074211</v>
+        <v>-0.1369244268382346</v>
       </c>
       <c r="E333" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6250,16 +6283,16 @@
         <v>52</v>
       </c>
       <c r="B334">
-        <v>103.9828684879155</v>
+        <v>102.6288498072516</v>
       </c>
       <c r="C334">
-        <v>102.4151712133323</v>
+        <v>100.3058327268112</v>
       </c>
       <c r="D334">
-        <v>1.567697274583224</v>
+        <v>2.32301708044038</v>
       </c>
       <c r="E334" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6267,16 +6300,16 @@
         <v>52</v>
       </c>
       <c r="B335">
-        <v>102.3277567948386</v>
+        <v>99.63857681634184</v>
       </c>
       <c r="C335">
-        <v>97.2715882677836</v>
+        <v>94.80087043833353</v>
       </c>
       <c r="D335">
-        <v>5.05616852705505</v>
+        <v>4.837706378008306</v>
       </c>
       <c r="E335" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6284,16 +6317,16 @@
         <v>52</v>
       </c>
       <c r="B336">
-        <v>102.0706897259596</v>
+        <v>99.12370611227132</v>
       </c>
       <c r="C336">
-        <v>95.96097932810657</v>
+        <v>93.26244286823585</v>
       </c>
       <c r="D336">
-        <v>6.109710397852979</v>
+        <v>5.86126324403547</v>
       </c>
       <c r="E336" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6301,16 +6334,16 @@
         <v>52</v>
       </c>
       <c r="B337">
-        <v>104.4357287283779</v>
+        <v>103.5423335467071</v>
       </c>
       <c r="C337">
-        <v>104.7546602675912</v>
+        <v>103.0588908754651</v>
       </c>
       <c r="D337">
-        <v>-0.3189315392133238</v>
+        <v>0.4834426712420452</v>
       </c>
       <c r="E337" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6318,16 +6351,16 @@
         <v>53</v>
       </c>
       <c r="B338">
-        <v>101.1809011053704</v>
+        <v>103.5164893726329</v>
       </c>
       <c r="C338">
-        <v>98.01051974825486</v>
+        <v>100.6627675882776</v>
       </c>
       <c r="D338">
-        <v>3.170381357115531</v>
+        <v>2.853721784355258</v>
       </c>
       <c r="E338" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6335,16 +6368,16 @@
         <v>53</v>
       </c>
       <c r="B339">
-        <v>99.30099003129841</v>
+        <v>102.6136158878025</v>
       </c>
       <c r="C339">
-        <v>92.7789031504378</v>
+        <v>96.44831316762044</v>
       </c>
       <c r="D339">
-        <v>6.522086880860613</v>
+        <v>6.165302720182083</v>
       </c>
       <c r="E339" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6352,16 +6385,16 @@
         <v>53</v>
       </c>
       <c r="B340">
-        <v>103.096401609571</v>
+        <v>104.4273070325374</v>
       </c>
       <c r="C340">
-        <v>103.5442045044892</v>
+        <v>105.068105908695</v>
       </c>
       <c r="D340">
-        <v>-0.4478028949182402</v>
+        <v>-0.6407988761575751</v>
       </c>
       <c r="E340" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6369,16 +6402,16 @@
         <v>53</v>
       </c>
       <c r="B341">
-        <v>102.4917747241591</v>
+        <v>104.2567898611815</v>
       </c>
       <c r="C341">
-        <v>100.2232924912705</v>
+        <v>102.8661179014986</v>
       </c>
       <c r="D341">
-        <v>2.268482232888616</v>
+        <v>1.390671959682976</v>
       </c>
       <c r="E341" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6386,16 +6419,16 @@
         <v>53</v>
       </c>
       <c r="B342">
-        <v>99.51743017110232</v>
+        <v>102.5941308219263</v>
       </c>
       <c r="C342">
-        <v>94.81109255053009</v>
+        <v>97.64189313523246</v>
       </c>
       <c r="D342">
-        <v>4.706337620572228</v>
+        <v>4.95223768669382</v>
       </c>
       <c r="E342" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6403,16 +6436,16 @@
         <v>53</v>
       </c>
       <c r="B343">
-        <v>98.99843617019444</v>
+        <v>102.3376662740183</v>
       </c>
       <c r="C343">
-        <v>93.23752496848046</v>
+        <v>96.35402402345605</v>
       </c>
       <c r="D343">
-        <v>5.760911201713981</v>
+        <v>5.983642250562227</v>
       </c>
       <c r="E343" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6420,16 +6453,16 @@
         <v>53</v>
       </c>
       <c r="B344">
-        <v>103.4114794590763</v>
+        <v>104.7088912829247</v>
       </c>
       <c r="C344">
-        <v>103.0321097523068</v>
+        <v>105.1702465437372</v>
       </c>
       <c r="D344">
-        <v>0.3793697067695376</v>
+        <v>-0.4613552608124536</v>
       </c>
       <c r="E344" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6437,16 +6470,16 @@
         <v>54</v>
       </c>
       <c r="B345">
-        <v>103.4417008831539</v>
+        <v>103.5344053746249</v>
       </c>
       <c r="C345">
-        <v>100.6348630048129</v>
+        <v>103.4716031667094</v>
       </c>
       <c r="D345">
-        <v>2.806837878341</v>
+        <v>0.06280220791553859</v>
       </c>
       <c r="E345" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6454,16 +6487,16 @@
         <v>54</v>
       </c>
       <c r="B346">
-        <v>102.4869150308295</v>
+        <v>102.7056982454528</v>
       </c>
       <c r="C346">
-        <v>96.1802151641286</v>
+        <v>102.6433987171754</v>
       </c>
       <c r="D346">
-        <v>6.30669986670091</v>
+        <v>0.06229952827742125</v>
       </c>
       <c r="E346" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6471,16 +6504,16 @@
         <v>54</v>
       </c>
       <c r="B347">
-        <v>104.4053816858582</v>
+        <v>104.3697991386932</v>
       </c>
       <c r="C347">
-        <v>105.3033675328296</v>
+        <v>104.3064901951407</v>
       </c>
       <c r="D347">
-        <v>-0.8979858469713804</v>
+        <v>0.06330894355257044</v>
       </c>
       <c r="E347" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6488,16 +6521,16 @@
         <v>54</v>
       </c>
       <c r="B348">
-        <v>104.1795246021874</v>
+        <v>104.164247984106</v>
       </c>
       <c r="C348">
-        <v>102.7967981632465</v>
+        <v>104.1010637243849</v>
       </c>
       <c r="D348">
-        <v>1.382726438940864</v>
+        <v>0.06318425972111186</v>
       </c>
       <c r="E348" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6505,16 +6538,16 @@
         <v>54</v>
       </c>
       <c r="B349">
-        <v>102.52128270277</v>
+        <v>102.7475063204104</v>
       </c>
       <c r="C349">
-        <v>97.64044543559912</v>
+        <v>102.6851814320664</v>
       </c>
       <c r="D349">
-        <v>4.880837267170847</v>
+        <v>0.0623248883440084</v>
       </c>
       <c r="E349" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6522,16 +6555,16 @@
         <v>54</v>
       </c>
       <c r="B350">
-        <v>102.26372945947</v>
+        <v>102.5267546766554</v>
       </c>
       <c r="C350">
-        <v>96.32688285689767</v>
+        <v>102.4645636925009</v>
       </c>
       <c r="D350">
-        <v>5.936846602572317</v>
+        <v>0.06219098415455449</v>
       </c>
       <c r="E350" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6539,16 +6572,16 @@
         <v>54</v>
       </c>
       <c r="B351">
-        <v>104.6332413081089</v>
+        <v>104.5519594381336</v>
       </c>
       <c r="C351">
-        <v>105.1415488000647</v>
+        <v>104.4885399992442</v>
       </c>
       <c r="D351">
-        <v>-0.5083074919558754</v>
+        <v>0.06341943888938317</v>
       </c>
       <c r="E351" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6556,16 +6589,16 @@
         <v>55</v>
       </c>
       <c r="B352">
-        <v>103.4825981905367</v>
+        <v>101.4593859641259</v>
       </c>
       <c r="C352">
-        <v>103.4716031579401</v>
+        <v>101.1722336912383</v>
       </c>
       <c r="D352">
-        <v>0.01099503259661105</v>
+        <v>0.2871522728876528</v>
       </c>
       <c r="E352" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6573,16 +6606,16 @@
         <v>55</v>
       </c>
       <c r="B353">
-        <v>102.6242949942016</v>
+        <v>96.96206547892837</v>
       </c>
       <c r="C353">
-        <v>102.6133911563739</v>
+        <v>96.6881126207596</v>
       </c>
       <c r="D353">
-        <v>0.01090383782771198</v>
+        <v>0.2739528581687694</v>
       </c>
       <c r="E353" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6590,16 +6623,16 @@
         <v>55</v>
       </c>
       <c r="B354">
-        <v>104.348079846679</v>
+        <v>106.1736997991979</v>
       </c>
       <c r="C354">
-        <v>104.3369928566018</v>
+        <v>105.8727074982988</v>
       </c>
       <c r="D354">
-        <v>0.01108699007720304</v>
+        <v>0.3009923008991535</v>
       </c>
       <c r="E354" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6607,16 +6640,16 @@
         <v>55</v>
       </c>
       <c r="B355">
-        <v>104.1102578808078</v>
+        <v>103.5579234312434</v>
       </c>
       <c r="C355">
-        <v>104.0991961593295</v>
+        <v>103.2646362410305</v>
       </c>
       <c r="D355">
-        <v>0.0110617214783133</v>
+        <v>0.2932871902129079</v>
       </c>
       <c r="E355" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6624,16 +6657,16 @@
         <v>55</v>
       </c>
       <c r="B356">
-        <v>102.6973211422739</v>
+        <v>98.54666466603911</v>
       </c>
       <c r="C356">
-        <v>102.6864095454133</v>
+        <v>98.2680366191906</v>
       </c>
       <c r="D356">
-        <v>0.01091159686055221</v>
+        <v>0.2786280468485103</v>
       </c>
       <c r="E356" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6641,16 +6674,16 @@
         <v>55</v>
       </c>
       <c r="B357">
-        <v>102.4754517070361</v>
+        <v>97.26336128852709</v>
       </c>
       <c r="C357">
-        <v>102.464563683817</v>
+        <v>96.98850214681083</v>
       </c>
       <c r="D357">
-        <v>0.01088802321909554</v>
+        <v>0.2748591417162629</v>
       </c>
       <c r="E357" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6658,16 +6691,16 @@
         <v>55</v>
       </c>
       <c r="B358">
-        <v>104.4996430840696</v>
+        <v>105.8429931131407</v>
       </c>
       <c r="C358">
-        <v>104.4885399903888</v>
+        <v>105.5429942648275</v>
       </c>
       <c r="D358">
-        <v>0.01110309368075946</v>
+        <v>0.2999988483131659</v>
       </c>
       <c r="E358" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6675,16 +6708,16 @@
         <v>56</v>
       </c>
       <c r="B359">
-        <v>101.2224582762651</v>
+        <v>99.74084156252955</v>
       </c>
       <c r="C359">
-        <v>101.1722336785614</v>
+        <v>99.48192384116452</v>
       </c>
       <c r="D359">
-        <v>0.05022459770366083</v>
+        <v>0.2589177213650373</v>
       </c>
       <c r="E359" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6692,16 +6725,16 @@
         <v>56</v>
       </c>
       <c r="B360">
-        <v>96.73602857100462</v>
+        <v>95.75106403436952</v>
       </c>
       <c r="C360">
-        <v>96.68811260865532</v>
+        <v>95.50287033371339</v>
       </c>
       <c r="D360">
-        <v>0.04791596234930751</v>
+        <v>0.248193700656131</v>
       </c>
       <c r="E360" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6709,16 +6742,16 @@
         <v>56</v>
       </c>
       <c r="B361">
-        <v>105.9253527640014</v>
+        <v>103.9030863326436</v>
       </c>
       <c r="C361">
-        <v>105.8727074850219</v>
+        <v>103.6329800610002</v>
       </c>
       <c r="D361">
-        <v>0.05264527897955418</v>
+        <v>0.2701062716434137</v>
       </c>
       <c r="E361" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6726,16 +6759,16 @@
         <v>56</v>
       </c>
       <c r="B362">
-        <v>103.2833657715376</v>
+        <v>101.7296737698656</v>
       </c>
       <c r="C362">
-        <v>103.232084997649</v>
+        <v>101.4654157138243</v>
       </c>
       <c r="D362">
-        <v>0.05128077388856411</v>
+        <v>0.2642580560412711</v>
       </c>
       <c r="E362" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6743,16 +6776,16 @@
         <v>56</v>
       </c>
       <c r="B363">
-        <v>98.33739647562983</v>
+        <v>97.03323682253108</v>
       </c>
       <c r="C363">
-        <v>98.28865213330114</v>
+        <v>96.78159124617753</v>
       </c>
       <c r="D363">
-        <v>0.04874434232868907</v>
+        <v>0.2516455763535532</v>
       </c>
       <c r="E363" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6760,16 +6793,16 @@
         <v>56</v>
       </c>
       <c r="B364">
-        <v>97.03657660912498</v>
+        <v>95.90839367382729</v>
       </c>
       <c r="C364">
-        <v>96.98850213466766</v>
+        <v>95.65977207379647</v>
       </c>
       <c r="D364">
-        <v>0.04807447445732294</v>
+        <v>0.2486216000308161</v>
       </c>
       <c r="E364" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6777,16 +6810,16 @@
         <v>56</v>
       </c>
       <c r="B365">
-        <v>105.5954657722516</v>
+        <v>103.7319927237259</v>
       </c>
       <c r="C365">
-        <v>105.5429942515933</v>
+        <v>103.4623514498608</v>
       </c>
       <c r="D365">
-        <v>0.05247152065831528</v>
+        <v>0.2696412738651048</v>
       </c>
       <c r="E365" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6794,16 +6827,16 @@
         <v>57</v>
       </c>
       <c r="B366">
-        <v>99.527214621135</v>
+        <v>99.8903434641373</v>
       </c>
       <c r="C366">
-        <v>99.48192381970912</v>
+        <v>99.70063801409665</v>
       </c>
       <c r="D366">
-        <v>0.04529080142587816</v>
+        <v>0.1897054500406483</v>
       </c>
       <c r="E366" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6811,16 +6844,16 @@
         <v>57</v>
       </c>
       <c r="B367">
-        <v>95.54628523598248</v>
+        <v>97.10560002157561</v>
       </c>
       <c r="C367">
-        <v>95.50287031314511</v>
+        <v>96.92118318092095</v>
       </c>
       <c r="D367">
-        <v>0.04341492283737125</v>
+        <v>0.1844168406546629</v>
       </c>
       <c r="E367" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6828,16 +6861,16 @@
         <v>57</v>
       </c>
       <c r="B368">
-        <v>103.6802279755579</v>
+        <v>102.7549463178881</v>
       </c>
       <c r="C368">
-        <v>103.6329800386192</v>
+        <v>102.5598005944966</v>
       </c>
       <c r="D368">
-        <v>0.04724793693874574</v>
+        <v>0.1951457233915619</v>
       </c>
       <c r="E368" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6845,16 +6878,16 @@
         <v>57</v>
       </c>
       <c r="B369">
-        <v>101.4853918780544</v>
+        <v>101.5534274711198</v>
       </c>
       <c r="C369">
-        <v>101.4391793180302</v>
+        <v>101.3605635966604</v>
       </c>
       <c r="D369">
-        <v>0.04621256002427288</v>
+        <v>0.1928638744594622</v>
       </c>
       <c r="E369" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6862,16 +6895,16 @@
         <v>57</v>
       </c>
       <c r="B370">
-        <v>96.8422760858582</v>
+        <v>97.72854280772071</v>
       </c>
       <c r="C370">
-        <v>96.79824948434175</v>
+        <v>97.54294291335438</v>
       </c>
       <c r="D370">
-        <v>0.04402660151644966</v>
+        <v>0.1855998943663337</v>
       </c>
       <c r="E370" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6879,16 +6912,16 @@
         <v>57</v>
       </c>
       <c r="B371">
-        <v>95.70326182543559</v>
+        <v>96.97215787903572</v>
       </c>
       <c r="C371">
-        <v>95.65977205319282</v>
+        <v>96.78799446329511</v>
       </c>
       <c r="D371">
-        <v>0.04348977224276496</v>
+        <v>0.1841634157406133</v>
       </c>
       <c r="E371" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6896,16 +6929,16 @@
         <v>57</v>
       </c>
       <c r="B372">
-        <v>103.5095180256864</v>
+        <v>102.8963460814196</v>
       </c>
       <c r="C372">
-        <v>103.4623514275182</v>
+        <v>102.7009318205013</v>
       </c>
       <c r="D372">
-        <v>0.04716659816817526</v>
+        <v>0.1954142609182696</v>
       </c>
       <c r="E372" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6913,16 +6946,16 @@
         <v>58</v>
       </c>
       <c r="B373">
-        <v>99.72057357344767</v>
+        <v>100.7088179648015</v>
       </c>
       <c r="C373">
-        <v>99.68738322556231</v>
+        <v>100.5268224843882</v>
       </c>
       <c r="D373">
-        <v>0.03319034788535191</v>
+        <v>0.1819954804133488</v>
       </c>
       <c r="E373" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6930,16 +6963,16 @@
         <v>58</v>
       </c>
       <c r="B374">
-        <v>96.94056297665911</v>
+        <v>98.31891214869432</v>
       </c>
       <c r="C374">
-        <v>96.90829790944079</v>
+        <v>98.14123557566099</v>
       </c>
       <c r="D374">
-        <v>0.03226506721831868</v>
+        <v>0.1776765730333381</v>
       </c>
       <c r="E374" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6947,16 +6980,16 @@
         <v>58</v>
       </c>
       <c r="B375">
-        <v>102.5803078553577</v>
+        <v>103.1568168749539</v>
       </c>
       <c r="C375">
-        <v>102.5461656920919</v>
+        <v>102.9703975044909</v>
       </c>
       <c r="D375">
-        <v>0.03414216326586939</v>
+        <v>0.1864193704630708</v>
       </c>
       <c r="E375" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6964,16 +6997,16 @@
         <v>58</v>
       </c>
       <c r="B376">
-        <v>101.3682520262212</v>
+        <v>102.3534677273629</v>
       </c>
       <c r="C376">
-        <v>101.3345132757435</v>
+        <v>102.1685001256428</v>
       </c>
       <c r="D376">
-        <v>0.03373875047766717</v>
+        <v>0.1849676017201318</v>
       </c>
       <c r="E376" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6981,16 +7014,16 @@
         <v>58</v>
       </c>
       <c r="B377">
-        <v>97.5705180436503</v>
+        <v>98.59819954179167</v>
       </c>
       <c r="C377">
-        <v>97.53804330627992</v>
+        <v>98.4200182558215</v>
       </c>
       <c r="D377">
-        <v>0.03247473737037865</v>
+        <v>0.1781812859701688</v>
       </c>
       <c r="E377" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6998,16 +7031,16 @@
         <v>58</v>
       </c>
       <c r="B378">
-        <v>96.80734762739243</v>
+        <v>97.89751429116035</v>
       </c>
       <c r="C378">
-        <v>96.77512689870554</v>
+        <v>97.72059924534067</v>
       </c>
       <c r="D378">
-        <v>0.03222072868689452</v>
+        <v>0.1769150458196833</v>
       </c>
       <c r="E378" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7015,16 +7048,16 @@
         <v>58</v>
       </c>
       <c r="B379">
-        <v>102.7214673011411</v>
+        <v>103.6008532934051</v>
       </c>
       <c r="C379">
-        <v>102.6872781552825</v>
+        <v>103.4136314845566</v>
       </c>
       <c r="D379">
-        <v>0.03418914585866162</v>
+        <v>0.187221808848534</v>
       </c>
       <c r="E379" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -7032,16 +7065,16 @@
         <v>59</v>
       </c>
       <c r="B380">
-        <v>100.543812508687</v>
+        <v>101.0485120585237</v>
       </c>
       <c r="C380">
-        <v>100.5119703364907</v>
+        <v>100.8679100974179</v>
       </c>
       <c r="D380">
-        <v>0.03184217219627783</v>
+        <v>0.1806019611057792</v>
       </c>
       <c r="E380" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -7049,16 +7082,16 @@
         <v>59</v>
       </c>
       <c r="B381">
-        <v>98.01993211035413</v>
+        <v>98.41465835959715</v>
       </c>
       <c r="C381">
-        <v>97.98888924974392</v>
+        <v>98.23876383191711</v>
       </c>
       <c r="D381">
-        <v>0.03104286061021355</v>
+        <v>0.1758945276800432</v>
       </c>
       <c r="E381" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7066,16 +7099,16 @@
         <v>59</v>
       </c>
       <c r="B382">
-        <v>103.1326794064792</v>
+        <v>103.7528551075429</v>
       </c>
       <c r="C382">
-        <v>103.1000173415068</v>
+        <v>103.5674197288221</v>
       </c>
       <c r="D382">
-        <v>0.03266206497239921</v>
+        <v>0.1854353787208396</v>
       </c>
       <c r="E382" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7083,16 +7116,16 @@
         <v>59</v>
       </c>
       <c r="B383">
-        <v>102.1725853422724</v>
+        <v>102.6571571626879</v>
       </c>
       <c r="C383">
-        <v>102.1402273385819</v>
+        <v>102.4736801027349</v>
       </c>
       <c r="D383">
-        <v>0.03235800369051844</v>
+        <v>0.183477059953006</v>
       </c>
       <c r="E383" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7100,16 +7133,16 @@
         <v>59</v>
       </c>
       <c r="B384">
-        <v>98.44511886653196</v>
+        <v>98.96801118792916</v>
       </c>
       <c r="C384">
-        <v>98.41394134950113</v>
+        <v>98.79112766393494</v>
       </c>
       <c r="D384">
-        <v>0.03117751703082661</v>
+        <v>0.1768835239942206</v>
       </c>
       <c r="E384" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7117,16 +7150,16 @@
         <v>59</v>
       </c>
       <c r="B385">
-        <v>97.73711499023969</v>
+        <v>98.25626909435962</v>
       </c>
       <c r="C385">
-        <v>97.70616169766171</v>
+        <v>98.08065765260876</v>
       </c>
       <c r="D385">
-        <v>0.0309532925779763</v>
+        <v>0.1756114417508599</v>
       </c>
       <c r="E385" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7134,16 +7167,16 @@
         <v>59</v>
       </c>
       <c r="B386">
-        <v>103.4311094080434</v>
+        <v>103.9201048783539</v>
       </c>
       <c r="C386">
-        <v>103.3983528304475</v>
+        <v>103.7343705775016</v>
       </c>
       <c r="D386">
-        <v>0.03275657759587602</v>
+        <v>0.1857343008523031</v>
       </c>
       <c r="E386" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7151,16 +7184,16 @@
         <v>60</v>
       </c>
       <c r="B387">
-        <v>100.8995133753122</v>
+        <v>101.2632779791656</v>
       </c>
       <c r="C387">
-        <v>100.8679100864914</v>
+        <v>101.0897154979227</v>
       </c>
       <c r="D387">
-        <v>0.03160328882077579</v>
+        <v>0.1735624812428824</v>
       </c>
       <c r="E387" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7168,16 +7201,16 @@
         <v>60</v>
       </c>
       <c r="B388">
-        <v>98.26954336279434</v>
+        <v>98.74278703909332</v>
       </c>
       <c r="C388">
-        <v>98.23876382127544</v>
+        <v>98.57354461019561</v>
       </c>
       <c r="D388">
-        <v>0.03077954151889628</v>
+        <v>0.1692424288977037</v>
       </c>
       <c r="E388" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7185,16 +7218,16 @@
         <v>60</v>
       </c>
       <c r="B389">
-        <v>103.5998687995258</v>
+        <v>103.8481065257557</v>
       </c>
       <c r="C389">
-        <v>103.5674197176032</v>
+        <v>103.6701137192746</v>
       </c>
       <c r="D389">
-        <v>0.03244908192259288</v>
+        <v>0.1779928064810434</v>
       </c>
       <c r="E389" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7202,16 +7235,16 @@
         <v>60</v>
       </c>
       <c r="B390">
-        <v>102.4946344841521</v>
+        <v>102.8247057239817</v>
       </c>
       <c r="C390">
-        <v>102.4625315787186</v>
+        <v>102.6484669984075</v>
       </c>
       <c r="D390">
-        <v>0.03210290543350425</v>
+        <v>0.176238725574251</v>
       </c>
       <c r="E390" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7219,16 +7252,16 @@
         <v>60</v>
       </c>
       <c r="B391">
-        <v>98.82924840178424</v>
+        <v>99.25012018015225</v>
       </c>
       <c r="C391">
-        <v>98.79829355198673</v>
+        <v>99.08000819616471</v>
       </c>
       <c r="D391">
-        <v>0.03095484979751006</v>
+        <v>0.1701119839875389</v>
       </c>
       <c r="E391" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7236,16 +7269,16 @@
         <v>60</v>
       </c>
       <c r="B392">
-        <v>98.11138764668571</v>
+        <v>98.57126139984857</v>
       </c>
       <c r="C392">
-        <v>98.08065764198425</v>
+        <v>98.40231296119235</v>
       </c>
       <c r="D392">
-        <v>0.03073000470146781</v>
+        <v>0.1689484386562157</v>
       </c>
       <c r="E392" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7253,16 +7286,16 @@
         <v>60</v>
       </c>
       <c r="B393">
-        <v>103.7668719561599</v>
+        <v>104.0288144988832</v>
       </c>
       <c r="C393">
-        <v>103.7343705662646</v>
+        <v>103.8505119638922</v>
       </c>
       <c r="D393">
-        <v>0.03250138989530171</v>
+        <v>0.1783025349909906</v>
       </c>
       <c r="E393" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7270,16 +7303,16 @@
         <v>61</v>
       </c>
       <c r="B394">
-        <v>101.0887295584996</v>
+        <v>103.4216551354013</v>
       </c>
       <c r="C394">
-        <v>101.058366597128</v>
+        <v>103.323011430116</v>
       </c>
       <c r="D394">
-        <v>0.0303629613715799</v>
+        <v>0.09864370528526933</v>
       </c>
       <c r="E394" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7287,16 +7320,16 @@
         <v>61</v>
       </c>
       <c r="B395">
-        <v>98.57258321127158</v>
+        <v>102.1871452955314</v>
       </c>
       <c r="C395">
-        <v>98.54297599838627</v>
+        <v>102.0896790672905</v>
       </c>
       <c r="D395">
-        <v>0.02960721288530976</v>
+        <v>0.09746622824090423</v>
       </c>
       <c r="E395" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7304,16 +7337,16 @@
         <v>61</v>
       </c>
       <c r="B396">
-        <v>103.669102612936</v>
+        <v>104.671078930841</v>
       </c>
       <c r="C396">
-        <v>103.6379646119757</v>
+        <v>104.5712435235616</v>
       </c>
       <c r="D396">
-        <v>0.03113800096026864</v>
+        <v>0.0998354072794001</v>
       </c>
       <c r="E396" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7321,16 +7354,16 @@
         <v>61</v>
       </c>
       <c r="B397">
-        <v>102.6372586905028</v>
+        <v>104.4006789325256</v>
       </c>
       <c r="C397">
-        <v>102.6064306136784</v>
+        <v>104.3011014331061</v>
       </c>
       <c r="D397">
-        <v>0.03082807682436339</v>
+        <v>0.09957749941946759</v>
       </c>
       <c r="E397" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7338,16 +7371,16 @@
         <v>61</v>
       </c>
       <c r="B398">
-        <v>99.08561061872874</v>
+        <v>102.1961597618358</v>
       </c>
       <c r="C398">
-        <v>99.05584931318228</v>
+        <v>102.0986849355856</v>
       </c>
       <c r="D398">
-        <v>0.02976130554645806</v>
+        <v>0.0974748262502203</v>
       </c>
       <c r="E398" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7355,16 +7388,16 @@
         <v>61</v>
       </c>
       <c r="B399">
-        <v>98.40135323230989</v>
+        <v>101.8432742320717</v>
       </c>
       <c r="C399">
-        <v>98.37179744997738</v>
+        <v>101.7461359884854</v>
       </c>
       <c r="D399">
-        <v>0.02955578233250833</v>
+        <v>0.097138243586258</v>
       </c>
       <c r="E399" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7372,16 +7405,16 @@
         <v>61</v>
       </c>
       <c r="B400">
-        <v>103.849499098109</v>
+        <v>105.0244980004538</v>
       </c>
       <c r="C400">
-        <v>103.8183069133487</v>
+        <v>104.9243255016195</v>
       </c>
       <c r="D400">
-        <v>0.03119218476028607</v>
+        <v>0.1001724988342545</v>
       </c>
       <c r="E400" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7389,16 +7422,16 @@
         <v>62</v>
       </c>
       <c r="B401">
-        <v>103.3402788879597</v>
+        <v>100.4853902723553</v>
       </c>
       <c r="C401">
-        <v>103.3230114170216</v>
+        <v>98.30911163888629</v>
       </c>
       <c r="D401">
-        <v>0.0172674709380658</v>
+        <v>2.176278633468982</v>
       </c>
       <c r="E401" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7406,16 +7439,16 @@
         <v>62</v>
       </c>
       <c r="B402">
-        <v>102.0349963696122</v>
+        <v>97.96636014790491</v>
       </c>
       <c r="C402">
-        <v>102.0179470026719</v>
+        <v>92.68330045745363</v>
       </c>
       <c r="D402">
-        <v>0.01704936694034132</v>
+        <v>5.283059690451282</v>
       </c>
       <c r="E402" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7423,16 +7456,16 @@
         <v>62</v>
       </c>
       <c r="B403">
-        <v>104.6622592307138</v>
+        <v>103.069192761098</v>
       </c>
       <c r="C403">
-        <v>104.6447708656829</v>
+        <v>104.2833693902023</v>
       </c>
       <c r="D403">
-        <v>0.01748836503084306</v>
+        <v>-1.214176629104315</v>
       </c>
       <c r="E403" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7440,16 +7473,16 @@
         <v>62</v>
       </c>
       <c r="B404">
-        <v>104.3150231921995</v>
+        <v>102.2110232288453</v>
       </c>
       <c r="C404">
-        <v>104.2975928479933</v>
+        <v>100.6258899200998</v>
       </c>
       <c r="D404">
-        <v>0.01743034420617562</v>
+        <v>1.585133308745469</v>
       </c>
       <c r="E404" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7457,16 +7490,16 @@
         <v>62</v>
       </c>
       <c r="B405">
-        <v>102.1180378861747</v>
+        <v>98.26339651273933</v>
       </c>
       <c r="C405">
-        <v>102.1009746435512</v>
+        <v>94.87614582462665</v>
       </c>
       <c r="D405">
-        <v>0.01706324262354997</v>
+        <v>3.387250688112687</v>
       </c>
       <c r="E405" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7474,16 +7507,16 @@
         <v>62</v>
       </c>
       <c r="B406">
-        <v>101.7631399171323</v>
+        <v>97.5131255954548</v>
       </c>
       <c r="C406">
-        <v>101.7461359755909</v>
+        <v>93.08656937297503</v>
       </c>
       <c r="D406">
-        <v>0.01700394154143225</v>
+        <v>4.426556222479761</v>
       </c>
       <c r="E406" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7491,16 +7524,1325 @@
         <v>62</v>
       </c>
       <c r="B407">
-        <v>104.9418605728712</v>
+        <v>103.5482515459253</v>
       </c>
       <c r="C407">
-        <v>104.9243254883222</v>
+        <v>103.8283761944696</v>
       </c>
       <c r="D407">
-        <v>0.01753508454908115</v>
+        <v>-0.2801246485443727</v>
       </c>
       <c r="E407" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" t="s">
+        <v>63</v>
+      </c>
+      <c r="B408">
+        <v>100.3632221488093</v>
+      </c>
+      <c r="C408">
+        <v>98.16450043735964</v>
+      </c>
+      <c r="D408">
+        <v>2.19872171144965</v>
+      </c>
+      <c r="E408" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" t="s">
+        <v>63</v>
+      </c>
+      <c r="B409">
+        <v>97.78090630179047</v>
+      </c>
+      <c r="C409">
+        <v>92.48424971221009</v>
+      </c>
+      <c r="D409">
+        <v>5.29665658958038</v>
+      </c>
+      <c r="E409" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" t="s">
+        <v>63</v>
+      </c>
+      <c r="B410">
+        <v>103.013734900377</v>
+      </c>
+      <c r="C410">
+        <v>104.2005836944578</v>
+      </c>
+      <c r="D410">
+        <v>-1.186848794080845</v>
+      </c>
+      <c r="E410" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" t="s">
+        <v>63</v>
+      </c>
+      <c r="B411">
+        <v>102.1167604064721</v>
+      </c>
+      <c r="C411">
+        <v>100.4763502446808</v>
+      </c>
+      <c r="D411">
+        <v>1.640410161791294</v>
+      </c>
+      <c r="E411" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" t="s">
+        <v>63</v>
+      </c>
+      <c r="B412">
+        <v>98.10123878152727</v>
+      </c>
+      <c r="C412">
+        <v>94.72484684445962</v>
+      </c>
+      <c r="D412">
+        <v>3.376391937067652</v>
+      </c>
+      <c r="E412" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" t="s">
+        <v>63</v>
+      </c>
+      <c r="B413">
+        <v>97.33106193729573</v>
+      </c>
+      <c r="C413">
+        <v>92.91572039091146</v>
+      </c>
+      <c r="D413">
+        <v>4.415341546384269</v>
+      </c>
+      <c r="E413" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" t="s">
+        <v>63</v>
+      </c>
+      <c r="B414">
+        <v>103.4898434230637</v>
+      </c>
+      <c r="C414">
+        <v>103.7134087577082</v>
+      </c>
+      <c r="D414">
+        <v>-0.223565334644519</v>
+      </c>
+      <c r="E414" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" t="s">
+        <v>64</v>
+      </c>
+      <c r="B415">
+        <v>104.7593366656561</v>
+      </c>
+      <c r="C415">
+        <v>99.52884070917597</v>
+      </c>
+      <c r="D415">
+        <v>5.230495956480141</v>
+      </c>
+      <c r="E415" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" t="s">
+        <v>64</v>
+      </c>
+      <c r="B416">
+        <v>104.4383760432008</v>
+      </c>
+      <c r="C416">
+        <v>92.17851851274342</v>
+      </c>
+      <c r="D416">
+        <v>12.25985753045737</v>
+      </c>
+      <c r="E416" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" t="s">
+        <v>64</v>
+      </c>
+      <c r="B417">
+        <v>105.0812836661563</v>
+      </c>
+      <c r="C417">
+        <v>107.5064777274249</v>
+      </c>
+      <c r="D417">
+        <v>-2.425194061268584</v>
+      </c>
+      <c r="E417" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" t="s">
+        <v>64</v>
+      </c>
+      <c r="B418">
+        <v>104.9931524938121</v>
+      </c>
+      <c r="C418">
+        <v>101.4309263662164</v>
+      </c>
+      <c r="D418">
+        <v>3.56222612759575</v>
+      </c>
+      <c r="E418" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" t="s">
+        <v>64</v>
+      </c>
+      <c r="B419">
+        <v>104.4656392853608</v>
+      </c>
+      <c r="C419">
+        <v>96.22475480001103</v>
+      </c>
+      <c r="D419">
+        <v>8.240884485349724</v>
+      </c>
+      <c r="E419" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" t="s">
+        <v>64</v>
+      </c>
+      <c r="B420">
+        <v>104.38254411346</v>
+      </c>
+      <c r="C420">
+        <v>93.95293434970715</v>
+      </c>
+      <c r="D420">
+        <v>10.42960976375281</v>
+      </c>
+      <c r="E420" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" t="s">
+        <v>64</v>
+      </c>
+      <c r="B421">
+        <v>105.1374893363337</v>
+      </c>
+      <c r="C421">
+        <v>105.4552444485367</v>
+      </c>
+      <c r="D421">
+        <v>-0.3177551122029882</v>
+      </c>
+      <c r="E421" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" t="s">
+        <v>65</v>
+      </c>
+      <c r="B422">
+        <v>104.8148435954558</v>
+      </c>
+      <c r="C422">
+        <v>99.49410837998028</v>
+      </c>
+      <c r="D422">
+        <v>5.320735215475494</v>
+      </c>
+      <c r="E422" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" t="s">
+        <v>65</v>
+      </c>
+      <c r="B423">
+        <v>104.550985430077</v>
+      </c>
+      <c r="C423">
+        <v>92.18312431965747</v>
+      </c>
+      <c r="D423">
+        <v>12.3678611104195</v>
+      </c>
+      <c r="E423" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" t="s">
+        <v>65</v>
+      </c>
+      <c r="B424">
+        <v>105.0793676668627</v>
+      </c>
+      <c r="C424">
+        <v>107.4259278384135</v>
+      </c>
+      <c r="D424">
+        <v>-2.346560171550806</v>
+      </c>
+      <c r="E424" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" t="s">
+        <v>65</v>
+      </c>
+      <c r="B425">
+        <v>105.0069701010874</v>
+      </c>
+      <c r="C425">
+        <v>101.401378420365</v>
+      </c>
+      <c r="D425">
+        <v>3.605591680722441</v>
+      </c>
+      <c r="E425" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" t="s">
+        <v>65</v>
+      </c>
+      <c r="B426">
+        <v>104.5734038605789</v>
+      </c>
+      <c r="C426">
+        <v>96.19331285171388</v>
+      </c>
+      <c r="D426">
+        <v>8.380091008865051</v>
+      </c>
+      <c r="E426" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" t="s">
+        <v>65</v>
+      </c>
+      <c r="B427">
+        <v>104.5050718458409</v>
+      </c>
+      <c r="C427">
+        <v>93.93554191410107</v>
+      </c>
+      <c r="D427">
+        <v>10.56952993173982</v>
+      </c>
+      <c r="E427" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" t="s">
+        <v>65</v>
+      </c>
+      <c r="B428">
+        <v>105.1255335640161</v>
+      </c>
+      <c r="C428">
+        <v>105.401360313686</v>
+      </c>
+      <c r="D428">
+        <v>-0.2758267496699034</v>
+      </c>
+      <c r="E428" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" t="s">
+        <v>66</v>
+      </c>
+      <c r="B429">
+        <v>100.2765643884035</v>
+      </c>
+      <c r="C429">
+        <v>100.0757261543505</v>
+      </c>
+      <c r="D429">
+        <v>0.2008382340530659</v>
+      </c>
+      <c r="E429" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" t="s">
+        <v>66</v>
+      </c>
+      <c r="B430">
+        <v>97.31027795878167</v>
+      </c>
+      <c r="C430">
+        <v>97.11538073130227</v>
+      </c>
+      <c r="D430">
+        <v>0.1948972274794016</v>
+      </c>
+      <c r="E430" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" t="s">
+        <v>66</v>
+      </c>
+      <c r="B431">
+        <v>103.3332714330635</v>
+      </c>
+      <c r="C431">
+        <v>103.1263110941237</v>
+      </c>
+      <c r="D431">
+        <v>0.2069603389398367</v>
+      </c>
+      <c r="E431" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" t="s">
+        <v>66</v>
+      </c>
+      <c r="B432">
+        <v>102.0101153667307</v>
+      </c>
+      <c r="C432">
+        <v>101.8058051019069</v>
+      </c>
+      <c r="D432">
+        <v>0.2043102648237749</v>
+      </c>
+      <c r="E432" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" t="s">
+        <v>66</v>
+      </c>
+      <c r="B433">
+        <v>98.01179312837775</v>
+      </c>
+      <c r="C433">
+        <v>97.81549087601859</v>
+      </c>
+      <c r="D433">
+        <v>0.1963022523591604</v>
+      </c>
+      <c r="E433" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" t="s">
+        <v>66</v>
+      </c>
+      <c r="B434">
+        <v>97.20218740101437</v>
+      </c>
+      <c r="C434">
+        <v>97.0075066619724</v>
+      </c>
+      <c r="D434">
+        <v>0.1946807390419707</v>
+      </c>
+      <c r="E434" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" t="s">
+        <v>66</v>
+      </c>
+      <c r="B435">
+        <v>103.4481798651037</v>
+      </c>
+      <c r="C435">
+        <v>103.2409893825933</v>
+      </c>
+      <c r="D435">
+        <v>0.2071904825103985</v>
+      </c>
+      <c r="E435" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" t="s">
+        <v>67</v>
+      </c>
+      <c r="B436">
+        <v>102.5813080209067</v>
+      </c>
+      <c r="C436">
+        <v>99.73218787064766</v>
+      </c>
+      <c r="D436">
+        <v>2.849120150259083</v>
+      </c>
+      <c r="E436" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" t="s">
+        <v>67</v>
+      </c>
+      <c r="B437">
+        <v>101.1973296333525</v>
+      </c>
+      <c r="C437">
+        <v>95.10009706873075</v>
+      </c>
+      <c r="D437">
+        <v>6.097232564621763</v>
+      </c>
+      <c r="E437" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" t="s">
+        <v>67</v>
+      </c>
+      <c r="B438">
+        <v>103.9842137475929</v>
+      </c>
+      <c r="C438">
+        <v>104.5967030541549</v>
+      </c>
+      <c r="D438">
+        <v>-0.6124893065619688</v>
+      </c>
+      <c r="E438" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" t="s">
+        <v>67</v>
+      </c>
+      <c r="B439">
+        <v>103.6594374713688</v>
+      </c>
+      <c r="C439">
+        <v>101.9952176634392</v>
+      </c>
+      <c r="D439">
+        <v>1.664219807929584</v>
+      </c>
+      <c r="E439" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" t="s">
+        <v>67</v>
+      </c>
+      <c r="B440">
+        <v>101.2280233029932</v>
+      </c>
+      <c r="C440">
+        <v>96.56826382741342</v>
+      </c>
+      <c r="D440">
+        <v>4.659759475579804</v>
+      </c>
+      <c r="E440" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" t="s">
+        <v>67</v>
+      </c>
+      <c r="B441">
+        <v>100.8310793889001</v>
+      </c>
+      <c r="C441">
+        <v>95.14020374119362</v>
+      </c>
+      <c r="D441">
+        <v>5.690875647706491</v>
+      </c>
+      <c r="E441" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" t="s">
+        <v>67</v>
+      </c>
+      <c r="B442">
+        <v>104.361917169346</v>
+      </c>
+      <c r="C442">
+        <v>104.5510748344043</v>
+      </c>
+      <c r="D442">
+        <v>-0.1891576650583175</v>
+      </c>
+      <c r="E442" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" t="s">
+        <v>68</v>
+      </c>
+      <c r="B443">
+        <v>100.9948564451392</v>
+      </c>
+      <c r="C443">
+        <v>100.6785130747671</v>
+      </c>
+      <c r="D443">
+        <v>0.3163433703721381</v>
+      </c>
+      <c r="E443" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" t="s">
+        <v>68</v>
+      </c>
+      <c r="B444">
+        <v>95.9414237360934</v>
+      </c>
+      <c r="C444">
+        <v>95.64138034563751</v>
+      </c>
+      <c r="D444">
+        <v>0.3000433904558832</v>
+      </c>
+      <c r="E444" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" t="s">
+        <v>68</v>
+      </c>
+      <c r="B445">
+        <v>106.3234134073476</v>
+      </c>
+      <c r="C445">
+        <v>105.9898756579987</v>
+      </c>
+      <c r="D445">
+        <v>0.3335377493489204</v>
+      </c>
+      <c r="E445" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" t="s">
+        <v>68</v>
+      </c>
+      <c r="B446">
+        <v>103.1632424666777</v>
+      </c>
+      <c r="C446">
+        <v>102.8399522904718</v>
+      </c>
+      <c r="D446">
+        <v>0.3232901762059015</v>
+      </c>
+      <c r="E446" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" t="s">
+        <v>68</v>
+      </c>
+      <c r="B447">
+        <v>97.90517951757462</v>
+      </c>
+      <c r="C447">
+        <v>97.59875476764914</v>
+      </c>
+      <c r="D447">
+        <v>0.3064247499254833</v>
+      </c>
+      <c r="E447" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" t="s">
+        <v>68</v>
+      </c>
+      <c r="B448">
+        <v>96.44254427142258</v>
+      </c>
+      <c r="C448">
+        <v>96.14084222264673</v>
+      </c>
+      <c r="D448">
+        <v>0.3017020487758515</v>
+      </c>
+      <c r="E448" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" t="s">
+        <v>68</v>
+      </c>
+      <c r="B449">
+        <v>105.7678844458208</v>
+      </c>
+      <c r="C449">
+        <v>105.4361834246068</v>
+      </c>
+      <c r="D449">
+        <v>0.3317010212140161</v>
+      </c>
+      <c r="E449" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" t="s">
         <v>69</v>
+      </c>
+      <c r="B450">
+        <v>97.92983043530333</v>
+      </c>
+      <c r="C450">
+        <v>97.55652308939406</v>
+      </c>
+      <c r="D450">
+        <v>0.373307345909268</v>
+      </c>
+      <c r="E450" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" t="s">
+        <v>69</v>
+      </c>
+      <c r="B451">
+        <v>91.67926332471907</v>
+      </c>
+      <c r="C451">
+        <v>91.33017009728233</v>
+      </c>
+      <c r="D451">
+        <v>0.3490932274367395</v>
+      </c>
+      <c r="E451" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" t="s">
+        <v>69</v>
+      </c>
+      <c r="B452">
+        <v>104.6151088285864</v>
+      </c>
+      <c r="C452">
+        <v>104.2158910662862</v>
+      </c>
+      <c r="D452">
+        <v>0.3992177623002107</v>
+      </c>
+      <c r="E452" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" t="s">
+        <v>69</v>
+      </c>
+      <c r="B453">
+        <v>100.0698503741795</v>
+      </c>
+      <c r="C453">
+        <v>99.6883292764042</v>
+      </c>
+      <c r="D453">
+        <v>0.381521097775277</v>
+      </c>
+      <c r="E453" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" t="s">
+        <v>69</v>
+      </c>
+      <c r="B454">
+        <v>94.62654776786434</v>
+      </c>
+      <c r="C454">
+        <v>94.26596265180896</v>
+      </c>
+      <c r="D454">
+        <v>0.3605851160553755</v>
+      </c>
+      <c r="E454" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" t="s">
+        <v>69</v>
+      </c>
+      <c r="B455">
+        <v>92.75652475094721</v>
+      </c>
+      <c r="C455">
+        <v>92.40319220250724</v>
+      </c>
+      <c r="D455">
+        <v>0.3533325484399654</v>
+      </c>
+      <c r="E455" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" t="s">
+        <v>69</v>
+      </c>
+      <c r="B456">
+        <v>103.3952750543476</v>
+      </c>
+      <c r="C456">
+        <v>103.000856628797</v>
+      </c>
+      <c r="D456">
+        <v>0.3944184255506116</v>
+      </c>
+      <c r="E456" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" t="s">
+        <v>70</v>
+      </c>
+      <c r="B457">
+        <v>102.9987315468809</v>
+      </c>
+      <c r="C457">
+        <v>98.07963942065361</v>
+      </c>
+      <c r="D457">
+        <v>4.91909212622727</v>
+      </c>
+      <c r="E457" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" t="s">
+        <v>70</v>
+      </c>
+      <c r="B458">
+        <v>101.9560681968173</v>
+      </c>
+      <c r="C458">
+        <v>90.94896631136265</v>
+      </c>
+      <c r="D458">
+        <v>11.00710188545466</v>
+      </c>
+      <c r="E458" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" t="s">
+        <v>70</v>
+      </c>
+      <c r="B459">
+        <v>104.0520577920599</v>
+      </c>
+      <c r="C459">
+        <v>105.8002534333668</v>
+      </c>
+      <c r="D459">
+        <v>-1.748195641306935</v>
+      </c>
+      <c r="E459" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" t="s">
+        <v>70</v>
+      </c>
+      <c r="B460">
+        <v>103.855012987562</v>
+      </c>
+      <c r="C460">
+        <v>100.0912312150907</v>
+      </c>
+      <c r="D460">
+        <v>3.763781772471319</v>
+      </c>
+      <c r="E460" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" t="s">
+        <v>70</v>
+      </c>
+      <c r="B461">
+        <v>101.9302220200948</v>
+      </c>
+      <c r="C461">
+        <v>94.61851075981636</v>
+      </c>
+      <c r="D461">
+        <v>7.311711260278415</v>
+      </c>
+      <c r="E461" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" t="s">
+        <v>70</v>
+      </c>
+      <c r="B462">
+        <v>101.6290221697815</v>
+      </c>
+      <c r="C462">
+        <v>92.27044586073799</v>
+      </c>
+      <c r="D462">
+        <v>9.358576309043457</v>
+      </c>
+      <c r="E462" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" t="s">
+        <v>70</v>
+      </c>
+      <c r="B463">
+        <v>104.386901239131</v>
+      </c>
+      <c r="C463">
+        <v>104.2691093193436</v>
+      </c>
+      <c r="D463">
+        <v>0.1177919197873791</v>
+      </c>
+      <c r="E463" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" t="s">
+        <v>71</v>
+      </c>
+      <c r="B464">
+        <v>100.0959810331512</v>
+      </c>
+      <c r="C464">
+        <v>99.89937947441886</v>
+      </c>
+      <c r="D464">
+        <v>0.1966015587323824</v>
+      </c>
+      <c r="E464" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" t="s">
+        <v>71</v>
+      </c>
+      <c r="B465">
+        <v>97.19892706528682</v>
+      </c>
+      <c r="C465">
+        <v>97.0080156983077</v>
+      </c>
+      <c r="D465">
+        <v>0.1909113669791225</v>
+      </c>
+      <c r="E465" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" t="s">
+        <v>71</v>
+      </c>
+      <c r="B466">
+        <v>103.0793828851553</v>
+      </c>
+      <c r="C466">
+        <v>102.8769215361657</v>
+      </c>
+      <c r="D466">
+        <v>0.2024613489895302</v>
+      </c>
+      <c r="E466" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" t="s">
+        <v>71</v>
+      </c>
+      <c r="B467">
+        <v>101.8029867219911</v>
+      </c>
+      <c r="C467">
+        <v>101.6030323815014</v>
+      </c>
+      <c r="D467">
+        <v>0.1999543404897679</v>
+      </c>
+      <c r="E467" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" t="s">
+        <v>71</v>
+      </c>
+      <c r="B468">
+        <v>97.8701681773469</v>
+      </c>
+      <c r="C468">
+        <v>97.67793840529737</v>
+      </c>
+      <c r="D468">
+        <v>0.1922297720495294</v>
+      </c>
+      <c r="E468" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" t="s">
+        <v>71</v>
+      </c>
+      <c r="B469">
+        <v>97.08089434988196</v>
+      </c>
+      <c r="C469">
+        <v>96.89021481454674</v>
+      </c>
+      <c r="D469">
+        <v>0.1906795353352209</v>
+      </c>
+      <c r="E469" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" t="s">
+        <v>71</v>
+      </c>
+      <c r="B470">
+        <v>103.2047086719197</v>
+      </c>
+      <c r="C470">
+        <v>103.0020011667432</v>
+      </c>
+      <c r="D470">
+        <v>0.2027075051765195</v>
+      </c>
+      <c r="E470" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" t="s">
+        <v>72</v>
+      </c>
+      <c r="B471">
+        <v>97.59950832885508</v>
+      </c>
+      <c r="C471">
+        <v>97.23981256846422</v>
+      </c>
+      <c r="D471">
+        <v>0.3596957603908635</v>
+      </c>
+      <c r="E471" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" t="s">
+        <v>72</v>
+      </c>
+      <c r="B472">
+        <v>91.63430797354565</v>
+      </c>
+      <c r="C472">
+        <v>91.29696272215314</v>
+      </c>
+      <c r="D472">
+        <v>0.3373452513925059</v>
+      </c>
+      <c r="E472" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" t="s">
+        <v>72</v>
+      </c>
+      <c r="B473">
+        <v>103.9608757324367</v>
+      </c>
+      <c r="C473">
+        <v>103.5773348108763</v>
+      </c>
+      <c r="D473">
+        <v>0.383540921560467</v>
+      </c>
+      <c r="E473" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" t="s">
+        <v>72</v>
+      </c>
+      <c r="B474">
+        <v>99.74613466480263</v>
+      </c>
+      <c r="C474">
+        <v>99.37846121352756</v>
+      </c>
+      <c r="D474">
+        <v>0.367673451275067</v>
+      </c>
+      <c r="E474" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" t="s">
+        <v>72</v>
+      </c>
+      <c r="B475">
+        <v>94.34791464695711</v>
+      </c>
+      <c r="C475">
+        <v>94.00033819967504</v>
+      </c>
+      <c r="D475">
+        <v>0.3475764472820657</v>
+      </c>
+      <c r="E475" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" t="s">
+        <v>72</v>
+      </c>
+      <c r="B476">
+        <v>92.57523621642541</v>
+      </c>
+      <c r="C476">
+        <v>92.23430867225343</v>
+      </c>
+      <c r="D476">
+        <v>0.3409275441719757</v>
+      </c>
+      <c r="E476" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" t="s">
+        <v>72</v>
+      </c>
+      <c r="B477">
+        <v>102.9000924705669</v>
+      </c>
+      <c r="C477">
+        <v>102.5205888882608</v>
+      </c>
+      <c r="D477">
+        <v>0.3795035823060999</v>
+      </c>
+      <c r="E477" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" t="s">
+        <v>73</v>
+      </c>
+      <c r="B478">
+        <v>100.5469759276631</v>
+      </c>
+      <c r="C478">
+        <v>100.365272919348</v>
+      </c>
+      <c r="D478">
+        <v>0.1817030083151252</v>
+      </c>
+      <c r="E478" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" t="s">
+        <v>73</v>
+      </c>
+      <c r="B479">
+        <v>97.8940052666059</v>
+      </c>
+      <c r="C479">
+        <v>97.71709656210385</v>
+      </c>
+      <c r="D479">
+        <v>0.1769087045020541</v>
+      </c>
+      <c r="E479" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" t="s">
+        <v>73</v>
+      </c>
+      <c r="B480">
+        <v>103.2718432621609</v>
+      </c>
+      <c r="C480">
+        <v>103.0852160222876</v>
+      </c>
+      <c r="D480">
+        <v>0.1866272398732889</v>
+      </c>
+      <c r="E480" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" t="s">
+        <v>73</v>
+      </c>
+      <c r="B481">
+        <v>102.1609656972187</v>
+      </c>
+      <c r="C481">
+        <v>101.9763459746632</v>
+      </c>
+      <c r="D481">
+        <v>0.184619722555567</v>
+      </c>
+      <c r="E481" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" t="s">
+        <v>73</v>
+      </c>
+      <c r="B482">
+        <v>98.457746156488</v>
+      </c>
+      <c r="C482">
+        <v>98.27981869021158</v>
+      </c>
+      <c r="D482">
+        <v>0.1779274662764152</v>
+      </c>
+      <c r="E482" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" t="s">
+        <v>73</v>
+      </c>
+      <c r="B483">
+        <v>97.74019010184061</v>
+      </c>
+      <c r="C483">
+        <v>97.56355936371104</v>
+      </c>
+      <c r="D483">
+        <v>0.1766307381295746</v>
+      </c>
+      <c r="E483" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" t="s">
+        <v>73</v>
+      </c>
+      <c r="B484">
+        <v>103.4343636703005</v>
+      </c>
+      <c r="C484">
+        <v>103.2474427324139</v>
+      </c>
+      <c r="D484">
+        <v>0.186920937886569</v>
+      </c>
+      <c r="E484" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
